--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$86</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>46 (42)</t>
+          <t>47 (43)</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       <c r="R49" s="39" t="inlineStr"/>
       <c r="S49" s="39" t="inlineStr"/>
     </row>
-    <row r="50" ht="141" customHeight="1">
+    <row r="50" ht="168" customHeight="1">
       <c r="A50" s="40" t="n"/>
       <c r="B50" s="40" t="n"/>
       <c r="C50" s="40" t="n"/>
@@ -12565,7 +12565,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_supervision.py: TxBlockedMonitor baseline, rise while engaged and panda-reset tests, in CI unit tests on every PR. Targeted, not proven by mutation; the txRateExceeded and heartbeatLost branches in selfdrived.py have no test</t>
+            <t>• test_supervision.py: TxBlockedMonitor baseline, rise while engaged and panda-reset tests. NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted, not proven by mutation; the txRateExceeded and heartbeatLost branches in selfdrived.py have no test</t>
           </r>
           <r>
             <rPr>
@@ -13104,7 +13104,7 @@
       <c r="R53" s="48" t="inlineStr"/>
       <c r="S53" s="48" t="inlineStr"/>
     </row>
-    <row r="54" ht="276" customHeight="1">
+    <row r="54" ht="409" customHeight="1">
       <c r="A54" s="30" t="inlineStr">
         <is>
           <r>
@@ -13356,7 +13356,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_supervision.py (consecutive samples, single-sample absorption, 0.5 s bound with stale samples, engagement grace), in CI unit tests on every PR. Targeted at the cause, not proven by mutation</t>
+            <t>• test_supervision.py (13 tests: consecutive samples, single-sample absorption, 0.5 s bound with stale samples, engagement grace). NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted at the cause, not proven by mutation</t>
           </r>
           <r>
             <rPr>
@@ -13424,12 +13424,40 @@
             </rPr>
             <t>Panda status supervision per TSR-615, TSR-621 and TSR-626a: controlsMismatch within 2 samples and 0.5 s (time-based); safety model/parameter mismatch as NO_ENTRY from start instead of a 10 s grace; pandaStates older than 0.2 s treated as mismatch; immediate disable on heartbeatLost, rising safetyTxBlocked, txRateExceeded and any panda fault flag</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-055 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Make the host supervision tests run in CI: test_supervision.py and test_input_freshness.py define plain classes, which tools/test_runner.py (unittest loader) collects as 0 tests. Derive them from unittest.TestCase (or the repo's test base class), check that the unit_tests job reports them, and prove them by a mutation of supervision.py and input_freshness.py so D can drop below 8</t>
+          </r>
         </is>
       </c>
       <c r="O54" s="38" t="inlineStr">
         <is>
           <t>open
-in progress</t>
+in progress
+open</t>
         </is>
       </c>
       <c r="P54" s="33" t="inlineStr">
@@ -15470,7 +15498,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_input_freshness.py (6 tests: bound per service, wall clock for selfdriveState, inputs not yet seen), in CI unit tests on every PR. Targeted at the gate logic, not proven by mutation; no test stops selfdrived while engaged</t>
+            <t>• test_input_freshness.py (6 tests: bound per service, wall clock for selfdriveState, inputs not yet seen). NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted at the gate logic, not proven by mutation; no test stops selfdrived while engaged</t>
           </r>
           <r>
             <rPr>
@@ -16640,7 +16668,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_input_freshness.py (bound per service on the log clock), in CI unit tests on every PR; targeted at the gate, not proven by mutation. No test stops modeld or plannerd while engaged</t>
+            <t>• test_input_freshness.py (bound per service on the log clock). NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted at the gate, not proven by mutation. No test stops modeld or plannerd while engaged</t>
           </r>
           <r>
             <rPr>
@@ -20733,7 +20761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22533,52 +22561,87 @@
       <c r="H46" s="60" t="inlineStr"/>
       <c r="I46" s="60" t="inlineStr"/>
     </row>
-    <row r="47" ht="73.5" customHeight="1">
+    <row r="47" ht="87" customHeight="1">
       <c r="A47" s="60" t="inlineStr">
         <is>
+          <t>SWF-ACT-055</t>
+        </is>
+      </c>
+      <c r="B47" s="60" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C47" s="60" t="inlineStr">
+        <is>
+          <t>Make the host supervision tests run in CI: test_supervision.py and test_input_freshness.py define plain classes, which tools/test_runner.py (unittest loader) collects as 0 tests. Derive them from unittest.TestCase (or the repo's test base class), check that the unit_tests job reports them, and prove them by a mutation of supervision.py and input_freshness.py so D can drop below 8</t>
+        </is>
+      </c>
+      <c r="D47" s="60" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E47" s="60" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F47" s="60" t="inlineStr">
+        <is>
+          <t>SWF-034.C1</t>
+        </is>
+      </c>
+      <c r="G47" s="60" t="inlineStr"/>
+      <c r="H47" s="60" t="inlineStr"/>
+      <c r="I47" s="60" t="inlineStr"/>
+    </row>
+    <row r="48" ht="73.5" customHeight="1">
+      <c r="A48" s="60" t="inlineStr">
+        <is>
           <t>SWF-ACT-054</t>
         </is>
       </c>
-      <c r="B47" s="60" t="inlineStr">
+      <c r="B48" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C47" s="60" t="inlineStr">
+      <c r="C48" s="60" t="inlineStr">
         <is>
           <t>Pin an opendbc commit that contains jherrodthomas/opendbc#15 (ATC-20, SWSR-518 amended per DQ-079; ATC-26, SWSR-311 amended per DQ-080), with its impact records moved to Integrated, and re-rate SWF-054 and SWF-055 at the new baseline. The fork merged it as 9859cb0 (master 515b9a2 also carries opendbc#16); the LionDriver pin is still 9a13f60</t>
         </is>
       </c>
-      <c r="D47" s="60" t="inlineStr">
+      <c r="D48" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E47" s="60" t="inlineStr">
+      <c r="E48" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F47" s="60" t="inlineStr">
+      <c r="F48" s="60" t="inlineStr">
         <is>
           <t>SWF-054.C1
 SWF-055.C1</t>
         </is>
       </c>
-      <c r="G47" s="60" t="inlineStr">
+      <c r="G48" s="60" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H47" s="63" t="inlineStr">
+      <c r="H48" s="63" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I47" s="60" t="inlineStr"/>
+      <c r="I48" s="60" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I47"/>
+  <autoFilter ref="A1:I48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$115</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -252,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -393,6 +393,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -814,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.8 · draft</t>
+          <t>0.9 · draft</t>
         </is>
       </c>
     </row>
@@ -854,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
+    <row r="10" ht="105" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
@@ -862,7 +865,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053).</t>
+          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071).</t>
         </is>
       </c>
     </row>
@@ -892,7 +895,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -902,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -912,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
@@ -943,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>47 (43)</t>
+          <t>56 (52)</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S86"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20591,21 +20594,5562 @@
       <c r="R86" s="48" t="inlineStr"/>
       <c r="S86" s="48" t="inlineStr"/>
     </row>
+    <row r="87" ht="141" customHeight="1">
+      <c r="A87" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-051
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>CAN parser and Toyota carState</t>
+          </r>
+        </is>
+      </c>
+      <c r="B87" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-051
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide brakePressed, gasPressed, steeringTorque/steeringPressed, cruise state, vEgo and EPS fault from current vehicle CAN, and report invalid or missing data as canValid false within the RX budget</t>
+          </r>
+        </is>
+      </c>
+      <c r="C87" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Automated control not released on a driver brake or cancel seen only by the host</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-009 (driver steering not seen) and HZ-007 (old vEgo in planning)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>selfdrived misses a brake or cancel edge; controlsd keeps steering against a driver input or plans with an old speed</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>brakePressed, gasPressed, steeringPressed, cruise state or vEgo held at an old value with canValid true</t>
+          </r>
+        </is>
+      </c>
+      <c r="D87" s="31" t="inlineStr">
+        <is>
+          <t>HZ-008
+HZ-009</t>
+        </is>
+      </c>
+      <c r="E87" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-056 · value_stale
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Vehicle input lost, delayed or frozen while carState still reports it as current and valid</t>
+          </r>
+        </is>
+      </c>
+      <c r="G87" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H87" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Frozen frames are not detectable on the host: no Toyota RX message carries a counter, and BRAKE_MODULE 0x226 and WHEEL_SPEEDS 0xAA carry neither checksum nor counter (toyota_nodsu_pt.dbc:18, _toyota_2017.dbc:67). A repeated frame keeps the parser alive and valid</t>
+          </r>
+        </is>
+      </c>
+      <c r="I87" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Vehicle-side design; the parser checks timing only for these messages</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/can/parser.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J87" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L87" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N87" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-056 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>carState input supervision for the reference car: fixed RX timeouts from the DBC rates instead of the learned 1 Hz default, reject frames shorter than the DBC length for every signal carState uses, and a plausibility cross-check for the messages without checksum or counter (BRAKE_MODULE against PCM_CRUISE, WHEEL_SPEEDS against the IMU); with unit tests in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O87" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P87" s="33" t="inlineStr"/>
+      <c r="Q87" s="33" t="inlineStr"/>
+      <c r="R87" s="39" t="inlineStr"/>
+      <c r="S87" s="39" t="inlineStr"/>
+    </row>
+    <row r="88" ht="235.5" customHeight="1">
+      <c r="A88" s="40" t="n"/>
+      <c r="B88" s="40" t="n"/>
+      <c r="C88" s="40" t="n"/>
+      <c r="D88" s="40" t="n"/>
+      <c r="E88" s="40" t="n"/>
+      <c r="F88" s="40" t="n"/>
+      <c r="G88" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Message timeouts are learned at run time. A message read by carstate.py is registered on first access with an assumed 1 Hz, i.e. a 10 s timeout, until more than 1 s of samples gives its rate (parser.py:77-81, 166-171). A message that stops in that first window is flagged after up to 10 s</t>
+          </r>
+        </is>
+      </c>
+      <c r="I88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J88" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• opendbc can tests (test_packer_parser can_valid and timeout cases) exist but are not run by LionDriver CI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/can/tests/test_packer_parser.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L88" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-056 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>carState input supervision for the reference car: fixed RX timeouts from the DBC rates instead of the learned 1 Hz default, reject frames shorter than the DBC length for every signal carState uses, and a plausibility cross-check for the messages without checksum or counter (BRAKE_MODULE against PCM_CRUISE, WHEEL_SPEEDS against the IMU); with unit tests in LionDriver CI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-044 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Add NaN/inf and stale-input injection for controlsd and card (enable them in test_fuzzy.py with the Corolla fingerprint, or a dedicated test), and run the opendbc car tests (test_models, test_car_interfaces, test_lateral_limits) for Toyota in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O88" s="38" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P88" s="33" t="inlineStr"/>
+      <c r="Q88" s="33" t="inlineStr"/>
+      <c r="R88" s="39" t="inlineStr"/>
+      <c r="S88" s="39" t="inlineStr"/>
+    </row>
+    <row r="89" ht="235.5" customHeight="1">
+      <c r="A89" s="42" t="n"/>
+      <c r="B89" s="42" t="n"/>
+      <c r="C89" s="42" t="n"/>
+      <c r="D89" s="42" t="n"/>
+      <c r="E89" s="42" t="n"/>
+      <c r="F89" s="42" t="n"/>
+      <c r="G89" s="43" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H89" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A frame with a bad checksum is dropped without a timestamp refresh, so the last good value stays in carState until the message times out (10 learned periods) and canValid then needs 5 consecutive invalid evaluations (parser.py:51-65, 184-199): about 0.3 s for BRAKE_MODULE before the host sees invalid data</t>
+          </r>
+        </is>
+      </c>
+      <c r="I89" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J89" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As SWF-056.C2 (opendbc can tests not run by LionDriver CI)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/can/tests/test_packer_parser.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L89" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M89" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N89" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-056 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>carState input supervision for the reference car: fixed RX timeouts from the DBC rates instead of the learned 1 Hz default, reject frames shorter than the DBC length for every signal carState uses, and a plausibility cross-check for the messages without checksum or counter (BRAKE_MODULE against PCM_CRUISE, WHEEL_SPEEDS against the IMU); with unit tests in LionDriver CI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-044 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Add NaN/inf and stale-input injection for controlsd and card (enable them in test_fuzzy.py with the Corolla fingerprint, or a dedicated test), and run the opendbc car tests (test_models, test_car_interfaces, test_lateral_limits) for Toyota in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O89" s="53" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P89" s="43" t="inlineStr"/>
+      <c r="Q89" s="43" t="inlineStr"/>
+      <c r="R89" s="48" t="inlineStr"/>
+      <c r="S89" s="48" t="inlineStr"/>
+    </row>
+    <row r="90" ht="114" customHeight="1">
+      <c r="A90" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-051
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>CAN parser and Toyota carState</t>
+          </r>
+        </is>
+      </c>
+      <c r="B90" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-051
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide brakePressed, gasPressed, steeringTorque/steeringPressed, cruise state, vEgo and EPS fault from current vehicle CAN, and report invalid or missing data as canValid false within the RX budget</t>
+          </r>
+        </is>
+      </c>
+      <c r="C90" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Automated control not released on brake or cancel</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item resists driver steering (driver torque mis-read)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-010 (spurious cruise enable) and HZ-007 (wrong vEgo)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Wrong engagement, override or disengagement decisions; wrong speed in planning and lateral limits</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>brakePressed, gasPressed, steeringTorque, cruise state, EPS fault or vEgo wrong while valid</t>
+          </r>
+        </is>
+      </c>
+      <c r="D90" s="31" t="inlineStr">
+        <is>
+          <t>HZ-008
+HZ-009
+HZ-010</t>
+        </is>
+      </c>
+      <c r="E90" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-057 · corrupted
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Safety-relevant carState field decoded with the wrong sign, scale or bit for the Corolla TSS2</t>
+          </r>
+        </is>
+      </c>
+      <c r="G90" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Defect in the Toyota DBC or in carstate.py signal use (steeringTorque sign, GAS_RELEASED inversion, LKA_STATE fault codes, PCM_CRUISE decoding; carstate.py:19-22, 59-167)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J90" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L90" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-044 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Add NaN/inf and stale-input injection for controlsd and card (enable them in test_fuzzy.py with the Corolla fingerprint, or a dedicated test), and run the opendbc car tests (test_models, test_car_interfaces, test_lateral_limits) for Toyota in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O90" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P90" s="33" t="inlineStr"/>
+      <c r="Q90" s="33" t="inlineStr"/>
+      <c r="R90" s="39" t="inlineStr"/>
+      <c r="S90" s="39" t="inlineStr"/>
+    </row>
+    <row r="91" ht="141" customHeight="1">
+      <c r="A91" s="42" t="n"/>
+      <c r="B91" s="42" t="n"/>
+      <c r="C91" s="42" t="n"/>
+      <c r="D91" s="42" t="n"/>
+      <c r="E91" s="42" t="n"/>
+      <c r="F91" s="42" t="n"/>
+      <c r="G91" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H91" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Short frames are not rejected: the parser skips only frames over 64 bytes and reads missing bytes as 0 (parser.py:219, dbc.py:66), so a truncated BRAKE_MODULE reads BRAKE_PRESSED = 0 with no checksum to catch it. The panda-side length fault is proposed, not implemented (change-2026-10-13-opendbc-rx-length-fault)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I91" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J91" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L91" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M91" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N91" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-056 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>carState input supervision for the reference car: fixed RX timeouts from the DBC rates instead of the learned 1 Hz default, reject frames shorter than the DBC length for every signal carState uses, and a plausibility cross-check for the messages without checksum or counter (BRAKE_MODULE against PCM_CRUISE, WHEEL_SPEEDS against the IMU); with unit tests in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O91" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P91" s="43" t="inlineStr"/>
+      <c r="Q91" s="43" t="inlineStr"/>
+      <c r="R91" s="48" t="inlineStr"/>
+      <c r="S91" s="48" t="inlineStr"/>
+    </row>
+    <row r="92" ht="114" customHeight="1">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-052
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Fingerprinting and CarParams</t>
+          </r>
+        </is>
+      </c>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-052
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Identify the reference vehicle and produce its CarParams (TOYOTA_COROLLA_TSS2, safety parameter 73, openpilot longitudinal)</t>
+          </r>
+        </is>
+      </c>
+      <c r="C92" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral or longitudinal control outside what the analyses assume, within the panda envelope</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Host controllers and CarController use limits and scaling of another car; the panda refuses a mode or parameter other than TOYOTA/73</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Wrong platform, tune, limits or flags in CarParams</t>
+          </r>
+        </is>
+      </c>
+      <c r="D92" s="31" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-005</t>
+        </is>
+      </c>
+      <c r="E92" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F92" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-058 · wrong_mode
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>CarParams of another platform or parameter set used on the reference car</t>
+          </r>
+        </is>
+      </c>
+      <c r="G92" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Fuzzy fingerprint: when no exact FW match is found, Toyota platform codes select a platform (fw_versions.py:146-170, values.py:449-480); the Corolla TSS2 shares its platform with the Lexus UX Hybrid and the Corolla Cross (values.py:201-215). CP.fuzzyFingerprint is recorded but nothing acts on it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-013</t>
+          </r>
+        </is>
+      </c>
+      <c r="I92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J92" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• opendbc test_fw_fingerprint exists but is not run by LionDriver CI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/tests/test_fw_fingerprint.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L92" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M92" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-057 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Pin the reference identification: accept only an exact FW match to TOYOTA_COROLLA_TSS2 with the expected CarParams for the assured configuration (report a fuzzy match through assured_config), ignore FINGERPRINT in release builds, and re-query FW after a VIN-cache hit when an ECU version changed</t>
+          </r>
+        </is>
+      </c>
+      <c r="O92" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P92" s="33" t="inlineStr"/>
+      <c r="Q92" s="33" t="inlineStr"/>
+      <c r="R92" s="39" t="inlineStr"/>
+      <c r="S92" s="39" t="inlineStr"/>
+    </row>
+    <row r="93" ht="114" customHeight="1">
+      <c r="A93" s="42" t="n"/>
+      <c r="B93" s="42" t="n"/>
+      <c r="C93" s="42" t="n"/>
+      <c r="D93" s="42" t="n"/>
+      <c r="E93" s="42" t="n"/>
+      <c r="F93" s="42" t="n"/>
+      <c r="G93" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H93" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The FINGERPRINT environment variable overrides identification, and cached CarParams FW are reused when the VIN is known, so a replaced ECU is not re-queried (car_helpers.py:93-98, 140-142)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I93" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No launch path sets FINGERPRINT; the cache is upstream behaviour</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/car_helpers.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J93" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L93" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M93" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N93" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-057 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Pin the reference identification: accept only an exact FW match to TOYOTA_COROLLA_TSS2 with the expected CarParams for the assured configuration (report a fuzzy match through assured_config), ignore FINGERPRINT in release builds, and re-query FW after a VIN-cache hit when an ECU version changed</t>
+          </r>
+        </is>
+      </c>
+      <c r="O93" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P93" s="43" t="inlineStr"/>
+      <c r="Q93" s="43" t="inlineStr"/>
+      <c r="R93" s="48" t="inlineStr"/>
+      <c r="S93" s="48" t="inlineStr"/>
+    </row>
+    <row r="94" ht="114" customHeight="1">
+      <c r="A94" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-053
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>CAN packer and Toyota message construction</t>
+          </r>
+        </is>
+      </c>
+      <c r="B94" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-053
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Pack actuation and HUD frames with the commanded values, the correct scaling, counter and checksum</t>
+          </r>
+        </is>
+      </c>
+      <c r="C94" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Steering torque other than commanded</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Acceleration other than commanded</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The panda checks the packed value against its limits; an in-limit wrong value passes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>STEERING_LKA torque or ACC_CONTROL acceleration differs from the CarController output</t>
+          </r>
+        </is>
+      </c>
+      <c r="D94" s="50" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-005</t>
+        </is>
+      </c>
+      <c r="E94" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-059 · corrupted
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Actuation frame packed with a value other than the one commanded</t>
+          </r>
+        </is>
+      </c>
+      <c r="G94" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H94" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Scaling or signal-definition defect in the packer or toyotacan.py; out-of-range values are masked to the signal width without an error (packer.py:24-27, 62), so a scaling defect can wrap instead of saturating</t>
+          </r>
+        </is>
+      </c>
+      <c r="I94" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J94" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K94" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause; it compares sendcan</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L94" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M94" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N94" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-044 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Add NaN/inf and stale-input injection for controlsd and card (enable them in test_fuzzy.py with the Corolla fingerprint, or a dedicated test), and run the opendbc car tests (test_models, test_car_interfaces, test_lateral_limits) for Toyota in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O94" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P94" s="43" t="inlineStr"/>
+      <c r="Q94" s="43" t="inlineStr"/>
+      <c r="R94" s="48" t="inlineStr"/>
+      <c r="S94" s="48" t="inlineStr"/>
+    </row>
+    <row r="95" ht="114" customHeight="1">
+      <c r="A95" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-054
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>card main loop and stock AEB interlock</t>
+          </r>
+        </is>
+      </c>
+      <c r="B95" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-054
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run the car interface every CAN cycle, publish carState, and actuate only the latest carControl</t>
+          </r>
+        </is>
+      </c>
+      <c r="C95" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Loss of lateral and longitudinal control with an alert</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The panda revokes 50 ms after the last STEERING_LKA (TSR-408); selfdrived raises controlsMismatch, commIssue and processNotRunning; manager does not restart card</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No carState and no sendcan</t>
+          </r>
+        </is>
+      </c>
+      <c r="D95" s="50" t="inlineStr">
+        <is>
+          <t>HZ-004</t>
+        </is>
+      </c>
+      <c r="E95" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-060 · crash
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>card stops while engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="G95" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H95" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unhandled exception: the loop has no exception handling (card.py:277-284). A non-finite torque or acceleration raises in the CarController (int(round(nan)), carcontroller.py:105; math.floor in packer.py:24); controlsd sanitises its actuators (controlsd.py:171-180), so the path needs a value made non-finite inside card (CarState or pitch compensation)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I95" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J95" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K95" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_car_interfaces fuzzes update and apply for all platforms in CI; generic, not designed for non-finite input. card is in the test_fuzzy NOT_TESTED list</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/tests/test_car_interfaces.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L95" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M95" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N95" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-044 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Add NaN/inf and stale-input injection for controlsd and card (enable them in test_fuzzy.py with the Corolla fingerprint, or a dedicated test), and run the opendbc car tests (test_models, test_car_interfaces, test_lateral_limits) for Toyota in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O95" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P95" s="43" t="inlineStr"/>
+      <c r="Q95" s="43" t="inlineStr"/>
+      <c r="R95" s="48" t="inlineStr"/>
+      <c r="S95" s="48" t="inlineStr"/>
+    </row>
+    <row r="96" ht="114" customHeight="1">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-062
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Monitoring policy and dmonitoringd</t>
+          </r>
+        </is>
+      </c>
+      <c r="B96" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-061
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate an inattentive or unresponsive driver within the policy times (vision 5/8/13 s, wheel-touch 5/15/25 s) and request the terminal reaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="C96" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Automated control continues with an inattentive driver longer than the policy allows</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver warned late; forced deceleration and lockout later</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Pre-alert, alert or terminal step reached after more than 5/8/13 s (vision) or 5/15/25 s (wheel-touch)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D96" s="31" t="inlineStr">
+        <is>
+          <t>HZ-013</t>
+        </is>
+      </c>
+      <c r="E96" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F96" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-061 · late
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalation of an inattentive or unresponsive driver later than the policy times</t>
+          </r>
+        </is>
+      </c>
+      <c r="G96" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H96" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Timers count frames, not time: one awareness step of DT_DMON = 0.05 s per driverStateV2 message (policy.py:198, 207; dmonitoringd.py:21-23). A model running at 16 Hz still passes the frequency check and stretches the 13 s terminal to about 16 s</t>
+          </r>
+        </is>
+      </c>
+      <c r="I96" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J96" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_monitoring.py (13 policy scenarios, CI) steps the policy in frames, so it cannot see a rate error</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L96" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M96" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N96" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-058 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O96" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P96" s="33" t="inlineStr"/>
+      <c r="Q96" s="33" t="inlineStr"/>
+      <c r="R96" s="39" t="inlineStr"/>
+      <c r="S96" s="39" t="inlineStr"/>
+    </row>
+    <row r="97" ht="114" customHeight="1">
+      <c r="A97" s="40" t="n"/>
+      <c r="B97" s="40" t="n"/>
+      <c r="C97" s="40" t="n"/>
+      <c r="D97" s="40" t="n"/>
+      <c r="E97" s="40" t="n"/>
+      <c r="F97" s="40" t="n"/>
+      <c r="G97" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H97" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Defect in the awareness arithmetic, thresholds or recovery factor (1 - T1/T3, 1 - T2/T3, recovery 1.25-5; policy.py:31-47, 196-207, 354-369)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I97" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream code with policy unit tests that are not requirements-based; ruff and ty in CI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/policy.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J97" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K97" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_monitoring.py scenarios (distracted, invisible, uncertain, last-second responder) in CI; targeted at the policy, not proven by mutation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L97" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N97" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-058 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O97" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P97" s="33" t="inlineStr"/>
+      <c r="Q97" s="33" t="inlineStr"/>
+      <c r="R97" s="39" t="inlineStr"/>
+      <c r="S97" s="39" t="inlineStr"/>
+    </row>
+    <row r="98" ht="114" customHeight="1">
+      <c r="A98" s="42" t="n"/>
+      <c r="B98" s="42" t="n"/>
+      <c r="C98" s="42" t="n"/>
+      <c r="D98" s="42" t="n"/>
+      <c r="E98" s="42" t="n"/>
+      <c r="F98" s="42" t="n"/>
+      <c r="G98" s="43" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H98" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Exemptions reset or hold awareness: below 2.8 m/s awareness is held at the pre-alert level, and under the wheel-touch policy any steering or gas input resets it (policy.py:29, 335, 345, 446). A light accelerator touch satisfies the wheel-touch policy</t>
+          </r>
+        </is>
+      </c>
+      <c r="I98" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream design, as FSR-039 states the wheel-touch times; whether a gas touch is acceptable evidence of attention is not recorded</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/policy.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J98" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K98" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_monitoring.py covers the wheel-touch fallback; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L98" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M98" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N98" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-058 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O98" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P98" s="43" t="inlineStr"/>
+      <c r="Q98" s="43" t="inlineStr"/>
+      <c r="R98" s="48" t="inlineStr"/>
+      <c r="S98" s="48" t="inlineStr"/>
+    </row>
+    <row r="99" ht="114" customHeight="1">
+      <c r="A99" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-062
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Monitoring policy and dmonitoringd</t>
+          </r>
+        </is>
+      </c>
+      <c r="B99" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-061
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate an inattentive or unresponsive driver within the policy times (vision 5/8/13 s, wheel-touch 5/15/25 s) and request the terminal reaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="C99" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Automated control continues with an unresponsive driver</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>After 5 s at the terminal level noResponseForceDecel sets v_cruise 0, so the car slows to a stop while lateral control continues</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>driverDistracted3 / driverUnresponsive3 shown; the item stays engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="D99" s="50" t="inlineStr">
+        <is>
+          <t>HZ-013</t>
+        </is>
+      </c>
+      <c r="E99" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F99" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-062 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Terminal unresponsive-driver state reached without the item reaching the SG-010 safe state</t>
+          </r>
+        </is>
+      </c>
+      <c r="G99" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H99" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design the six driver-monitoring events are PERMANENT alerts only, with no SOFT_DISABLE or IMMEDIATE_DISABLE (events.py:524-570); the terminal reaction is the forced deceleration with lateral control kept. Whether that is the SG-010 safe state of FSR-040 is not recorded; it is queued for the lead (DQ-220)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I99" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream design; FSR-040 names a safe state that the FSC does not define for this path</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/fsc.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J99" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K99" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_longitudinal runs the force_decel maneuver in CI and test_monitoring checks the alert levels; neither checks that the reaction meets FSR-040</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L99" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M99" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N99" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-059 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+          </r>
+        </is>
+      </c>
+      <c r="O99" s="59" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="P99" s="43" t="inlineStr"/>
+      <c r="Q99" s="43" t="inlineStr"/>
+      <c r="R99" s="48" t="inlineStr"/>
+      <c r="S99" s="48" t="inlineStr"/>
+    </row>
+    <row r="100" ht="181.5" customHeight="1">
+      <c r="A100" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-061
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver-monitoring model process</t>
+          </r>
+        </is>
+      </c>
+      <c r="B100" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-060
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Estimate face, eye and attention state of the driver for every cabin camera frame</t>
+          </r>
+        </is>
+      </c>
+      <c r="C100" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Automated control continues with an inattentive driver without escalation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The policy judges the driver attentive, or keeps an old attentive pose, so awareness does not count down</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Face pose, eyes or face probability held or NaN with driverStateV2.valid true</t>
+          </r>
+        </is>
+      </c>
+      <c r="D100" s="31" t="inlineStr">
+        <is>
+          <t>HZ-013</t>
+        </is>
+      </c>
+      <c r="E100" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F100" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-063 · value_frozen
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver state stale, frozen or non-finite while dmonitoringd treats it as valid</t>
+          </r>
+        </is>
+      </c>
+      <c r="G100" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H100" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No finiteness or validity check: driverStateV2 is always published valid (dmonitoringmodeld.py:99) and neither process checks for NaN. By code reading a NaN pose with a finite std compares false against the pose thresholds, so the driver counts as attentive (policy.py:228-246); a NaN face probability counts as no face (the conservative direction). Not tested</t>
+          </r>
+        </is>
+      </c>
+      <c r="I100" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J100" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test injects non-finite model output; dmonitoringmodeld is excluded from process replay and test_fuzzy, and model_replay is not run in CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="L100" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M100" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N100" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-058 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-060 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run model_replay for dmonitoringmodeld and modeld in LionDriver CI, and add a non-finite / stale output injection test for dmonitoringd and modeld consumers</t>
+          </r>
+        </is>
+      </c>
+      <c r="O100" s="38" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P100" s="33" t="inlineStr"/>
+      <c r="Q100" s="33" t="inlineStr"/>
+      <c r="R100" s="39" t="inlineStr"/>
+      <c r="S100" s="39" t="inlineStr"/>
+    </row>
+    <row r="101" ht="114" customHeight="1">
+      <c r="A101" s="42" t="n"/>
+      <c r="B101" s="42" t="n"/>
+      <c r="C101" s="42" t="n"/>
+      <c r="D101" s="42" t="n"/>
+      <c r="E101" s="42" t="n"/>
+      <c r="F101" s="42" t="n"/>
+      <c r="G101" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H101" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Empty face arrays make _update_states return early, so face_detected and the last pose stay as they were while the event logic runs (policy.py:264-266)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I101" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J101" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L101" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M101" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N101" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-058 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O101" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P101" s="43" t="inlineStr"/>
+      <c r="Q101" s="43" t="inlineStr"/>
+      <c r="R101" s="48" t="inlineStr"/>
+      <c r="S101" s="48" t="inlineStr"/>
+    </row>
+    <row r="102" ht="114" customHeight="1">
+      <c r="A102" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-060
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B102" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-061
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate an inattentive or unresponsive driver within the policy times (vision 5/8/13 s, wheel-touch 5/15/25 s) and request the terminal reaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="C102" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Disengagement after the 3 s soft disable with an alert; no driver monitoring for the rest of the drive</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>selfdrived commIssue and processNotRunning (SOFT_DISABLE); manager does not restart the process</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No driverMonitoringState</t>
+          </r>
+        </is>
+      </c>
+      <c r="D102" s="50" t="inlineStr"/>
+      <c r="E102" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F102" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-064 · crash
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>dmonitoringd or dmonitoringmodeld stops while engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="G102" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H102" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unhandled exception: brakeDisengageProbs[0] is read without a length check (policy.py:447); model and warp loading have no error handling (dmonitoringmodeld.py:22-48); no try/except in either loop</t>
+          </r>
+        </is>
+      </c>
+      <c r="I102" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J102" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K102" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• dmonitoringd is replayed in process_replay (CI) on recorded inputs; generic. Both processes are in the test_fuzzy NOT_TESTED list</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L102" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M102" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N102" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-058 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O102" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P102" s="43" t="inlineStr"/>
+      <c r="Q102" s="43" t="inlineStr"/>
+      <c r="R102" s="48" t="inlineStr"/>
+      <c r="S102" s="48" t="inlineStr"/>
+    </row>
+    <row r="103" ht="235.5" customHeight="1">
+      <c r="A103" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-071
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal planner and MPC</t>
+          </r>
+        </is>
+      </c>
+      <c r="B103" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-070
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Plan an acceleration within the envelope that keeps the following distance to a lead and stops for a stopped lead</t>
+          </r>
+        </is>
+      </c>
+      <c r="C103" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Insufficient or late deceleration for a lead</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005 (acceleration toward a lead)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>controlsd requests the acceleration; the panda bounds only the range -3.5..2.0 m/s²</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>aTarget above what the lead and the following distance allow</t>
+          </r>
+        </is>
+      </c>
+      <c r="D103" s="31" t="inlineStr">
+        <is>
+          <t>HZ-007
+HZ-005</t>
+        </is>
+      </c>
+      <c r="E103" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F103" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-065 · value_high
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Planned acceleration too high, or deceleration too low, for the lead</t>
+          </r>
+        </is>
+      </c>
+      <c r="G103" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H103" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Plans from invalid or stale inputs: plannerd has no validity gate of its own and uses the leads whatever radarState.valid says (long_mpc.py:313-314); longitudinalPlan.valid = sm.all_checks() is published, but controlsd does not read it, so the reaction is selfdrived commIssue (soft disable, 3 s of continued control) (longitudinal_planner.py:156; selfdrived.py:425-431)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I103" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J103" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L103" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M103" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N103" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-061 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-040 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-602 in controlsd: check age and valid of selfdriveState, carState, modelV2, longitudinalPlan, vehicleParameters and deviceMotion before use (≤ 2 periods); set latActive/longActive false and raise an immediate-disable event when stale; derive carControl.valid from these checks and have card stop actuating on carControl.valid false; give cruiseMismatch a disable type</t>
+          </r>
+        </is>
+      </c>
+      <c r="O103" s="38" t="inlineStr">
+        <is>
+          <t>open
+in progress</t>
+        </is>
+      </c>
+      <c r="P103" s="33" t="inlineStr">
+        <is>
+          <t>10/3/4</t>
+        </is>
+      </c>
+      <c r="Q103" s="41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R103" s="39" t="inlineStr"/>
+      <c r="S103" s="39" t="inlineStr"/>
+    </row>
+    <row r="104" ht="195" customHeight="1">
+      <c r="A104" s="40" t="n"/>
+      <c r="B104" s="40" t="n"/>
+      <c r="C104" s="40" t="n"/>
+      <c r="D104" s="40" t="n"/>
+      <c r="E104" s="40" t="n"/>
+      <c r="F104" s="40" t="n"/>
+      <c r="G104" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H104" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>MPC failure: solution_status != 0 resets the solver and zeroes the trajectories, so the MPC candidate is 0 m/s² for that cycle and crash_cnt is cleared (long_mpc.py:221-242, 365-369); repeated failures lose the lead braking without an event</t>
+          </r>
+        </is>
+      </c>
+      <c r="I104" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J104" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_longitudinal maneuvers in CI exercise the MPC with leads; no solver-failure injection</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L104" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M104" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N104" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-061 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-062 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd robustness: on an MPC failure keep the last valid solution for a bounded time and raise an event if it persists; rate-limit the final aTarget (TSR-624); handle an unknown personality as relaxed; add MPC-failure injection and plannerd fuzzing in CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O104" s="38" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P104" s="33" t="inlineStr"/>
+      <c r="Q104" s="33" t="inlineStr"/>
+      <c r="R104" s="39" t="inlineStr"/>
+      <c r="S104" s="39" t="inlineStr"/>
+    </row>
+    <row r="105" ht="100.5" customHeight="1">
+      <c r="A105" s="42" t="n"/>
+      <c r="B105" s="42" t="n"/>
+      <c r="C105" s="42" t="n"/>
+      <c r="D105" s="42" t="n"/>
+      <c r="E105" s="42" t="n"/>
+      <c r="F105" s="42" t="n"/>
+      <c r="G105" s="43" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H105" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>If orientationNED is missing, the coast limit becomes ACCEL_MAX, which removes it (longitudinal_planner.py:76-79)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I105" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J105" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K105" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L105" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M105" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N105" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-061 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
+          </r>
+        </is>
+      </c>
+      <c r="O105" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P105" s="43" t="inlineStr"/>
+      <c r="Q105" s="43" t="inlineStr"/>
+      <c r="R105" s="48" t="inlineStr"/>
+      <c r="S105" s="48" t="inlineStr"/>
+    </row>
+    <row r="106" ht="168" customHeight="1">
+      <c r="A106" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-071
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal planner and MPC</t>
+          </r>
+        </is>
+      </c>
+      <c r="B106" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-070
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Plan an acceleration within the envelope that keeps the following distance to a lead and stops for a stopped lead</t>
+          </r>
+        </is>
+      </c>
+      <c r="C106" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Abrupt deceleration not required by traffic</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The CarController limits the rate to 0.12 m/s² per frame only while longActive; the panda has no jerk check (SWF-004)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>aTarget jumps when the minimum switches between the MPC, cruise and e2e candidates</t>
+          </r>
+        </is>
+      </c>
+      <c r="D106" s="50" t="inlineStr">
+        <is>
+          <t>HZ-006</t>
+        </is>
+      </c>
+      <c r="E106" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F106" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-066 · commission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Planned acceleration changes in a step</t>
+          </r>
+        </is>
+      </c>
+      <c r="G106" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H106" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design the final aTarget = clip(min(candidates)) has no rate limit (longitudinal_planner.py:142-149); J_CRUISE limits the cruise candidate only and the MPC jerk is a cost, not a constraint (long_mpc.py:39, 267). TSR-624 (ramp within j_down) is not implemented</t>
+          </r>
+        </is>
+      </c>
+      <c r="I106" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J106" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K106" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_longitudinal maneuvers in CI; pass-fail on collisions, not designed for jerk</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L106" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M106" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N106" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-050 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-624: announce deceleration that traffic does not require at least 1 s before its onset, and ramp it within a_min and j_down</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-062 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd robustness: on an MPC failure keep the last valid solution for a bounded time and raise an event if it persists; rate-limit the final aTarget (TSR-624); handle an unknown personality as relaxed; add MPC-failure injection and plannerd fuzzing in CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O106" s="53" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P106" s="43" t="inlineStr"/>
+      <c r="Q106" s="43" t="inlineStr"/>
+      <c r="R106" s="48" t="inlineStr"/>
+      <c r="S106" s="48" t="inlineStr"/>
+    </row>
+    <row r="107" ht="100.5" customHeight="1">
+      <c r="A107" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-071
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal planner and MPC</t>
+          </r>
+        </is>
+      </c>
+      <c r="B107" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-070
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Plan an acceleration within the envelope that keeps the following distance to a lead and stops for a stopped lead</t>
+          </r>
+        </is>
+      </c>
+      <c r="C107" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Insufficient deceleration margin for a braking lead</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Plans that the CA-002/CA-004/CA-011 analyses do not cover</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Experimental (e2e) candidate active, or a following time shorter than relaxed (1.45 s standard, 1.25 s aggressive)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D107" s="50" t="inlineStr">
+        <is>
+          <t>HZ-007</t>
+        </is>
+      </c>
+      <c r="E107" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F107" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-067 · wrong_mode
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Planning in a mode or following distance outside the assured configuration</t>
+          </r>
+        </is>
+      </c>
+      <c r="G107" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H107" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The driver can leave the assured configuration while driving: the distance button cycles the personality and saves it, and ExperimentalMode can be toggled; both are only logged (selfdrived.py:502-506, 607-626). Whether to refuse engagement outside the assured configuration is queued for the lead (DQ-221)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I107" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Defaults set to the assured values; the deviation is logged with a configuration hash</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/assured_config.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J107" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K107" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_assured_config.py checks that deviations are reported (CI); it is not designed to keep the configuration</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_assured_config.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L107" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M107" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N107" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-063 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Apply the lead's decision on engagement outside the assured configuration (DQ-221): refuse engagement or keep logging, with a test</t>
+          </r>
+        </is>
+      </c>
+      <c r="O107" s="59" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="P107" s="43" t="inlineStr"/>
+      <c r="Q107" s="43" t="inlineStr"/>
+      <c r="R107" s="48" t="inlineStr"/>
+      <c r="S107" s="48" t="inlineStr"/>
+    </row>
+    <row r="108" ht="100.5" customHeight="1">
+      <c r="A108" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-070
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal planning (plannerd)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B108" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-070
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Plan an acceleration within the envelope that keeps the following distance to a lead and stops for a stopped lead</t>
+          </r>
+        </is>
+      </c>
+      <c r="C108" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No deceleration for a lead for up to 0.5 s, then coasting while the item is still shown engaged during the soft disable</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>controlsd ends longitudinal control 0.5 s after the last plan (TSR-602); the PCM then coasts; selfdrived commIssue / processNotRunning soft disable; no restart</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>longitudinalPlan stale</t>
+          </r>
+        </is>
+      </c>
+      <c r="D108" s="31" t="inlineStr">
+        <is>
+          <t>HZ-007</t>
+        </is>
+      </c>
+      <c r="E108" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-068 · crash
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd stops or runs late while engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="G108" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H108" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unhandled exception: no try/except; an unknown personality value raises NotImplementedError in the MPC cost setup (long_mpc.py:60-79)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I108" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J108" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K108" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• plannerd is replayed in process_replay (CI); generic. plannerd is in the test_fuzzy NOT_TESTED list</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L108" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M108" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N108" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-062 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd robustness: on an MPC failure keep the last valid solution for a bounded time and raise an event if it persists; rate-limit the final aTarget (TSR-624); handle an unknown personality as relaxed; add MPC-failure injection and plannerd fuzzing in CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="O108" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P108" s="33" t="inlineStr"/>
+      <c r="Q108" s="33" t="inlineStr"/>
+      <c r="R108" s="39" t="inlineStr"/>
+      <c r="S108" s="39" t="inlineStr"/>
+    </row>
+    <row r="109" ht="100.5" customHeight="1">
+      <c r="A109" s="42" t="n"/>
+      <c r="B109" s="42" t="n"/>
+      <c r="C109" s="42" t="n"/>
+      <c r="D109" s="42" t="n"/>
+      <c r="E109" s="42" t="n"/>
+      <c r="F109" s="42" t="n"/>
+      <c r="G109" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H109" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Slow MPC: the loop is paced by modelV2 (20 Hz) and solve_time is published but nothing acts on it (longitudinal_planner.py:161)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I109" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J109" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause; test_onroad timing checks are device-only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L109" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M109" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N109" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-048 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench or HIL fault injection (WP-V-05) - stop or stall selfdrived, modeld, plannerd and controlsd while engaged and measure time to zero torque/acceleration and to the alert; run test_onroad timing tests on a comma 3X for each release</t>
+          </r>
+        </is>
+      </c>
+      <c r="O109" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P109" s="43" t="inlineStr"/>
+      <c r="Q109" s="43" t="inlineStr"/>
+      <c r="R109" s="48" t="inlineStr"/>
+      <c r="S109" s="48" t="inlineStr"/>
+    </row>
+    <row r="110" ht="100.5" customHeight="1">
+      <c r="A110" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-072
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Forward collision warning decision</t>
+          </r>
+        </is>
+      </c>
+      <c r="B110" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-071
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Raise a forward collision warning when a collision with the lead is predicted</t>
+          </r>
+        </is>
+      </c>
+      <c r="C110" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver not warned of an imminent collision with a lead while engaged</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No FCW alert from the item</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>longitudinalPlan.fcw stays false</t>
+          </r>
+        </is>
+      </c>
+      <c r="D110" s="50" t="inlineStr">
+        <is>
+          <t>HZ-007</t>
+        </is>
+      </c>
+      <c r="E110" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F110" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-069 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Forward collision warning not raised for a predicted collision</t>
+          </r>
+        </is>
+      </c>
+      <c r="G110" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H110" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>FCW needs crash_cnt &gt; 2 with leadOne.modelProb &gt; 0.9 (long_mpc.py:338-342; longitudinal_planner.py:121): a radar-only lead (low-speed override, modelProb 0, radard.py:83, 174) never triggers it, and an MPC reset clears the counter (SWF-065.C2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I110" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J110" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K110" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_stopped_vehicle checks that a collision is preceded by FCW in its scenarios (CI); targeted, not proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/stopped_vehicle/test_stopped_vehicle.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L110" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N110" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-064 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+          </r>
+        </is>
+      </c>
+      <c r="O110" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P110" s="43" t="inlineStr"/>
+      <c r="Q110" s="43" t="inlineStr"/>
+      <c r="R110" s="48" t="inlineStr"/>
+      <c r="S110" s="48" t="inlineStr"/>
+    </row>
+    <row r="111" ht="100.5" customHeight="1">
+      <c r="A111" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-081
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lead selection and radar/vision fusion</t>
+          </r>
+        </is>
+      </c>
+      <c r="B111" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-080
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide the lead state (distance, relative speed and acceleration) from radar tracks matched to model leads, and flag radar faults</t>
+          </r>
+        </is>
+      </c>
+      <c r="C111" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Insufficient or late deceleration for a lead</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Planner keeps the cruise speed or brakes late; FCW not raised</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>leadOne absent or at a wrong distance</t>
+          </r>
+        </is>
+      </c>
+      <c r="D111" s="31" t="inlineStr">
+        <is>
+          <t>HZ-007</t>
+        </is>
+      </c>
+      <c r="E111" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F111" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-070 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lead missed or reported late while a lead is present</t>
+          </r>
+        </is>
+      </c>
+      <c r="G111" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H111" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design a radar track is used above 4 m/s only when matched to a model lead with probability &gt; 0.5 and inside the match window (radard.py:113-133, 156-157); a stationary target seen only by radar is ignored (FI-2026-001 RC-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I111" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J111" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K111" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_stopped_vehicle test_radar_only_stationary_target reproduces the gap and is marked expectedFailure (CI)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/stopped_vehicle/test_stopped_vehicle.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L111" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M111" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N111" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-064 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+          </r>
+        </is>
+      </c>
+      <c r="O111" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P111" s="33" t="inlineStr"/>
+      <c r="Q111" s="33" t="inlineStr"/>
+      <c r="R111" s="39" t="inlineStr"/>
+      <c r="S111" s="39" t="inlineStr"/>
+    </row>
+    <row r="112" ht="195" customHeight="1">
+      <c r="A112" s="40" t="n"/>
+      <c r="B112" s="40" t="n"/>
+      <c r="C112" s="40" t="n"/>
+      <c r="D112" s="40" t="n"/>
+      <c r="E112" s="40" t="n"/>
+      <c r="F112" s="40" t="n"/>
+      <c r="G112" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H112" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Radar faults reach the planner as data: plannerd uses the leads whatever radarState.valid says, and radarFault / radarTempUnavailable are SOFT_DISABLE (selfdrived.py:408-414; events.py:878-886), so a faulted lead is used for the 3 s soft disable</t>
+          </r>
+        </is>
+      </c>
+      <c r="I112" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J112" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K112" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_leads.py checks only that radarTracks are invalid without radar CAN (CI); targeted at the fault report, not at its use</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_leads.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L112" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M112" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N112" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-061 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-064 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+          </r>
+        </is>
+      </c>
+      <c r="O112" s="38" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P112" s="33" t="inlineStr"/>
+      <c r="Q112" s="33" t="inlineStr"/>
+      <c r="R112" s="39" t="inlineStr"/>
+      <c r="S112" s="39" t="inlineStr"/>
+    </row>
+    <row r="113" ht="100.5" customHeight="1">
+      <c r="A113" s="42" t="n"/>
+      <c r="B113" s="42" t="n"/>
+      <c r="C113" s="42" t="n"/>
+      <c r="D113" s="42" t="n"/>
+      <c r="E113" s="42" t="n"/>
+      <c r="F113" s="42" t="n"/>
+      <c r="G113" s="43" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H113" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard stops: the Kalman filter asserts 0.01 &lt; dt &lt; 0.2 (radard.py:33), there is no try/except and manager does not restart it; radarState then goes stale and the plan invalid (commIssue soft disable)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I113" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J113" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• radard is fuzzed in test_fuzzy with the Corolla TSS2 fingerprint (CI, 10 examples); generic</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_fuzzy.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L113" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M113" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N113" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-064 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+          </r>
+        </is>
+      </c>
+      <c r="O113" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P113" s="43" t="inlineStr"/>
+      <c r="Q113" s="43" t="inlineStr"/>
+      <c r="R113" s="48" t="inlineStr"/>
+      <c r="S113" s="48" t="inlineStr"/>
+    </row>
+    <row r="114" ht="114" customHeight="1">
+      <c r="A114" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-081
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lead selection and radar/vision fusion</t>
+          </r>
+        </is>
+      </c>
+      <c r="B114" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-080
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide the lead state (distance, relative speed and acceleration) from radar tracks matched to model leads, and flag radar faults</t>
+          </r>
+        </is>
+      </c>
+      <c r="C114" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unintended deceleration</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Planner brakes for it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>leadOne present at a short distance where no lead is</t>
+          </r>
+        </is>
+      </c>
+      <c r="D114" s="31" t="inlineStr">
+        <is>
+          <t>HZ-006</t>
+        </is>
+      </c>
+      <c r="E114" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F114" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-071 · commission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>False or wrong lead reported</t>
+          </r>
+        </is>
+      </c>
+      <c r="G114" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H114" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Low-speed override: below 4 m/s the closest radar track with |y| &lt; 1 m and 0.75 &lt; d &lt; 25 m becomes leadOne without model confirmation (radard.py:24, 98-101, 167-174)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I114" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J114" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K114" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L114" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M114" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N114" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-064 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+          </r>
+        </is>
+      </c>
+      <c r="O114" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P114" s="33" t="inlineStr"/>
+      <c r="Q114" s="33" t="inlineStr"/>
+      <c r="R114" s="39" t="inlineStr"/>
+      <c r="S114" s="39" t="inlineStr"/>
+    </row>
+    <row r="115" ht="114" customHeight="1">
+      <c r="A115" s="42" t="n"/>
+      <c r="B115" s="42" t="n"/>
+      <c r="C115" s="42" t="n"/>
+      <c r="D115" s="42" t="n"/>
+      <c r="E115" s="42" t="n"/>
+      <c r="F115" s="42" t="n"/>
+      <c r="G115" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H115" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Wrong track matched to the model lead (adjacent lane) inside the match window of max(25 %, 5 m) and 10 m/s (radard.py:113-133)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I115" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J115" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L115" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M115" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N115" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-064 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+          </r>
+        </is>
+      </c>
+      <c r="O115" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P115" s="43" t="inlineStr"/>
+      <c r="Q115" s="43" t="inlineStr"/>
+      <c r="R115" s="48" t="inlineStr"/>
+      <c r="S115" s="48" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S86"/>
-  <mergeCells count="142">
+  <autoFilter ref="A2:S115"/>
+  <mergeCells count="196">
     <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E92:E93"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="F111:F113"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D45:D46"/>
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="F45:F46"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C114:C115"/>
     <mergeCell ref="E7:E9"/>
+    <mergeCell ref="C87:C89"/>
+    <mergeCell ref="A114:A115"/>
     <mergeCell ref="E74:E75"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="E3:E5"/>
@@ -20615,13 +26159,17 @@
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="F72:F73"/>
     <mergeCell ref="A49:A51"/>
+    <mergeCell ref="F103:F105"/>
     <mergeCell ref="C49:C51"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="D66:D68"/>
     <mergeCell ref="A22:A23"/>
+    <mergeCell ref="F87:F89"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="E41:E42"/>
+    <mergeCell ref="B114:B115"/>
     <mergeCell ref="A35:A36"/>
+    <mergeCell ref="D114:D115"/>
     <mergeCell ref="C69:C70"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="F66:F68"/>
@@ -20630,24 +26178,35 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B90:B91"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="C45:C46"/>
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A90:A91"/>
     <mergeCell ref="F49:F51"/>
+    <mergeCell ref="C100:C101"/>
     <mergeCell ref="F35:F36"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="C47:C48"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="C96:C98"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="B76:B78"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="F100:F101"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B108:B109"/>
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="I1:M1"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="D111:D113"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="D30:D31"/>
@@ -20657,15 +26216,22 @@
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="E49:E51"/>
+    <mergeCell ref="A92:A93"/>
     <mergeCell ref="C74:C75"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B103:B105"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D103:D105"/>
     <mergeCell ref="E58:E59"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="D90:D91"/>
     <mergeCell ref="E52:E53"/>
+    <mergeCell ref="B87:B89"/>
+    <mergeCell ref="D87:D89"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="F74:F75"/>
+    <mergeCell ref="F96:F98"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E60:E61"/>
     <mergeCell ref="A41:A42"/>
@@ -20674,17 +26240,25 @@
     <mergeCell ref="C66:C68"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="E66:E68"/>
+    <mergeCell ref="A111:A113"/>
+    <mergeCell ref="C111:C113"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E108:E109"/>
     <mergeCell ref="F41:F42"/>
+    <mergeCell ref="E111:E113"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E114:E115"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="F43:F44"/>
     <mergeCell ref="F7:F9"/>
     <mergeCell ref="F52:F53"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="F92:F93"/>
+    <mergeCell ref="A87:A89"/>
     <mergeCell ref="F39:F40"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="E72:E73"/>
@@ -20693,9 +26267,11 @@
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="F14:F15"/>
+    <mergeCell ref="E87:E89"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B100:B101"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="A60:A61"/>
@@ -20704,26 +26280,39 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="C76:C78"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C92:C93"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="D54:D56"/>
+    <mergeCell ref="F114:F115"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="E90:E91"/>
     <mergeCell ref="C52:C53"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="D49:D51"/>
     <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="A100:A101"/>
     <mergeCell ref="D74:D75"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="A72:A73"/>
     <mergeCell ref="A47:A48"/>
+    <mergeCell ref="F90:F91"/>
     <mergeCell ref="C72:C73"/>
     <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D96:D98"/>
+    <mergeCell ref="A103:A105"/>
+    <mergeCell ref="C103:C105"/>
     <mergeCell ref="D58:D59"/>
     <mergeCell ref="F58:F59"/>
     <mergeCell ref="A66:A68"/>
+    <mergeCell ref="E100:E101"/>
     <mergeCell ref="E47:E48"/>
+    <mergeCell ref="E103:E105"/>
     <mergeCell ref="D60:D61"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="F60:F61"/>
@@ -20733,12 +26322,14 @@
     <mergeCell ref="F69:F70"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F76:F78"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="C108:C109"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20746,7 +26337,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 0.8 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -20761,7 +26352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20776,122 +26367,122 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="60" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="C1" s="60" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="59" t="inlineStr">
+      <c r="D1" s="60" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="60" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="59" t="inlineStr">
+      <c r="F1" s="60" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="59" t="inlineStr">
+      <c r="G1" s="60" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="59" t="inlineStr">
+      <c r="H1" s="60" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="59" t="inlineStr">
+      <c r="I1" s="60" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>Run the opendbc safety suite and the mutation tests as a blocking gate in LionDriver CI for every change and submodule bump</t>
         </is>
       </c>
-      <c r="D2" s="60" t="inlineStr">
+      <c r="D2" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="E2" s="62" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F2" s="60" t="inlineStr"/>
-      <c r="G2" s="60" t="inlineStr">
+      <c r="F2" s="61" t="inlineStr"/>
+      <c r="G2" s="61" t="inlineStr">
         <is>
           <t>10/5/3</t>
         </is>
       </c>
-      <c r="H2" s="62" t="inlineStr">
+      <c r="H2" s="63" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I2" s="60" t="inlineStr">
+      <c r="I2" s="61" t="inlineStr">
         <is>
           <t>.github/workflows/safety.yaml (CR-CI-05, merged from liondriver-dev): safety tests with 100% line coverage, MISRA and mutation jobs on push and pull request. Branch protection making them blocking is not verified here</t>
         </is>
       </c>
     </row>
     <row r="3" ht="141" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>Requirements-based tests for the panda safety model, traced to the draft TSRs and SWSRs (assurance WP-S-02, WP-W-02); the requirements exist as drafts, the tests do not</t>
         </is>
       </c>
-      <c r="D3" s="60" t="inlineStr">
+      <c r="D3" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="60" t="inlineStr">
+      <c r="E3" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="60" t="inlineStr">
+      <c r="F3" s="61" t="inlineStr">
         <is>
           <t>SWF-001.C2
 SWF-002.C1
@@ -20905,426 +26496,426 @@
 SWF-017.C1</t>
         </is>
       </c>
-      <c r="G3" s="60" t="inlineStr">
+      <c r="G3" s="61" t="inlineStr">
         <is>
           <t>10/3/3</t>
         </is>
       </c>
-      <c r="H3" s="63" t="inlineStr">
+      <c r="H3" s="64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I3" s="60" t="inlineStr"/>
+      <c r="I3" s="61" t="inlineStr"/>
     </row>
     <row r="4" ht="46.5" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from vehicle measurements (FSC FOI-001, DFA DM-10) and set panda limits from them, independently of the SoC limits</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="61" t="inlineStr">
         <is>
           <t>SWF-001.C1
 SWF-003.C1
 SWF-003.C3</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr"/>
-      <c r="H4" s="60" t="inlineStr"/>
-      <c r="I4" s="60" t="inlineStr"/>
+      <c r="G4" s="61" t="inlineStr"/>
+      <c r="H4" s="61" t="inlineStr"/>
+      <c r="I4" s="61" t="inlineStr"/>
     </row>
     <row r="5" ht="100.5" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-004</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>Implement the panda configuration lock (LD-DES-001 DR-01..DR-07, DR-05 for ELM327)</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F5" s="60" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>SWF-013.C1</t>
         </is>
       </c>
-      <c r="G5" s="60" t="inlineStr"/>
-      <c r="H5" s="60" t="inlineStr"/>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr"/>
+      <c r="H5" s="61" t="inlineStr"/>
+      <c r="I5" s="61" t="inlineStr">
         <is>
           <t>Implemented for the reference build in panda#4 (9f60e17); D-12 decided. The reference build is the default since #36/#41 (SWF-ACT-009 completed). DR-05 (ELM327 refused after the car mode until ignition off) in panda#16 (a55bdfc). Open: the remaining LD-DES-001 requirements (firmware authenticity), HIL test test_11_reference_lock not run (D-04)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46.5" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-005</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>Add an acceleration-rate (jerk) check to the panda longitudinal checks, or justify the absence with characterized powertrain rate limits (OI-002)</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="60" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>SWF-004.C1</t>
         </is>
       </c>
-      <c r="G6" s="60" t="inlineStr"/>
-      <c r="H6" s="60" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr"/>
+      <c r="G6" s="61" t="inlineStr"/>
+      <c r="H6" s="61" t="inlineStr"/>
+      <c r="I6" s="61" t="inlineStr"/>
     </row>
     <row r="7" ht="46.5" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-006</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>Verify on the vehicle that the PCM cancels cruise on brake (FSC FOI-006) so PCM_CRUISE can be credited as the diverse brake path; add a safety test for brake-without-cruise-cancel</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr">
+      <c r="E7" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="60" t="inlineStr">
+      <c r="F7" s="61" t="inlineStr">
         <is>
           <t>SWF-005.C1</t>
         </is>
       </c>
-      <c r="G7" s="60" t="inlineStr"/>
-      <c r="H7" s="60" t="inlineStr"/>
-      <c r="I7" s="60" t="inlineStr"/>
+      <c r="G7" s="61" t="inlineStr"/>
+      <c r="H7" s="61" t="inlineStr"/>
+      <c r="I7" s="61" t="inlineStr"/>
     </row>
     <row r="8" ht="114" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-007</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>Derive RX-lag and heartbeat timeouts from the FTTI and check them at 8 Hz or faster while controls are allowed (LD-DES-001 DR-20)</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="60" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>SWF-006.C1
 SWF-014.C1
 SWF-014.C2</t>
         </is>
       </c>
-      <c r="G8" s="60" t="inlineStr"/>
-      <c r="H8" s="60" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="G8" s="61" t="inlineStr"/>
+      <c r="H8" s="61" t="inlineStr"/>
+      <c r="I8" s="61" t="inlineStr">
         <is>
           <t>RX lag: 5 periods at 100 Hz (opendbc#1, panda#3). Heartbeat loss: 0.3 s at 100 Hz (panda#7, BL-003). BL-005: actuation frames supervised for arrival, 50 ms STEERING_LKA and 100 ms ACC_CONTROL (TSR-408, opendbc#11, reference build by default), which bounds a control-loop stall behind a live heartbeat (SWF-014.C2 AP L). Engaged mismatch still about 3 s at 1 Hz; FTTI derivation and confirmation of the timeouts on reference logs open</t>
         </is>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-008</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>Add a unit or static check that every host TX path calls can_send with skip_tx_hook=false</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr">
+      <c r="E9" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="60" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>SWF-016.C1</t>
         </is>
       </c>
-      <c r="G9" s="60" t="inlineStr"/>
-      <c r="H9" s="60" t="inlineStr"/>
-      <c r="I9" s="60" t="inlineStr"/>
+      <c r="G9" s="61" t="inlineStr"/>
+      <c r="H9" s="61" t="inlineStr"/>
+      <c r="I9" s="61" t="inlineStr"/>
     </row>
     <row r="10" ht="127.5" customHeight="1">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-009</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>Make LIONDRIVER_REFERENCE=1 (with RELEASE=1) the only firmware build used for the reference configuration: set it in openpilot's panda build and the release procedure, and have the host check it (e.g. a version or health flag) before engaging</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr">
+      <c r="E10" s="62" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F10" s="60" t="inlineStr">
+      <c r="F10" s="61" t="inlineStr">
         <is>
           <t>SWF-001.C3
 SWF-008.C1
 SWF-013.C2</t>
         </is>
       </c>
-      <c r="G10" s="60" t="inlineStr">
+      <c r="G10" s="61" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H10" s="63" t="inlineStr">
+      <c r="H10" s="64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="61" t="inlineStr">
         <is>
           <t>SConstruct builds the panda firmware and pandad with LIONDRIVER_REFERENCE=1 by default (#36, #41); pandad sets a car mode only on a panda reporting HEALTH_FLAG_REFERENCE_BUILD (TSR-619, panda#12); release_variant.sh selects the reference variant and the CI job panda_reference_release_build checks every firmware compile for -DLIONDRIVER_REFERENCE (#80, green at 20569e9). The signed release image and its install check stay with PFMEA (PFM-001) and SWF-ACT-028</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-010</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>Restrict ELM327 TX to the UDS services fingerprinting and radar disable need, and refuse it above standstill (WP-W-04 OI-6)</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F11" s="60" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>SWF-015.C1</t>
         </is>
       </c>
-      <c r="G11" s="60" t="inlineStr"/>
-      <c r="H11" s="60" t="inlineStr"/>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="G11" s="61" t="inlineStr"/>
+      <c r="H11" s="61" t="inlineStr"/>
+      <c r="I11" s="61" t="inlineStr">
         <is>
           <t>Reference build: ELM327 refused after the car mode until ignition off (panda#16, DR-05, host-tested). Open: frame-content restriction and a motion condition before the car mode</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46.5" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-011</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>Confirm the LSI range from the STM32H725 datasheet and run the watchdog HIL test (test_10_hw_watchdog) on the bench, including a long soak for spurious resets (D-04)</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr">
+      <c r="E12" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="60" t="inlineStr">
+      <c r="F12" s="61" t="inlineStr">
         <is>
           <t>SWF-018.C1
 SWF-019.C1</t>
         </is>
       </c>
-      <c r="G12" s="60" t="inlineStr"/>
-      <c r="H12" s="60" t="inlineStr"/>
-      <c r="I12" s="60" t="inlineStr"/>
+      <c r="G12" s="61" t="inlineStr"/>
+      <c r="H12" s="61" t="inlineStr"/>
+      <c r="I12" s="61" t="inlineStr"/>
     </row>
     <row r="13" ht="73.5" customHeight="1">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-020</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>Bind the heartbeat to the command path. Send engaged=1 only while selfdriveState is enabled and the forwarding thread has sent a sendcan batch less than 0.1 s ago, or add a sequence or age field the panda checks (TSR-409, TSR-602). Coordinate with SWF-ACT-007 (panda engaged-mismatch at 0.3 s)</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="E13" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="60" t="inlineStr">
+      <c r="F13" s="61" t="inlineStr">
         <is>
           <t>SWF-020.C1</t>
         </is>
       </c>
-      <c r="G13" s="60" t="inlineStr"/>
-      <c r="H13" s="60" t="inlineStr"/>
-      <c r="I13" s="60" t="inlineStr"/>
+      <c r="G13" s="61" t="inlineStr"/>
+      <c r="H13" s="61" t="inlineStr"/>
+      <c r="I13" s="61" t="inlineStr"/>
     </row>
     <row r="14" ht="87" customHeight="1">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-021</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>Make link failure bounded and visible. Send the heartbeat independently of the health read. Give control transfers a finite timeout and bound the fail-recovery loop. Clear connected and exit on a persistent failure. Do not reset or DFU-recover the internal panda from pandad.py while onroad unless needed. In selfdrived (EL-04), raise the controlsAllowed-mismatch alert within 0.1-0.2 s instead of 200 frames</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr">
+      <c r="E14" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F14" s="60" t="inlineStr">
+      <c r="F14" s="61" t="inlineStr">
         <is>
           <t>SWF-021.C1
 SWF-021.C2
@@ -21332,313 +26923,313 @@
 SWF-027.C2</t>
         </is>
       </c>
-      <c r="G14" s="60" t="inlineStr"/>
-      <c r="H14" s="60" t="inlineStr"/>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="G14" s="61" t="inlineStr"/>
+      <c r="H14" s="61" t="inlineStr"/>
+      <c r="I14" s="61" t="inlineStr">
         <is>
           <t>selfdrived part done in part: controlsMismatch within 2 samples and 0.5 s (#51, TSR-621), pandaHeartbeatLost on the panda flag (TSR-615). The pandad parts (heartbeat independent of the health read, finite control-transfer timeout) are open</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-022</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="61" t="inlineStr">
         <is>
           <t>Host allow-list for the reference configuration (TOYOTA, param 73, alternative experience 0) before 0xdc/0xdf. Read back the mode, param and alternative experience from health, and set safety_configured_ only on a match. Retry or refuse ControlsReady on a mismatch</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="E15" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F15" s="60" t="inlineStr">
+      <c r="F15" s="61" t="inlineStr">
         <is>
           <t>SWF-022.C1
 SWF-022.C2</t>
         </is>
       </c>
-      <c r="G15" s="60" t="inlineStr"/>
-      <c r="H15" s="60" t="inlineStr"/>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="G15" s="61" t="inlineStr"/>
+      <c r="H15" s="61" t="inlineStr"/>
+      <c r="I15" s="61" t="inlineStr">
         <is>
           <t>Not started on the host. BL-005: the panda reference lock refuses any mode but TOYOTA/73 in the default build, which removes the unsafe direction of SWF-022.C1; the host allow-list and readback remain for diagnosability</t>
         </is>
       </c>
     </row>
     <row r="16" ht="73.5" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-023</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="61" t="inlineStr">
         <is>
           <t>Derive the sendcan maximum age from the FTTI and the control period (e.g. 0.1 s). Compare it in one clock domain (stamp with CLOCK_BOOTTIME, or compare with CLOCK_MONOTONIC). After a stall, keep only the newest frame per address instead of replaying the backlog. Decide whether events with valid=false are forwarded</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr">
+      <c r="D16" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E16" s="60" t="inlineStr">
+      <c r="E16" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="60" t="inlineStr">
+      <c r="F16" s="61" t="inlineStr">
         <is>
           <t>SWF-023.C1
 SWF-024.C1</t>
         </is>
       </c>
-      <c r="G16" s="60" t="inlineStr"/>
-      <c r="H16" s="60" t="inlineStr"/>
-      <c r="I16" s="60" t="inlineStr"/>
+      <c r="G16" s="61" t="inlineStr"/>
+      <c r="H16" s="61" t="inlineStr"/>
+      <c r="I16" s="61" t="inlineStr"/>
     </row>
     <row r="17" ht="73.5" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-024</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>Add host unit tests for the pandad logic, run in CI (unit_tests via test_native.py): the sendcan age gate including the clock domain, the heartbeat engaged derivation, the fault-bit mapping, and the safety setter sequence and readback, using a fake Panda. Show they fail on mutated gates so D can be rated as proven</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F17" s="60" t="inlineStr">
+      <c r="F17" s="61" t="inlineStr">
         <is>
           <t>SWF-023.C1
 SWF-024.C1
 SWF-025.C1</t>
         </is>
       </c>
-      <c r="G17" s="60" t="inlineStr"/>
-      <c r="H17" s="60" t="inlineStr"/>
-      <c r="I17" s="60" t="inlineStr"/>
+      <c r="G17" s="61" t="inlineStr"/>
+      <c r="H17" s="61" t="inlineStr"/>
+      <c r="I17" s="61" t="inlineStr"/>
     </row>
     <row r="18" ht="87" customHeight="1">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-025</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="61" t="inlineStr">
         <is>
           <t>Fix the faults mapping. Size the list from the mapped bits only, log unknown bits, and add the panda bit 27 (interruptRateSoundDma) to cereal FaultType (log.capnp, pandad.cc:257-268)</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E18" s="61" t="inlineStr">
+      <c r="E18" s="62" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F18" s="60" t="inlineStr">
+      <c r="F18" s="61" t="inlineStr">
         <is>
           <t>SWF-025.C1</t>
         </is>
       </c>
-      <c r="G18" s="60" t="inlineStr">
+      <c r="G18" s="61" t="inlineStr">
         <is>
           <t>8/5/4</t>
         </is>
       </c>
-      <c r="H18" s="64" t="inlineStr">
+      <c r="H18" s="65" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="61" t="inlineStr">
         <is>
           <t>Merged in jherrodthomas/LionDriver#48 (3534bc2): fill_panda_faults, interruptRateSoundDma @27, tests/test_pandad_faults run by test_native.py in CI unit_tests; fails with the old sizing. Impact record assurance/07-supporting/impact/change-2026-10-13-pandad-fault-mapping.md. SWF-025.C1 re-rated O 8-&gt;5, D 10-&gt;4 (AP H-&gt;M)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-026</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="61" t="inlineStr">
         <is>
           <t>Report frames that pandad drops (age gate, failed bulk write) in pandaStates or a pandad event, and have selfdrived disable with an alert while engaged (closes System FMEA SFM-005.C2 and SFM-011.C2 on the host side)</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="E19" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="F19" s="61" t="inlineStr">
         <is>
           <t>SWF-024.C1
 SWF-024.C2</t>
         </is>
       </c>
-      <c r="G19" s="60" t="inlineStr"/>
-      <c r="H19" s="60" t="inlineStr"/>
-      <c r="I19" s="60" t="inlineStr"/>
+      <c r="G19" s="61" t="inlineStr"/>
+      <c r="H19" s="61" t="inlineStr"/>
+      <c r="I19" s="61" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-027</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>Replace the XOR checksums on the SPI link with a CRC (host spi.cc and panda firmware), or justify XOR with a residual-error analysis that uses the measured SPI error rate (spi_error_count) and the Toyota message checksum as a diverse check</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="E20" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="F20" s="61" t="inlineStr">
         <is>
           <t>SWF-026.C1</t>
         </is>
       </c>
-      <c r="G20" s="60" t="inlineStr"/>
-      <c r="H20" s="60" t="inlineStr"/>
-      <c r="I20" s="60" t="inlineStr"/>
+      <c r="G20" s="61" t="inlineStr"/>
+      <c r="H20" s="61" t="inlineStr"/>
+      <c r="I20" s="61" t="inlineStr"/>
     </row>
     <row r="21" ht="87" customHeight="1">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-028</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="61" t="inlineStr">
         <is>
           <t>Build and flash only the LIONDRIVER_REFERENCE firmware for the reference configuration, and have pandad check a reference-build flag or version before setting a car mode (with SWF-ACT-009). Compile out BOARDD_SKIP_FW_CHECK, STARTED, FAKESEND, SPI_ERR_PROB and BOARDD_LOOPBACK in release builds</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E21" s="60" t="inlineStr">
+      <c r="E21" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F21" s="60" t="inlineStr">
+      <c r="F21" s="61" t="inlineStr">
         <is>
           <t>SWF-022.C1
 SWF-028.C1
 SWF-028.C2</t>
         </is>
       </c>
-      <c r="G21" s="60" t="inlineStr"/>
-      <c r="H21" s="60" t="inlineStr"/>
-      <c r="I21" s="60" t="inlineStr">
+      <c r="G21" s="61" t="inlineStr"/>
+      <c r="H21" s="61" t="inlineStr"/>
+      <c r="I21" s="61" t="inlineStr">
         <is>
           <t>Reference firmware built by default and the reference-build flag checked before a car mode (#36, #41, TSR-619). Open: check that the panda runs the assured release image (version or signature of the released build, not any reference build), a host test of the check, and compiling out the test hooks</t>
         </is>
       </c>
     </row>
     <row r="22" ht="114" customHeight="1">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-029</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C22" s="60" t="inlineStr">
+      <c r="C22" s="61" t="inlineStr">
         <is>
           <t>Run the pandad hardware tests (test_pandad.py, test_pandad_spi.py, test_pandad_loopback.py) on a comma 3X before release. While engaged on a bench, inject: stopping selfdrived, controlsd and card; killing or hanging pandad; SPI errors; and a panda reset. Measure the time to no output and to the SoC alert (FSR-007 verification, D-04)</t>
         </is>
       </c>
-      <c r="D22" s="60" t="inlineStr">
+      <c r="D22" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E22" s="60" t="inlineStr">
+      <c r="E22" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F22" s="60" t="inlineStr">
+      <c r="F22" s="61" t="inlineStr">
         <is>
           <t>SWF-020.C1
 SWF-021.C1
@@ -21650,37 +27241,37 @@
 SWF-029.C2</t>
         </is>
       </c>
-      <c r="G22" s="60" t="inlineStr"/>
-      <c r="H22" s="60" t="inlineStr"/>
-      <c r="I22" s="60" t="inlineStr"/>
+      <c r="G22" s="61" t="inlineStr"/>
+      <c r="H22" s="61" t="inlineStr"/>
+      <c r="I22" s="61" t="inlineStr"/>
     </row>
     <row r="23" ht="87" customHeight="1">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-030</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C23" s="60" t="inlineStr">
+      <c r="C23" s="61" t="inlineStr">
         <is>
           <t>Requirements-based tests for selfdrived traced to FSR-030/033/034/036 and TSR-601/606/617/621: state machine, data_sample/update_events with synthetic carState, pandaStates and SubMaster faults (brake, cancel, stale or missing services, panda mismatch), helpers.py and alert priority; prove them with a mutation run on state.py, selfdrived.py and helpers.py</t>
         </is>
       </c>
-      <c r="D23" s="60" t="inlineStr">
+      <c r="D23" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E23" s="60" t="inlineStr">
+      <c r="E23" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F23" s="60" t="inlineStr">
+      <c r="F23" s="61" t="inlineStr">
         <is>
           <t>SWF-030.C1
 SWF-031.C2
@@ -21688,116 +27279,116 @@
 SWF-034.C1</t>
         </is>
       </c>
-      <c r="G23" s="60" t="inlineStr">
+      <c r="G23" s="61" t="inlineStr">
         <is>
           <t>10/5/4</t>
         </is>
       </c>
-      <c r="H23" s="62" t="inlineStr">
+      <c r="H23" s="63" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I23" s="60" t="inlineStr"/>
+      <c r="I23" s="61" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-031</t>
         </is>
       </c>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C24" s="60" t="inlineStr">
+      <c r="C24" s="61" t="inlineStr">
         <is>
           <t>Reference-configuration guard: refuse engagement (permanent NO_ENTRY) when REPLAY, SIMULATION or TESTING_CLOSET is set or the big-model (chestnut) path is active, and exclude that path from reference builds (TSR-603, TSR-613)</t>
         </is>
       </c>
-      <c r="D24" s="60" t="inlineStr">
+      <c r="D24" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E24" s="60" t="inlineStr">
+      <c r="E24" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F24" s="60" t="inlineStr">
+      <c r="F24" s="61" t="inlineStr">
         <is>
           <t>SWF-030.C2
 SWF-032.C2</t>
         </is>
       </c>
-      <c r="G24" s="60" t="inlineStr"/>
-      <c r="H24" s="60" t="inlineStr"/>
-      <c r="I24" s="60" t="inlineStr"/>
+      <c r="G24" s="61" t="inlineStr"/>
+      <c r="H24" s="61" t="inlineStr"/>
+      <c r="I24" s="61" t="inlineStr"/>
     </row>
     <row r="25" ht="46.5" customHeight="1">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-032</t>
         </is>
       </c>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C25" s="60" t="inlineStr">
+      <c r="C25" s="61" t="inlineStr">
         <is>
           <t>Supervise carState freshness in selfdrived (age of the last message, at most 2 periods) and raise an immediate disable when it is stale, instead of reusing the previous carState</t>
         </is>
       </c>
-      <c r="D25" s="60" t="inlineStr">
+      <c r="D25" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E25" s="60" t="inlineStr">
+      <c r="E25" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F25" s="60" t="inlineStr">
+      <c r="F25" s="61" t="inlineStr">
         <is>
           <t>SWF-031.C1</t>
         </is>
       </c>
-      <c r="G25" s="60" t="inlineStr"/>
-      <c r="H25" s="60" t="inlineStr"/>
-      <c r="I25" s="60" t="inlineStr"/>
+      <c r="G25" s="61" t="inlineStr"/>
+      <c r="H25" s="61" t="inlineStr"/>
+      <c r="I25" s="61" t="inlineStr"/>
     </row>
     <row r="26" ht="87" customHeight="1">
-      <c r="A26" s="60" t="inlineStr">
+      <c r="A26" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-033</t>
         </is>
       </c>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C26" s="60" t="inlineStr">
+      <c r="C26" s="61" t="inlineStr">
         <is>
           <t>Panda status supervision per TSR-615, TSR-621 and TSR-626a: controlsMismatch within 2 samples and 0.5 s (time-based); safety model/parameter mismatch as NO_ENTRY from start instead of a 10 s grace; pandaStates older than 0.2 s treated as mismatch; immediate disable on heartbeatLost, rising safetyTxBlocked, txRateExceeded and any panda fault flag</t>
         </is>
       </c>
-      <c r="D26" s="60" t="inlineStr">
+      <c r="D26" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E26" s="60" t="inlineStr">
+      <c r="E26" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F26" s="60" t="inlineStr">
+      <c r="F26" s="61" t="inlineStr">
         <is>
           <t>SWF-032.C1
 SWF-034.C1
@@ -21805,468 +27396,474 @@
 SWF-034.C3</t>
         </is>
       </c>
-      <c r="G26" s="60" t="inlineStr"/>
-      <c r="H26" s="60" t="inlineStr"/>
-      <c r="I26" s="60" t="inlineStr">
+      <c r="G26" s="61" t="inlineStr"/>
+      <c r="H26" s="61" t="inlineStr"/>
+      <c r="I26" s="61" t="inlineStr">
         <is>
           <t>controlsMismatch within 2 consecutive samples and 0.5 s done (selfdrived/supervision.py, unit tests; impact record change-2026-10-13-host-supervision.md). Open: safety-model mismatch as NO_ENTRY from start, pandaStates age</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46.5" customHeight="1">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-034</t>
         </is>
       </c>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C27" s="60" t="inlineStr">
+      <c r="C27" s="61" t="inlineStr">
         <is>
           <t>Give cruiseMismatch a warning and an ACC cancel retry within 1 s (TSR-308, GAP-19)</t>
         </is>
       </c>
-      <c r="D27" s="60" t="inlineStr">
+      <c r="D27" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E27" s="61" t="inlineStr">
+      <c r="E27" s="62" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F27" s="60" t="inlineStr">
+      <c r="F27" s="61" t="inlineStr">
         <is>
           <t>SWF-039.C1</t>
         </is>
       </c>
-      <c r="G27" s="60" t="inlineStr"/>
-      <c r="H27" s="60" t="inlineStr"/>
-      <c r="I27" s="60" t="inlineStr">
+      <c r="G27" s="61" t="inlineStr"/>
+      <c r="H27" s="61" t="inlineStr"/>
+      <c r="I27" s="61" t="inlineStr">
         <is>
           <t>cruiseMismatch after 1 s with a repeating prompt; controlsd keeps requesting the cancel (change-2026-10-13-host-supervision.md). Vehicle check under SWF-ACT-049</t>
         </is>
       </c>
     </row>
     <row r="28" ht="73.5" customHeight="1">
-      <c r="A28" s="60" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-035</t>
         </is>
       </c>
-      <c r="B28" s="60" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C28" s="60" t="inlineStr">
+      <c r="C28" s="61" t="inlineStr">
         <is>
           <t>Classify reactions per TSR-601 (immediate disable for loss or staleness of a control-law input) and justify each remaining SOFT_DISABLE against the FTTI (SFM-016, GAP-16); make soft-disable and mismatch timers time-based (monotonic clock); move blocking Params writes out of the 100 Hz loop</t>
         </is>
       </c>
-      <c r="D28" s="60" t="inlineStr">
+      <c r="D28" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E28" s="60" t="inlineStr">
+      <c r="E28" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F28" s="60" t="inlineStr">
+      <c r="F28" s="61" t="inlineStr">
         <is>
           <t>SWF-033.C1
 SWF-033.C2</t>
         </is>
       </c>
-      <c r="G28" s="60" t="inlineStr"/>
-      <c r="H28" s="60" t="inlineStr"/>
-      <c r="I28" s="60" t="inlineStr"/>
+      <c r="G28" s="61" t="inlineStr"/>
+      <c r="H28" s="61" t="inlineStr"/>
+      <c r="I28" s="61" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="60" t="inlineStr">
+      <c r="A29" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-036</t>
         </is>
       </c>
-      <c r="B29" s="60" t="inlineStr">
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C29" s="60" t="inlineStr">
+      <c r="C29" s="61" t="inlineStr">
         <is>
           <t>Rank soft and immediate disable takeover alerts above every WARNING and PERMANENT alert except FCW, keep the takeover sound when an AEB alert is shown, name the fault class in the text (canError, TSR-606), and add a test of the ordering</t>
         </is>
       </c>
-      <c r="D29" s="60" t="inlineStr">
+      <c r="D29" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E29" s="60" t="inlineStr">
+      <c r="E29" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F29" s="60" t="inlineStr">
+      <c r="F29" s="61" t="inlineStr">
         <is>
           <t>SWF-035.C1</t>
         </is>
       </c>
-      <c r="G29" s="60" t="inlineStr"/>
-      <c r="H29" s="60" t="inlineStr"/>
-      <c r="I29" s="60" t="inlineStr"/>
+      <c r="G29" s="61" t="inlineStr"/>
+      <c r="H29" s="61" t="inlineStr"/>
+      <c r="I29" s="61" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-037</t>
         </is>
       </c>
-      <c r="B30" s="60" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C30" s="60" t="inlineStr">
+      <c r="C30" s="61" t="inlineStr">
         <is>
           <t>selfdrived liveness: ui and soundd raise the critical takeover alert within 0.5 s of missing selfdriveState while engaged (EL-05 change, TSR-622); add a process watchdog for selfdrived; remove selfdrived from the fuzz NOT_TESTED list</t>
         </is>
       </c>
-      <c r="D30" s="60" t="inlineStr">
+      <c r="D30" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E30" s="60" t="inlineStr">
+      <c r="E30" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F30" s="60" t="inlineStr">
+      <c r="F30" s="61" t="inlineStr">
         <is>
           <t>SWF-036.C1
 SWF-036.C2</t>
         </is>
       </c>
-      <c r="G30" s="60" t="inlineStr"/>
-      <c r="H30" s="60" t="inlineStr"/>
-      <c r="I30" s="60" t="inlineStr"/>
+      <c r="G30" s="61" t="inlineStr"/>
+      <c r="H30" s="61" t="inlineStr"/>
+      <c r="I30" s="61" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-038</t>
         </is>
       </c>
-      <c r="B31" s="60" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C31" s="60" t="inlineStr">
+      <c r="C31" s="61" t="inlineStr">
         <is>
           <t>Revisit TSR-617: set excessive-actuation thresholds from the vehicle envelope and fork drive logs, bound the device_motion_valid reset, check longitudinal response during override, and add unit tests for helpers.py</t>
         </is>
       </c>
-      <c r="D31" s="60" t="inlineStr">
+      <c r="D31" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E31" s="60" t="inlineStr">
+      <c r="E31" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F31" s="60" t="inlineStr">
+      <c r="F31" s="61" t="inlineStr">
         <is>
           <t>SWF-037.C1
 SWF-037.C2</t>
         </is>
       </c>
-      <c r="G31" s="60" t="inlineStr"/>
-      <c r="H31" s="60" t="inlineStr"/>
-      <c r="I31" s="60" t="inlineStr"/>
+      <c r="G31" s="61" t="inlineStr"/>
+      <c r="H31" s="61" t="inlineStr"/>
+      <c r="I31" s="61" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-039</t>
         </is>
       </c>
-      <c r="B32" s="60" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C32" s="60" t="inlineStr">
+      <c r="C32" s="61" t="inlineStr">
         <is>
           <t>Resolve FSR-033 against the implementation: either revise FSR-033 to the actual yield strategy (integrator freeze, panda bound, override force verified by the FSR-031 vehicle test) or ramp the torque request down while steeringPressed</t>
         </is>
       </c>
-      <c r="D32" s="60" t="inlineStr">
+      <c r="D32" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E32" s="60" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F32" s="60" t="inlineStr">
+      <c r="F32" s="61" t="inlineStr">
         <is>
           <t>SWF-038.C1</t>
         </is>
       </c>
-      <c r="G32" s="60" t="inlineStr"/>
-      <c r="H32" s="60" t="inlineStr"/>
-      <c r="I32" s="60" t="inlineStr"/>
+      <c r="G32" s="61" t="inlineStr"/>
+      <c r="H32" s="61" t="inlineStr"/>
+      <c r="I32" s="61" t="inlineStr"/>
     </row>
     <row r="33" ht="87" customHeight="1">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="A33" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-040</t>
         </is>
       </c>
-      <c r="B33" s="60" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C33" s="60" t="inlineStr">
+      <c r="C33" s="61" t="inlineStr">
         <is>
           <t>Implement TSR-602 in controlsd: check age and valid of selfdriveState, carState, modelV2, longitudinalPlan, vehicleParameters and deviceMotion before use (≤ 2 periods); set latActive/longActive false and raise an immediate-disable event when stale; derive carControl.valid from these checks and have card stop actuating on carControl.valid false; give cruiseMismatch a disable type</t>
         </is>
       </c>
-      <c r="D33" s="60" t="inlineStr">
+      <c r="D33" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E33" s="60" t="inlineStr">
+      <c r="E33" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F33" s="60" t="inlineStr">
+      <c r="F33" s="61" t="inlineStr">
         <is>
           <t>SWF-040.C1
 SWF-042.C3
 SWF-043.C1
 SWF-043.C2
-SWF-048.C1</t>
-        </is>
-      </c>
-      <c r="G33" s="60" t="inlineStr">
+SWF-048.C1
+SWF-065.C1</t>
+        </is>
+      </c>
+      <c r="G33" s="61" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H33" s="63" t="inlineStr">
+      <c r="H33" s="64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I33" s="60" t="inlineStr">
+      <c r="I33" s="61" t="inlineStr">
         <is>
           <t>latActive/longActive gated on selfdriveState, carState, modelV2, longitudinalPlan (controls/lib/input_freshness.py, unit tests); threshold 10 periods, not 2; vehicleParameters and deviceMotion not yet included; reaction via commIssue (change-2026-10-13-host-supervision.md, OI-1)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-041</t>
         </is>
       </c>
-      <c r="B34" s="60" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C34" s="60" t="inlineStr">
+      <c r="C34" s="61" t="inlineStr">
         <is>
           <t>Implement TSR-604: treat any non-finite input or actuator value as a fault (immediate disable with alert), reset desired_curvature and both controllers' state, and guard lateralDelay before the int() conversion</t>
         </is>
       </c>
-      <c r="D34" s="60" t="inlineStr">
+      <c r="D34" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E34" s="60" t="inlineStr">
+      <c r="E34" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F34" s="60" t="inlineStr">
+      <c r="F34" s="61" t="inlineStr">
         <is>
           <t>SWF-045.C1
 SWF-045.C2
 SWF-047.C1</t>
         </is>
       </c>
-      <c r="G34" s="60" t="inlineStr">
+      <c r="G34" s="61" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H34" s="63" t="inlineStr">
+      <c r="H34" s="64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I34" s="60" t="inlineStr">
+      <c r="I34" s="61" t="inlineStr">
         <is>
           <t>Non-finite desired curvature, roll, aTarget and lateralDelay no longer reach the controllers (one step skipped, desired_curvature reset); no fault event or alert yet (change-2026-10-13-host-supervision.md)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="46.5" customHeight="1">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-042</t>
         </is>
       </c>
-      <c r="B35" s="60" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C35" s="60" t="inlineStr">
+      <c r="C35" s="61" t="inlineStr">
         <is>
           <t>Reset the LatControlTorque PID (and LatControlPID) in reset(), or record why upstream carries the integrator over engagements; check against current upstream openpilot</t>
         </is>
       </c>
-      <c r="D35" s="60" t="inlineStr">
+      <c r="D35" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E35" s="60" t="inlineStr">
+      <c r="E35" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F35" s="60" t="inlineStr">
+      <c r="F35" s="61" t="inlineStr">
         <is>
           <t>SWF-042.C1</t>
         </is>
       </c>
-      <c r="G35" s="60" t="inlineStr"/>
-      <c r="H35" s="60" t="inlineStr"/>
-      <c r="I35" s="60" t="inlineStr"/>
+      <c r="G35" s="61" t="inlineStr"/>
+      <c r="H35" s="61" t="inlineStr"/>
+      <c r="I35" s="61" t="inlineStr"/>
     </row>
     <row r="36" ht="87" customHeight="1">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-043</t>
         </is>
       </c>
-      <c r="B36" s="60" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C36" s="60" t="inlineStr">
+      <c r="C36" s="61" t="inlineStr">
         <is>
           <t>Requirements-based unit tests for controlsd and the Toyota CarController (latActive/longActive gating table per FSR-006, zero torque and request bit off when not active, controller reset across disengagement, cancel on every disengagement path, active-torque frames accepted by the panda model at the limits), run in LionDriver CI and proven by mutation</t>
         </is>
       </c>
-      <c r="D36" s="60" t="inlineStr">
+      <c r="D36" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E36" s="60" t="inlineStr">
+      <c r="E36" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F36" s="60" t="inlineStr">
+      <c r="F36" s="61" t="inlineStr">
         <is>
           <t>SWF-041.C1
 SWF-042.C1
 SWF-047.C3</t>
         </is>
       </c>
-      <c r="G36" s="60" t="inlineStr"/>
-      <c r="H36" s="60" t="inlineStr"/>
-      <c r="I36" s="60" t="inlineStr"/>
+      <c r="G36" s="61" t="inlineStr"/>
+      <c r="H36" s="61" t="inlineStr"/>
+      <c r="I36" s="61" t="inlineStr"/>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="60" t="inlineStr">
+    <row r="37" ht="127.5" customHeight="1">
+      <c r="A37" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-044</t>
         </is>
       </c>
-      <c r="B37" s="60" t="inlineStr">
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C37" s="60" t="inlineStr">
+      <c r="C37" s="61" t="inlineStr">
         <is>
           <t>Add NaN/inf and stale-input injection for controlsd and card (enable them in test_fuzzy.py with the Corolla fingerprint, or a dedicated test), and run the opendbc car tests (test_models, test_car_interfaces, test_lateral_limits) for Toyota in LionDriver CI</t>
         </is>
       </c>
-      <c r="D37" s="60" t="inlineStr">
+      <c r="D37" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E37" s="60" t="inlineStr">
+      <c r="E37" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F37" s="60" t="inlineStr">
+      <c r="F37" s="61" t="inlineStr">
         <is>
           <t>SWF-045.C1
 SWF-045.C2
 SWF-047.C1
-SWF-047.C3</t>
-        </is>
-      </c>
-      <c r="G37" s="60" t="inlineStr"/>
-      <c r="H37" s="60" t="inlineStr"/>
-      <c r="I37" s="60" t="inlineStr"/>
+SWF-047.C3
+SWF-056.C2
+SWF-056.C3
+SWF-057.C1
+SWF-059.C1
+SWF-060.C1</t>
+        </is>
+      </c>
+      <c r="G37" s="61" t="inlineStr"/>
+      <c r="H37" s="61" t="inlineStr"/>
+      <c r="I37" s="61" t="inlineStr"/>
     </row>
     <row r="38" ht="73.5" customHeight="1">
-      <c r="A38" s="60" t="inlineStr">
+      <c r="A38" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-045</t>
         </is>
       </c>
-      <c r="B38" s="60" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C38" s="60" t="inlineStr">
+      <c r="C38" s="61" t="inlineStr">
         <is>
           <t>Implement TSR-605 margins on the host: bound latAccelOffset and torque parameters in controlsd, apply the acceleration rate limit after pitch compensation and the CarController PID, gate pitch compensation on a valid calibrated pose, and keep host torque/accel limits below the panda limits</t>
         </is>
       </c>
-      <c r="D38" s="60" t="inlineStr">
+      <c r="D38" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E38" s="60" t="inlineStr">
+      <c r="E38" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F38" s="60" t="inlineStr">
+      <c r="F38" s="61" t="inlineStr">
         <is>
           <t>SWF-042.C2
 SWF-042.C3
@@ -22274,374 +27871,710 @@
 SWF-046.C2</t>
         </is>
       </c>
-      <c r="G38" s="60" t="inlineStr"/>
-      <c r="H38" s="60" t="inlineStr"/>
-      <c r="I38" s="60" t="inlineStr"/>
+      <c r="G38" s="61" t="inlineStr"/>
+      <c r="H38" s="61" t="inlineStr"/>
+      <c r="I38" s="61" t="inlineStr"/>
     </row>
     <row r="39" ht="46.5" customHeight="1">
-      <c r="A39" s="60" t="inlineStr">
+      <c r="A39" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-046</t>
         </is>
       </c>
-      <c r="B39" s="60" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C39" s="60" t="inlineStr">
+      <c r="C39" s="61" t="inlineStr">
         <is>
           <t>SoC counterpart of TSR-304 (STPA OI-2, FSR-033) - ramp commanded torque toward zero while steeringPressed, or leave latActive during a lateral override, with the override threshold taken from WP-C-08</t>
         </is>
       </c>
-      <c r="D39" s="60" t="inlineStr">
+      <c r="D39" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E39" s="60" t="inlineStr">
+      <c r="E39" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F39" s="60" t="inlineStr">
+      <c r="F39" s="61" t="inlineStr">
         <is>
           <t>SWF-044.C1</t>
         </is>
       </c>
-      <c r="G39" s="60" t="inlineStr"/>
-      <c r="H39" s="60" t="inlineStr"/>
-      <c r="I39" s="60" t="inlineStr"/>
+      <c r="G39" s="61" t="inlineStr"/>
+      <c r="H39" s="61" t="inlineStr"/>
+      <c r="I39" s="61" t="inlineStr"/>
     </row>
     <row r="40" ht="33" customHeight="1">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="A40" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-047</t>
         </is>
       </c>
-      <c r="B40" s="60" t="inlineStr">
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C40" s="60" t="inlineStr">
+      <c r="C40" s="61" t="inlineStr">
         <is>
           <t>Implement TSR-613: remove the lateralManeuverPlan subscription and the maneuver/joystick processes from the reference build</t>
         </is>
       </c>
-      <c r="D40" s="60" t="inlineStr">
+      <c r="D40" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E40" s="60" t="inlineStr">
+      <c r="E40" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F40" s="60" t="inlineStr">
+      <c r="F40" s="61" t="inlineStr">
         <is>
           <t>SWF-040.C1
 SWF-049.C1</t>
         </is>
       </c>
-      <c r="G40" s="60" t="inlineStr"/>
-      <c r="H40" s="60" t="inlineStr"/>
-      <c r="I40" s="60" t="inlineStr"/>
+      <c r="G40" s="61" t="inlineStr"/>
+      <c r="H40" s="61" t="inlineStr"/>
+      <c r="I40" s="61" t="inlineStr"/>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A41" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-048</t>
         </is>
       </c>
-      <c r="B41" s="60" t="inlineStr">
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C41" s="60" t="inlineStr">
+      <c r="C41" s="61" t="inlineStr">
         <is>
           <t>Bench or HIL fault injection (WP-V-05) - stop or stall selfdrived, modeld, plannerd and controlsd while engaged and measure time to zero torque/acceleration and to the alert; run test_onroad timing tests on a comma 3X for each release</t>
         </is>
       </c>
-      <c r="D41" s="60" t="inlineStr">
+      <c r="D41" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E41" s="60" t="inlineStr">
+      <c r="E41" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F41" s="60" t="inlineStr">
+      <c r="F41" s="61" t="inlineStr">
         <is>
           <t>SWF-043.C1
-SWF-047.C2</t>
-        </is>
-      </c>
-      <c r="G41" s="60" t="inlineStr"/>
-      <c r="H41" s="60" t="inlineStr"/>
-      <c r="I41" s="60" t="inlineStr"/>
+SWF-047.C2
+SWF-068.C2</t>
+        </is>
+      </c>
+      <c r="G41" s="61" t="inlineStr"/>
+      <c r="H41" s="61" t="inlineStr"/>
+      <c r="I41" s="61" t="inlineStr"/>
     </row>
     <row r="42" ht="33" customHeight="1">
-      <c r="A42" s="60" t="inlineStr">
+      <c r="A42" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-049</t>
         </is>
       </c>
-      <c r="B42" s="60" t="inlineStr">
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C42" s="60" t="inlineStr">
+      <c r="C42" s="61" t="inlineStr">
         <is>
           <t>Vehicle test of PCM cancel and cluster state on each host disengagement path (fault disable, cancel button, brake, selfdrived loss)</t>
         </is>
       </c>
-      <c r="D42" s="60" t="inlineStr">
+      <c r="D42" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E42" s="60" t="inlineStr">
+      <c r="E42" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F42" s="60" t="inlineStr">
+      <c r="F42" s="61" t="inlineStr">
         <is>
           <t>SWF-039.C1
 SWF-048.C1</t>
         </is>
       </c>
-      <c r="G42" s="60" t="inlineStr"/>
-      <c r="H42" s="60" t="inlineStr"/>
-      <c r="I42" s="60" t="inlineStr"/>
+      <c r="G42" s="61" t="inlineStr"/>
+      <c r="H42" s="61" t="inlineStr"/>
+      <c r="I42" s="61" t="inlineStr"/>
     </row>
     <row r="43" ht="33" customHeight="1">
-      <c r="A43" s="60" t="inlineStr">
+      <c r="A43" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-050</t>
         </is>
       </c>
-      <c r="B43" s="60" t="inlineStr">
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C43" s="60" t="inlineStr">
+      <c r="C43" s="61" t="inlineStr">
         <is>
           <t>Implement TSR-624: announce deceleration that traffic does not require at least 1 s before its onset, and ramp it within a_min and j_down</t>
         </is>
       </c>
-      <c r="D43" s="60" t="inlineStr">
+      <c r="D43" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E43" s="60" t="inlineStr">
+      <c r="E43" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F43" s="60" t="inlineStr">
-        <is>
-          <t>SWF-050.C1</t>
-        </is>
-      </c>
-      <c r="G43" s="60" t="inlineStr"/>
-      <c r="H43" s="60" t="inlineStr"/>
-      <c r="I43" s="60" t="inlineStr"/>
+      <c r="F43" s="61" t="inlineStr">
+        <is>
+          <t>SWF-050.C1
+SWF-066.C1</t>
+        </is>
+      </c>
+      <c r="G43" s="61" t="inlineStr"/>
+      <c r="H43" s="61" t="inlineStr"/>
+      <c r="I43" s="61" t="inlineStr"/>
     </row>
     <row r="44" ht="33" customHeight="1">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A44" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-051</t>
         </is>
       </c>
-      <c r="B44" s="60" t="inlineStr">
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C44" s="60" t="inlineStr">
+      <c r="C44" s="61" t="inlineStr">
         <is>
           <t>Implement TSR-625: gate FCW on fresh and valid modelV2 and longitudinalPlan, with a unit test for a stale and an invalid input</t>
         </is>
       </c>
-      <c r="D44" s="60" t="inlineStr">
+      <c r="D44" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E44" s="60" t="inlineStr">
+      <c r="E44" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F44" s="60" t="inlineStr">
+      <c r="F44" s="61" t="inlineStr">
         <is>
           <t>SWF-051.C1</t>
         </is>
       </c>
-      <c r="G44" s="60" t="inlineStr"/>
-      <c r="H44" s="60" t="inlineStr"/>
-      <c r="I44" s="60" t="inlineStr"/>
+      <c r="G44" s="61" t="inlineStr"/>
+      <c r="H44" s="61" t="inlineStr"/>
+      <c r="I44" s="61" t="inlineStr"/>
     </row>
     <row r="45" ht="33" customHeight="1">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="A45" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-052</t>
         </is>
       </c>
-      <c r="B45" s="60" t="inlineStr">
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C45" s="60" t="inlineStr">
+      <c r="C45" s="61" t="inlineStr">
         <is>
           <t>Send the inactive acceleration from the Toyota CarController whenever CC.longActive is false, with a unit test</t>
         </is>
       </c>
-      <c r="D45" s="60" t="inlineStr">
+      <c r="D45" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E45" s="60" t="inlineStr">
+      <c r="E45" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F45" s="60" t="inlineStr">
+      <c r="F45" s="61" t="inlineStr">
         <is>
           <t>SWF-052.C1</t>
         </is>
       </c>
-      <c r="G45" s="60" t="inlineStr"/>
-      <c r="H45" s="60" t="inlineStr"/>
-      <c r="I45" s="60" t="inlineStr"/>
+      <c r="G45" s="61" t="inlineStr"/>
+      <c r="H45" s="61" t="inlineStr"/>
+      <c r="I45" s="61" t="inlineStr"/>
     </row>
     <row r="46" ht="46.5" customHeight="1">
-      <c r="A46" s="60" t="inlineStr">
+      <c r="A46" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-053</t>
         </is>
       </c>
-      <c r="B46" s="60" t="inlineStr">
+      <c r="B46" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C46" s="60" t="inlineStr">
+      <c r="C46" s="61" t="inlineStr">
         <is>
           <t>Vehicle test of the PCM response when the inactive value replaces an active deceleration (TSR-208, AOU-05R); if the PCM steps, specify an item-side ramp after revocation (FSR-04.03)</t>
         </is>
       </c>
-      <c r="D46" s="60" t="inlineStr">
+      <c r="D46" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E46" s="60" t="inlineStr">
+      <c r="E46" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F46" s="60" t="inlineStr">
+      <c r="F46" s="61" t="inlineStr">
         <is>
           <t>SWF-053.C1</t>
         </is>
       </c>
-      <c r="G46" s="60" t="inlineStr"/>
-      <c r="H46" s="60" t="inlineStr"/>
-      <c r="I46" s="60" t="inlineStr"/>
+      <c r="G46" s="61" t="inlineStr"/>
+      <c r="H46" s="61" t="inlineStr"/>
+      <c r="I46" s="61" t="inlineStr"/>
     </row>
     <row r="47" ht="87" customHeight="1">
-      <c r="A47" s="60" t="inlineStr">
+      <c r="A47" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-055</t>
         </is>
       </c>
-      <c r="B47" s="60" t="inlineStr">
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C47" s="60" t="inlineStr">
+      <c r="C47" s="61" t="inlineStr">
         <is>
           <t>Make the host supervision tests run in CI: test_supervision.py and test_input_freshness.py define plain classes, which tools/test_runner.py (unittest loader) collects as 0 tests. Derive them from unittest.TestCase (or the repo's test base class), check that the unit_tests job reports them, and prove them by a mutation of supervision.py and input_freshness.py so D can drop below 8</t>
         </is>
       </c>
-      <c r="D47" s="60" t="inlineStr">
+      <c r="D47" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E47" s="60" t="inlineStr">
+      <c r="E47" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F47" s="60" t="inlineStr">
+      <c r="F47" s="61" t="inlineStr">
         <is>
           <t>SWF-034.C1</t>
         </is>
       </c>
-      <c r="G47" s="60" t="inlineStr"/>
-      <c r="H47" s="60" t="inlineStr"/>
-      <c r="I47" s="60" t="inlineStr"/>
+      <c r="G47" s="61" t="inlineStr"/>
+      <c r="H47" s="61" t="inlineStr"/>
+      <c r="I47" s="61" t="inlineStr"/>
     </row>
     <row r="48" ht="73.5" customHeight="1">
-      <c r="A48" s="60" t="inlineStr">
+      <c r="A48" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-054</t>
         </is>
       </c>
-      <c r="B48" s="60" t="inlineStr">
+      <c r="B48" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C48" s="60" t="inlineStr">
+      <c r="C48" s="61" t="inlineStr">
         <is>
           <t>Pin an opendbc commit that contains jherrodthomas/opendbc#15 (ATC-20, SWSR-518 amended per DQ-079; ATC-26, SWSR-311 amended per DQ-080), with its impact records moved to Integrated, and re-rate SWF-054 and SWF-055 at the new baseline. The fork merged it as 9859cb0 (master 515b9a2 also carries opendbc#16); the LionDriver pin is still 9a13f60</t>
         </is>
       </c>
-      <c r="D48" s="60" t="inlineStr">
+      <c r="D48" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E48" s="60" t="inlineStr">
+      <c r="E48" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F48" s="60" t="inlineStr">
+      <c r="F48" s="61" t="inlineStr">
         <is>
           <t>SWF-054.C1
 SWF-055.C1</t>
         </is>
       </c>
-      <c r="G48" s="60" t="inlineStr">
+      <c r="G48" s="61" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H48" s="63" t="inlineStr">
+      <c r="H48" s="64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I48" s="60" t="inlineStr"/>
+      <c r="I48" s="61" t="inlineStr"/>
+    </row>
+    <row r="49" ht="87" customHeight="1">
+      <c r="A49" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-056</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C49" s="61" t="inlineStr">
+        <is>
+          <t>carState input supervision for the reference car: fixed RX timeouts from the DBC rates instead of the learned 1 Hz default, reject frames shorter than the DBC length for every signal carState uses, and a plausibility cross-check for the messages without checksum or counter (BRAKE_MODULE against PCM_CRUISE, WHEEL_SPEEDS against the IMU); with unit tests in LionDriver CI</t>
+        </is>
+      </c>
+      <c r="D49" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F49" s="61" t="inlineStr">
+        <is>
+          <t>SWF-056.C1
+SWF-056.C2
+SWF-056.C3
+SWF-057.C2</t>
+        </is>
+      </c>
+      <c r="G49" s="61" t="inlineStr"/>
+      <c r="H49" s="61" t="inlineStr"/>
+      <c r="I49" s="61" t="inlineStr"/>
+    </row>
+    <row r="50" ht="73.5" customHeight="1">
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-057</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C50" s="61" t="inlineStr">
+        <is>
+          <t>Pin the reference identification: accept only an exact FW match to TOYOTA_COROLLA_TSS2 with the expected CarParams for the assured configuration (report a fuzzy match through assured_config), ignore FINGERPRINT in release builds, and re-query FW after a VIN-cache hit when an ECU version changed</t>
+        </is>
+      </c>
+      <c r="D50" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E50" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F50" s="61" t="inlineStr">
+        <is>
+          <t>SWF-058.C1
+SWF-058.C2</t>
+        </is>
+      </c>
+      <c r="G50" s="61" t="inlineStr"/>
+      <c r="H50" s="61" t="inlineStr"/>
+      <c r="I50" s="61" t="inlineStr"/>
+    </row>
+    <row r="51" ht="87" customHeight="1">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-058</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C51" s="61" t="inlineStr">
+        <is>
+          <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+        </is>
+      </c>
+      <c r="D51" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F51" s="61" t="inlineStr">
+        <is>
+          <t>SWF-061.C1
+SWF-061.C2
+SWF-061.C3
+SWF-063.C1
+SWF-063.C2
+SWF-064.C1</t>
+        </is>
+      </c>
+      <c r="G51" s="61" t="inlineStr"/>
+      <c r="H51" s="61" t="inlineStr"/>
+      <c r="I51" s="61" t="inlineStr"/>
+    </row>
+    <row r="52" ht="46.5" customHeight="1">
+      <c r="A52" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-059</t>
+        </is>
+      </c>
+      <c r="B52" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C52" s="61" t="inlineStr">
+        <is>
+          <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+        </is>
+      </c>
+      <c r="D52" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E52" s="61" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="F52" s="61" t="inlineStr">
+        <is>
+          <t>SWF-062.C1</t>
+        </is>
+      </c>
+      <c r="G52" s="61" t="inlineStr"/>
+      <c r="H52" s="61" t="inlineStr"/>
+      <c r="I52" s="61" t="inlineStr"/>
+    </row>
+    <row r="53" ht="46.5" customHeight="1">
+      <c r="A53" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-060</t>
+        </is>
+      </c>
+      <c r="B53" s="61" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C53" s="61" t="inlineStr">
+        <is>
+          <t>Run model_replay for dmonitoringmodeld and modeld in LionDriver CI, and add a non-finite / stale output injection test for dmonitoringd and modeld consumers</t>
+        </is>
+      </c>
+      <c r="D53" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E53" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F53" s="61" t="inlineStr">
+        <is>
+          <t>SWF-063.C1</t>
+        </is>
+      </c>
+      <c r="G53" s="61" t="inlineStr"/>
+      <c r="H53" s="61" t="inlineStr"/>
+      <c r="I53" s="61" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-061</t>
+        </is>
+      </c>
+      <c r="B54" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C54" s="61" t="inlineStr">
+        <is>
+          <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
+        </is>
+      </c>
+      <c r="D54" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E54" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F54" s="61" t="inlineStr">
+        <is>
+          <t>SWF-065.C1
+SWF-065.C2
+SWF-065.C3
+SWF-070.C2</t>
+        </is>
+      </c>
+      <c r="G54" s="61" t="inlineStr"/>
+      <c r="H54" s="61" t="inlineStr"/>
+      <c r="I54" s="61" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-062</t>
+        </is>
+      </c>
+      <c r="B55" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C55" s="61" t="inlineStr">
+        <is>
+          <t>plannerd robustness: on an MPC failure keep the last valid solution for a bounded time and raise an event if it persists; rate-limit the final aTarget (TSR-624); handle an unknown personality as relaxed; add MPC-failure injection and plannerd fuzzing in CI</t>
+        </is>
+      </c>
+      <c r="D55" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E55" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F55" s="61" t="inlineStr">
+        <is>
+          <t>SWF-065.C2
+SWF-066.C1
+SWF-068.C1</t>
+        </is>
+      </c>
+      <c r="G55" s="61" t="inlineStr"/>
+      <c r="H55" s="61" t="inlineStr"/>
+      <c r="I55" s="61" t="inlineStr"/>
+    </row>
+    <row r="56" ht="33" customHeight="1">
+      <c r="A56" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-063</t>
+        </is>
+      </c>
+      <c r="B56" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C56" s="61" t="inlineStr">
+        <is>
+          <t>Apply the lead's decision on engagement outside the assured configuration (DQ-221): refuse engagement or keep logging, with a test</t>
+        </is>
+      </c>
+      <c r="D56" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E56" s="61" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="F56" s="61" t="inlineStr">
+        <is>
+          <t>SWF-067.C1</t>
+        </is>
+      </c>
+      <c r="G56" s="61" t="inlineStr"/>
+      <c r="H56" s="61" t="inlineStr"/>
+      <c r="I56" s="61" t="inlineStr"/>
+    </row>
+    <row r="57" ht="87" customHeight="1">
+      <c r="A57" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-064</t>
+        </is>
+      </c>
+      <c r="B57" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C57" s="61" t="inlineStr">
+        <is>
+          <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+        </is>
+      </c>
+      <c r="D57" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E57" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F57" s="61" t="inlineStr">
+        <is>
+          <t>SWF-069.C1
+SWF-070.C1
+SWF-070.C2
+SWF-070.C3
+SWF-071.C1
+SWF-071.C2</t>
+        </is>
+      </c>
+      <c r="G57" s="61" t="inlineStr"/>
+      <c r="H57" s="61" t="inlineStr"/>
+      <c r="I57" s="61" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I48"/>
+  <autoFilter ref="A1:I57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22652,7 +28585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22663,624 +28596,624 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="60" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="C1" s="60" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="59" t="inlineStr">
+      <c r="D1" s="60" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="60" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>Panda safety model (opendbc safety + panda firmware integration)</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D2" s="60" t="inlineStr"/>
-      <c r="E2" s="60" t="inlineStr"/>
+      <c r="D2" s="61" t="inlineStr"/>
+      <c r="E2" s="61" t="inlineStr"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    RX validation and RX timing checks</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D3" s="60" t="inlineStr">
+      <c r="D3" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="60" t="inlineStr">
+      <c r="E3" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-005: Validate safety-relevant RX messages (checksum, counter, quality flag, timing)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    TX whitelist and dispatch</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-001: Transmit only whitelisted messages, each passed through the mode-specific check</t>
         </is>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Forwarding hook</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-007: Block stock-camera messages the item replaces; forward all others, including stock pre-collision messages</t>
         </is>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-005</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Controls-allowed logic</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-004: Allow controls on rising edge of PCM cruise; withdraw on cruise off, brake press, invalid or lagging safety messages</t>
         </is>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-006</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Steering torque checks</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr">
+      <c r="E7" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-002: Block steering requests outside torque magnitude, rate and measured-torque-error limits, and any torque while controls are not allowed</t>
         </is>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-007</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Longitudinal checks</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-003: Block acceleration outside the range, and any non-inactive acceleration while controls are not allowed or the accelerator is pressed</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-008</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Toyota safety mode</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr">
+      <c r="E9" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-006: Decode Toyota vehicle state: EPS torque, cruise state, brake, accelerator, wheel speeds</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-009</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Relay malfunction detection</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr">
+      <c r="E10" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-008: Detect a relay malfunction and block all item transmission</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-010</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Safety mode registry and initialization</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-009: Install only the safety model and parameter intended for the vehicle</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-011</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda main loop: safety mode and heartbeat</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr">
+      <c r="E12" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-010: Withdraw controls when the host heartbeat is lost or reports not engaged</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-012</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda host command handler</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="E13" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-011: Accept host configuration commands only when they cannot widen what is transmitted</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-013</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda CAN send path</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr">
+      <c r="E14" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-012: Route every host transmission through the safety check</t>
         </is>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-014</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda hardware watchdog and 100 Hz safety task</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="E15" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-013: Reset the MCU, which releases the relay, within 0.1 s when the safety task or main loop stops; never reset while both run normally</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>pandad (panda daemon and SoC-panda link)</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr"/>
-      <c r="E16" s="60" t="inlineStr"/>
+      <c r="D16" s="61" t="inlineStr"/>
+      <c r="E16" s="61" t="inlineStr"/>
     </row>
     <row r="17" ht="46.5" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-021</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Main loop and heartbeat</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-020: Send the heartbeat at 10 Hz. It reports engaged only while the SoC is engaged and actively commanding, so that the panda can withdraw authority when the host stops (supports FSR-005 and FSR-007, which are allocated to EL-07)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="33" customHeight="1">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-022</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Safety mode setter</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="E18" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-021: Put the panda in the safety model, parameter and alternative experience for the identified vehicle, only when onroad, and in NO_OUTPUT when offroad, with ignition off or on exit</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-023</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    sendcan forwarding thread</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="E19" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-022: Forward each sendcan batch to the panda once, in order, only while it is fresh, and make any failure to forward visible to the SoC</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-024</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    CAN RX and panda state publishing</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="E20" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-023: Publish received CAN and the panda state (mode, parameter, controlsAllowed, RX-check validity, faults) correctly and on time, so the SoC can detect a mismatch or fault and disable</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33" customHeight="1">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-025</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    SPI transport</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E21" s="60" t="inlineStr">
+      <c r="E21" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-024: Transfer commands and data between SoC and panda without undetected corruption. Detect link failure in bounded time and report it</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33" customHeight="1">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-026</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Launcher and firmware check</t>
         </is>
       </c>
-      <c r="C22" s="60" t="inlineStr">
+      <c r="C22" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D22" s="60" t="inlineStr">
+      <c r="D22" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E22" s="60" t="inlineStr">
+      <c r="E22" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-025: Run pandad only against the intended panda firmware. Recover a panda in DFU or bootstub without disturbing an active drive</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>selfdrived (engagement supervision)</t>
         </is>
       </c>
-      <c r="C23" s="60" t="inlineStr">
+      <c r="C23" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D23" s="60" t="inlineStr"/>
-      <c r="E23" s="60" t="inlineStr"/>
+      <c r="D23" s="61" t="inlineStr"/>
+      <c r="E23" s="61" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-031</t>
         </is>
       </c>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Engagement state machine</t>
         </is>
       </c>
-      <c r="C24" s="60" t="inlineStr">
+      <c r="C24" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D24" s="60" t="inlineStr">
+      <c r="D24" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E24" s="60" t="inlineStr">
+      <c r="E24" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-030: Engage only on an ENABLE event with no NO_ENTRY event active
 SWF-FN-031: Go to disabled in the same cycle on USER_DISABLE or IMMEDIATE_DISABLE, and within SOFT_DISABLE_TIME on a persisting SOFT_DISABLE
@@ -23289,27 +29222,27 @@
       </c>
     </row>
     <row r="25" ht="73.5" customHeight="1">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-032</t>
         </is>
       </c>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Input sampling and event generation</t>
         </is>
       </c>
-      <c r="C25" s="60" t="inlineStr">
+      <c r="C25" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D25" s="60" t="inlineStr">
+      <c r="D25" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E25" s="60" t="inlineStr">
+      <c r="E25" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-032: Raise fault and driver-action events from carState, pandaStates and process/message supervision, including controlsMismatch when the panda safety model, parameter or controls-allowed disagrees
 SWF-FN-038: Detect PCM cruise active while not engaged and warn the driver
@@ -23318,154 +29251,154 @@
       </c>
     </row>
     <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="60" t="inlineStr">
+      <c r="A26" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-033</t>
         </is>
       </c>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Event catalogue and reaction mapping</t>
         </is>
       </c>
-      <c r="C26" s="60" t="inlineStr">
+      <c r="C26" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D26" s="60" t="inlineStr">
+      <c r="D26" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E26" s="60" t="inlineStr">
+      <c r="E26" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-033: Give each event the reaction type (no entry, soft or immediate disable, user disable) and alert its fault requires</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-034</t>
         </is>
       </c>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Alert manager</t>
         </is>
       </c>
-      <c r="C27" s="60" t="inlineStr">
+      <c r="C27" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D27" s="60" t="inlineStr">
+      <c r="D27" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E27" s="60" t="inlineStr">
+      <c r="E27" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-034: Present the most urgent alert; every takeover request visual and audible</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="60" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-035</t>
         </is>
       </c>
-      <c r="B28" s="60" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Excessive actuation check</t>
         </is>
       </c>
-      <c r="C28" s="60" t="inlineStr">
+      <c r="C28" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D28" s="60" t="inlineStr">
+      <c r="D28" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E28" s="60" t="inlineStr">
+      <c r="E28" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-035: Detect excessive longitudinal or lateral vehicle response while engaged and soft-disable</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33" customHeight="1">
-      <c r="A29" s="60" t="inlineStr">
+      <c r="A29" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-036</t>
         </is>
       </c>
-      <c r="B29" s="60" t="inlineStr">
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    selfdriveState publication and main loop</t>
         </is>
       </c>
-      <c r="C29" s="60" t="inlineStr">
+      <c r="C29" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D29" s="60" t="inlineStr">
+      <c r="D29" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E29" s="60" t="inlineStr">
+      <c r="E29" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-036: Publish selfdriveState (enabled, active, alert) every 10 ms cycle, consistent with the state machine</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="B30" s="60" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>Control (controlsd, lateral/longitudinal controllers, Toyota CarController hand-off)</t>
         </is>
       </c>
-      <c r="C30" s="60" t="inlineStr">
+      <c r="C30" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D30" s="60" t="inlineStr"/>
-      <c r="E30" s="60" t="inlineStr"/>
+      <c r="D30" s="61" t="inlineStr"/>
+      <c r="E30" s="61" t="inlineStr"/>
     </row>
     <row r="31" ht="127.5" customHeight="1">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-041</t>
         </is>
       </c>
-      <c r="B31" s="60" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    controlsd main loop, input handling and actuator gating</t>
         </is>
       </c>
-      <c r="C31" s="60" t="inlineStr">
+      <c r="C31" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D31" s="60" t="inlineStr">
+      <c r="D31" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E31" s="60" t="inlineStr">
+      <c r="E31" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-040: Request lateral control only while selfdriveState is active, no EPS fault is reported and the car is above the minimum steer speed; request longitudinal control only while enabled and not overridden
 SWF-FN-041: Compute actuation only from fresh, valid and finite inputs (selfdriveState, modelV2, longitudinalPlan, vehicleParameters, lateralTorqueParameters, deviceMotion), and stop actuating otherwise
@@ -23475,108 +29408,108 @@
       </c>
     </row>
     <row r="32" ht="33" customHeight="1">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-042</t>
         </is>
       </c>
-      <c r="B32" s="60" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Lateral torque controller</t>
         </is>
       </c>
-      <c r="C32" s="60" t="inlineStr">
+      <c r="C32" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D32" s="60" t="inlineStr">
+      <c r="D32" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E32" s="60" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-042: Generate a steering torque request that tracks the limited desired curvature within the envelope and yields while the driver steers</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="A33" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-043</t>
         </is>
       </c>
-      <c r="B33" s="60" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Longitudinal controller</t>
         </is>
       </c>
-      <c r="C33" s="60" t="inlineStr">
+      <c r="C33" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D33" s="60" t="inlineStr">
+      <c r="D33" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E33" s="60" t="inlineStr">
+      <c r="E33" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-044: Generate an acceleration request within the range and rate envelope from the longitudinal plan</t>
         </is>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-044</t>
         </is>
       </c>
-      <c r="B34" s="60" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Curvature limiter</t>
         </is>
       </c>
-      <c r="C34" s="60" t="inlineStr">
+      <c r="C34" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D34" s="60" t="inlineStr">
+      <c r="D34" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E34" s="60" t="inlineStr">
+      <c r="E34" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-043: Limit desired curvature to the lateral acceleration, lateral jerk and curvature bounds</t>
         </is>
       </c>
     </row>
     <row r="35" ht="46.5" customHeight="1">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-045</t>
         </is>
       </c>
-      <c r="B35" s="60" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Toyota CarController</t>
         </is>
       </c>
-      <c r="C35" s="60" t="inlineStr">
+      <c r="C35" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D35" s="60" t="inlineStr">
+      <c r="D35" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E35" s="60" t="inlineStr">
+      <c r="E35" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-045: Apply torque magnitude, rate and measured-torque limits; send zero torque with the request bit cleared when lateral control is not active; send the ACC command within the acceleration range
 SWF-FN-050: Send the inactive acceleration in ACC_CONTROL whenever longitudinal control is not active</t>
@@ -23584,34 +29517,353 @@
       </c>
     </row>
     <row r="36" ht="33" customHeight="1">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-046</t>
         </is>
       </c>
-      <c r="B36" s="60" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    card actuation hand-off</t>
         </is>
       </c>
-      <c r="C36" s="60" t="inlineStr">
+      <c r="C36" s="61" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D36" s="60" t="inlineStr">
+      <c r="D36" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E36" s="60" t="inlineStr">
+      <c r="E36" s="61" t="inlineStr">
         <is>
           <t>SWF-FN-047: Deliver every 10 ms control step to the vehicle, and stop sending item frames when carControl is no longer received</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-050</t>
+        </is>
+      </c>
+      <c r="B37" s="61" t="inlineStr">
+        <is>
+          <t>Car interface (card and the opendbc Toyota port, CAN parse and pack)</t>
+        </is>
+      </c>
+      <c r="C37" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D37" s="61" t="inlineStr"/>
+      <c r="E37" s="61" t="inlineStr"/>
+    </row>
+    <row r="38" ht="46.5" customHeight="1">
+      <c r="A38" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-051</t>
+        </is>
+      </c>
+      <c r="B38" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CAN parser and Toyota carState</t>
+        </is>
+      </c>
+      <c r="C38" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D38" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-050</t>
+        </is>
+      </c>
+      <c r="E38" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-051: Provide brakePressed, gasPressed, steeringTorque/steeringPressed, cruise state, vEgo and EPS fault from current vehicle CAN, and report invalid or missing data as canValid false within the RX budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="33" customHeight="1">
+      <c r="A39" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-052</t>
+        </is>
+      </c>
+      <c r="B39" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Fingerprinting and CarParams</t>
+        </is>
+      </c>
+      <c r="C39" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D39" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-050</t>
+        </is>
+      </c>
+      <c r="E39" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-052: Identify the reference vehicle and produce its CarParams (TOYOTA_COROLLA_TSS2, safety parameter 73, openpilot longitudinal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="33" customHeight="1">
+      <c r="A40" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-053</t>
+        </is>
+      </c>
+      <c r="B40" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CAN packer and Toyota message construction</t>
+        </is>
+      </c>
+      <c r="C40" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D40" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-050</t>
+        </is>
+      </c>
+      <c r="E40" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-053: Pack actuation and HUD frames with the commanded values, the correct scaling, counter and checksum</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="33" customHeight="1">
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-054</t>
+        </is>
+      </c>
+      <c r="B41" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    card main loop and stock AEB interlock</t>
+        </is>
+      </c>
+      <c r="C41" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D41" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-050</t>
+        </is>
+      </c>
+      <c r="E41" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-054: Run the car interface every CAN cycle, publish carState, and actuate only the latest carControl</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-060</t>
+        </is>
+      </c>
+      <c r="B42" s="61" t="inlineStr">
+        <is>
+          <t>Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
+        </is>
+      </c>
+      <c r="C42" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D42" s="61" t="inlineStr"/>
+      <c r="E42" s="61" t="inlineStr"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-061</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Driver-monitoring model process</t>
+        </is>
+      </c>
+      <c r="C43" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D43" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-060</t>
+        </is>
+      </c>
+      <c r="E43" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-060: Estimate face, eye and attention state of the driver for every cabin camera frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="33" customHeight="1">
+      <c r="A44" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-062</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Monitoring policy and dmonitoringd</t>
+        </is>
+      </c>
+      <c r="C44" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D44" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-060</t>
+        </is>
+      </c>
+      <c r="E44" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-061: Escalate an inattentive or unresponsive driver within the policy times (vision 5/8/13 s, wheel-touch 5/15/25 s) and request the terminal reaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-070</t>
+        </is>
+      </c>
+      <c r="B45" s="61" t="inlineStr">
+        <is>
+          <t>Longitudinal planning (plannerd)</t>
+        </is>
+      </c>
+      <c r="C45" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D45" s="61" t="inlineStr"/>
+      <c r="E45" s="61" t="inlineStr"/>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-071</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Longitudinal planner and MPC</t>
+        </is>
+      </c>
+      <c r="C46" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D46" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-070</t>
+        </is>
+      </c>
+      <c r="E46" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-070: Plan an acceleration within the envelope that keeps the following distance to a lead and stops for a stopped lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-072</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Forward collision warning decision</t>
+        </is>
+      </c>
+      <c r="C47" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D47" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-070</t>
+        </is>
+      </c>
+      <c r="E47" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-071: Raise a forward collision warning when a collision with the lead is predicted</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-080</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="inlineStr">
+        <is>
+          <t>Lead estimation (radard and the Toyota radar interface)</t>
+        </is>
+      </c>
+      <c r="C48" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D48" s="61" t="inlineStr"/>
+      <c r="E48" s="61" t="inlineStr"/>
+    </row>
+    <row r="49" ht="33" customHeight="1">
+      <c r="A49" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-081</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Lead selection and radar/vision fusion</t>
+        </is>
+      </c>
+      <c r="C49" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D49" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-080</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-080: Provide the lead state (distance, relative speed and acceleration) from radar tracks matched to model leads, and flag radar faults</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E36"/>
+  <autoFilter ref="A1:E49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$133</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.9 · draft</t>
+          <t>1.0 · draft</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="105" customHeight="1">
+    <row r="10" ht="150" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
@@ -865,7 +865,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071).</t>
+          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071). P3 elements: modeld as a software element (SWF-072..074; model performance is SOTIF), localization and calibration (SWF-075..077), camerad (SWF-078), sensord (SWF-079), messaging (SWF-080, SWF-081), manager (SWF-082, SWF-083), updated (SWF-084).</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>56 (52)</t>
+          <t>63 (59)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26128,12 +26128,3658 @@
       <c r="R115" s="48" t="inlineStr"/>
       <c r="S115" s="48" t="inlineStr"/>
     </row>
+    <row r="116" ht="181.5" customHeight="1">
+      <c r="A116" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-091
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Model execution, output parsing and validity</t>
+          </r>
+        </is>
+      </c>
+      <c r="B116" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-090
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Publish model outputs (desired curvature, leads) for every road frame, computed from the current frame and calibration, and mark output that is not fit for use as invalid</t>
+          </r>
+        </is>
+      </c>
+      <c r="C116" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral control steers toward the lane boundary</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-007 (wrong or missing lead)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>controlsd steers on it unless the curvature is non-finite (SWF-045); radard and plannerd use the leads</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>desiredCurvature or leads wrong while modelV2.valid is true</t>
+          </r>
+        </is>
+      </c>
+      <c r="D116" s="31" t="inlineStr">
+        <is>
+          <t>HZ-003
+HZ-007</t>
+        </is>
+      </c>
+      <c r="E116" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F116" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-072 · value_stale
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modelV2 published as valid while its content is non-finite, from an old frame, or computed with an invalid calibration</t>
+          </r>
+        </is>
+      </c>
+      <c r="G116" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H116" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modelV2.valid only says a calibration has been seen (fill_model_msg.py:59, 79; modeld.py:434). The small model's outputs get no finiteness check (modeld.py:210-211 checks the big model only; TSR-616, GAP-22): non-finite leads reach radard and plannerd</t>
+          </r>
+        </is>
+      </c>
+      <c r="I116" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J116" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K116" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L116" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M116" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N116" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-065 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-060 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run model_replay for dmonitoringmodeld and modeld in LionDriver CI, and add a non-finite / stale output injection test for dmonitoringd and modeld consumers</t>
+          </r>
+        </is>
+      </c>
+      <c r="O116" s="38" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P116" s="33" t="inlineStr"/>
+      <c r="Q116" s="33" t="inlineStr"/>
+      <c r="R116" s="39" t="inlineStr"/>
+      <c r="S116" s="39" t="inlineStr"/>
+    </row>
+    <row r="117" ht="114" customHeight="1">
+      <c r="A117" s="40" t="n"/>
+      <c r="B117" s="40" t="n"/>
+      <c r="C117" s="40" t="n"/>
+      <c r="D117" s="40" t="n"/>
+      <c r="E117" s="40" t="n"/>
+      <c r="F117" s="40" t="n"/>
+      <c r="G117" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H117" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Frame-drop accounting misses repeats: dropped frames are max(0, frame_id gap - 1), so a repeated or regressing frame_id counts as 0 (modeld.py:385); drops are forced to 0 for the first 10 runs and filtered with a 10 s time constant (386-389), so modeldLagging comes late</t>
+          </r>
+        </is>
+      </c>
+      <c r="I117" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J117" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L117" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M117" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N117" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-065 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O117" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P117" s="33" t="inlineStr"/>
+      <c r="Q117" s="33" t="inlineStr"/>
+      <c r="R117" s="39" t="inlineStr"/>
+      <c r="S117" s="39" t="inlineStr"/>
+    </row>
+    <row r="118" ht="114" customHeight="1">
+      <c r="A118" s="42" t="n"/>
+      <c r="B118" s="42" t="n"/>
+      <c r="C118" s="42" t="n"/>
+      <c r="D118" s="42" t="n"/>
+      <c r="E118" s="42" t="n"/>
+      <c r="F118" s="42" t="n"/>
+      <c r="G118" s="43" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H118" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The calibration is used whenever extrinsicsCalibration updates, without checking calStatus or valid (modeld.py:367-375), so a recalibrating or invalid calibration warps the input; selfdrived reacts to the calibration status separately</t>
+          </r>
+        </is>
+      </c>
+      <c r="I118" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J118" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K118" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L118" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M118" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N118" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-065 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O118" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P118" s="43" t="inlineStr"/>
+      <c r="Q118" s="43" t="inlineStr"/>
+      <c r="R118" s="48" t="inlineStr"/>
+      <c r="S118" s="48" t="inlineStr"/>
+    </row>
+    <row r="119" ht="181.5" customHeight="1">
+      <c r="A119" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-090
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driving model process (modeld)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B119" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-090
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Publish model outputs (desired curvature, leads) for every road frame, computed from the current frame and calibration, and mark output that is not fit for use as invalid</t>
+          </r>
+        </is>
+      </c>
+      <c r="C119" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Loss of lateral control while engaged; the take-over alert follows within about 0.5 s</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>controlsd ends lateral control 0.5 s after the last modelV2 (TSR-602); selfdrived commIssue / processNotRunning soft disable; manager does not restart modeld</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No modelV2</t>
+          </r>
+        </is>
+      </c>
+      <c r="D119" s="50" t="inlineStr">
+        <is>
+          <t>HZ-004</t>
+        </is>
+      </c>
+      <c r="E119" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F119" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-073 · crash
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld stops while engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="G119" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H119" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unhandled exception in the small-model path: a run exception re-raises (modeld.py:412-413); a short frame buffer or a missing output head raises (modeld.py:194; parse_model_outputs.py:24-28)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I119" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J119" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K119" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L119" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M119" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N119" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-065 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-066 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unit tests for modeld output handling (parse, finiteness, frame-drop accounting) and include modeld in model_replay in LionDriver CI (with SWF-ACT-060)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O119" s="53" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P119" s="43" t="inlineStr"/>
+      <c r="Q119" s="43" t="inlineStr"/>
+      <c r="R119" s="48" t="inlineStr"/>
+      <c r="S119" s="48" t="inlineStr"/>
+    </row>
+    <row r="120" ht="114" customHeight="1">
+      <c r="A120" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-090
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driving model process (modeld)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B120" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-090
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Publish model outputs (desired curvature, leads) for every road frame, computed from the current frame and calibration, and mark output that is not fit for use as invalid</t>
+          </r>
+        </is>
+      </c>
+      <c r="C120" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Any lateral or longitudinal hazard within the panda envelope</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Outputs of an unvalidated model reach the controllers</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driving or DM model weights or warp other than the analysed ones</t>
+          </r>
+        </is>
+      </c>
+      <c r="D120" s="50" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E120" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F120" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-074 · wrong_mode
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A model file other than the released one is loaded</t>
+          </r>
+        </is>
+      </c>
+      <c r="G120" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H120" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Models are loaded with pickle and no hash, version or signature check (helpers.py:15-20; modeld.py:158-159; dmonitoringmodeld.py:22-48; GAP-22, TSR-616); they are compiled at build time from git-LFS sources (modeld/SConscript:41-52)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I120" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Build from pinned LFS objects; release procedure (WP-P-10) draft</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/modeld/SConscript</t>
+          </r>
+        </is>
+      </c>
+      <c r="J120" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K120" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L120" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M120" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N120" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-065 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O120" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P120" s="43" t="inlineStr"/>
+      <c r="Q120" s="43" t="inlineStr"/>
+      <c r="R120" s="48" t="inlineStr"/>
+      <c r="S120" s="48" t="inlineStr"/>
+    </row>
+    <row r="121" ht="100.5" customHeight="1">
+      <c r="A121" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-102
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera calibration (calibrationd)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B121" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-101
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Report camera calibration as valid only when the learned extrinsics match the mount</t>
+          </r>
+        </is>
+      </c>
+      <c r="C121" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral control steers toward the lane boundary</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld warps the frames with a wrong pose; desired curvature biased</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>rpyCalib off by less than the recalibration thresholds</t>
+          </r>
+        </is>
+      </c>
+      <c r="D121" s="50" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E121" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F121" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-075 · corrupted
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera calibration reported valid while the extrinsics do not match the mount</t>
+          </r>
+        </is>
+      </c>
+      <c r="G121" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H121" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Calibration learns only above 15 mph with a yaw rate below 2 deg/s and recalibrates only beyond the spread thresholds (calibrationd.py:33-46, 138-167, 190-201), so a mount that moved by less than the thresholds stays calibrated</t>
+          </r>
+        </is>
+      </c>
+      <c r="I121" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J121" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K121" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_calibrationd.py (CI) checks status transitions on synthetic data; targeted at the thresholds, not proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/locationd/test/test_calibrationd.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L121" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="M121" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N121" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-067 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+          </r>
+        </is>
+      </c>
+      <c r="O121" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P121" s="43" t="inlineStr"/>
+      <c r="Q121" s="43" t="inlineStr"/>
+      <c r="R121" s="48" t="inlineStr"/>
+      <c r="S121" s="48" t="inlineStr"/>
+    </row>
+    <row r="122" ht="127.5" customHeight="1">
+      <c r="A122" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-103
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Online vehicle parameters (paramsd, torqued, lagd)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B122" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-102
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide vehicle parameters within plausible bounds and report them invalid otherwise</t>
+          </r>
+        </is>
+      </c>
+      <c r="C122" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral control steers toward the lane boundary or overshoots</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral controller gain or feed-forward wrong; vehicleParameters valid false raises paramsdTemporaryError only while calibrated</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>steerRatio, stiffness, roll, angle offset, torque factor or lateral delay outside a plausible range</t>
+          </r>
+        </is>
+      </c>
+      <c r="D122" s="50" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E122" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-076 · value_high
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Learned vehicle parameters implausible while used by controlsd</t>
+          </r>
+        </is>
+      </c>
+      <c r="G122" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H122" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>paramsd publishes values that are not clipped to its own validity bounds (paramsd.py:155-182), and controlsd uses steerRatio and stiffness with only a 0.1 floor and no validity gate (controlsd.py:88-91; SWF-042.C3)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I122" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J122" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_paramsd.py (CI) checks the saved-parameter handling; not designed for out-of-bound use</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/locationd/test/test_paramsd.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L122" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M122" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N122" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-045 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-605 margins on the host: bound latAccelOffset and torque parameters in controlsd, apply the acceleration rate limit after pitch compensation and the CarController PID, gate pitch compensation on a valid calibrated pose, and keep host torque/accel limits below the panda limits</t>
+          </r>
+        </is>
+      </c>
+      <c r="O122" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P122" s="43" t="inlineStr"/>
+      <c r="Q122" s="43" t="inlineStr"/>
+      <c r="R122" s="48" t="inlineStr"/>
+      <c r="S122" s="48" t="inlineStr"/>
+    </row>
+    <row r="123" ht="114" customHeight="1">
+      <c r="A123" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-101
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>locationd pose filter</t>
+          </r>
+        </is>
+      </c>
+      <c r="B123" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-100
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide a calibrated pose from valid IMU and camera odometry, and report invalid inputs within the reaction time</t>
+          </r>
+        </is>
+      </c>
+      <c r="C123" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-003 (roll compensation) and to an undetected excessive actuation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Roll compensation, the excessive-actuation monitor and torqued work on a wrong pose</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>deviceMotion from an IMU that stopped or is implausible</t>
+          </r>
+        </is>
+      </c>
+      <c r="D123" s="50" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E123" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F123" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-077 · late
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>IMU or pose fault reported to the supervision late</t>
+          </r>
+        </is>
+      </c>
+      <c r="G123" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H123" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>selfdrived ignores accelerometer and gyro in its alive/valid checks and raises sensorDataInvalid only after 10 s without data (selfdrived.py:101, 454-456); deviceMotion.sensorsOK is not consumed by selfdrived (only paramsd and torqued)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I123" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J123" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K123" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_locationd_scenarios.py (CI; downloads a route) covers sensor faults in locationd; not designed for the selfdrived reaction time</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/locationd/test/test_locationd_scenarios.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L123" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M123" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N123" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-067 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+          </r>
+        </is>
+      </c>
+      <c r="O123" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P123" s="43" t="inlineStr"/>
+      <c r="Q123" s="43" t="inlineStr"/>
+      <c r="R123" s="48" t="inlineStr"/>
+      <c r="S123" s="48" t="inlineStr"/>
+    </row>
+    <row r="124" ht="100.5" customHeight="1">
+      <c r="A124" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-110
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera acquisition (camerad)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B124" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-110
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Deliver every road, wide and driver camera frame once, in order and synchronised, and make a stopped or failed camera visible</t>
+          </r>
+        </is>
+      </c>
+      <c r="C124" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral control from degraded model output</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld runs on fewer or skewed frames (SWF-072); selfdrived cameraMalfunction / cameraFrameRate only when the rate or liveness fails</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Gaps in the frame stream, or main and wide frames out of sync</t>
+          </r>
+        </is>
+      </c>
+      <c r="D124" s="31" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E124" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F124" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-078 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Road camera frames stop, are dropped or lose sync without an error flag</t>
+          </r>
+        </is>
+      </c>
+      <c r="G124" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H124" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>camerad never marks a frame invalid (messages default to valid, cereal/messaging/messaging.h:47); frames that fail sync or arrive out of order are dropped silently (spectra.cc:1407-1481), and a sensor that fails bring-up or an I2C write is only disabled with a log (spectra.cc:320-351)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I124" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J124" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K124" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_camerad.py (frame skips, sync, stress) is a hardware test, not run in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="L124" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M124" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N124" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-068 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera stream supervision: never ignore a road stream for the reference device (refuse engagement if it is absent at start), mark frames invalid on sync failure, and raise an event when a sensor is disabled; run the camerad hardware tests per release</t>
+          </r>
+        </is>
+      </c>
+      <c r="O124" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P124" s="33" t="inlineStr"/>
+      <c r="Q124" s="33" t="inlineStr"/>
+      <c r="R124" s="39" t="inlineStr"/>
+      <c r="S124" s="39" t="inlineStr"/>
+    </row>
+    <row r="125" ht="100.5" customHeight="1">
+      <c r="A125" s="40" t="n"/>
+      <c r="B125" s="40" t="n"/>
+      <c r="C125" s="40" t="n"/>
+      <c r="D125" s="40" t="n"/>
+      <c r="E125" s="40" t="n"/>
+      <c r="F125" s="40" t="n"/>
+      <c r="G125" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H125" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>If the narrow or wide road stream is absent when selfdrived initialises, it is put on the ignore_alive and ignore_valid lists for the whole drive (selfdrived.py:518-524), so a camera that is not up at start is never supervised</t>
+          </r>
+        </is>
+      </c>
+      <c r="I125" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J125" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K125" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L125" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M125" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N125" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-068 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera stream supervision: never ignore a road stream for the reference device (refuse engagement if it is absent at start), mark frames invalid on sync failure, and raise an event when a sensor is disabled; run the camerad hardware tests per release</t>
+          </r>
+        </is>
+      </c>
+      <c r="O125" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P125" s="33" t="inlineStr"/>
+      <c r="Q125" s="33" t="inlineStr"/>
+      <c r="R125" s="39" t="inlineStr"/>
+      <c r="S125" s="39" t="inlineStr"/>
+    </row>
+    <row r="126" ht="100.5" customHeight="1">
+      <c r="A126" s="42" t="n"/>
+      <c r="B126" s="42" t="n"/>
+      <c r="C126" s="42" t="n"/>
+      <c r="D126" s="42" t="n"/>
+      <c r="E126" s="42" t="n"/>
+      <c r="F126" s="42" t="n"/>
+      <c r="G126" s="43" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H126" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>First-frame sync across cameras gives up after 40 frames and runs unsynchronised with only a log (spectra.cc:1550-1576); modeld only logs a main/wide skew over 10 ms (modeld.py:352-354)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I126" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J126" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K126" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L126" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M126" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N126" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-068 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera stream supervision: never ignore a road stream for the reference device (refuse engagement if it is absent at start), mark frames invalid on sync failure, and raise an event when a sensor is disabled; run the camerad hardware tests per release</t>
+          </r>
+        </is>
+      </c>
+      <c r="O126" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P126" s="43" t="inlineStr"/>
+      <c r="Q126" s="43" t="inlineStr"/>
+      <c r="R126" s="48" t="inlineStr"/>
+      <c r="S126" s="48" t="inlineStr"/>
+    </row>
+    <row r="127" ht="100.5" customHeight="1">
+      <c r="A127" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-120
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>IMU acquisition (sensord)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B127" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-120
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Deliver accelerometer and gyro samples with correct timestamps, and mark implausible data invalid</t>
+          </r>
+        </is>
+      </c>
+      <c r="C127" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-003 through a wrong pose (SWF-077)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>locationd rejects them only if they fail its norm and cross-checks</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Accelerometer or gyro values out of range or repeated with valid true</t>
+          </r>
+        </is>
+      </c>
+      <c r="D127" s="50" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E127" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F127" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-079 · value_frozen
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>IMU samples implausible or stuck while published as valid</t>
+          </r>
+        </is>
+      </c>
+      <c r="G127" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H127" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No range, stuck-value or plausibility check at the source: every sample after the 0.5 s warm-up is valid (sensord.py:68-70; i2c_sensor.py:58-63); init and read errors are logged and sensord keeps running without the sensor (sensord.py:73-76, 104-126); self-test only with LSM_SELF_TEST=1</t>
+          </r>
+        </is>
+      </c>
+      <c r="I127" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J127" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K127" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_sensord.py is a hardware test, not run in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="L127" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M127" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N127" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-067 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+          </r>
+        </is>
+      </c>
+      <c r="O127" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P127" s="43" t="inlineStr"/>
+      <c r="Q127" s="43" t="inlineStr"/>
+      <c r="R127" s="48" t="inlineStr"/>
+      <c r="S127" s="48" t="inlineStr"/>
+    </row>
+    <row r="128" ht="87" customHeight="1">
+      <c r="A128" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-132
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>msgq ring buffer</t>
+          </r>
+        </is>
+      </c>
+      <c r="B128" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-131
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Deliver every published message intact to each subscriber, or make the loss visible</t>
+          </r>
+        </is>
+      </c>
+      <c r="C128" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-003 and HZ-007 through stale or wrong inputs</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Consumers see only gaps beyond 10 periods (SubMaster) or parse errors</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A reader skips messages or receives a corrupted payload</t>
+          </r>
+        </is>
+      </c>
+      <c r="D128" s="31" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E128" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-080 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Messages lost or altered between publisher and subscriber without the subscriber knowing</t>
+          </r>
+        </is>
+      </c>
+      <c r="G128" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H128" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A lapped reader is reset to the write pointer and silently skips the lost messages (msgq.cc:72-76, 262-293, 331-333, 385-426); a 16th subscriber evicts every reader, which reconnect silently (msgq.h:9; msgq.cc:196-207, 324-327)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I128" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J128" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K128" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• msgq tests (msgq_repo/msgq/tests) are outside openpilot/ and not run by LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="L128" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M128" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N128" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-069 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run the msgq tests in LionDriver CI and assess whether a payload checksum or a lost-message counter is needed for the safety-relevant services (selfdriveState, carControl, sendcan, pandaStates)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O128" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P128" s="33" t="inlineStr"/>
+      <c r="Q128" s="33" t="inlineStr"/>
+      <c r="R128" s="39" t="inlineStr"/>
+      <c r="S128" s="39" t="inlineStr"/>
+    </row>
+    <row r="129" ht="87" customHeight="1">
+      <c r="A129" s="42" t="n"/>
+      <c r="B129" s="42" t="n"/>
+      <c r="C129" s="42" t="n"/>
+      <c r="D129" s="42" t="n"/>
+      <c r="E129" s="42" t="n"/>
+      <c r="F129" s="42" t="n"/>
+      <c r="G129" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H129" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No checksum on payloads in shared memory: a writer defect or a memory fault reaches the consumer; only corrupt sizes are caught, by assert (abort, msgq.cc:399-400)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I129" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J129" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K129" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L129" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M129" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N129" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-069 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run the msgq tests in LionDriver CI and assess whether a payload checksum or a lost-message counter is needed for the safety-relevant services (selfdriveState, carControl, sendcan, pandaStates)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O129" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P129" s="43" t="inlineStr"/>
+      <c r="Q129" s="43" t="inlineStr"/>
+      <c r="R129" s="48" t="inlineStr"/>
+      <c r="S129" s="48" t="inlineStr"/>
+    </row>
+    <row r="130" ht="141" customHeight="1">
+      <c r="A130" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-131
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SubMaster liveness and validity</t>
+          </r>
+        </is>
+      </c>
+      <c r="B130" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-130
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Report an input as alive and valid only while it is received at its rate and flagged valid</t>
+          </r>
+        </is>
+      </c>
+      <c r="C130" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-003 and HZ-007 (control on held inputs)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Consumers act on held values for 0.1 s (100 Hz) to 1 s (10 Hz pandaStates) before any reaction</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SubMaster.alive true for up to 10 periods after the last message; freq_ok true on a 10 s or 1 s average</t>
+          </r>
+        </is>
+      </c>
+      <c r="D130" s="50" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E130" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F130" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-081 · value_stale
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>An input is reported alive and valid while it is stale</t>
+          </r>
+        </is>
+      </c>
+      <c r="G130" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H130" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design alive means received within 10 nominal periods and freq_ok passes if the 10 s or the 1 s average is within 0.8..1.2 of the rate (__init__.py:138-178, 265-278); TSR-602 asks 2 periods. SIMULATION=1 relaxes both checks (__init__.py:213, 265-266)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I130" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J130" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K130" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_pub_sub_master.py (CI) tests the alive and valid semantics; targeted at the mechanism, not at the bound</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/cereal/messaging/tests/test_pub_sub_master.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L130" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="M130" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N130" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-040 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-602 in controlsd: check age and valid of selfdriveState, carState, modelV2, longitudinalPlan, vehicleParameters and deviceMotion before use (≤ 2 periods); set latActive/longActive false and raise an immediate-disable event when stale; derive carControl.valid from these checks and have card stop actuating on carControl.valid false; give cruiseMismatch a disable type</t>
+          </r>
+        </is>
+      </c>
+      <c r="O130" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+      <c r="P130" s="43" t="inlineStr">
+        <is>
+          <t>10/3/4</t>
+        </is>
+      </c>
+      <c r="Q130" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R130" s="48" t="inlineStr"/>
+      <c r="S130" s="48" t="inlineStr"/>
+    </row>
+    <row r="131" ht="127.5" customHeight="1">
+      <c r="A131" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-140
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Process manager (manager)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B131" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-140
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run every process the configuration needs and report any that is not running</t>
+          </r>
+        </is>
+      </c>
+      <c r="C131" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Take-over alerts not presented while the item runs</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No processNotRunning event; a process that selfdrived does not subscribe to (soundd, ui) is then not supervised at all</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A process blocked or never started has no process entry, so managerState shows shouldBeRunning false</t>
+          </r>
+        </is>
+      </c>
+      <c r="D131" s="50" t="inlineStr">
+        <is>
+          <t>HZ-012</t>
+        </is>
+      </c>
+      <c r="E131" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F131" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-082 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A process the drive needs is not running and is not reported</t>
+          </r>
+        </is>
+      </c>
+      <c r="G131" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H131" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The BLOCK environment variable or a process that never starts leaves proc None, so shouldBeRunning is false and no event fires (manager.py:110-112; process.py:121-129)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I131" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No launch path sets BLOCK; setting it needs a shell on the device</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/manager.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J131" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K131" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_manager.py (CI) checks blacklisted processes do not start; not designed for the missing report</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/test/test_manager.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L131" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M131" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N131" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-070 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only</t>
+          </r>
+        </is>
+      </c>
+      <c r="O131" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P131" s="43" t="inlineStr"/>
+      <c r="Q131" s="43" t="inlineStr"/>
+      <c r="R131" s="48" t="inlineStr"/>
+      <c r="S131" s="48" t="inlineStr"/>
+    </row>
+    <row r="132" ht="114" customHeight="1">
+      <c r="A132" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-140
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Process manager (manager)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B132" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-140
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run every process the configuration needs and report any that is not running</t>
+          </r>
+        </is>
+      </c>
+      <c r="C132" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item unavailable after one crash, with an alert</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>processNotRunning (SOFT_DISABLE, NO_ENTRY) for the rest of the drive</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No restart and no watchdog: start() returns while proc is set, so the process is restarted only after an offroad transition</t>
+          </r>
+        </is>
+      </c>
+      <c r="D132" s="50" t="inlineStr"/>
+      <c r="E132" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F132" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-083 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A crashed process stays down for the rest of the drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="G132" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H132" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design manager has no restart policy or process watchdog (process.py:142-154, 223-238)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I132" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J132" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K132" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_manager.py (CI); test_clean_exit is skipped; nothing tests restart behaviour</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/test/test_manager.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L132" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M132" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N132" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-070 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only</t>
+          </r>
+        </is>
+      </c>
+      <c r="O132" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P132" s="43" t="inlineStr"/>
+      <c r="Q132" s="43" t="inlineStr"/>
+      <c r="R132" s="48" t="inlineStr"/>
+      <c r="S132" s="48" t="inlineStr"/>
+    </row>
+    <row r="133" ht="114" customHeight="1">
+      <c r="A133" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-150
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Software update (updated)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B133" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-150
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Install only the released, assured software version, and never change running software while driving</t>
+          </r>
+        </is>
+      </c>
+      <c r="C133" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unassured host and panda software drives the car</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>It is swapped in at the next boot; pandad flashes the panda build of that checkout</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The finalized overlay holds another commit of the tracked branch, or of another remote</t>
+          </r>
+        </is>
+      </c>
+      <c r="D133" s="50" t="inlineStr">
+        <is>
+          <t>HZ-002</t>
+        </is>
+      </c>
+      <c r="E133" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F133" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-084 · wrong_mode
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>An update installs software other than the released, assured version</t>
+          </r>
+        </is>
+      </c>
+      <c r="G133" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H133" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No signature or commit-pin check: updated fetches the UpdaterTargetBranch (or the current branch) from the install's origin and trusts the git transport (updated.py:237-248, 343-410); there is no automatic rollback (launch_chffrplus.sh:52-65)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I133" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J133" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K133" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No updated tests exist</t>
+          </r>
+        </is>
+      </c>
+      <c r="L133" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M133" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N133" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-071 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Update integrity: pin the update to signed release tags of the LionDriver repository and verify the signature before finalizing; define rollback (with the PFMEA OTA steps)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O133" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P133" s="43" t="inlineStr"/>
+      <c r="Q133" s="43" t="inlineStr"/>
+      <c r="R133" s="48" t="inlineStr"/>
+      <c r="S133" s="48" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S115"/>
-  <mergeCells count="196">
+  <autoFilter ref="A2:S133"/>
+  <mergeCells count="214">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="E92:E93"/>
+    <mergeCell ref="B124:B126"/>
     <mergeCell ref="E39:E40"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="C128:C129"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
@@ -26144,6 +29790,7 @@
     <mergeCell ref="D45:D46"/>
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E124:E126"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="C114:C115"/>
@@ -26161,6 +29808,8 @@
     <mergeCell ref="A49:A51"/>
     <mergeCell ref="F103:F105"/>
     <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C116:C118"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="D66:D68"/>
     <mergeCell ref="A22:A23"/>
@@ -26185,7 +29834,9 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="A90:A91"/>
     <mergeCell ref="F49:F51"/>
+    <mergeCell ref="E128:E129"/>
     <mergeCell ref="C100:C101"/>
+    <mergeCell ref="F116:F118"/>
     <mergeCell ref="F35:F36"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="C47:C48"/>
@@ -26209,8 +29860,10 @@
     <mergeCell ref="D111:D113"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A124:A126"/>
     <mergeCell ref="D30:D31"/>
     <mergeCell ref="D39:D40"/>
+    <mergeCell ref="C124:C126"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B32:B33"/>
@@ -26227,6 +29880,7 @@
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="D90:D91"/>
     <mergeCell ref="E52:E53"/>
+    <mergeCell ref="A116:A118"/>
     <mergeCell ref="B87:B89"/>
     <mergeCell ref="D87:D89"/>
     <mergeCell ref="C20:C21"/>
@@ -26237,6 +29891,7 @@
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="E69:E70"/>
     <mergeCell ref="E76:E78"/>
+    <mergeCell ref="E116:E118"/>
     <mergeCell ref="C66:C68"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="E66:E68"/>
@@ -26251,6 +29906,8 @@
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E114:E115"/>
+    <mergeCell ref="D124:D126"/>
+    <mergeCell ref="F124:F126"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="F43:F44"/>
@@ -26267,11 +29924,14 @@
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B116:B118"/>
     <mergeCell ref="E87:E89"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D128:D129"/>
     <mergeCell ref="B100:B101"/>
+    <mergeCell ref="F128:F129"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="A60:A61"/>
@@ -26325,11 +29985,12 @@
     <mergeCell ref="D100:D101"/>
     <mergeCell ref="C108:C109"/>
     <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D116:D118"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -26337,7 +29998,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.0 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -26352,7 +30013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27621,7 +31282,7 @@
       <c r="H32" s="61" t="inlineStr"/>
       <c r="I32" s="61" t="inlineStr"/>
     </row>
-    <row r="33" ht="87" customHeight="1">
+    <row r="33" ht="100.5" customHeight="1">
       <c r="A33" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-040</t>
@@ -27654,7 +31315,8 @@
 SWF-043.C1
 SWF-043.C2
 SWF-048.C1
-SWF-065.C1</t>
+SWF-065.C1
+SWF-081.C1</t>
         </is>
       </c>
       <c r="G33" s="61" t="inlineStr">
@@ -27868,7 +31530,8 @@
           <t>SWF-042.C2
 SWF-042.C3
 SWF-046.C1
-SWF-046.C2</t>
+SWF-046.C2
+SWF-076.C1</t>
         </is>
       </c>
       <c r="G38" s="61" t="inlineStr"/>
@@ -28416,7 +32079,8 @@
       </c>
       <c r="F53" s="61" t="inlineStr">
         <is>
-          <t>SWF-063.C1</t>
+          <t>SWF-063.C1
+SWF-072.C1</t>
         </is>
       </c>
       <c r="G53" s="61" t="inlineStr"/>
@@ -28573,8 +32237,263 @@
       <c r="H57" s="61" t="inlineStr"/>
       <c r="I57" s="61" t="inlineStr"/>
     </row>
+    <row r="58" ht="73.5" customHeight="1">
+      <c r="A58" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-065</t>
+        </is>
+      </c>
+      <c r="B58" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C58" s="61" t="inlineStr">
+        <is>
+          <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+        </is>
+      </c>
+      <c r="D58" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E58" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F58" s="61" t="inlineStr">
+        <is>
+          <t>SWF-072.C1
+SWF-072.C2
+SWF-072.C3
+SWF-073.C1
+SWF-074.C1</t>
+        </is>
+      </c>
+      <c r="G58" s="61" t="inlineStr"/>
+      <c r="H58" s="61" t="inlineStr"/>
+      <c r="I58" s="61" t="inlineStr"/>
+    </row>
+    <row r="59" ht="46.5" customHeight="1">
+      <c r="A59" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-066</t>
+        </is>
+      </c>
+      <c r="B59" s="61" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C59" s="61" t="inlineStr">
+        <is>
+          <t>Unit tests for modeld output handling (parse, finiteness, frame-drop accounting) and include modeld in model_replay in LionDriver CI (with SWF-ACT-060)</t>
+        </is>
+      </c>
+      <c r="D59" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E59" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F59" s="61" t="inlineStr">
+        <is>
+          <t>SWF-073.C1</t>
+        </is>
+      </c>
+      <c r="G59" s="61" t="inlineStr"/>
+      <c r="H59" s="61" t="inlineStr"/>
+      <c r="I59" s="61" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-067</t>
+        </is>
+      </c>
+      <c r="B60" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C60" s="61" t="inlineStr">
+        <is>
+          <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+        </is>
+      </c>
+      <c r="D60" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E60" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F60" s="61" t="inlineStr">
+        <is>
+          <t>SWF-075.C1
+SWF-077.C1
+SWF-079.C1</t>
+        </is>
+      </c>
+      <c r="G60" s="61" t="inlineStr"/>
+      <c r="H60" s="61" t="inlineStr"/>
+      <c r="I60" s="61" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-068</t>
+        </is>
+      </c>
+      <c r="B61" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C61" s="61" t="inlineStr">
+        <is>
+          <t>Camera stream supervision: never ignore a road stream for the reference device (refuse engagement if it is absent at start), mark frames invalid on sync failure, and raise an event when a sensor is disabled; run the camerad hardware tests per release</t>
+        </is>
+      </c>
+      <c r="D61" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E61" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F61" s="61" t="inlineStr">
+        <is>
+          <t>SWF-078.C1
+SWF-078.C2
+SWF-078.C3</t>
+        </is>
+      </c>
+      <c r="G61" s="61" t="inlineStr"/>
+      <c r="H61" s="61" t="inlineStr"/>
+      <c r="I61" s="61" t="inlineStr"/>
+    </row>
+    <row r="62" ht="46.5" customHeight="1">
+      <c r="A62" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-069</t>
+        </is>
+      </c>
+      <c r="B62" s="61" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C62" s="61" t="inlineStr">
+        <is>
+          <t>Run the msgq tests in LionDriver CI and assess whether a payload checksum or a lost-message counter is needed for the safety-relevant services (selfdriveState, carControl, sendcan, pandaStates)</t>
+        </is>
+      </c>
+      <c r="D62" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E62" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F62" s="61" t="inlineStr">
+        <is>
+          <t>SWF-080.C1
+SWF-080.C2</t>
+        </is>
+      </c>
+      <c r="G62" s="61" t="inlineStr"/>
+      <c r="H62" s="61" t="inlineStr"/>
+      <c r="I62" s="61" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-070</t>
+        </is>
+      </c>
+      <c r="B63" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C63" s="61" t="inlineStr">
+        <is>
+          <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only</t>
+        </is>
+      </c>
+      <c r="D63" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E63" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F63" s="61" t="inlineStr">
+        <is>
+          <t>SWF-082.C1
+SWF-083.C1</t>
+        </is>
+      </c>
+      <c r="G63" s="61" t="inlineStr"/>
+      <c r="H63" s="61" t="inlineStr"/>
+      <c r="I63" s="61" t="inlineStr"/>
+    </row>
+    <row r="64" ht="46.5" customHeight="1">
+      <c r="A64" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-071</t>
+        </is>
+      </c>
+      <c r="B64" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C64" s="61" t="inlineStr">
+        <is>
+          <t>Update integrity: pin the update to signed release tags of the LionDriver repository and verify the signature before finalizing; define rollback (with the PFMEA OTA steps)</t>
+        </is>
+      </c>
+      <c r="D64" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E64" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F64" s="61" t="inlineStr">
+        <is>
+          <t>SWF-084.C1</t>
+        </is>
+      </c>
+      <c r="G64" s="61" t="inlineStr"/>
+      <c r="H64" s="61" t="inlineStr"/>
+      <c r="I64" s="61" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I57"/>
+  <autoFilter ref="A1:I64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28585,7 +32504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -29862,8 +33781,319 @@
         </is>
       </c>
     </row>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-090</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="inlineStr">
+        <is>
+          <t>Driving model process (modeld)</t>
+        </is>
+      </c>
+      <c r="C50" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D50" s="61" t="inlineStr"/>
+      <c r="E50" s="61" t="inlineStr"/>
+    </row>
+    <row r="51" ht="33" customHeight="1">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-091</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Model execution, output parsing and validity</t>
+        </is>
+      </c>
+      <c r="C51" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D51" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-090</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-090: Publish model outputs (desired curvature, leads) for every road frame, computed from the current frame and calibration, and mark output that is not fit for use as invalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="A52" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-100</t>
+        </is>
+      </c>
+      <c r="B52" s="61" t="inlineStr">
+        <is>
+          <t>Localization and calibration (locationd, calibrationd, paramsd, torqued, lagd)</t>
+        </is>
+      </c>
+      <c r="C52" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D52" s="61" t="inlineStr"/>
+      <c r="E52" s="61" t="inlineStr"/>
+    </row>
+    <row r="53" ht="33" customHeight="1">
+      <c r="A53" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-101</t>
+        </is>
+      </c>
+      <c r="B53" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    locationd pose filter</t>
+        </is>
+      </c>
+      <c r="C53" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D53" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-100</t>
+        </is>
+      </c>
+      <c r="E53" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-100: Provide a calibrated pose from valid IMU and camera odometry, and report invalid inputs within the reaction time</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="A54" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-102</t>
+        </is>
+      </c>
+      <c r="B54" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Camera calibration (calibrationd)</t>
+        </is>
+      </c>
+      <c r="C54" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D54" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-100</t>
+        </is>
+      </c>
+      <c r="E54" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-101: Report camera calibration as valid only when the learned extrinsics match the mount</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-103</t>
+        </is>
+      </c>
+      <c r="B55" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Online vehicle parameters (paramsd, torqued, lagd)</t>
+        </is>
+      </c>
+      <c r="C55" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D55" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-100</t>
+        </is>
+      </c>
+      <c r="E55" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-102: Provide vehicle parameters within plausible bounds and report them invalid otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33" customHeight="1">
+      <c r="A56" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-110</t>
+        </is>
+      </c>
+      <c r="B56" s="61" t="inlineStr">
+        <is>
+          <t>Camera acquisition (camerad)</t>
+        </is>
+      </c>
+      <c r="C56" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D56" s="61" t="inlineStr"/>
+      <c r="E56" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-110: Deliver every road, wide and driver camera frame once, in order and synchronised, and make a stopped or failed camera visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33" customHeight="1">
+      <c r="A57" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-120</t>
+        </is>
+      </c>
+      <c r="B57" s="61" t="inlineStr">
+        <is>
+          <t>IMU acquisition (sensord)</t>
+        </is>
+      </c>
+      <c r="C57" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D57" s="61" t="inlineStr"/>
+      <c r="E57" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-120: Deliver accelerometer and gyro samples with correct timestamps, and mark implausible data invalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-130</t>
+        </is>
+      </c>
+      <c r="B58" s="61" t="inlineStr">
+        <is>
+          <t>Messaging (cereal and msgq)</t>
+        </is>
+      </c>
+      <c r="C58" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D58" s="61" t="inlineStr"/>
+      <c r="E58" s="61" t="inlineStr"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-131</t>
+        </is>
+      </c>
+      <c r="B59" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SubMaster liveness and validity</t>
+        </is>
+      </c>
+      <c r="C59" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D59" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-130</t>
+        </is>
+      </c>
+      <c r="E59" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-130: Report an input as alive and valid only while it is received at its rate and flagged valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="A60" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-132</t>
+        </is>
+      </c>
+      <c r="B60" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    msgq ring buffer</t>
+        </is>
+      </c>
+      <c r="C60" s="61" t="inlineStr">
+        <is>
+          <t>sw_unit</t>
+        </is>
+      </c>
+      <c r="D60" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-130</t>
+        </is>
+      </c>
+      <c r="E60" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-131: Deliver every published message intact to each subscriber, or make the loss visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-140</t>
+        </is>
+      </c>
+      <c r="B61" s="61" t="inlineStr">
+        <is>
+          <t>Process manager (manager)</t>
+        </is>
+      </c>
+      <c r="C61" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D61" s="61" t="inlineStr"/>
+      <c r="E61" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-140: Run every process the configuration needs and report any that is not running</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="33" customHeight="1">
+      <c r="A62" s="61" t="inlineStr">
+        <is>
+          <t>SWF-SE-150</t>
+        </is>
+      </c>
+      <c r="B62" s="61" t="inlineStr">
+        <is>
+          <t>Software update (updated)</t>
+        </is>
+      </c>
+      <c r="C62" s="61" t="inlineStr">
+        <is>
+          <t>sw_element</t>
+        </is>
+      </c>
+      <c r="D62" s="61" t="inlineStr"/>
+      <c r="E62" s="61" t="inlineStr">
+        <is>
+          <t>SWF-FN-150: Install only the released, assured software version, and never change running software while driving</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E49"/>
+  <autoFilter ref="A1:E62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -23056,7 +23056,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream design; FSR-040 names a safe state that the FSC does not define for this path</t>
+            <t>• Upstream design; FSR-040 names a safe state that the FSC does not define for this path. Requirements not documented and no field-exposure evidence cited, so O 8 (RT-2 §2), as SWF-083.C1 and SFM-025.C1</t>
           </r>
           <r>
             <rPr>
@@ -23070,7 +23070,7 @@
         </is>
       </c>
       <c r="J99" s="45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K99" s="44" t="inlineStr">
         <is>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$137</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.0 · draft</t>
+          <t>1.1 · draft</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="150" customHeight="1">
+    <row r="10" ht="180" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
@@ -865,7 +865,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071). P3 elements: modeld as a software element (SWF-072..074; model performance is SOTIF), localization and calibration (SWF-075..077), camerad (SWF-078), sensord (SWF-079), messaging (SWF-080, SWF-081), manager (SWF-082, SWF-083), updated (SWF-084).</t>
+          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071). P3 elements: modeld as a software element (SWF-072..074; model performance is SOTIF), localization and calibration (SWF-075..077), camerad (SWF-078), sensord (SWF-079), messaging (SWF-080, SWF-081), manager (SWF-082, SWF-083), updated (SWF-084). Rev 1.1: driver-monitoring demo mode (SWF-085) and the forced stop after the terminal alert (SWF-086), for FTA finding F-37.</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>63 (59)</t>
+          <t>65 (61)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S133"/>
+  <dimension ref="A1:S137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -29825,9 +29825,730 @@
       <c r="R133" s="48" t="inlineStr"/>
       <c r="S133" s="48" t="inlineStr"/>
     </row>
+    <row r="134" ht="222" customHeight="1">
+      <c r="A134" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-062
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Monitoring policy and dmonitoringd</t>
+          </r>
+        </is>
+      </c>
+      <c r="B134" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-061
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate an inattentive or unresponsive driver within the policy times (vision 5/8/13 s, wheel-touch 5/15/25 s) and request the terminal reaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="C134" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Monitoring of the actual driver can be lost (the passenger's face monitored) while automated control continues</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Alerts still escalate on the camera input, with strict pose thresholds and no wheel-touch reset; but the wheel-side lock is off while engaged (policy.py:261), so the monitored seat can switch, and the policy ignores the real speed, gear and engagement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>run_step uses a synthetic vehicle state (speed 30 m/s, enabled, no driver input, brake-disengage probability 1.0, zero calibration) instead of carState, selfdriveState and extrinsicsCalibration, and skips the input validity gate except for driverStateV2 (dmonitoringd.py:26-29; policy.py:431-440)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D134" s="31" t="inlineStr">
+        <is>
+          <t>HZ-013</t>
+        </is>
+      </c>
+      <c r="E134" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F134" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-085 · wrong_mode
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring evaluates the driver in demo mode while the item is engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="G134" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H134" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The cabin camera dialog sets IsDriverViewEnabled and clears it only when the dialog closes (ui/onroad/cabin_camera_dialog.py:18-22; ui/mici/onroad/cabin_camera_dialog.py:44, 52). The dialog opens only offroad, but stays open across the onroad transition: the comma four UI pops it 2.5 s after going onroad (mici/layouts/main.py:112-124, not while onboarding), the comma 3X UI on its interactive timeout or a touch (cabin_camera_dialog.py:16). dmonitoringd re-reads the parameter every 40 frames, 2 s (dmonitoringd.py:36-38). While open, the comma four dialog also publishes its own selfdriveState with only alertSound set (mici cabin_camera_dialog.py:48, 102-116), a second publisher beside selfdrived</t>
+          </r>
+        </is>
+      </c>
+      <c r="I134" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• The dialog buttons are disabled onroad (layouts/settings/device.py:61; mici device_layout.py:185); the comma four UI closes dialogs after going onroad. Upstream code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirement implemented (TSR-610 not met)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/ui/mici/layouts/main.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J134" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K134" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test covers demo mode with the item started; test_widget_leaks only constructs the dialogs</t>
+          </r>
+        </is>
+      </c>
+      <c r="L134" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M134" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N134" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-072 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Demo-mode interlock (TSR-610): selfdrived refuses engagement while IsDriverViewEnabled is set and raises a fault if it is set while engaged; the UI clears the parameter on the onroad transition; dmonitoringd ignores demo mode while started. Add a test with the item started</t>
+          </r>
+        </is>
+      </c>
+      <c r="O134" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P134" s="33" t="inlineStr"/>
+      <c r="Q134" s="33" t="inlineStr"/>
+      <c r="R134" s="39" t="inlineStr"/>
+      <c r="S134" s="39" t="inlineStr"/>
+    </row>
+    <row r="135" ht="114" customHeight="1">
+      <c r="A135" s="42" t="n"/>
+      <c r="B135" s="42" t="n"/>
+      <c r="C135" s="42" t="n"/>
+      <c r="D135" s="42" t="n"/>
+      <c r="E135" s="42" t="n"/>
+      <c r="F135" s="42" t="n"/>
+      <c r="G135" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H135" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No engagement interlock: nothing in selfdrived or controlsd reads IsDriverViewEnabled, so a parameter left set (written by tooling, or a UI crash before hide_event; it is cleared only at manager start, params_keys.h:61) keeps demo mode for the drive (GAP-20, TSR-610 not met)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I135" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream design with no interlock; requirement TSR-610 not implemented, so O 8 (RT-2 §2), as the other by-design gaps</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/dmonitoringd.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J135" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K135" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test; fault-injection scenario VS-FI-23 (params tampering) is specified in WP-V-05 but not run</t>
+          </r>
+        </is>
+      </c>
+      <c r="L135" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M135" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N135" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-072 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Demo-mode interlock (TSR-610): selfdrived refuses engagement while IsDriverViewEnabled is set and raises a fault if it is set while engaged; the UI clears the parameter on the onroad transition; dmonitoringd ignores demo mode while started. Add a test with the item started</t>
+          </r>
+        </is>
+      </c>
+      <c r="O135" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P135" s="43" t="inlineStr"/>
+      <c r="Q135" s="43" t="inlineStr"/>
+      <c r="R135" s="48" t="inlineStr"/>
+      <c r="S135" s="48" t="inlineStr"/>
+    </row>
+    <row r="136" ht="141" customHeight="1">
+      <c r="A136" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-060
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B136" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-061
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate an inattentive or unresponsive driver within the policy times (vision 5/8/13 s, wheel-touch 5/15/25 s) and request the terminal reaction</t>
+          </r>
+        </is>
+      </c>
+      <c r="C136" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Automated control continues with an unresponsive driver, or the stop takes too long</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd keeps v_cruise at the set speed, or slows at -1.2 m/s² only; lateral control continues</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>noResponseForceDecel false, stale, or not turned into controlsState.forceDecel; or the planner decelerates too weakly to stop in a useful time</t>
+          </r>
+        </is>
+      </c>
+      <c r="D136" s="31" t="inlineStr">
+        <is>
+          <t>HZ-013</t>
+        </is>
+      </c>
+      <c r="E136" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F136" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-086 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Forced deceleration not requested, not passed on, or not carried to a stop after the terminal alert</t>
+          </r>
+        </is>
+      </c>
+      <c r="G136" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H136" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The request crosses three processes with no freshness check on the flag: controlsd reads driverMonitoringState.noResponseForceDecel without an alive or valid check (controlsd.py:49-51, 235), and plannerd reads controlsState.forceDecel the same way (longitudinal_planner.py:84); its own valid flag is not read by controlsd (SWF-065.C1). A stopped dmonitoringd leaves the last value in place until selfdrived soft-disables (SWF-064)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I136" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J136" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K136" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_longitudinal sets controlsState.forceDecel directly in the plant (CI) and so tests the planner end only; nothing tests the policy-to-controlsd link or a stale flag</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L136" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M136" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N136" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-073 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd</t>
+          </r>
+        </is>
+      </c>
+      <c r="O136" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P136" s="33" t="inlineStr"/>
+      <c r="Q136" s="33" t="inlineStr"/>
+      <c r="R136" s="39" t="inlineStr"/>
+      <c r="S136" s="39" t="inlineStr"/>
+    </row>
+    <row r="137" ht="208.5" customHeight="1">
+      <c r="A137" s="42" t="n"/>
+      <c r="B137" s="42" t="n"/>
+      <c r="C137" s="42" t="n"/>
+      <c r="D137" s="42" t="n"/>
+      <c r="E137" s="42" t="n"/>
+      <c r="F137" s="42" t="n"/>
+      <c r="G137" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H137" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design the forced stop is only v_cruise = 0 on the cruise candidate: the planner slows at A_CRUISE_MIN, -1.2 m/s², jerk-limited (longitudinal_planner.py:22, 50-52, 84-85), about 25 s and 390 m from 110 km/h, with no stop-time requirement (TSR-633 not met; reaction queued for the lead as DQ-340). The Toyota port does not use CC.driverMonitoringEscalation (read only by the Volkswagen port, carcontroller.py:131)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I137" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream design; no LionDriver requirement for the stop time or deceleration (TSR-633 open), so O 8 (RT-2 §2)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/lib/longitudinal_planner.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J137" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K137" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_longitudinal force_decel maneuvers (CI) fail only if the plant does not decelerate at all (acceleration above -0.04 m/s² while moving, maneuver.py:84-86); no check of the stop time</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L137" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="M137" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N137" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-059 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-073 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd</t>
+          </r>
+        </is>
+      </c>
+      <c r="O137" s="59" t="inlineStr">
+        <is>
+          <t>decision pending
+open</t>
+        </is>
+      </c>
+      <c r="P137" s="43" t="inlineStr"/>
+      <c r="Q137" s="43" t="inlineStr"/>
+      <c r="R137" s="48" t="inlineStr"/>
+      <c r="S137" s="48" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S133"/>
-  <mergeCells count="214">
+  <autoFilter ref="A2:S137"/>
+  <mergeCells count="226">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="E92:E93"/>
     <mergeCell ref="B124:B126"/>
@@ -29839,6 +30560,7 @@
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="D108:D109"/>
     <mergeCell ref="F108:F109"/>
+    <mergeCell ref="C134:C135"/>
     <mergeCell ref="F111:F113"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D45:D46"/>
@@ -29859,6 +30581,8 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="F72:F73"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="F134:F135"/>
     <mergeCell ref="A49:A51"/>
     <mergeCell ref="F103:F105"/>
     <mergeCell ref="C49:C51"/>
@@ -29867,6 +30591,7 @@
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="D66:D68"/>
     <mergeCell ref="A22:A23"/>
+    <mergeCell ref="F136:F137"/>
     <mergeCell ref="F87:F89"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="E41:E42"/>
@@ -29927,6 +30652,7 @@
     <mergeCell ref="C74:C75"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B134:B135"/>
     <mergeCell ref="B103:B105"/>
     <mergeCell ref="C58:C59"/>
     <mergeCell ref="D103:D105"/>
@@ -29936,6 +30662,7 @@
     <mergeCell ref="E52:E53"/>
     <mergeCell ref="A116:A118"/>
     <mergeCell ref="B87:B89"/>
+    <mergeCell ref="D136:D137"/>
     <mergeCell ref="D87:D89"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="F74:F75"/>
@@ -29951,6 +30678,7 @@
     <mergeCell ref="E66:E68"/>
     <mergeCell ref="A111:A113"/>
     <mergeCell ref="C111:C113"/>
+    <mergeCell ref="A136:A137"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="D41:D42"/>
@@ -29958,6 +30686,7 @@
     <mergeCell ref="F41:F42"/>
     <mergeCell ref="E111:E113"/>
     <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A134:A135"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E114:E115"/>
     <mergeCell ref="D124:D126"/>
@@ -29975,6 +30704,7 @@
     <mergeCell ref="E72:E73"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C39:C40"/>
+    <mergeCell ref="E134:E135"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="F14:F15"/>
@@ -29989,6 +30719,7 @@
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B136:B137"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="A76:A78"/>
     <mergeCell ref="E54:E56"/>
@@ -30025,7 +30756,9 @@
     <mergeCell ref="F58:F59"/>
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="E100:E101"/>
+    <mergeCell ref="C136:C137"/>
     <mergeCell ref="E47:E48"/>
+    <mergeCell ref="E136:E137"/>
     <mergeCell ref="E103:E105"/>
     <mergeCell ref="D60:D61"/>
     <mergeCell ref="E22:E23"/>
@@ -30044,7 +30777,7 @@
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -30052,7 +30785,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.0 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.1 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -30067,7 +30800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32098,7 +32831,8 @@
       </c>
       <c r="F52" s="61" t="inlineStr">
         <is>
-          <t>SWF-062.C1</t>
+          <t>SWF-062.C1
+SWF-086.C2</t>
         </is>
       </c>
       <c r="G52" s="61" t="inlineStr"/>
@@ -32546,8 +33280,80 @@
       <c r="H64" s="61" t="inlineStr"/>
       <c r="I64" s="61" t="inlineStr"/>
     </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-072</t>
+        </is>
+      </c>
+      <c r="B65" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C65" s="61" t="inlineStr">
+        <is>
+          <t>Demo-mode interlock (TSR-610): selfdrived refuses engagement while IsDriverViewEnabled is set and raises a fault if it is set while engaged; the UI clears the parameter on the onroad transition; dmonitoringd ignores demo mode while started. Add a test with the item started</t>
+        </is>
+      </c>
+      <c r="D65" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E65" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F65" s="61" t="inlineStr">
+        <is>
+          <t>SWF-085.C1
+SWF-085.C2</t>
+        </is>
+      </c>
+      <c r="G65" s="61" t="inlineStr"/>
+      <c r="H65" s="61" t="inlineStr"/>
+      <c r="I65" s="61" t="inlineStr"/>
+    </row>
+    <row r="66" ht="73.5" customHeight="1">
+      <c r="A66" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-073</t>
+        </is>
+      </c>
+      <c r="B66" s="61" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C66" s="61" t="inlineStr">
+        <is>
+          <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd</t>
+        </is>
+      </c>
+      <c r="D66" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E66" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F66" s="61" t="inlineStr">
+        <is>
+          <t>SWF-086.C1
+SWF-086.C2</t>
+        </is>
+      </c>
+      <c r="G66" s="61" t="inlineStr"/>
+      <c r="H66" s="61" t="inlineStr"/>
+      <c r="I66" s="61" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I64"/>
+  <autoFilter ref="A1:I66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13685,7 +13685,7 @@
       <c r="R56" s="48" t="inlineStr"/>
       <c r="S56" s="48" t="inlineStr"/>
     </row>
-    <row r="57" ht="141" customHeight="1">
+    <row r="57" ht="208.5" customHeight="1">
       <c r="A57" s="49" t="inlineStr">
         <is>
           <r>
@@ -13791,6 +13791,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-013 (a driver-monitoring escalation masked, so an inattentive driver is not told; the forced stop still follows)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -13832,7 +13858,8 @@
       <c r="D57" s="50" t="inlineStr">
         <is>
           <t>HZ-012
-HZ-004</t>
+HZ-004
+HZ-013</t>
         </is>
       </c>
       <c r="E57" s="51" t="n">
@@ -13874,7 +13901,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Selection is by priority, then start frame (alertmanager.py:63). SoftDisableAlert is Priority.MID (events.py:161-166), below speedTooHigh (WARNING, HIGH, promptRepeat, events.py:995-1000), aeb/stockAeb (PERMANENT, HIGHEST, no sound, events.py:471-485) and driverDistracted3/driverUnresponsive3 (HIGH); the takeover text and warningSoft can be hidden for the first 2.5 s and only the last 0.5 s becomes ImmediateDisableAlert (events.py:224-228)</t>
+            <t>Selection is by priority, then start frame (alertmanager.py:63). SoftDisableAlert is Priority.MID (events.py:161-166), below speedTooHigh (WARNING, HIGH, promptRepeat, events.py:995-1000), aeb/stockAeb (PERMANENT, HIGHEST, no sound, events.py:471-485) and driverDistracted3/driverUnresponsive3 (HIGH); the takeover text and warningSoft can be hidden for the first 2.5 s and only the last 0.5 s becomes ImmediateDisableAlert (events.py:224-228). The same rule masks the driver-monitoring escalation: driverDistracted2 / driverUnresponsive2 (MID, events.py:532-563) under speedTooHigh, and the level 3 alerts (HIGH) under aeb or fcw (HIGHEST) or a later-starting HIGH alert</t>
           </r>
         </is>
       </c>
@@ -29076,7 +29103,7 @@
       <c r="R130" s="48" t="inlineStr"/>
       <c r="S130" s="48" t="inlineStr"/>
     </row>
-    <row r="131" ht="127.5" customHeight="1">
+    <row r="131" ht="181.5" customHeight="1">
       <c r="A131" s="49" t="inlineStr">
         <is>
           <r>
@@ -29156,6 +29183,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-013 (driver-monitoring alerts not presented when soundd or ui is not running; the forced stop does not depend on them)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -29196,7 +29249,8 @@
       </c>
       <c r="D131" s="50" t="inlineStr">
         <is>
-          <t>HZ-012</t>
+          <t>HZ-012
+HZ-013</t>
         </is>
       </c>
       <c r="E131" s="51" t="n">

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$138</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.1 · draft</t>
+          <t>1.2 · draft</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="180" customHeight="1">
+    <row r="10" ht="195" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
@@ -865,7 +865,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071). P3 elements: modeld as a software element (SWF-072..074; model performance is SOTIF), localization and calibration (SWF-075..077), camerad (SWF-078), sensord (SWF-079), messaging (SWF-080, SWF-081), manager (SWF-082, SWF-083), updated (SWF-084). Rev 1.1: driver-monitoring demo mode (SWF-085) and the forced stop after the terminal alert (SWF-086), for FTA finding F-37.</t>
+          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071). P3 elements: modeld as a software element (SWF-072..074; model performance is SOTIF), localization and calibration (SWF-075..077), camerad (SWF-078), sensord (SWF-079), messaging (SWF-080, SWF-081), manager (SWF-082, SWF-083), updated (SWF-084). Rev 1.1: driver-monitoring demo mode (SWF-085) and the forced stop after the terminal alert (SWF-086), for FTA finding F-37. Rev 1.2: no driver-override check on the LKA path in the envelope (SWF-087), for F-28.</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>65 (61)</t>
+          <t>66 (62)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S137"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -30600,8 +30600,250 @@
       <c r="R137" s="48" t="inlineStr"/>
       <c r="S137" s="48" t="inlineStr"/>
     </row>
+    <row r="138" ht="208.5" customHeight="1">
+      <c r="A138" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Steering torque checks</t>
+          </r>
+        </is>
+      </c>
+      <c r="B138" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-014
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Back steering torque off toward zero while the driver overrides, and reject frames that increase torque opposing the driver beyond a driver allowance (TSR-304; not implemented on the LKA path)</t>
+          </r>
+        </is>
+      </c>
+      <c r="C138" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item resists the driver's steering within the panda torque bound</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The only override check is the host's MAX_USER_TORQUE of 500 units (carcontroller.py:33, 83); with a host fault, or below 500 units by design (SWF-038), torque up to the 1500 limit keeps opposing the driver</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>STEERING_LKA (0x2E4) frames that oppose the driver pass: the Toyota LKA check is magnitude, rate and measured-torque error only (TorqueMotorLimited); STEER_TORQUE_DRIVER is decoded (toyota.h:221-223) but used only on the LTA path (toyota.h:421-424)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D138" s="50" t="inlineStr">
+        <is>
+          <t>HZ-009</t>
+        </is>
+      </c>
+      <c r="E138" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F138" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-087 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Envelope passes LKA torque that opposes the driver while the driver overrides the steering</t>
+          </r>
+        </is>
+      </c>
+      <c r="G138" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H138" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design the envelope has no driver-override check on the LKA path (GAP-02): TSR-304 (driver allowance, and back-off while the driver torque exceeds T_ovr; decided as DQ-053, 2026-10-14) is not implemented in toyota.h, in either build</t>
+          </r>
+        </is>
+      </c>
+      <c r="I138" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream design (a bounded torque the driver can overpower); requirement TSR-304 not implemented, so O 8 (RT-2 §2), as the other by-design gaps</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/modes/toyota.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J138" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K138" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_toyota.py tests the measured-torque limit (MotorTorqueSteeringSafetyTest, MAX_TORQUE_ERROR 350); no test of torque opposing the driver on the LKA path</t>
+          </r>
+        </is>
+      </c>
+      <c r="L138" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M138" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N138" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-074 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Envelope override check (TSR-304, DQ-053): in toyota.h reject 0x2E4 frames that increase torque opposing STEER_TORQUE_DRIVER beyond the driver allowance, and back off toward zero at no less than the down rate while the override lasts; report the state to the SoC (TSR-628). Add opendbc safety tests and mutation for both branches; host counterpart SWF-ACT-046</t>
+          </r>
+        </is>
+      </c>
+      <c r="O138" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P138" s="43" t="inlineStr"/>
+      <c r="Q138" s="43" t="inlineStr"/>
+      <c r="R138" s="48" t="inlineStr"/>
+      <c r="S138" s="48" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S137"/>
+  <autoFilter ref="A2:S138"/>
   <mergeCells count="226">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="E92:E93"/>
@@ -30831,7 +31073,7 @@
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -30839,7 +31081,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.1 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.2 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -30854,7 +31096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -33406,8 +33648,43 @@
       <c r="H66" s="61" t="inlineStr"/>
       <c r="I66" s="61" t="inlineStr"/>
     </row>
+    <row r="67" ht="87" customHeight="1">
+      <c r="A67" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-074</t>
+        </is>
+      </c>
+      <c r="B67" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C67" s="61" t="inlineStr">
+        <is>
+          <t>Envelope override check (TSR-304, DQ-053): in toyota.h reject 0x2E4 frames that increase torque opposing STEER_TORQUE_DRIVER beyond the driver allowance, and back off toward zero at no less than the down rate while the override lasts; report the state to the SoC (TSR-628). Add opendbc safety tests and mutation for both branches; host counterpart SWF-ACT-046</t>
+        </is>
+      </c>
+      <c r="D67" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E67" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F67" s="61" t="inlineStr">
+        <is>
+          <t>SWF-087.C1</t>
+        </is>
+      </c>
+      <c r="G67" s="61" t="inlineStr"/>
+      <c r="H67" s="61" t="inlineStr"/>
+      <c r="I67" s="61" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I66"/>
+  <autoFilter ref="A1:I67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33582,7 +33859,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-006</t>
@@ -33605,7 +33882,8 @@
       </c>
       <c r="E7" s="61" t="inlineStr">
         <is>
-          <t>SWF-FN-002: Block steering requests outside torque magnitude, rate and measured-torque-error limits, and any torque while controls are not allowed</t>
+          <t>SWF-FN-002: Block steering requests outside torque magnitude, rate and measured-torque-error limits, and any torque while controls are not allowed
+SWF-FN-014: Back steering torque off toward zero while the driver overrides, and reject frames that increase torque opposing the driver beyond a driver allowance (TSR-304; not implemented on the LKA path)</t>
         </is>
       </c>
     </row>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$137</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>65 (61)</t>
+          <t>67 (63)</t>
         </is>
       </c>
     </row>
@@ -13976,7 +13976,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Rank soft and immediate disable takeover alerts above every WARNING and PERMANENT alert except FCW, keep the takeover sound when an AEB alert is shown, name the fault class in the text (canError, TSR-606), and add a test of the ordering</t>
+            <t>Rank soft and immediate disable takeover alerts above every WARNING and PERMANENT alert except FCW, keep the takeover sound when an AEB alert is shown, name the fault class in the text (canError, TSR-606), and add a test of the ordering. Rank the driver-monitoring level 2 and 3 alerts so that speedTooHigh or a later-starting HIGH alert cannot mask them (WP-A-03 DFI-25, SWF-035)</t>
           </r>
         </is>
       </c>
@@ -22449,7 +22449,7 @@
       <c r="R95" s="48" t="inlineStr"/>
       <c r="S95" s="48" t="inlineStr"/>
     </row>
-    <row r="96" ht="114" customHeight="1">
+    <row r="96" ht="141" customHeight="1">
       <c r="A96" s="30" t="inlineStr">
         <is>
           <r>
@@ -22677,7 +22677,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
           </r>
         </is>
       </c>
@@ -22691,7 +22691,7 @@
       <c r="R96" s="39" t="inlineStr"/>
       <c r="S96" s="39" t="inlineStr"/>
     </row>
-    <row r="97" ht="114" customHeight="1">
+    <row r="97" ht="141" customHeight="1">
       <c r="A97" s="40" t="n"/>
       <c r="B97" s="40" t="n"/>
       <c r="C97" s="40" t="n"/>
@@ -22786,7 +22786,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
           </r>
         </is>
       </c>
@@ -22800,7 +22800,7 @@
       <c r="R97" s="39" t="inlineStr"/>
       <c r="S97" s="39" t="inlineStr"/>
     </row>
-    <row r="98" ht="114" customHeight="1">
+    <row r="98" ht="141" customHeight="1">
       <c r="A98" s="42" t="n"/>
       <c r="B98" s="42" t="n"/>
       <c r="C98" s="42" t="n"/>
@@ -22895,7 +22895,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
           </r>
         </is>
       </c>
@@ -23071,7 +23071,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>By design the six driver-monitoring events are PERMANENT alerts only, with no SOFT_DISABLE or IMMEDIATE_DISABLE (events.py:524-570); the terminal reaction is the forced deceleration with lateral control kept. Whether that is the SG-010 safe state of FSR-040 is not recorded; it is queued for the lead (DQ-220)</t>
+            <t>By design the six driver-monitoring events are PERMANENT alerts only, with no SOFT_DISABLE or IMMEDIATE_DISABLE (events.py:524-570); the terminal reaction is the forced deceleration with lateral control kept. Whether that is the SG-010 safe state of FSR-040 is not recorded; it is queued for the lead (DQ-365, which absorbed DQ-220)</t>
           </r>
         </is>
       </c>
@@ -23146,7 +23146,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-365, which absorbed DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
           </r>
         </is>
       </c>
@@ -23160,7 +23160,7 @@
       <c r="R99" s="48" t="inlineStr"/>
       <c r="S99" s="48" t="inlineStr"/>
     </row>
-    <row r="100" ht="181.5" customHeight="1">
+    <row r="100" ht="208.5" customHeight="1">
       <c r="A100" s="30" t="inlineStr">
         <is>
           <r>
@@ -23379,7 +23379,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
           </r>
           <r>
             <rPr>
@@ -23421,7 +23421,7 @@
       <c r="R100" s="39" t="inlineStr"/>
       <c r="S100" s="39" t="inlineStr"/>
     </row>
-    <row r="101" ht="114" customHeight="1">
+    <row r="101" ht="141" customHeight="1">
       <c r="A101" s="42" t="n"/>
       <c r="B101" s="42" t="n"/>
       <c r="C101" s="42" t="n"/>
@@ -23498,7 +23498,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
           </r>
         </is>
       </c>
@@ -23512,7 +23512,7 @@
       <c r="R101" s="48" t="inlineStr"/>
       <c r="S101" s="48" t="inlineStr"/>
     </row>
-    <row r="102" ht="114" customHeight="1">
+    <row r="102" ht="141" customHeight="1">
       <c r="A102" s="49" t="inlineStr">
         <is>
           <r>
@@ -23736,7 +23736,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+            <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
           </r>
         </is>
       </c>
@@ -26428,7 +26428,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
           <r>
             <rPr>
@@ -26547,7 +26547,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
         </is>
       </c>
@@ -26638,7 +26638,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
         </is>
       </c>
@@ -26871,7 +26871,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
           <r>
             <rPr>
@@ -27141,7 +27141,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
         </is>
       </c>
@@ -28529,7 +28529,7 @@
       <c r="R127" s="48" t="inlineStr"/>
       <c r="S127" s="48" t="inlineStr"/>
     </row>
-    <row r="128" ht="87" customHeight="1">
+    <row r="128" ht="195" customHeight="1">
       <c r="A128" s="30" t="inlineStr">
         <is>
           <r>
@@ -28750,11 +28750,39 @@
             </rPr>
             <t>Run the msgq tests in LionDriver CI and assess whether a payload checksum or a lost-message counter is needed for the safety-relevant services (selfdriveState, carControl, sendcan, pandaStates)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-075 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>msgq protection for the control and supervision topics (WP-A-03 DFI-29): sequence or E2E protection so a skipped or altered message is detected, a subscriber-count guard so a 16th reader cannot evict the others, and host supervision of control credited only where it is independent of msgq</t>
+          </r>
         </is>
       </c>
       <c r="O128" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P128" s="33" t="inlineStr"/>
@@ -28762,7 +28790,7 @@
       <c r="R128" s="39" t="inlineStr"/>
       <c r="S128" s="39" t="inlineStr"/>
     </row>
-    <row r="129" ht="87" customHeight="1">
+    <row r="129" ht="195" customHeight="1">
       <c r="A129" s="42" t="n"/>
       <c r="B129" s="42" t="n"/>
       <c r="C129" s="42" t="n"/>
@@ -28841,11 +28869,39 @@
             </rPr>
             <t>Run the msgq tests in LionDriver CI and assess whether a payload checksum or a lost-message counter is needed for the safety-relevant services (selfdriveState, carControl, sendcan, pandaStates)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-075 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>msgq protection for the control and supervision topics (WP-A-03 DFI-29): sequence or E2E protection so a skipped or altered message is detected, a subscriber-count guard so a 16th reader cannot evict the others, and host supervision of control credited only where it is independent of msgq</t>
+          </r>
         </is>
       </c>
       <c r="O129" s="53" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P129" s="43" t="inlineStr"/>
@@ -29367,7 +29423,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only</t>
+            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only. WP-A-03 DFI-25</t>
           </r>
         </is>
       </c>
@@ -29605,7 +29661,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only</t>
+            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only. WP-A-03 DFI-25</t>
           </r>
         </is>
       </c>
@@ -30109,11 +30165,39 @@
             </rPr>
             <t>Demo-mode interlock (TSR-610): selfdrived refuses engagement while IsDriverViewEnabled is set and raises a fault if it is set while engaged; the UI clears the parameter on the onroad transition; dmonitoringd ignores demo mode while started. Add a test with the item started</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-076 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>One publisher per control topic, enforced at subscribe time (WP-A-03 DFI-31): the comma four cabin-camera dialog must not publish selfdriveState, and the dialog is closed before the item goes onroad</t>
+          </r>
         </is>
       </c>
       <c r="O134" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P134" s="33" t="inlineStr"/>
@@ -30221,7 +30305,7 @@
       <c r="R135" s="48" t="inlineStr"/>
       <c r="S135" s="48" t="inlineStr"/>
     </row>
-    <row r="136" ht="141" customHeight="1">
+    <row r="136" ht="154.5" customHeight="1">
       <c r="A136" s="30" t="inlineStr">
         <is>
           <r>
@@ -30449,7 +30533,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd</t>
+            <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd, and do not route the terminal reaction through plannerd alone (WP-A-03 DFI-33)</t>
           </r>
         </is>
       </c>
@@ -30463,7 +30547,7 @@
       <c r="R136" s="39" t="inlineStr"/>
       <c r="S136" s="39" t="inlineStr"/>
     </row>
-    <row r="137" ht="208.5" customHeight="1">
+    <row r="137" ht="235.5" customHeight="1">
       <c r="A137" s="42" t="n"/>
       <c r="B137" s="42" t="n"/>
       <c r="C137" s="42" t="n"/>
@@ -30558,7 +30642,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-365, which absorbed DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
           </r>
           <r>
             <rPr>
@@ -30585,7 +30669,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd</t>
+            <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd, and do not route the terminal reaction through plannerd alone (WP-A-03 DFI-33)</t>
           </r>
         </is>
       </c>
@@ -30854,7 +30938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -31981,7 +32065,7 @@
       <c r="H28" s="61" t="inlineStr"/>
       <c r="I28" s="61" t="inlineStr"/>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29" ht="87" customHeight="1">
       <c r="A29" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-036</t>
@@ -31994,7 +32078,7 @@
       </c>
       <c r="C29" s="61" t="inlineStr">
         <is>
-          <t>Rank soft and immediate disable takeover alerts above every WARNING and PERMANENT alert except FCW, keep the takeover sound when an AEB alert is shown, name the fault class in the text (canError, TSR-606), and add a test of the ordering</t>
+          <t>Rank soft and immediate disable takeover alerts above every WARNING and PERMANENT alert except FCW, keep the takeover sound when an AEB alert is shown, name the fault class in the text (canError, TSR-606), and add a test of the ordering. Rank the driver-monitoring level 2 and 3 alerts so that speedTooHigh or a later-starting HIGH alert cannot mask them (WP-A-03 DFI-25, SWF-035)</t>
         </is>
       </c>
       <c r="D29" s="61" t="inlineStr">
@@ -32830,7 +32914,7 @@
       </c>
       <c r="C51" s="61" t="inlineStr">
         <is>
-          <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays)</t>
+          <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
         </is>
       </c>
       <c r="D51" s="61" t="inlineStr">
@@ -32870,7 +32954,7 @@
       </c>
       <c r="C52" s="61" t="inlineStr">
         <is>
-          <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+          <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-365, which absorbed DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
         </is>
       </c>
       <c r="D52" s="61" t="inlineStr">
@@ -33092,7 +33176,7 @@
       </c>
       <c r="C58" s="61" t="inlineStr">
         <is>
-          <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22)</t>
+          <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
         </is>
       </c>
       <c r="D58" s="61" t="inlineStr">
@@ -33276,7 +33360,7 @@
       </c>
       <c r="C63" s="61" t="inlineStr">
         <is>
-          <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only</t>
+          <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only. WP-A-03 DFI-25</t>
         </is>
       </c>
       <c r="D63" s="61" t="inlineStr">
@@ -33370,7 +33454,7 @@
       <c r="H65" s="61" t="inlineStr"/>
       <c r="I65" s="61" t="inlineStr"/>
     </row>
-    <row r="66" ht="73.5" customHeight="1">
+    <row r="66" ht="87" customHeight="1">
       <c r="A66" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-073</t>
@@ -33383,7 +33467,7 @@
       </c>
       <c r="C66" s="61" t="inlineStr">
         <is>
-          <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd</t>
+          <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd, and do not route the terminal reaction through plannerd alone (WP-A-03 DFI-33)</t>
         </is>
       </c>
       <c r="D66" s="61" t="inlineStr">
@@ -33406,8 +33490,79 @@
       <c r="H66" s="61" t="inlineStr"/>
       <c r="I66" s="61" t="inlineStr"/>
     </row>
+    <row r="67" ht="73.5" customHeight="1">
+      <c r="A67" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-075</t>
+        </is>
+      </c>
+      <c r="B67" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C67" s="61" t="inlineStr">
+        <is>
+          <t>msgq protection for the control and supervision topics (WP-A-03 DFI-29): sequence or E2E protection so a skipped or altered message is detected, a subscriber-count guard so a 16th reader cannot evict the others, and host supervision of control credited only where it is independent of msgq</t>
+        </is>
+      </c>
+      <c r="D67" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E67" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F67" s="61" t="inlineStr">
+        <is>
+          <t>SWF-080.C1
+SWF-080.C2</t>
+        </is>
+      </c>
+      <c r="G67" s="61" t="inlineStr"/>
+      <c r="H67" s="61" t="inlineStr"/>
+      <c r="I67" s="61" t="inlineStr"/>
+    </row>
+    <row r="68" ht="46.5" customHeight="1">
+      <c r="A68" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-076</t>
+        </is>
+      </c>
+      <c r="B68" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C68" s="61" t="inlineStr">
+        <is>
+          <t>One publisher per control topic, enforced at subscribe time (WP-A-03 DFI-31): the comma four cabin-camera dialog must not publish selfdriveState, and the dialog is closed before the item goes onroad</t>
+        </is>
+      </c>
+      <c r="D68" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E68" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F68" s="61" t="inlineStr">
+        <is>
+          <t>SWF-085.C1</t>
+        </is>
+      </c>
+      <c r="G68" s="61" t="inlineStr"/>
+      <c r="H68" s="61" t="inlineStr"/>
+      <c r="I68" s="61" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I66"/>
+  <autoFilter ref="A1:I68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$140</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.2 · draft</t>
+          <t>1.3 · draft</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>68 (64)</t>
+          <t>69 (64)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S138"/>
+  <dimension ref="A1:S140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12512,7 +12512,7 @@
       <c r="R49" s="39" t="inlineStr"/>
       <c r="S49" s="39" t="inlineStr"/>
     </row>
-    <row r="50" ht="168" customHeight="1">
+    <row r="50" ht="154.5" customHeight="1">
       <c r="A50" s="40" t="n"/>
       <c r="B50" s="40" t="n"/>
       <c r="C50" s="40" t="n"/>
@@ -12568,7 +12568,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_supervision.py: TxBlockedMonitor baseline, rise while engaged and panda-reset tests. NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted, not proven by mutation; the txRateExceeded and heartbeatLost branches in selfdrived.py have no test</t>
+            <t>• test_supervision.py: TxBlockedMonitor baseline, rise while engaged and panda-reset tests. Not run in CI at BL-005 (plain classes, collected as 0 tests; passed by hand 2026-10-16); run in CI since #179 (487d4ef, SWF-ACT-055). Targeted, not proven by mutation; the txRateExceeded and heartbeatLost branches in selfdrived.py have no test</t>
           </r>
           <r>
             <rPr>
@@ -13359,7 +13359,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_supervision.py (13 tests: consecutive samples, single-sample absorption, 0.5 s bound with stale samples, engagement grace). NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted at the cause, not proven by mutation</t>
+            <t>• test_supervision.py (13 tests: consecutive samples, single-sample absorption, 0.5 s bound with stale samples, engagement grace). Not run in CI at BL-005 (plain classes, collected as 0 tests; passed by hand 2026-10-16); run in CI since #179 (487d4ef, SWF-ACT-055). Targeted at the cause, not proven by mutation</t>
           </r>
           <r>
             <rPr>
@@ -13460,7 +13460,7 @@
         <is>
           <t>open
 in progress
-open</t>
+in progress</t>
         </is>
       </c>
       <c r="P54" s="33" t="inlineStr">
@@ -15528,7 +15528,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_input_freshness.py (6 tests: bound per service, wall clock for selfdriveState, inputs not yet seen). NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted at the gate logic, not proven by mutation; no test stops selfdrived while engaged</t>
+            <t>• test_input_freshness.py (6 tests: bound per service, wall clock for selfdriveState, inputs not yet seen). Not run in CI at BL-005 (plain classes, collected as 0 tests; passed by hand 2026-10-16); run in CI since #179 (487d4ef, SWF-ACT-055). Targeted at the gate logic, not proven by mutation; no test stops selfdrived while engaged</t>
           </r>
           <r>
             <rPr>
@@ -16698,7 +16698,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_input_freshness.py (bound per service on the log clock). NOT run in CI: plain pytest-style classes, which tools/test_runner.py (unittest) collects as 0 tests; pass when run by hand at BL-005 (2026-10-16) (SWF-ACT-055). Targeted at the gate, not proven by mutation. No test stops modeld or plannerd while engaged</t>
+            <t>• test_input_freshness.py (bound per service on the log clock). Not run in CI at BL-005 (plain classes, collected as 0 tests; passed by hand 2026-10-16); run in CI since #179 (487d4ef, SWF-ACT-055). Targeted at the gate, not proven by mutation. No test stops modeld or plannerd while engaged</t>
           </r>
           <r>
             <rPr>
@@ -22909,7 +22909,7 @@
       <c r="R98" s="48" t="inlineStr"/>
       <c r="S98" s="48" t="inlineStr"/>
     </row>
-    <row r="99" ht="114" customHeight="1">
+    <row r="99" ht="154.5" customHeight="1">
       <c r="A99" s="49" t="inlineStr">
         <is>
           <r>
@@ -23071,7 +23071,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>By design the six driver-monitoring events are PERMANENT alerts only, with no SOFT_DISABLE or IMMEDIATE_DISABLE (events.py:524-570); the terminal reaction is the forced deceleration with lateral control kept. Whether that is the SG-010 safe state of FSR-040 is not recorded; it is queued for the lead (DQ-365, which absorbed DQ-220)</t>
+            <t>By design the six driver-monitoring events are PERMANENT alerts only, with no SOFT_DISABLE or IMMEDIATE_DISABLE (events.py:524-570); the terminal reaction is the forced deceleration with lateral control kept. The SG-010 safe state is decided (DQ-365 A, which absorbed DQ-220; TSR-633) as stop in lane, stay stopped and held, re-engagement locked out until the driver responds. The code does not hold at standstill or lock out until a later disengagement (TSR-633 not met)</t>
           </r>
         </is>
       </c>
@@ -23083,7 +23083,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream design; FSR-040 names a safe state that the FSC does not define for this path. Requirements not documented and no field-exposure evidence cited, so O 8 (RT-2 §2), as SWF-083.C1 and SFM-025.C1</t>
+            <t>• Upstream design; the safe state is now defined (TSR-633, DQ-365 A) but not implemented. No field-exposure evidence cited, so O 8 (RT-2 §2), as SWF-083.C1 and SFM-025.C1</t>
           </r>
           <r>
             <rPr>
@@ -23146,13 +23146,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-365, which absorbed DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
-          </r>
-        </is>
-      </c>
-      <c r="O99" s="59" t="inlineStr">
-        <is>
-          <t>decision pending</t>
+            <t>Implement the SG-010 safe state decided in DQ-365 (A, which absorbed DQ-220; TSR-633): after the forced deceleration keep the vehicle stopped and held and lock out re-engagement and resumption until the driver responds; add a terminal-alert test that checks standstill, hold and lockout</t>
+          </r>
+        </is>
+      </c>
+      <c r="O99" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
         </is>
       </c>
       <c r="P99" s="43" t="inlineStr"/>
@@ -30547,7 +30547,7 @@
       <c r="R136" s="39" t="inlineStr"/>
       <c r="S136" s="39" t="inlineStr"/>
     </row>
-    <row r="137" ht="235.5" customHeight="1">
+    <row r="137" ht="262.5" customHeight="1">
       <c r="A137" s="42" t="n"/>
       <c r="B137" s="42" t="n"/>
       <c r="C137" s="42" t="n"/>
@@ -30642,7 +30642,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-365, which absorbed DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+            <t>Implement the SG-010 safe state decided in DQ-365 (A, which absorbed DQ-220; TSR-633): after the forced deceleration keep the vehicle stopped and held and lock out re-engagement and resumption until the driver responds; add a terminal-alert test that checks standstill, hold and lockout</t>
           </r>
           <r>
             <rPr>
@@ -30673,9 +30673,9 @@
           </r>
         </is>
       </c>
-      <c r="O137" s="59" t="inlineStr">
-        <is>
-          <t>decision pending
+      <c r="O137" s="53" t="inlineStr">
+        <is>
+          <t>open
 open</t>
         </is>
       </c>
@@ -30926,9 +30926,367 @@
       <c r="R138" s="48" t="inlineStr"/>
       <c r="S138" s="48" t="inlineStr"/>
     </row>
+    <row r="139" ht="127.5" customHeight="1">
+      <c r="A139" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-054
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>card main loop and stock AEB interlock</t>
+          </r>
+        </is>
+      </c>
+      <c r="B139" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-055
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Raise the EPS-fault warning while engaged (TSR-607); the take-over request, with the lighter prompt only for the first 1.5 s after an override or at standstill, and at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering</t>
+          </r>
+        </is>
+      </c>
+      <c r="C139" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver not prompted to take over while lateral control is lost; lane departure (counterpart of SFM-038.C1)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The item stays engaged with lateral assist lost; the envelope refuses lateral frames (EPS-fault refusal, reference build) and the panda siren sounds after about 1 s of a persistent fault while authority is granted</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>steerTempUnavailableSilent (LOW priority, small alert with prompt chime, no soft disable; events.py:516-521) instead of steerTempUnavailable (soft disable), or no EPS event at all while the driver keeps steering</t>
+          </r>
+        </is>
+      </c>
+      <c r="D139" s="31" t="inlineStr">
+        <is>
+          <t>HZ-004</t>
+        </is>
+      </c>
+      <c r="E139" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F139" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-088 · late
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>EPS-fault warning held at the low-priority prompt, or not given, for the whole of a temporary EPS fault while engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="G139" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H139" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design at BL-005, after a steering override in the last 1.5 s or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent and silent_steer_warning stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; TSR-607 (b), DQ-342 A; GAP-03)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I139" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot design (a softer alert after an override); TSR-607 (b) not implemented at BL-005, so O 8 (RT-2 §2), as the other by-design gaps</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/car_events.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J139" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K139" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test of the EPS-fault events at BL-005</t>
+          </r>
+        </is>
+      </c>
+      <c r="L139" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M139" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N139" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-077 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate the EPS-fault warning per TSR-607 (DQ-342 A, DQ-366 A): allow steerTempUnavailableSilent only for the first 1.5 s of the fault (steer_fault_frames, STEER_FAULT_SILENT_FRAMES), then the take-over request; give at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering; unit tests</t>
+          </r>
+        </is>
+      </c>
+      <c r="O139" s="56" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P139" s="33" t="inlineStr">
+        <is>
+          <t>10/3/8</t>
+        </is>
+      </c>
+      <c r="Q139" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R139" s="39" t="inlineStr"/>
+      <c r="S139" s="39" t="inlineStr"/>
+    </row>
+    <row r="140" ht="127.5" customHeight="1">
+      <c r="A140" s="42" t="n"/>
+      <c r="B140" s="42" t="n"/>
+      <c r="C140" s="42" t="n"/>
+      <c r="D140" s="42" t="n"/>
+      <c r="E140" s="42" t="n"/>
+      <c r="F140" s="42" t="n"/>
+      <c r="G140" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H140" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design at BL-005, a temporary EPS fault that starts while the driver is steering raises no EPS event while they keep steering (no_steer_warning, car_events.py:164-166); the take-over request follows only on release (TSR-607 (c), DQ-366 A)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I140" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot design; TSR-607 (c) not implemented at BL-005, so O 8 (RT-2 §2)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/car_events.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J140" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K140" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test of the EPS-fault events at BL-005</t>
+          </r>
+        </is>
+      </c>
+      <c r="L140" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M140" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N140" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-077 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate the EPS-fault warning per TSR-607 (DQ-342 A, DQ-366 A): allow steerTempUnavailableSilent only for the first 1.5 s of the fault (steer_fault_frames, STEER_FAULT_SILENT_FRAMES), then the take-over request; give at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering; unit tests</t>
+          </r>
+        </is>
+      </c>
+      <c r="O140" s="47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P140" s="43" t="inlineStr">
+        <is>
+          <t>10/3/8</t>
+        </is>
+      </c>
+      <c r="Q140" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R140" s="48" t="inlineStr"/>
+      <c r="S140" s="48" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S138"/>
-  <mergeCells count="226">
+  <autoFilter ref="A2:S140"/>
+  <mergeCells count="232">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="E92:E93"/>
     <mergeCell ref="B124:B126"/>
@@ -30993,6 +31351,7 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="A90:A91"/>
     <mergeCell ref="F49:F51"/>
+    <mergeCell ref="D139:D140"/>
     <mergeCell ref="E128:E129"/>
     <mergeCell ref="C100:C101"/>
     <mergeCell ref="F116:F118"/>
@@ -31002,7 +31361,9 @@
     <mergeCell ref="A96:A98"/>
     <mergeCell ref="C96:C98"/>
     <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A139:A140"/>
     <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C139:C140"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="B76:B78"/>
     <mergeCell ref="B3:B5"/>
@@ -31049,6 +31410,7 @@
     <mergeCell ref="F96:F98"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F139:F140"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="E69:E70"/>
     <mergeCell ref="E76:E78"/>
@@ -31087,6 +31449,7 @@
     <mergeCell ref="E134:E135"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E139:E140"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="B116:B118"/>
     <mergeCell ref="E87:E89"/>
@@ -31131,6 +31494,7 @@
     <mergeCell ref="E45:E46"/>
     <mergeCell ref="D96:D98"/>
     <mergeCell ref="A103:A105"/>
+    <mergeCell ref="B139:B140"/>
     <mergeCell ref="C103:C105"/>
     <mergeCell ref="D58:D59"/>
     <mergeCell ref="F58:F59"/>
@@ -31157,7 +31521,7 @@
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138 R139 R140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -31165,7 +31529,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.2 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.3 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -31180,7 +31544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -33013,7 +33377,7 @@
       </c>
       <c r="E47" s="61" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F47" s="61" t="inlineStr">
@@ -33023,7 +33387,11 @@
       </c>
       <c r="G47" s="61" t="inlineStr"/>
       <c r="H47" s="61" t="inlineStr"/>
-      <c r="I47" s="61" t="inlineStr"/>
+      <c r="I47" s="61" t="inlineStr">
+        <is>
+          <t>Run in CI: #179 (487d4ef, 2026-10-17) derives both from unittest.TestCase; the unit_tests job of tests run 38991473673 reports 1555 passed (1535 before: 19 newly collected and 1 new EPS test). Mutation proof not done, so D stays 8</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="73.5" customHeight="1">
       <c r="A48" s="61" t="inlineStr">
@@ -33183,7 +33551,7 @@
       <c r="H51" s="61" t="inlineStr"/>
       <c r="I51" s="61" t="inlineStr"/>
     </row>
-    <row r="52" ht="46.5" customHeight="1">
+    <row r="52" ht="73.5" customHeight="1">
       <c r="A52" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-059</t>
@@ -33196,7 +33564,7 @@
       </c>
       <c r="C52" s="61" t="inlineStr">
         <is>
-          <t>Define the SG-010 safe state for FSR-040 (lead decision DQ-365, which absorbed DQ-220) and, if it differs from the current forced deceleration with lateral kept, implement it with a terminal-alert test</t>
+          <t>Implement the SG-010 safe state decided in DQ-365 (A, which absorbed DQ-220; TSR-633): after the forced deceleration keep the vehicle stopped and held and lock out re-engagement and resumption until the driver responds; add a terminal-alert test that checks standstill, hold and lockout</t>
         </is>
       </c>
       <c r="D52" s="61" t="inlineStr">
@@ -33206,7 +33574,7 @@
       </c>
       <c r="E52" s="61" t="inlineStr">
         <is>
-          <t>decision pending</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F52" s="61" t="inlineStr">
@@ -33838,8 +34206,56 @@
       <c r="H69" s="61" t="inlineStr"/>
       <c r="I69" s="61" t="inlineStr"/>
     </row>
+    <row r="70" ht="100.5" customHeight="1">
+      <c r="A70" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-077</t>
+        </is>
+      </c>
+      <c r="B70" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C70" s="61" t="inlineStr">
+        <is>
+          <t>Escalate the EPS-fault warning per TSR-607 (DQ-342 A, DQ-366 A): allow steerTempUnavailableSilent only for the first 1.5 s of the fault (steer_fault_frames, STEER_FAULT_SILENT_FRAMES), then the take-over request; give at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering; unit tests</t>
+        </is>
+      </c>
+      <c r="D70" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E70" s="62" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F70" s="61" t="inlineStr">
+        <is>
+          <t>SWF-088.C1
+SWF-088.C2</t>
+        </is>
+      </c>
+      <c r="G70" s="61" t="inlineStr">
+        <is>
+          <t>10/3/8</t>
+        </is>
+      </c>
+      <c r="H70" s="63" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I70" s="61" t="inlineStr">
+        <is>
+          <t>#174 (7158a9a) and #179 (487d4ef): openpilot/selfdrive/car/car_events.py:17, 169-187; openpilot/selfdrive/car/tests/test_steer_fault_warning.py (7 tests, unittest, collected by the unit_tests job); impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Implemented and unit-tested after BL-005, not verified on the vehicle and not proven by mutation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I69"/>
+  <autoFilter ref="A1:I70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34909,7 +35325,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="33" customHeight="1">
+    <row r="41" ht="73.5" customHeight="1">
       <c r="A41" s="61" t="inlineStr">
         <is>
           <t>SWF-SE-054</t>
@@ -34932,7 +35348,8 @@
       </c>
       <c r="E41" s="61" t="inlineStr">
         <is>
-          <t>SWF-FN-054: Run the car interface every CAN cycle, publish carState, and actuate only the latest carControl</t>
+          <t>SWF-FN-054: Run the car interface every CAN cycle, publish carState, and actuate only the latest carControl
+SWF-FN-055: Raise the EPS-fault warning while engaged (TSR-607); the take-over request, with the lighter prompt only for the first 1.5 s after an override or at standstill, and at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering</t>
         </is>
       </c>
     </row>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$142</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.3 · draft</t>
+          <t>1.4 · draft</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-005</t>
+          <t>BL-006</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="195" customHeight="1">
+    <row r="10" ht="210" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
@@ -865,7 +865,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>P1 elements for AC-001 at BL-005 (liondriver-dev 1033d98, panda a55bdfc, opendbc 9a13f60; the LIONDRIVER_REFERENCE build is the default): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071). P3 elements: modeld as a software element (SWF-072..074; model performance is SOTIF), localization and calibration (SWF-075..077), camerad (SWF-078), sensord (SWF-079), messaging (SWF-080, SWF-081), manager (SWF-082, SWF-083), updated (SWF-084). Rev 1.1: driver-monitoring demo mode (SWF-085) and the forced stop after the terminal alert (SWF-086), for FTA finding F-37. Rev 1.2: no driver-override check on the LKA path in the envelope (SWF-087), for F-28.</t>
+          <t>P1 elements for AC-001 at BL-006 (proposed; liondriver-dev c61e31b, panda 0a7da85, opendbc 62b89a3; the LIONDRIVER_REFERENCE build is the default; rows of code unchanged since BL-005 keep their BL-005 ratings): panda safety model (opendbc safety core, Toyota mode, panda firmware integration incl. hardware watchdog, SWF-001..019, SWF-054, SWF-055), pandad (SWF-020..029), selfdrived (SWF-030..039), controlsd with the Toyota CarController hand-off (SWF-040..053). P2 elements: card and the Toyota port (SWF-056..060), driver monitoring (SWF-061..064), plannerd (SWF-065..069), radard (SWF-070, SWF-071). P3 elements: modeld as a software element (SWF-072..074; model performance is SOTIF), localization and calibration (SWF-075..077), camerad (SWF-078), sensord (SWF-079), messaging (SWF-080, SWF-081), manager (SWF-082, SWF-083), updated (SWF-084). Rev 1.1: driver-monitoring demo mode (SWF-085) and the forced stop after the terminal alert (SWF-086), for FTA finding F-37. Rev 1.2: no driver-override check on the LKA path in the envelope (SWF-087), for F-28.</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>69 (64)</t>
+          <t>70 (64)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S140"/>
+  <dimension ref="A1:S142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20238,7 +20238,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>By design at BL-005: rx_checks_allow_engagement looks only at the RX checks (safety.h:405-416); a TX-rate revocation (safety.h:279-282) sets the report flag but no engagement block. Decision DQ-079 (answered, option A) amended SWSR-518: no re-grant until one full 250 ms window without a rejected frame. The code is jherrodthomas/opendbc#15 (ATC-20), merged in the fork, not in the BL-005 pin</t>
+            <t>Defect in the TX-rate engagement block: rx_checks_allow_engagement must refuse a grant until one full 250 ms window passes without a rejected frame after a TX-rate revocation (SWSR-518 amended per DQ-079). Implemented in the reference build by opendbc#15 (ATC-20, a0938fa), in the pin since BL-006</t>
           </r>
         </is>
       </c>
@@ -20250,7 +20250,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Requirement amended (WP-W-02 SWSR-518, DQ-079); implementation not pinned</t>
+            <t>• Requirement amended (WP-W-02 SWSR-518, DQ-079) and implemented in the reference build; MISRA C:2012 in CI in both variants</t>
           </r>
           <r>
             <rPr>
@@ -20264,17 +20264,17 @@
         </is>
       </c>
       <c r="J85" s="45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K85" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• The reference model (SM-TOY-AUTH) follows the amended requirement and records the pinned C as deviation tx_rate_regrant; the back-to-back gate tolerates the deviation until the pin moves, so it does not fail on this cause. test_tx_rate_no_reengagement_while_excess_persists exists only in opendbc#15</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_tx_rate_no_reengagement_while_excess_persists (test_toyota.py), run with 100 % line coverage and mutation in the reference variant in CI (safety.yaml mutation_reference); the back-to-back model checks the requirement with the tx_rate_regrant deviation removed (B2B-TOY-AUTH §11). Not on target</t>
           </r>
           <r>
             <rPr>
@@ -20283,16 +20283,16 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/05-software/reference-models</t>
-          </r>
-        </is>
-      </c>
-      <c r="L85" s="54" t="n">
-        <v>9</v>
-      </c>
-      <c r="M85" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L85" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M85" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="N85" s="44" t="inlineStr">
@@ -20317,9 +20317,9 @@
           </r>
         </is>
       </c>
-      <c r="O85" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O85" s="47" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="P85" s="43" t="inlineStr">
@@ -20524,7 +20524,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>By design at BL-005: SWSR-311 resets all edge state on a mode change (safety.h:589) and SWSR-301 grants on a rising edge (safety.h:683-701); the back-to-back test found that the reset makes a held CRUISE_ACTIVE count as a new edge (B2B-06, scenario D19b). Decision DQ-080 (answered, option A): require cruise off and on again; SWSR-311 amended. The code is jherrodthomas/opendbc#15 (ATC-26, pcm_cruise_seen_disengaged), merged in the fork, not in the BL-005 pin</t>
+            <t>Defect in the mode-set edge rule: after a safety-mode change a rising edge must count only after CRUISE_ACTIVE = 0 has been received (SWSR-311 amended per DQ-080, pcm_cruise_seen_disengaged). Implemented in the reference build by opendbc#15 (ATC-26, 3ed789a), in the pin since BL-006</t>
           </r>
         </is>
       </c>
@@ -20536,7 +20536,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Requirement amended (WP-W-02 SWSR-311, DQ-080); implementation not pinned. In the reference build only TOYOTA can be active (safety-mode lock), so the path is a mode re-set to the same mode</t>
+            <t>• Requirement amended (WP-W-02 SWSR-311, DQ-080) and implemented in the reference build; in the reference build only TOYOTA can be active (safety-mode lock), so the path is a mode re-set to the same mode</t>
           </r>
           <r>
             <rPr>
@@ -20550,17 +20550,17 @@
         </is>
       </c>
       <c r="J86" s="45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K86" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Back-to-back reference model: scenario D19b reproduces the finding; the deviation mode_set_regrant is tolerated until the pin moves, so the gate does not fail on it. test_no_grant_after_mode_set_without_new_engagement exists only in opendbc#15</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_no_grant_after_mode_set_without_new_engagement (test_toyota.py), run with 100 % line coverage and mutation in the reference variant in CI; back-to-back scenario D19b with the mode_set_regrant deviation removed (B2B-TOY-AUTH §11). Not on target</t>
           </r>
           <r>
             <rPr>
@@ -20569,16 +20569,16 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/05-software/reference-models</t>
-          </r>
-        </is>
-      </c>
-      <c r="L86" s="54" t="n">
-        <v>9</v>
-      </c>
-      <c r="M86" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L86" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M86" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="N86" s="44" t="inlineStr">
@@ -20603,9 +20603,9 @@
           </r>
         </is>
       </c>
-      <c r="O86" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O86" s="47" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="P86" s="43" t="inlineStr">
@@ -21462,7 +21462,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Short frames are not rejected: the parser skips only frames over 64 bytes and reads missing bytes as 0 (parser.py:219, dbc.py:66), so a truncated BRAKE_MODULE reads BRAKE_PRESSED = 0 with no checksum to catch it. The panda-side length fault is proposed, not implemented (change-2026-10-13-opendbc-rx-length-fault)</t>
+            <t>Short frames are not rejected: the parser skips only frames over 64 bytes and reads missing bytes as 0 (parser.py:219, dbc.py:66), so a truncated BRAKE_MODULE reads BRAKE_PRESSED = 0 with no checksum to catch it. Host code unchanged at BL-006; the panda-side length fault is implemented in the reference build since BL-006 (opendbc#18, a safety mechanism of SWF-057)</t>
           </r>
         </is>
       </c>
@@ -30926,7 +30926,7 @@
       <c r="R138" s="48" t="inlineStr"/>
       <c r="S138" s="48" t="inlineStr"/>
     </row>
-    <row r="139" ht="127.5" customHeight="1">
+    <row r="139" ht="249" customHeight="1">
       <c r="A139" s="30" t="inlineStr">
         <is>
           <r>
@@ -31088,7 +31088,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>By design at BL-005, after a steering override in the last 1.5 s or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent and silent_steer_warning stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; TSR-607 (b), DQ-342 A; GAP-03)</t>
+            <t>Defect in the EPS-fault escalation: after a steering override in the last 1.5 s or at standstill, steerTempUnavailableSilent is allowed only while steer_fault_frames &lt;= STEER_FAULT_SILENT_FRAMES (1.5 s), then steerTempUnavailable (car_events.py:17, 169-187; TSR-607 (b), DQ-342 A, #174). At BL-005 the silent warning stayed latched for the whole fault (GAP-03)</t>
           </r>
         </is>
       </c>
@@ -31100,7 +31100,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream openpilot design (a softer alert after an override); TSR-607 (b) not implemented at BL-005, so O 8 (RT-2 §2), as the other by-design gaps</t>
+            <t>• LionDriver change to upstream code with a requirement (TSR-607 (b)) and targeted unit tests; reviewed in the PR, not independently; O 5 as the other new host code with targeted tests (SWF-034.C1)</t>
           </r>
           <r>
             <rPr>
@@ -31109,28 +31109,37 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/car/car_events.py</t>
+   assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md</t>
           </r>
         </is>
       </c>
       <c r="J139" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K139" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_steer_fault_warning.py (7 unittest tests, collected by the unit_tests job); targeted at the escalation, not proven by mutation (D 8 at best, RT-2), not on the vehicle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/tests/test_steer_fault_warning.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L139" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="K139" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test of the EPS-fault events at BL-005</t>
-          </r>
-        </is>
-      </c>
-      <c r="L139" s="36" t="n">
-        <v>10</v>
-      </c>
       <c r="M139" s="37" t="inlineStr">
         <is>
           <t>H</t>
@@ -31156,27 +31165,57 @@
             </rPr>
             <t>Escalate the EPS-fault warning per TSR-607 (DQ-342 A, DQ-366 A): allow steerTempUnavailableSilent only for the first 1.5 s of the fault (steer_fault_frames, STEER_FAULT_SILENT_FRAMES), then the take-over request; give at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering; unit tests</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-078 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Prove the EPS-fault warning tests: mutate the escalation in car_events.py (the STEER_FAULT_SILENT_FRAMES comparisons, the silent_steer_warning latch and the steering-held branch) and show test_steer_fault_warning.py fails on each mutant, in CI, so D can drop to 4 (System FMEA SFM-ACT-023 points to the same run)</t>
+          </r>
         </is>
       </c>
       <c r="O139" s="56" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>completed
+open</t>
         </is>
       </c>
       <c r="P139" s="33" t="inlineStr">
         <is>
-          <t>10/3/8</t>
-        </is>
-      </c>
-      <c r="Q139" s="37" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>10/5/8
+10/5/4</t>
+        </is>
+      </c>
+      <c r="Q139" s="33" t="inlineStr">
+        <is>
+          <t>H
+H</t>
         </is>
       </c>
       <c r="R139" s="39" t="inlineStr"/>
       <c r="S139" s="39" t="inlineStr"/>
     </row>
-    <row r="140" ht="127.5" customHeight="1">
+    <row r="140" ht="249" customHeight="1">
       <c r="A140" s="42" t="n"/>
       <c r="B140" s="42" t="n"/>
       <c r="C140" s="42" t="n"/>
@@ -31196,7 +31235,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>By design at BL-005, a temporary EPS fault that starts while the driver is steering raises no EPS event while they keep steering (no_steer_warning, car_events.py:164-166); the take-over request follows only on release (TSR-607 (c), DQ-366 A)</t>
+            <t>Defect in the EPS-fault prompt while the driver keeps steering: after 1.5 s of a fault that started while steering, steerTempUnavailableSilent is raised until release, then the take-over request (car_events.py:169-176; TSR-607 (c), DQ-366 A, f350f5b). At BL-005 no event was raised while steering</t>
           </r>
         </is>
       </c>
@@ -31208,7 +31247,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream openpilot design; TSR-607 (c) not implemented at BL-005, so O 8 (RT-2 §2)</t>
+            <t>• LionDriver change to upstream code with a requirement (TSR-607 (c)) and a targeted unit test; reviewed in the PR, not independently; O 5</t>
           </r>
           <r>
             <rPr>
@@ -31222,23 +31261,32 @@
         </is>
       </c>
       <c r="J140" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K140" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_steer_fault_warning.py (the steering-held case), collected by the unit_tests job; not proven by mutation, not on the vehicle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/tests/test_steer_fault_warning.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L140" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="K140" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test of the EPS-fault events at BL-005</t>
-          </r>
-        </is>
-      </c>
-      <c r="L140" s="54" t="n">
-        <v>10</v>
-      </c>
       <c r="M140" s="52" t="inlineStr">
         <is>
           <t>H</t>
@@ -31264,28 +31312,537 @@
             </rPr>
             <t>Escalate the EPS-fault warning per TSR-607 (DQ-342 A, DQ-366 A): allow steerTempUnavailableSilent only for the first 1.5 s of the fault (steer_fault_frames, STEER_FAULT_SILENT_FRAMES), then the take-over request; give at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering; unit tests</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-078 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Prove the EPS-fault warning tests: mutate the escalation in car_events.py (the STEER_FAULT_SILENT_FRAMES comparisons, the silent_steer_warning latch and the steering-held branch) and show test_steer_fault_warning.py fails on each mutant, in CI, so D can drop to 4 (System FMEA SFM-ACT-023 points to the same run)</t>
+          </r>
         </is>
       </c>
       <c r="O140" s="47" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>completed
+open</t>
         </is>
       </c>
       <c r="P140" s="43" t="inlineStr">
         <is>
-          <t>10/3/8</t>
-        </is>
-      </c>
-      <c r="Q140" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>10/5/8
+10/5/4</t>
+        </is>
+      </c>
+      <c r="Q140" s="43" t="inlineStr">
+        <is>
+          <t>H
+H</t>
         </is>
       </c>
       <c r="R140" s="48" t="inlineStr"/>
       <c r="S140" s="48" t="inlineStr"/>
     </row>
+    <row r="141" ht="154.5" customHeight="1">
+      <c r="A141" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Controls-allowed logic</t>
+          </r>
+        </is>
+      </c>
+      <c r="B141" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-004
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Allow controls on rising edge of PCM cruise; withdraw on cruise off, brake press, invalid or lagging safety messages</t>
+          </r>
+        </is>
+      </c>
+      <c r="C141" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Brief actuation without the driver's cruise engagement, from an implausible PCM state</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The item holds authority while main is off until the 150 ms main-off tolerance revokes it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>pcm_engage_pending stays set after toyota_cruise_main_check refuses a CRUISE_ACTIVE edge for MAIN_ON = 0, so a heartbeat-engaged flag within 1 s grants controls_allowed</t>
+          </r>
+        </is>
+      </c>
+      <c r="D141" s="50" t="inlineStr">
+        <is>
+          <t>HZ-010</t>
+        </is>
+      </c>
+      <c r="E141" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-089 · commission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Authority granted while PCM cruise main is off, through an engagement window left open by a refused cruise edge</t>
+          </r>
+        </is>
+      </c>
+      <c r="G141" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H141" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Defect in the reference-build engagement window (LS-06, TSR-301): the window was opened before the MAIN_ON = 0 refusal and not closed by it, against SWSR-405(c). Found by the state-machine charts (SM-F1, #158) after BL-005; fixed by opendbc#17 (032bbef, pcm_engage_cancel), in the pin since BL-006</t>
+          </r>
+        </is>
+      </c>
+      <c r="I141" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Requirement SWSR-405(c); reference-build code with MISRA C:2012 in CI in both variants</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/07-supporting/impact/change-2026-10-17-pin-98d3be1.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J141" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K141" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_main_off_closes_engagement_window (test_toyota.py, both paths and a control case; removing either call fails it), run with 100 % line coverage and mutation in the reference variant in CI. Not on target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L141" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M141" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N141" s="44" t="inlineStr"/>
+      <c r="O141" s="44" t="inlineStr"/>
+      <c r="P141" s="43" t="inlineStr"/>
+      <c r="Q141" s="43" t="inlineStr"/>
+      <c r="R141" s="48" t="inlineStr"/>
+      <c r="S141" s="48" t="inlineStr"/>
+    </row>
+    <row r="142" ht="195" customHeight="1">
+      <c r="A142" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-009
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Relay malfunction detection</t>
+          </r>
+        </is>
+      </c>
+      <c r="B142" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Detect a relay malfunction and block all item transmission</t>
+          </r>
+        </is>
+      </c>
+      <c r="C142" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item and stock camera commands combine on the bus until the malfunction is detected again</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006 (stock ACC and item 0x343 combine on the bus, as SWF-012)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A mode cycle (host request or heartbeat-loss recovery) followed by a quick re-engagement grants authority with the harness relay still faulty</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set_safety_hooks clears relay_malfunction, and stock_ecu_check looks again only after the new mode has run for more than 1 s</t>
+          </r>
+        </is>
+      </c>
+      <c r="D142" s="50" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E142" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F142" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-090 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Relay-malfunction reaction cleared by a safety-mode change before the malfunction is detected again</t>
+          </r>
+        </is>
+      </c>
+      <c r="G142" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H142" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Defect at BL-005 (DFA DM-25): the relay-malfunction reaction lived in opendbc state that a mode change resets. Fixed in the reference build by panda#17 (0a7da85): the reference lock latches a relay malfunction for the ignition cycle and refuses TOYOTA until ignition off, in the pin since BL-006</t>
+          </r>
+        </is>
+      </c>
+      <c r="I142" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Reference lock (TSR-619 family) extended by DFA DM-25; MISRA C:2012 clean in both variants; firmware built with -Werror</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/07-supporting/impact/change-2026-10-17-relay-malfunction-latch.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J142" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K142" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Host unit tests compiled against the real firmware headers, run by panda CI (reference_lock suite, 18 tests, 4 new; 3 fail without the gate). Not on target hardware</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   panda/tests/reference_lock/test_reference_lock.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L142" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M142" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N142" s="44" t="inlineStr"/>
+      <c r="O142" s="44" t="inlineStr"/>
+      <c r="P142" s="43" t="inlineStr"/>
+      <c r="Q142" s="43" t="inlineStr"/>
+      <c r="R142" s="48" t="inlineStr"/>
+      <c r="S142" s="48" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S140"/>
+  <autoFilter ref="A2:S142"/>
   <mergeCells count="232">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="E92:E93"/>
@@ -31521,7 +32078,7 @@
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138 R139 R140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138 R139 R140 R141 R142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -31529,7 +32086,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.3 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.4 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -31544,7 +32101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -33414,9 +33971,9 @@
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E48" s="61" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E48" s="62" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F48" s="61" t="inlineStr">
@@ -33435,7 +33992,11 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I48" s="61" t="inlineStr"/>
+      <c r="I48" s="61" t="inlineStr">
+        <is>
+          <t>Pinned at 515b9a2 (change-2026-10-16-pin-515b9a2), now 62b89a3 in BL-006; impact records change-2026-10-13-tx-rate-reengagement and change-2026-10-14-mode-set-regrant Integrated 2026-10-16; SWF-054.C1 and SWF-055.C1 re-rated at BL-006 (rev 1.4)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="87" customHeight="1">
       <c r="A49" s="61" t="inlineStr">
@@ -34206,7 +34767,7 @@
       <c r="H69" s="61" t="inlineStr"/>
       <c r="I69" s="61" t="inlineStr"/>
     </row>
-    <row r="70" ht="100.5" customHeight="1">
+    <row r="70" ht="114" customHeight="1">
       <c r="A70" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-077</t>
@@ -34240,7 +34801,7 @@
       </c>
       <c r="G70" s="61" t="inlineStr">
         <is>
-          <t>10/3/8</t>
+          <t>10/5/8</t>
         </is>
       </c>
       <c r="H70" s="63" t="inlineStr">
@@ -34250,12 +34811,56 @@
       </c>
       <c r="I70" s="61" t="inlineStr">
         <is>
-          <t>#174 (7158a9a) and #179 (487d4ef): openpilot/selfdrive/car/car_events.py:17, 169-187; openpilot/selfdrive/car/tests/test_steer_fault_warning.py (7 tests, unittest, collected by the unit_tests job); impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Implemented and unit-tested after BL-005, not verified on the vehicle and not proven by mutation</t>
-        </is>
-      </c>
+          <t>#174 (7158a9a) and #179 (487d4ef): openpilot/selfdrive/car/car_events.py:17, 169-187; openpilot/selfdrive/car/tests/test_steer_fault_warning.py (7 tests, unittest, collected by the unit_tests job); impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Implemented and unit-tested after BL-005, not verified on the vehicle and not proven by mutation. Achieved at BL-006: O5 D8 (rev 1.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="73.5" customHeight="1">
+      <c r="A71" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-078</t>
+        </is>
+      </c>
+      <c r="B71" s="61" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C71" s="61" t="inlineStr">
+        <is>
+          <t>Prove the EPS-fault warning tests: mutate the escalation in car_events.py (the STEER_FAULT_SILENT_FRAMES comparisons, the silent_steer_warning latch and the steering-held branch) and show test_steer_fault_warning.py fails on each mutant, in CI, so D can drop to 4 (System FMEA SFM-ACT-023 points to the same run)</t>
+        </is>
+      </c>
+      <c r="D71" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E71" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F71" s="61" t="inlineStr">
+        <is>
+          <t>SWF-088.C1
+SWF-088.C2</t>
+        </is>
+      </c>
+      <c r="G71" s="61" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="H71" s="63" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I71" s="61" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I70"/>
+  <autoFilter ref="A1:I71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -31014,7 +31014,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The item stays engaged with lateral assist lost; the envelope refuses lateral frames (EPS-fault refusal, reference build) and the panda siren sounds after about 1 s of a persistent fault while authority is granted</t>
+            <t>The item stays engaged with lateral assist lost; the envelope refuses lateral frames (EPS-fault refusal, reference build) and the panda siren sounds after about 1 s of a persistent fault while authority is granted (0.7 s since panda bf8102a, DQ-048)</t>
           </r>
           <r>
             <rPr>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -22611,7 +22611,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Timers count frames, not time: one awareness step of DT_DMON = 0.05 s per driverStateV2 message (policy.py:198, 207; dmonitoringd.py:21-23). A model running at 16 Hz still passes the frequency check and stretches the 13 s terminal to about 16 s</t>
+            <t>Timers count frames, not time: one awareness step of DT_DMON = 0.05 s per driverStateV2 message (policy.py:224, 233; dmonitoringd.py:21-23). A model running at 16 Hz still passes the frequency check and stretches the 13 s terminal to about 16 s</t>
           </r>
         </is>
       </c>
@@ -22711,7 +22711,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Defect in the awareness arithmetic, thresholds or recovery factor (1 - T1/T3, 1 - T2/T3, recovery 1.25-5; policy.py:31-47, 196-207, 354-369)</t>
+            <t>Defect in the awareness arithmetic, thresholds or recovery factor (1 - T1/T3, 1 - T2/T3, recovery 1.25-5; policy.py:31-52, 222-233, 383-401)</t>
           </r>
         </is>
       </c>
@@ -22820,7 +22820,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Exemptions reset or hold awareness: below 2.8 m/s awareness is held at the pre-alert level, and under the wheel-touch policy any steering or gas input resets it (policy.py:29, 335, 345, 446). A light accelerator touch satisfies the wheel-touch policy</t>
+            <t>Exemptions reset or hold awareness: below 2.8 m/s awareness is held at the pre-alert level, and under the wheel-touch policy any steering or gas input resets it (policy.py:29, 361, 374, 485). A light accelerator touch satisfies the wheel-touch policy</t>
           </r>
         </is>
       </c>
@@ -23322,7 +23322,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No finiteness or validity check: driverStateV2 is always published valid (dmonitoringmodeld.py:99) and neither process checks for NaN. By code reading a NaN pose with a finite std compares false against the pose thresholds, so the driver counts as attentive (policy.py:228-246); a NaN face probability counts as no face (the conservative direction). Not tested</t>
+            <t>No finiteness or validity check: driverStateV2 is always published valid (dmonitoringmodeld.py:99) and neither process checks for NaN. By code reading a NaN pose with a finite std compares false against the pose thresholds, so the driver counts as attentive (policy.py:254-272); a NaN face probability counts as no face (the conservative direction). Not tested</t>
           </r>
         </is>
       </c>
@@ -23441,7 +23441,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Empty face arrays make _update_states return early, so face_detected and the last pose stay as they were while the event logic runs (policy.py:264-266)</t>
+            <t>Empty face arrays make _update_states return early, so face_detected and the last pose stay as they were while the event logic runs (policy.py:290-292)</t>
           </r>
         </is>
       </c>
@@ -23670,7 +23670,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Unhandled exception: brakeDisengageProbs[0] is read without a length check (policy.py:447); model and warp loading have no error handling (dmonitoringmodeld.py:22-48); no try/except in either loop</t>
+            <t>Unhandled exception: brakeDisengageProbs[0] is read without a length check (policy.py:486); model and warp loading have no error handling (dmonitoringmodeld.py:22-48); no try/except in either loop</t>
           </r>
         </is>
       </c>
@@ -30023,7 +30023,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Alerts still escalate on the camera input, with strict pose thresholds and no wheel-touch reset; but the wheel-side lock is off while engaged (policy.py:261), so the monitored seat can switch, and the policy ignores the real speed, gear and engagement</t>
+            <t>Alerts still escalate on the camera input, with strict pose thresholds and no wheel-touch reset; but the wheel-side lock is off while engaged (policy.py:287), so the monitored seat can switch, and the policy ignores the real speed, gear and engagement</t>
           </r>
           <r>
             <rPr>
@@ -30049,7 +30049,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>run_step uses a synthetic vehicle state (speed 30 m/s, enabled, no driver input, brake-disengage probability 1.0, zero calibration) instead of carState, selfdriveState and extrinsicsCalibration, and skips the input validity gate except for driverStateV2 (dmonitoringd.py:26-29; policy.py:431-440)</t>
+            <t>run_step uses a synthetic vehicle state (speed 30 m/s, enabled, no driver input, brake-disengage probability 1.0, zero calibration) instead of carState, selfdriveState and extrinsicsCalibration, and skips the input validity gate except for driverStateV2 (dmonitoringd.py:26-29; policy.py:470-479)</t>
           </r>
         </is>
       </c>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -20335,7 +20335,7 @@
       <c r="R85" s="48" t="inlineStr"/>
       <c r="S85" s="48" t="inlineStr"/>
     </row>
-    <row r="86" ht="235.5" customHeight="1">
+    <row r="86" ht="289.5" customHeight="1">
       <c r="A86" s="49" t="inlineStr">
         <is>
           <r>
@@ -20441,6 +20441,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006 (the regained authority passes longitudinal commands too; braking without the driver's engagement, HE-04.4)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -20482,7 +20508,8 @@
       <c r="D86" s="50" t="inlineStr">
         <is>
           <t>HZ-010
-HZ-002</t>
+HZ-002
+HZ-006</t>
         </is>
       </c>
       <c r="E86" s="51" t="n">
@@ -31362,7 +31389,7 @@
       <c r="R140" s="48" t="inlineStr"/>
       <c r="S140" s="48" t="inlineStr"/>
     </row>
-    <row r="141" ht="154.5" customHeight="1">
+    <row r="141" ht="208.5" customHeight="1">
       <c r="A141" s="49" t="inlineStr">
         <is>
           <r>
@@ -31442,6 +31469,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006 (the grant covers longitudinal commands; braking without the driver's engagement for up to the 150 ms tolerance, HE-04.4)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -31482,7 +31535,8 @@
       </c>
       <c r="D141" s="50" t="inlineStr">
         <is>
-          <t>HZ-010</t>
+          <t>HZ-010
+HZ-006</t>
         </is>
       </c>
       <c r="E141" s="51" t="n">

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -5742,7 +5742,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• pandad (reference build) configures a car safety mode only on a panda whose health packet carries HEALTH_FLAG_REFERENCE_BUILD; otherwise the panda stays in NOOUTPUT and selfdrived raises controlsMismatch and pandaNotReferenceBuild (panda_safety.cc:73-83, selfdrived.py:375-379; TSR-619, TSR-514). A build opted out on both sides (firmware and pandad) is not caught</t>
+            <t>• pandad (reference build) configures a car safety mode only on a panda whose health packet carries HEALTH_FLAG_REFERENCE_BUILD; otherwise the panda stays in NOOUTPUT and selfdrived raises controlsMismatch and pandaNotReferenceBuild (panda_safety.cc:73-83, selfdrived.py:377-381; TSR-619, TSR-514). A build opted out on both sides (firmware and pandad) is not caught</t>
           </r>
           <r>
             <rPr>
@@ -11795,7 +11795,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Test-only environment flags reach the vehicle: REPLAY sets the state to enabled when a panda reports controlsAllowed, bypassing ENABLE/NO_ENTRY (selfdrived.py:489-490); SIMULATION ignores cabinCameraState and managerState and makes every SubMaster alive/freq check pass once seen (selfdrived.py:86-87; cereal/messaging/__init__.py:211,265-266)</t>
+            <t>Test-only environment flags reach the vehicle: REPLAY sets the state to enabled when a panda reports controlsAllowed, bypassing ENABLE/NO_ENTRY (selfdrived.py:493-494); SIMULATION ignores cabinCameraState and managerState and makes every SubMaster alive/freq check pass once seen (selfdrived.py:88-89; cereal/messaging/__init__.py:211,265-266)</t>
           </r>
         </is>
       </c>
@@ -12037,7 +12037,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>carState is read from its own socket with a 20 ms timeout and the previous carState is reused when nothing arrives (selfdrived.py:83, 472-473); carState is not in the SubMaster, so it has no alive/freq check. A card stall freezes brakePressed, cruiseState and canValid, so no driver-action event is raised; the stall is only seen indirectly (selfdrivedLagging after about 0.2 s, carOutput commIssue after 0.1 s), both SOFT_DISABLE (3 s or longer, SWF-033.C2)</t>
+            <t>carState is read from its own socket with a 20 ms timeout and the previous carState is reused when nothing arrives (selfdrived.py:85, 474-475); carState is not in the SubMaster, so it has no alive/freq check. A card stall freezes brakePressed, cruiseState and canValid, so no driver-action event is raised; the stall is only seen indirectly (selfdrivedLagging after about 0.2 s, carOutput commIssue after 0.1 s), both SOFT_DISABLE (3 s or longer, SWF-033.C2)</t>
           </r>
         </is>
       </c>
@@ -12049,7 +12049,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream design (TODO at selfdrived.py:82); ruff + ty; no freshness check on carState (TSR-602 asks it of controlsd only)</t>
+            <t>• Upstream design (TODO at selfdrived.py:84); ruff + ty; no freshness check on carState (TSR-602 asks it of controlsd only)</t>
           </r>
           <r>
             <rPr>
@@ -12058,7 +12058,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:82-83</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:84-85</t>
           </r>
         </is>
       </c>
@@ -12137,7 +12137,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Defect in the brake/gas rising-edge logic (selfdrived.py:253-256), in the canValid gate on car events (selfdrived.py:242-244), or in the USER_DISABLE priority of the state machine (state.py:31-33)</t>
+            <t>Defect in the brake/gas rising-edge logic (selfdrived.py:255-258), in the canValid gate on car events (selfdrived.py:244-246), or in the USER_DISABLE priority of the state machine (state.py:31-33)</t>
           </r>
         </is>
       </c>
@@ -12423,7 +12423,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Panda fault flags other than relayMalfunction get no reaction in selfdrived (pandaStates.faults: interruptRate*, heartbeatLoopWatchdog, registerDivergent, ...), and SPI error bursts are not supervised (IA host-supervision OI-2). At BL-004 heartbeatLost, safetyTxBlocked and txRateExceeded were not read either; since #51 they are (pandaTxRateExceeded, pandaHeartbeatLost, pandaTxBlocked, immediate disable; selfdrived.py:362-370, TSR-615). The EPS-fault flag is covered by the EPS status events from card</t>
+            <t>Panda fault flags other than relayMalfunction get no reaction in selfdrived (pandaStates.faults: interruptRate*, heartbeatLoopWatchdog, registerDivergent, ...), and SPI error bursts are not supervised (IA host-supervision OI-2). At BL-004 heartbeatLost, safetyTxBlocked and txRateExceeded were not read either; since #51 they are (pandaTxRateExceeded, pandaHeartbeatLost, pandaTxBlocked, immediate disable; selfdrived.py:364-372, TSR-615). The EPS-fault flag is covered by the EPS status events from card</t>
           </r>
         </is>
       </c>
@@ -12444,7 +12444,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:362-373</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:364-375</t>
           </r>
         </is>
       </c>
@@ -12532,7 +12532,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Defect in the BL-005 flag reactions: a wrong field, a missed panda index, or the safetyTxBlocked baseline not moved after a panda reset, so a flag the panda raises gives no disable (selfdrived.py:362-370, supervision.py TxBlockedMonitor)</t>
+            <t>Defect in the BL-005 flag reactions: a wrong field, a missed panda index, or the safetyTxBlocked baseline not moved after a panda reset, so a flag the panda raises gives no disable (selfdrived.py:364-372, supervision.py TxBlockedMonitor)</t>
           </r>
         </is>
       </c>
@@ -12649,7 +12649,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Diagnostics masked on the big-model path: commIssue is suppressed for every service while ChestnutLoading is set and for 5 s after, and posenet, locationd, paramsd and modeldLagging checks are skipped (selfdrived.py:384-388, 407, 461; GAP-17, TSR-603). Active only when the chestnut models are compiled and the accelerator or a USB-C cable is detected (modeld.py:232); nothing enforces its absence in the reference configuration</t>
+            <t>Diagnostics masked on the big-model path: commIssue is suppressed for every service while ChestnutLoading is set and for 5 s after, and posenet, locationd, paramsd and modeldLagging checks are skipped (selfdrived.py:386-390, 409, 463; GAP-17, TSR-603). Active only when the chestnut models are compiled and the accelerator or a USB-C cable is detected (modeld.py:232); nothing enforces its absence in the reference configuration</t>
           </r>
         </is>
       </c>
@@ -12918,7 +12918,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loss or staleness of an input to the control law is handled as SOFT_DISABLE (commIssue, commIssueAvgFreq, processNotRunning, modeldLagging, selfdrivedLagging; events.py:853-872, 886-896), i.e. 3 s of continued actuation (state.py:7, 38-41); sensorDataInvalid only after 10 s without IMU data (selfdrived.py:418-419). TSR-601 asks immediate disable; no event is justified against an FTTI (SFM-016, GAP-16)</t>
+            <t>Loss or staleness of an input to the control law is handled as SOFT_DISABLE (commIssue, commIssueAvgFreq, processNotRunning, modeldLagging, selfdrivedLagging; events.py:853-872, 886-896), i.e. 3 s of continued actuation (state.py:7, 38-41); sensorDataInvalid only after 10 s without IMU data (selfdrived.py:420-421). TSR-601 asks immediate disable; no event is justified against an FTTI (SFM-016, GAP-16)</t>
           </r>
         </is>
       </c>
@@ -13027,7 +13027,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Every timer counts loop iterations, not time: soft_disable_timer (state.py:20, 40), mismatch_counter, cruise_mismatch_counter and the sm.frame gates (selfdrived.py:338, 418, 425). The loop is paced by the carState receive (20 ms timeout) with monitor_time only (selfdrived.py:83, 586-588) and does blocking Params writes (selfdrived.py:220, 306, 468), so when it slows, every timeout stretches (3 s soft disable is 6 s at 50 Hz)</t>
+            <t>Every timer counts loop iterations, not time: soft_disable_timer (state.py:20, 40), mismatch_counter, cruise_mismatch_counter and the sm.frame gates (selfdrived.py:340, 420, 427). The loop is paced by the carState receive (20 ms timeout) with monitor_time only (selfdrived.py:85, 607-609) and does blocking Params writes (selfdrived.py:222, 308, 470), so when it slows, every timeout stretches (3 s soft disable is 6 s at 50 Hz)</t>
           </r>
         </is>
       </c>
@@ -13496,7 +13496,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Safety model, parameter and alternative-experience mismatch is ignored for the first 10 s after selfdrived starts (sm.frame*DT_CTRL &gt; 10, selfdrived.py:338), so an engagement in that window with a wrong mode or parameter that still grants controls is not refused</t>
+            <t>Safety model, parameter and alternative-experience mismatch is ignored for the first 10 s after selfdrived starts (sm.frame*DT_CTRL &gt; 10, selfdrived.py:340), so an engagement in that window with a wrong mode or parameter that still grants controls is not refused</t>
           </r>
           <r>
             <rPr>
@@ -13517,7 +13517,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Initialization takes up to 6 s (selfdrived.py:477-480); the wrong mode itself needs SWF-013 (reference lock not built at BL-004; default build at BL-005, so a wrong mode or parameter is refused by the panda and no grant follows)</t>
+            <t>• Initialization takes up to 6 s (selfdrived.py:479-482); the wrong mode itself needs SWF-013 (reference lock not built at BL-004; default build at BL-005, so a wrong mode or parameter is refused by the panda and no grant follows)</t>
           </r>
           <r>
             <rPr>
@@ -13526,7 +13526,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:337-339</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:339-341</t>
           </r>
         </is>
       </c>
@@ -14288,7 +14288,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Hang or starvation of the Python process (blocking Params writes in the 100 Hz loop, selfdrived.py:220, 306, 468; GIL contention with params_thread; CPU load); no process watchdog for selfdrived (process_config.py:97)</t>
+            <t>Hang or starvation of the Python process (blocking Params writes in the 100 Hz loop, selfdrived.py:222, 308, 470; GIL contention with params_thread; CPU load); no process watchdog for selfdrived (process_config.py:97)</t>
           </r>
           <r>
             <rPr>
@@ -14309,7 +14309,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Real-time priority CTRL_HIGH on core 4 (selfdrived.py:595); manager restarts a dead process but not a hung one (system/manager/process.py:223-238)</t>
+            <t>• Real-time priority CTRL_HIGH on core 4 (selfdrived.py:616); manager restarts a dead process but not a hung one (system/manager/process.py:223-238)</t>
           </r>
           <r>
             <rPr>
@@ -14318,7 +14318,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:594-597</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:615-618</t>
           </r>
         </is>
       </c>
@@ -14693,7 +14693,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The counter is reset whenever |aEgo - IMU acceleration| &gt;= 2 m/s² (device_motion_valid, helpers.py:45-46), which also holds in wheel slip or lock during a gross event (SFM-030.C2); no check until a calibrated pose exists (selfdrived.py:303); latched pose reused when deviceMotion stops (selfdrived.py:299-301)</t>
+            <t>The counter is reset whenever |aEgo - IMU acceleration| &gt;= 2 m/s² (device_motion_valid, helpers.py:45-46), which also holds in wheel slip or lock during a gross event (SFM-030.C2); no check until a calibrated pose exists (selfdrived.py:305); latched pose reused when deviceMotion stops (selfdrived.py:301-303)</t>
           </r>
         </is>
       </c>
@@ -15186,7 +15186,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>At BL-004 cruiseMismatch had no reaction or alert and was raised only after 6 s. Since #51 (BL-005) it is raised after 1 s (CRUISE_MISMATCH_TIME, selfdrived.py:459-463) with "Stock Cruise Still Engaged / Press Cancel or Brake" and a repeating prompt (TSR-308). Remaining cause: a defect in the new reaction, and the counter counts loop iterations, not time (SWF-033.C2). The cancel request itself is SWF-048</t>
+            <t>At BL-004 cruiseMismatch had no reaction or alert and was raised only after 6 s. Since #51 (BL-005) it is raised after 1 s (CRUISE_MISMATCH_TIME, selfdrived.py:461-465) with "Stock Cruise Still Engaged / Press Cancel or Brake" and a repeating prompt (TSR-308). Remaining cause: a defect in the new reaction, and the counter counts loop iterations, not time (SWF-033.C2). The cancel request itself is SWF-048</t>
           </r>
         </is>
       </c>
@@ -16807,7 +16807,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>selfdrived suppresses commIssue while the big model is loading or settling (selfdrived.py:386-388), so held modelV2 got no reaction for that window at BL-004. Since #51 the controlsd freshness gate stops lateral actuation on a modelV2 more than 0.5 s old whatever selfdrived suppresses; the alert is still masked (TSR-603)</t>
+            <t>selfdrived suppresses commIssue while the big model is loading or settling (selfdrived.py:388-390), so held modelV2 got no reaction for that window at BL-004. Since #51 the controlsd freshness gate stops lateral actuation on a modelV2 more than 0.5 s old whatever selfdrived suppresses; the alert is still masked (TSR-603)</t>
           </r>
         </is>
       </c>
@@ -18714,7 +18714,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>cancel = CS.cruiseState.enabled and not CC.enabled (controlsd.py:162), where CC.enabled is the unchecked selfdriveState (SWF-040.C1), and it is sent only inside the 33 Hz ACC_CONTROL frame (carcontroller.py:187, 253) while card is actuating. The selfdrived backstop does nothing: cruiseMismatch fires after 6 s (selfdrived.py:423-426) but has no alert or disable type (events.py:458-460, commented out)</t>
+            <t>cancel = CS.cruiseState.enabled and not CC.enabled (controlsd.py:162), where CC.enabled is the unchecked selfdriveState (SWF-040.C1), and it is sent only inside the 33 Hz ACC_CONTROL frame (carcontroller.py:187, 253) while card is actuating. The selfdrived backstop does nothing: cruiseMismatch fires after 6 s (selfdrived.py:425-428) but has no alert or disable type (events.py:458-460, commented out)</t>
           </r>
         </is>
       </c>
@@ -18992,7 +18992,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>controlsd uses lateralManeuverPlan whenever its last message was valid (controlsd.py:123-124), with no alive check (SubMaster valid changes only on receipt, cereal/messaging/__init__.py:261) and no check of the mode; selfdrived ignores lateralManeuverPlan in its alive/valid checks (selfdrived.py:85). The path is enabled by the LateralManeuverMode developer toggle (process_config.py:43-44, 109; developer.py:134, offroad only; cleared at manager start and offroad, params_keys.h:87)</t>
+            <t>controlsd uses lateralManeuverPlan whenever its last message was valid (controlsd.py:123-124), with no alive check (SubMaster valid changes only on receipt, cereal/messaging/__init__.py:261) and no check of the mode; selfdrived ignores lateralManeuverPlan in its alive/valid checks (selfdrived.py:87). The path is enabled by the LateralManeuverMode developer toggle (process_config.py:43-44, 109; developer.py:134, offroad only; cleared at manager start and offroad, params_keys.h:87)</t>
           </r>
         </is>
       </c>
@@ -19004,7 +19004,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Operational rule only (WP-V-07 bans developer modes; INS-19 reference parameters); TSR-613 (path absent from reference builds) not met (GAP-20). Permanent "Lateral Maneuver Mode" banner when active (selfdrived.py:184-186)</t>
+            <t>• Operational rule only (WP-V-07 bans developer modes; INS-19 reference parameters); TSR-613 (path absent from reference builds) not met (GAP-20). Permanent "Lateral Maneuver Mode" banner when active (selfdrived.py:186-188)</t>
           </r>
           <r>
             <rPr>
@@ -19428,7 +19428,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>fcw event from modelV2.meta.hardBrakePredicted or longitudinalPlan.fcw with no alive, valid or age check of its own (selfdrived.py:470-475)</t>
+            <t>fcw event from modelV2.meta.hardBrakePredicted or longitudinalPlan.fcw with no alive, valid or age check of its own (selfdrived.py:472-477)</t>
           </r>
         </is>
       </c>
@@ -23966,7 +23966,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Plans from invalid or stale inputs: plannerd has no validity gate of its own and uses the leads whatever radarState.valid says (long_mpc.py:313-314); longitudinalPlan.valid = sm.all_checks() is published, but controlsd does not read it, so the reaction is selfdrived commIssue (soft disable, 3 s of continued control) (longitudinal_planner.py:156; selfdrived.py:425-431)</t>
+            <t>Plans from invalid or stale inputs: plannerd has no validity gate of its own and uses the leads whatever radarState.valid says (long_mpc.py:313-314); longitudinalPlan.valid = sm.all_checks() is published, but controlsd does not read it, so the reaction is selfdrived commIssue (soft disable, 3 s of continued control) (longitudinal_planner.py:156; selfdrived.py:427-433)</t>
           </r>
         </is>
       </c>
@@ -25659,7 +25659,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Radar faults reach the planner as data: plannerd uses the leads whatever radarState.valid says, and radarFault / radarTempUnavailable are SOFT_DISABLE (selfdrived.py:408-414; events.py:878-886), so a faulted lead is used for the 3 s soft disable</t>
+            <t>Radar faults reach the planner as data: plannerd uses the leads whatever radarState.valid says, and radarFault / radarTempUnavailable are SOFT_DISABLE (selfdrived.py:410-416; events.py:878-886), so a faulted lead is used for the 3 s soft disable</t>
           </r>
         </is>
       </c>
@@ -27828,7 +27828,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>selfdrived ignores accelerometer and gyro in its alive/valid checks and raises sensorDataInvalid only after 10 s without data (selfdrived.py:101, 454-456); deviceMotion.sensorsOK is not consumed by selfdrived (only paramsd and torqued)</t>
+            <t>selfdrived ignores accelerometer and gyro in its alive/valid checks and raises sensorDataInvalid only after 10 s without data (selfdrived.py:103, 456-458); deviceMotion.sensorsOK is not consumed by selfdrived (only paramsd and torqued)</t>
           </r>
         </is>
       </c>
@@ -28161,7 +28161,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>If the narrow or wide road stream is absent when selfdrived initialises, it is put on the ignore_alive and ignore_valid lists for the whole drive (selfdrived.py:518-524), so a camera that is not up at start is never supervised</t>
+            <t>If the narrow or wide road stream is absent when selfdrived initialises, it is put on the ignore_alive and ignore_valid lists for the whole drive (selfdrived.py:539-545), so a camera that is not up at start is never supervised</t>
           </r>
         </is>
       </c>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -15207,7 +15207,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/controls/controlsd.py:194</t>
+   openpilot/selfdrive/controls/controlsd.py:195</t>
           </r>
         </is>
       </c>
@@ -17303,7 +17303,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>At BL-004 self.desired_curvature and the torque PID integrator became NaN and stayed NaN, the sanitiser replaced the outputs with 0 and only logged. At BL-005 the step with a non-finite input runs with latActive or longActive false and the controllers reset (controlsd.py:122-131, 141-144, 154-159); the output is zero for as long as the input stays non-finite, without an event</t>
+            <t>At BL-004 self.desired_curvature and the torque PID integrator became NaN and stayed NaN, the sanitiser replaced the outputs with 0 and only logged. At BL-005 the step with a non-finite input runs with latActive or longActive false and the controllers reset (controlsd.py:122-131, 141-144, 155-160); the output is zero for as long as the input stays non-finite, without an event</t>
           </r>
         </is>
       </c>
@@ -17353,7 +17353,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>A NaN desired curvature (modelV2 or lateralManeuverPlan) or roll. At BL-004 it latched self.desired_curvature and the PID integrator for the drive (reproduced with the BL-004 clip_curvature and PIDController in isolation, scratch probe). Since #51 (BL-005) the step runs with latActive false, the controller is reset and desired_curvature is reset if non-finite (controlsd.py:122-128, 141-142, 154-155), so the latch is gone. Remaining: a persistent non-finite input silently zeroes lateral output while the item shows engaged, with no event or alert (TSR-604 asks an immediate disable; IA host-supervision OI-4); other inputs (vEgo, curvature from carState, vehicleParameters) are not guarded</t>
+            <t>A NaN desired curvature (modelV2 or lateralManeuverPlan) or roll. At BL-004 it latched self.desired_curvature and the PID integrator for the drive (reproduced with the BL-004 clip_curvature and PIDController in isolation, scratch probe). Since #51 (BL-005) the step runs with latActive false, the controller is reset and desired_curvature is reset if non-finite (controlsd.py:122-128, 141-142, 155-156), so the latch is gone. Remaining: a persistent non-finite input silently zeroes lateral output while the item shows engaged, with no event or alert (TSR-604 asks an immediate disable; IA host-supervision OI-4); other inputs (vEgo, curvature from carState, vehicleParameters) are not guarded</t>
           </r>
         </is>
       </c>
@@ -17498,7 +17498,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>A NaN aTarget made the LongControl PID integrator NaN even with ki=0 (0·NaN), so accel stayed NaN, sanitised to 0, until the state machine left pid (longcontrol.py:56-71). Since #51 (BL-005) a non-finite aTarget sets longActive false and 0 is passed instead, and LongControl is reset (controlsd.py:129-131, 143-144). Remaining: zero acceleration request, no event, while the input stays non-finite</t>
+            <t>A NaN aTarget made the LongControl PID integrator NaN even with ki=0 (0·NaN), so accel stayed NaN, sanitised to 0, until the state machine left pid (longcontrol.py:65-80). Since #51 (BL-005) a non-finite aTarget sets longActive false and 0 is passed instead, and LongControl is reset (controlsd.py:129-131, 143-144). Remaining: zero acceleration request, no event, while the input stays non-finite</t>
           </r>
         </is>
       </c>
@@ -17812,7 +17812,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The 4 m/s³ windup/winddown limit is applied before the pitch compensation and the PID (carcontroller.py:197-238), so the sent command has no rate limit; pitch comes from CC.orientationNED, which controlsd fills from deviceMotion with no validity check (controlsd.py:69-71, 157-159)</t>
+            <t>The 4 m/s³ windup/winddown limit is applied before the pitch compensation and the PID (carcontroller.py:197-238), so the sent command has no rate limit; pitch comes from CC.orientationNED, which controlsd fills from deviceMotion with no validity check (controlsd.py:69-71, 158-160)</t>
           </r>
         </is>
       </c>
@@ -18172,7 +18172,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>controlsd raises on input it does not guard and exits; the 100 Hz loop has no exception handling. The example of BL-004, int(NaN) when lateralDelay is not finite (latcontrol_torque.py:100), is guarded since #51 (falls back to steerActuatorDelay, controlsd.py:157-159); other inputs are not</t>
+            <t>controlsd raises on input it does not guard and exits; the 100 Hz loop has no exception handling. The example of BL-004, int(NaN) when lateralDelay is not finite (latcontrol_torque.py:100), is guarded since #51 (falls back to steerActuatorDelay, controlsd.py:158-160); other inputs are not</t>
           </r>
         </is>
       </c>
@@ -18299,7 +18299,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loop overrun or scheduling delay (Python, CTRL_HIGH on core 4, controlsd.py:237); Ratekeeper only monitors (228-233) and the loop is paced by selfdriveState; card actuates the latest carControl each CAN cycle as long as it is alive within 10 periods (card.py:234; cereal/messaging/__init__.py:265)</t>
+            <t>Loop overrun or scheduling delay (Python, CTRL_HIGH on core 4, controlsd.py:238); Ratekeeper only monitors (228-233) and the loop is paced by selfdriveState; card actuates the latest carControl each CAN cycle as long as it is alive within 10 periods (card.py:234; cereal/messaging/__init__.py:265)</t>
           </r>
         </is>
       </c>
@@ -18714,7 +18714,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>cancel = CS.cruiseState.enabled and not CC.enabled (controlsd.py:162), where CC.enabled is the unchecked selfdriveState (SWF-040.C1), and it is sent only inside the 33 Hz ACC_CONTROL frame (carcontroller.py:187, 253) while card is actuating. The selfdrived backstop does nothing: cruiseMismatch fires after 6 s (selfdrived.py:425-428) but has no alert or disable type (events.py:458-460, commented out)</t>
+            <t>cancel = CS.cruiseState.enabled and not CC.enabled (controlsd.py:163), where CC.enabled is the unchecked selfdriveState (SWF-040.C1), and it is sent only inside the 33 Hz ACC_CONTROL frame (carcontroller.py:187, 253) while card is actuating. The selfdrived backstop does nothing: cruiseMismatch fires after 6 s (selfdrived.py:425-428) but has no alert or disable type (events.py:458-460, commented out)</t>
           </r>
         </is>
       </c>
@@ -19186,7 +19186,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>forceDecel set in the same cycle as softDisabling or noResponseForceDecel (controlsd.py:235-236); the planner sets the cruise target to 0 at once (longitudinal_planner.py:84-85)</t>
+            <t>forceDecel set in the same cycle as softDisabling or noResponseForceDecel (controlsd.py:236-237); the planner sets the cruise target to 0 at once (longitudinal_planner.py:84-85)</t>
           </r>
         </is>
       </c>
@@ -19718,7 +19718,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The Toyota CarController takes pcm_accel_cmd from actuators.accel with no longActive gate (carcontroller.py:197-250); the inactive value relies on LongControl returning 0 in its off state (longcontrol.py:56-58), so a defect or stale carControl upstream passes through</t>
+            <t>The Toyota CarController takes pcm_accel_cmd from actuators.accel with no longActive gate (carcontroller.py:197-250); the inactive value relies on LongControl returning 0 in its off state (longcontrol.py:65-67), so a defect or stale carControl upstream passes through</t>
           </r>
         </is>
       </c>
@@ -22396,7 +22396,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Unhandled exception: the loop has no exception handling (card.py:277-284). A non-finite torque or acceleration raises in the CarController (int(round(nan)), carcontroller.py:105; math.floor in packer.py:24); controlsd sanitises its actuators (controlsd.py:171-180), so the path needs a value made non-finite inside card (CarState or pitch compensation)</t>
+            <t>Unhandled exception: the loop has no exception handling (card.py:277-284). A non-finite torque or acceleration raises in the CarController (int(round(nan)), carcontroller.py:105; math.floor in packer.py:24); controlsd sanitises its actuators (controlsd.py:172-181), so the path needs a value made non-finite inside card (CarState or pitch compensation)</t>
           </r>
         </is>
       </c>
@@ -30494,7 +30494,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The request crosses three processes with no freshness check on the flag: controlsd reads driverMonitoringState.noResponseForceDecel without an alive or valid check (controlsd.py:49-51, 235), and plannerd reads controlsState.forceDecel the same way (longitudinal_planner.py:84); its own valid flag is not read by controlsd (SWF-065.C1). A stopped dmonitoringd leaves the last value in place until selfdrived soft-disables (SWF-064)</t>
+            <t>The request crosses three processes with no freshness check on the flag: controlsd reads driverMonitoringState.noResponseForceDecel without an alive or valid check (controlsd.py:49-51, 236), and plannerd reads controlsState.forceDecel the same way (longitudinal_planner.py:84); its own valid flag is not read by controlsd (SWF-065.C1). A stopped dmonitoringd leaves the last value in place until selfdrived soft-disables (SWF-064)</t>
           </r>
         </is>
       </c>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$143</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.4 · draft</t>
+          <t>1.5 · draft</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>70 (64)</t>
+          <t>71 (65)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S142"/>
+  <dimension ref="A1:S143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24571,8 +24571,8 @@
       <c r="R106" s="48" t="inlineStr"/>
       <c r="S106" s="48" t="inlineStr"/>
     </row>
-    <row r="107" ht="100.5" customHeight="1">
-      <c r="A107" s="49" t="inlineStr">
+    <row r="107" ht="154.5" customHeight="1">
+      <c r="A107" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24594,7 +24594,7 @@
           </r>
         </is>
       </c>
-      <c r="B107" s="49" t="inlineStr">
+      <c r="B107" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24616,7 +24616,7 @@
           </r>
         </is>
       </c>
-      <c r="C107" s="49" t="inlineStr">
+      <c r="C107" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24689,15 +24689,15 @@
           </r>
         </is>
       </c>
-      <c r="D107" s="50" t="inlineStr">
+      <c r="D107" s="31" t="inlineStr">
         <is>
           <t>HZ-007</t>
         </is>
       </c>
-      <c r="E107" s="51" t="n">
+      <c r="E107" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F107" s="49" t="inlineStr">
+      <c r="F107" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24720,24 +24720,141 @@
           </r>
         </is>
       </c>
-      <c r="G107" s="43" t="inlineStr">
+      <c r="G107" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H107" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The driver can leave the assured configuration while driving: the distance button cycles the personality and saves it, and ExperimentalMode can be toggled; both are only logged (selfdrived.py:502-506, 607-626). Whether to refuse engagement outside the assured configuration is queued for the lead (DQ-221)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I107" s="44" t="inlineStr">
+      <c r="H107" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Defect in the reference entry gate (DQ-221 A, #287): settings_in_scope computed wrongly in assured_config.evaluate, settingNotAssured not raised in add_reference_entry_events, reference_platform set wrongly, or distance_button_pressed still changing the personality, so the item engages in, or is moved to, a setting the analyses do not cover</t>
+          </r>
+        </is>
+      </c>
+      <c r="I107" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Lead decision DQ-221 A implemented in #287 (69cddaa, after BL-006); change record change-2026-10-19-reference-entry-checks; upstream review, ruff + ty. No SWSR yet (change record OI-1)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/07-supporting/impact/change-2026-10-19-reference-entry-checks.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J107" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K107" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_assured_config.py: each setting refuses entry, entry only, other platforms unchanged, distance button ignored on the reference platform. Collected by the CI unit_tests job but not yet run there (the scons jobs fail in setup on the git-lfs 404); run locally for #287 only. D 8 once CI runs it, D 4 with mutation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_assured_config.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L107" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M107" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N107" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-063 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Apply the lead's decision on engagement outside the assured configuration (DQ-221): refuse engagement or keep logging, with a test</t>
+          </r>
+        </is>
+      </c>
+      <c r="O107" s="57" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+      <c r="P107" s="33" t="inlineStr">
+        <is>
+          <t>10/5/8</t>
+        </is>
+      </c>
+      <c r="Q107" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R107" s="39" t="inlineStr"/>
+      <c r="S107" s="39" t="inlineStr"/>
+    </row>
+    <row r="108" ht="100.5" customHeight="1">
+      <c r="A108" s="42" t="n"/>
+      <c r="B108" s="42" t="n"/>
+      <c r="C108" s="42" t="n"/>
+      <c r="D108" s="42" t="n"/>
+      <c r="E108" s="42" t="n"/>
+      <c r="F108" s="42" t="n"/>
+      <c r="G108" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H108" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A setting changed in the settings menu while engaged (following distance, Experimental Mode) takes effect at once; the gate refuses only the next engagement (change record OI-3). Whether to lock the settings while engaged is queued for the lead (DQ-222)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I108" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24758,10 +24875,10 @@
           </r>
         </is>
       </c>
-      <c r="J107" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="K107" s="44" t="inlineStr">
+      <c r="J108" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K108" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24769,7 +24886,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_assured_config.py checks that deviations are reported (CI); it is not designed to keep the configuration</t>
+            <t>• No check while engaged; test_assured_config.py checks that the gate is entry-only, which is this behaviour</t>
           </r>
           <r>
             <rPr>
@@ -24782,48 +24899,48 @@
           </r>
         </is>
       </c>
-      <c r="L107" s="54" t="n">
-        <v>9</v>
-      </c>
-      <c r="M107" s="52" t="inlineStr">
+      <c r="L108" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M108" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N107" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-063 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Apply the lead's decision on engagement outside the assured configuration (DQ-221): refuse engagement or keep logging, with a test</t>
-          </r>
-        </is>
-      </c>
-      <c r="O107" s="59" t="inlineStr">
+      <c r="N108" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-079 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Apply the lead's decision on setting changes while engaged (DQ-222): lock the following distance and Experimental Mode while engaged on the reference platform, disengage on a change, or keep today's entry-only check; with a test</t>
+          </r>
+        </is>
+      </c>
+      <c r="O108" s="59" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
       </c>
-      <c r="P107" s="43" t="inlineStr"/>
-      <c r="Q107" s="43" t="inlineStr"/>
-      <c r="R107" s="48" t="inlineStr"/>
-      <c r="S107" s="48" t="inlineStr"/>
+      <c r="P108" s="43" t="inlineStr"/>
+      <c r="Q108" s="43" t="inlineStr"/>
+      <c r="R108" s="48" t="inlineStr"/>
+      <c r="S108" s="48" t="inlineStr"/>
     </row>
-    <row r="108" ht="100.5" customHeight="1">
-      <c r="A108" s="30" t="inlineStr">
+    <row r="109" ht="100.5" customHeight="1">
+      <c r="A109" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24845,7 +24962,7 @@
           </r>
         </is>
       </c>
-      <c r="B108" s="30" t="inlineStr">
+      <c r="B109" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24867,7 +24984,7 @@
           </r>
         </is>
       </c>
-      <c r="C108" s="30" t="inlineStr">
+      <c r="C109" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24940,15 +25057,15 @@
           </r>
         </is>
       </c>
-      <c r="D108" s="31" t="inlineStr">
+      <c r="D109" s="31" t="inlineStr">
         <is>
           <t>HZ-007</t>
         </is>
       </c>
-      <c r="E108" s="32" t="n">
+      <c r="E109" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F108" s="30" t="inlineStr">
+      <c r="F109" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24971,12 +25088,12 @@
           </r>
         </is>
       </c>
-      <c r="G108" s="33" t="inlineStr">
+      <c r="G109" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H108" s="34" t="inlineStr">
+      <c r="H109" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24988,7 +25105,7 @@
           </r>
         </is>
       </c>
-      <c r="I108" s="34" t="inlineStr">
+      <c r="I109" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25000,10 +25117,10 @@
           </r>
         </is>
       </c>
-      <c r="J108" s="35" t="n">
+      <c r="J109" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="K108" s="34" t="inlineStr">
+      <c r="K109" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25024,15 +25141,15 @@
           </r>
         </is>
       </c>
-      <c r="L108" s="36" t="n">
+      <c r="L109" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="M108" s="37" t="inlineStr">
+      <c r="M109" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N108" s="34" t="inlineStr">
+      <c r="N109" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25054,312 +25171,70 @@
           </r>
         </is>
       </c>
-      <c r="O108" s="38" t="inlineStr">
+      <c r="O109" s="38" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P108" s="33" t="inlineStr"/>
-      <c r="Q108" s="33" t="inlineStr"/>
-      <c r="R108" s="39" t="inlineStr"/>
-      <c r="S108" s="39" t="inlineStr"/>
-    </row>
-    <row r="109" ht="100.5" customHeight="1">
-      <c r="A109" s="42" t="n"/>
-      <c r="B109" s="42" t="n"/>
-      <c r="C109" s="42" t="n"/>
-      <c r="D109" s="42" t="n"/>
-      <c r="E109" s="42" t="n"/>
-      <c r="F109" s="42" t="n"/>
-      <c r="G109" s="43" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H109" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Slow MPC: the loop is paced by modelV2 (20 Hz) and solve_time is published but nothing acts on it (longitudinal_planner.py:161)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I109" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
-          </r>
-        </is>
-      </c>
-      <c r="J109" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="K109" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test targets this cause; test_onroad timing checks are device-only</t>
-          </r>
-        </is>
-      </c>
-      <c r="L109" s="54" t="n">
-        <v>10</v>
-      </c>
-      <c r="M109" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N109" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-048 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Bench or HIL fault injection (WP-V-05) - stop or stall selfdrived, modeld, plannerd and controlsd while engaged and measure time to zero torque/acceleration and to the alert; run test_onroad timing tests on a comma 3X for each release</t>
-          </r>
-        </is>
-      </c>
-      <c r="O109" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P109" s="43" t="inlineStr"/>
-      <c r="Q109" s="43" t="inlineStr"/>
-      <c r="R109" s="48" t="inlineStr"/>
-      <c r="S109" s="48" t="inlineStr"/>
+      <c r="P109" s="33" t="inlineStr"/>
+      <c r="Q109" s="33" t="inlineStr"/>
+      <c r="R109" s="39" t="inlineStr"/>
+      <c r="S109" s="39" t="inlineStr"/>
     </row>
     <row r="110" ht="100.5" customHeight="1">
-      <c r="A110" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-072
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Forward collision warning decision</t>
-          </r>
-        </is>
-      </c>
-      <c r="B110" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-071
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Raise a forward collision warning when a collision with the lead is predicted</t>
-          </r>
-        </is>
-      </c>
-      <c r="C110" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driver not warned of an imminent collision with a lead while engaged</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>No FCW alert from the item</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>longitudinalPlan.fcw stays false</t>
-          </r>
-        </is>
-      </c>
-      <c r="D110" s="50" t="inlineStr">
-        <is>
-          <t>HZ-007</t>
-        </is>
-      </c>
-      <c r="E110" s="51" t="n">
+      <c r="A110" s="42" t="n"/>
+      <c r="B110" s="42" t="n"/>
+      <c r="C110" s="42" t="n"/>
+      <c r="D110" s="42" t="n"/>
+      <c r="E110" s="42" t="n"/>
+      <c r="F110" s="42" t="n"/>
+      <c r="G110" s="43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H110" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Slow MPC: the loop is paced by modelV2 (20 Hz) and solve_time is published but nothing acts on it (longitudinal_planner.py:161)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I110" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J110" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K110" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause; test_onroad timing checks are device-only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L110" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="F110" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-069 · omission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Forward collision warning not raised for a predicted collision</t>
-          </r>
-        </is>
-      </c>
-      <c r="G110" s="43" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H110" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>FCW needs crash_cnt &gt; 2 with leadOne.modelProb &gt; 0.9 (long_mpc.py:338-342; longitudinal_planner.py:121): a radar-only lead (low-speed override, modelProb 0, radard.py:83, 174) never triggers it, and an MPC reset clears the counter (SWF-065.C2)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I110" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
-          </r>
-        </is>
-      </c>
-      <c r="J110" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="K110" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_stopped_vehicle checks that a collision is preceded by FCW in its scenarios (CI); targeted, not proven</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/test/stopped_vehicle/test_stopped_vehicle.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L110" s="45" t="n">
-        <v>8</v>
-      </c>
       <c r="M110" s="52" t="inlineStr">
         <is>
           <t>H</t>
@@ -25374,16 +25249,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-064 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+            <t xml:space="preserve">SWF-ACT-048 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench or HIL fault injection (WP-V-05) - stop or stall selfdrived, modeld, plannerd and controlsd while engaged and measure time to zero torque/acceleration and to the alert; run test_onroad timing tests on a comma 3X for each release</t>
           </r>
         </is>
       </c>
@@ -25398,51 +25273,51 @@
       <c r="S110" s="48" t="inlineStr"/>
     </row>
     <row r="111" ht="100.5" customHeight="1">
-      <c r="A111" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-081
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Lead selection and radar/vision fusion</t>
-          </r>
-        </is>
-      </c>
-      <c r="B111" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-080
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Provide the lead state (distance, relative speed and acceleration) from radar tracks matched to model leads, and flag radar faults</t>
-          </r>
-        </is>
-      </c>
-      <c r="C111" s="30" t="inlineStr">
+      <c r="A111" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-072
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Forward collision warning decision</t>
+          </r>
+        </is>
+      </c>
+      <c r="B111" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-071
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Raise a forward collision warning when a collision with the lead is predicted</t>
+          </r>
+        </is>
+      </c>
+      <c r="C111" s="49" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25459,7 +25334,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Insufficient or late deceleration for a lead</t>
+            <t>Driver not warned of an imminent collision with a lead while engaged</t>
           </r>
           <r>
             <rPr>
@@ -25485,7 +25360,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Planner keeps the cruise speed or brakes late; FCW not raised</t>
+            <t>No FCW alert from the item</t>
           </r>
           <r>
             <rPr>
@@ -25511,59 +25386,59 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>leadOne absent or at a wrong distance</t>
-          </r>
-        </is>
-      </c>
-      <c r="D111" s="31" t="inlineStr">
+            <t>longitudinalPlan.fcw stays false</t>
+          </r>
+        </is>
+      </c>
+      <c r="D111" s="50" t="inlineStr">
         <is>
           <t>HZ-007</t>
         </is>
       </c>
-      <c r="E111" s="32" t="n">
+      <c r="E111" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="F111" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-070 · omission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Lead missed or reported late while a lead is present</t>
-          </r>
-        </is>
-      </c>
-      <c r="G111" s="33" t="inlineStr">
+      <c r="F111" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-069 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Forward collision warning not raised for a predicted collision</t>
+          </r>
+        </is>
+      </c>
+      <c r="G111" s="43" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H111" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>By design a radar track is used above 4 m/s only when matched to a model lead with probability &gt; 0.5 and inside the match window (radard.py:113-133, 156-157); a stationary target seen only by radar is ignored (FI-2026-001 RC-02)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I111" s="34" t="inlineStr">
+      <c r="H111" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>FCW needs crash_cnt &gt; 2 with leadOne.modelProb &gt; 0.9 (long_mpc.py:338-342; longitudinal_planner.py:121): a radar-only lead (low-speed override, modelProb 0, radard.py:83, 174) never triggers it, and an MPC reset clears the counter (SWF-065.C2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I111" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25575,18 +25450,18 @@
           </r>
         </is>
       </c>
-      <c r="J111" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="K111" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_stopped_vehicle test_radar_only_stationary_target reproduces the gap and is marked expectedFailure (CI)</t>
+      <c r="J111" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K111" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_stopped_vehicle checks that a collision is preceded by FCW in its scenarios (CI); targeted, not proven</t>
           </r>
           <r>
             <rPr>
@@ -25599,15 +25474,15 @@
           </r>
         </is>
       </c>
-      <c r="L111" s="35" t="n">
+      <c r="L111" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="M111" s="37" t="inlineStr">
+      <c r="M111" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N111" s="34" t="inlineStr">
+      <c r="N111" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25629,26 +25504,168 @@
           </r>
         </is>
       </c>
-      <c r="O111" s="38" t="inlineStr">
+      <c r="O111" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P111" s="33" t="inlineStr"/>
-      <c r="Q111" s="33" t="inlineStr"/>
-      <c r="R111" s="39" t="inlineStr"/>
-      <c r="S111" s="39" t="inlineStr"/>
+      <c r="P111" s="43" t="inlineStr"/>
+      <c r="Q111" s="43" t="inlineStr"/>
+      <c r="R111" s="48" t="inlineStr"/>
+      <c r="S111" s="48" t="inlineStr"/>
     </row>
-    <row r="112" ht="195" customHeight="1">
-      <c r="A112" s="40" t="n"/>
-      <c r="B112" s="40" t="n"/>
-      <c r="C112" s="40" t="n"/>
-      <c r="D112" s="40" t="n"/>
-      <c r="E112" s="40" t="n"/>
-      <c r="F112" s="40" t="n"/>
+    <row r="112" ht="100.5" customHeight="1">
+      <c r="A112" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-081
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lead selection and radar/vision fusion</t>
+          </r>
+        </is>
+      </c>
+      <c r="B112" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-080
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide the lead state (distance, relative speed and acceleration) from radar tracks matched to model leads, and flag radar faults</t>
+          </r>
+        </is>
+      </c>
+      <c r="C112" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Insufficient or late deceleration for a lead</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Planner keeps the cruise speed or brakes late; FCW not raised</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>leadOne absent or at a wrong distance</t>
+          </r>
+        </is>
+      </c>
+      <c r="D112" s="31" t="inlineStr">
+        <is>
+          <t>HZ-007</t>
+        </is>
+      </c>
+      <c r="E112" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F112" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-070 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lead missed or reported late while a lead is present</t>
+          </r>
+        </is>
+      </c>
       <c r="G112" s="33" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="H112" s="34" t="inlineStr">
@@ -25659,7 +25676,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Radar faults reach the planner as data: plannerd uses the leads whatever radarState.valid says, and radarFault / radarTempUnavailable are SOFT_DISABLE (selfdrived.py:410-416; events.py:878-886), so a faulted lead is used for the 3 s soft disable</t>
+            <t>By design a radar track is used above 4 m/s only when matched to a model lead with probability &gt; 0.5 and inside the match window (radard.py:113-133, 156-157); a stationary target seen only by radar is ignored (FI-2026-001 RC-02)</t>
           </r>
         </is>
       </c>
@@ -25676,7 +25693,7 @@
         </is>
       </c>
       <c r="J112" s="35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K112" s="34" t="inlineStr">
         <is>
@@ -25686,7 +25703,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_leads.py checks only that radarTracks are invalid without radar CAN (CI); targeted at the fault report, not at its use</t>
+            <t>• test_stopped_vehicle test_radar_only_stationary_target reproduces the gap and is marked expectedFailure (CI)</t>
           </r>
           <r>
             <rPr>
@@ -25695,7 +25712,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/controls/tests/test_leads.py</t>
+   openpilot/selfdrive/test/stopped_vehicle/test_stopped_vehicle.py</t>
           </r>
         </is>
       </c>
@@ -25716,33 +25733,6 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-061 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
             <t xml:space="preserve">SWF-ACT-064 · design change
 </t>
           </r>
@@ -25758,8 +25748,7 @@
       </c>
       <c r="O112" s="38" t="inlineStr">
         <is>
-          <t>open
-open</t>
+          <t>open</t>
         </is>
       </c>
       <c r="P112" s="33" t="inlineStr"/>
@@ -25767,19 +25756,147 @@
       <c r="R112" s="39" t="inlineStr"/>
       <c r="S112" s="39" t="inlineStr"/>
     </row>
-    <row r="113" ht="100.5" customHeight="1">
-      <c r="A113" s="42" t="n"/>
-      <c r="B113" s="42" t="n"/>
-      <c r="C113" s="42" t="n"/>
-      <c r="D113" s="42" t="n"/>
-      <c r="E113" s="42" t="n"/>
-      <c r="F113" s="42" t="n"/>
-      <c r="G113" s="43" t="inlineStr">
+    <row r="113" ht="195" customHeight="1">
+      <c r="A113" s="40" t="n"/>
+      <c r="B113" s="40" t="n"/>
+      <c r="C113" s="40" t="n"/>
+      <c r="D113" s="40" t="n"/>
+      <c r="E113" s="40" t="n"/>
+      <c r="F113" s="40" t="n"/>
+      <c r="G113" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H113" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Radar faults reach the planner as data: plannerd uses the leads whatever radarState.valid says, and radarFault / radarTempUnavailable are SOFT_DISABLE (selfdrived.py:410-416; events.py:878-886), so a faulted lead is used for the 3 s soft disable</t>
+          </r>
+        </is>
+      </c>
+      <c r="I113" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc/openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J113" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K113" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_leads.py checks only that radarTracks are invalid without radar CAN (CI); targeted at the fault report, not at its use</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_leads.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L113" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M113" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N113" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-061 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-064 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
+          </r>
+        </is>
+      </c>
+      <c r="O113" s="38" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P113" s="33" t="inlineStr"/>
+      <c r="Q113" s="33" t="inlineStr"/>
+      <c r="R113" s="39" t="inlineStr"/>
+      <c r="S113" s="39" t="inlineStr"/>
+    </row>
+    <row r="114" ht="100.5" customHeight="1">
+      <c r="A114" s="42" t="n"/>
+      <c r="B114" s="42" t="n"/>
+      <c r="C114" s="42" t="n"/>
+      <c r="D114" s="42" t="n"/>
+      <c r="E114" s="42" t="n"/>
+      <c r="F114" s="42" t="n"/>
+      <c r="G114" s="43" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H113" s="44" t="inlineStr">
+      <c r="H114" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25791,7 +25908,7 @@
           </r>
         </is>
       </c>
-      <c r="I113" s="44" t="inlineStr">
+      <c r="I114" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25803,10 +25920,10 @@
           </r>
         </is>
       </c>
-      <c r="J113" s="45" t="n">
+      <c r="J114" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="K113" s="44" t="inlineStr">
+      <c r="K114" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25827,15 +25944,15 @@
           </r>
         </is>
       </c>
-      <c r="L113" s="54" t="n">
+      <c r="L114" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="M113" s="52" t="inlineStr">
+      <c r="M114" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N113" s="44" t="inlineStr">
+      <c r="N114" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25857,18 +25974,18 @@
           </r>
         </is>
       </c>
-      <c r="O113" s="53" t="inlineStr">
+      <c r="O114" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P113" s="43" t="inlineStr"/>
-      <c r="Q113" s="43" t="inlineStr"/>
-      <c r="R113" s="48" t="inlineStr"/>
-      <c r="S113" s="48" t="inlineStr"/>
+      <c r="P114" s="43" t="inlineStr"/>
+      <c r="Q114" s="43" t="inlineStr"/>
+      <c r="R114" s="48" t="inlineStr"/>
+      <c r="S114" s="48" t="inlineStr"/>
     </row>
-    <row r="114" ht="114" customHeight="1">
-      <c r="A114" s="30" t="inlineStr">
+    <row r="115" ht="114" customHeight="1">
+      <c r="A115" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25890,7 +26007,7 @@
           </r>
         </is>
       </c>
-      <c r="B114" s="30" t="inlineStr">
+      <c r="B115" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25912,7 +26029,7 @@
           </r>
         </is>
       </c>
-      <c r="C114" s="30" t="inlineStr">
+      <c r="C115" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25985,15 +26102,15 @@
           </r>
         </is>
       </c>
-      <c r="D114" s="31" t="inlineStr">
+      <c r="D115" s="31" t="inlineStr">
         <is>
           <t>HZ-006</t>
         </is>
       </c>
-      <c r="E114" s="32" t="n">
+      <c r="E115" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F114" s="30" t="inlineStr">
+      <c r="F115" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26016,12 +26133,12 @@
           </r>
         </is>
       </c>
-      <c r="G114" s="33" t="inlineStr">
+      <c r="G115" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H114" s="34" t="inlineStr">
+      <c r="H115" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26033,7 +26150,7 @@
           </r>
         </is>
       </c>
-      <c r="I114" s="34" t="inlineStr">
+      <c r="I115" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26045,10 +26162,10 @@
           </r>
         </is>
       </c>
-      <c r="J114" s="35" t="n">
+      <c r="J115" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K114" s="34" t="inlineStr">
+      <c r="K115" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26069,15 +26186,15 @@
           </r>
         </is>
       </c>
-      <c r="L114" s="36" t="n">
+      <c r="L115" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="M114" s="37" t="inlineStr">
+      <c r="M115" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N114" s="34" t="inlineStr">
+      <c r="N115" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26099,29 +26216,29 @@
           </r>
         </is>
       </c>
-      <c r="O114" s="38" t="inlineStr">
+      <c r="O115" s="38" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P114" s="33" t="inlineStr"/>
-      <c r="Q114" s="33" t="inlineStr"/>
-      <c r="R114" s="39" t="inlineStr"/>
-      <c r="S114" s="39" t="inlineStr"/>
+      <c r="P115" s="33" t="inlineStr"/>
+      <c r="Q115" s="33" t="inlineStr"/>
+      <c r="R115" s="39" t="inlineStr"/>
+      <c r="S115" s="39" t="inlineStr"/>
     </row>
-    <row r="115" ht="114" customHeight="1">
-      <c r="A115" s="42" t="n"/>
-      <c r="B115" s="42" t="n"/>
-      <c r="C115" s="42" t="n"/>
-      <c r="D115" s="42" t="n"/>
-      <c r="E115" s="42" t="n"/>
-      <c r="F115" s="42" t="n"/>
-      <c r="G115" s="43" t="inlineStr">
+    <row r="116" ht="114" customHeight="1">
+      <c r="A116" s="42" t="n"/>
+      <c r="B116" s="42" t="n"/>
+      <c r="C116" s="42" t="n"/>
+      <c r="D116" s="42" t="n"/>
+      <c r="E116" s="42" t="n"/>
+      <c r="F116" s="42" t="n"/>
+      <c r="G116" s="43" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H115" s="44" t="inlineStr">
+      <c r="H116" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26133,7 +26250,7 @@
           </r>
         </is>
       </c>
-      <c r="I115" s="44" t="inlineStr">
+      <c r="I116" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26145,10 +26262,10 @@
           </r>
         </is>
       </c>
-      <c r="J115" s="45" t="n">
+      <c r="J116" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="K115" s="44" t="inlineStr">
+      <c r="K116" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26169,15 +26286,15 @@
           </r>
         </is>
       </c>
-      <c r="L115" s="54" t="n">
+      <c r="L116" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="M115" s="52" t="inlineStr">
+      <c r="M116" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N115" s="44" t="inlineStr">
+      <c r="N116" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26199,18 +26316,18 @@
           </r>
         </is>
       </c>
-      <c r="O115" s="53" t="inlineStr">
+      <c r="O116" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P115" s="43" t="inlineStr"/>
-      <c r="Q115" s="43" t="inlineStr"/>
-      <c r="R115" s="48" t="inlineStr"/>
-      <c r="S115" s="48" t="inlineStr"/>
+      <c r="P116" s="43" t="inlineStr"/>
+      <c r="Q116" s="43" t="inlineStr"/>
+      <c r="R116" s="48" t="inlineStr"/>
+      <c r="S116" s="48" t="inlineStr"/>
     </row>
-    <row r="116" ht="181.5" customHeight="1">
-      <c r="A116" s="30" t="inlineStr">
+    <row r="117" ht="181.5" customHeight="1">
+      <c r="A117" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26232,7 +26349,7 @@
           </r>
         </is>
       </c>
-      <c r="B116" s="30" t="inlineStr">
+      <c r="B117" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26254,7 +26371,7 @@
           </r>
         </is>
       </c>
-      <c r="C116" s="30" t="inlineStr">
+      <c r="C117" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26353,16 +26470,16 @@
           </r>
         </is>
       </c>
-      <c r="D116" s="31" t="inlineStr">
+      <c r="D117" s="31" t="inlineStr">
         <is>
           <t>HZ-003
 HZ-007</t>
         </is>
       </c>
-      <c r="E116" s="32" t="n">
+      <c r="E117" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F116" s="30" t="inlineStr">
+      <c r="F117" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26385,12 +26502,12 @@
           </r>
         </is>
       </c>
-      <c r="G116" s="33" t="inlineStr">
+      <c r="G117" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H116" s="34" t="inlineStr">
+      <c r="H117" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26402,7 +26519,7 @@
           </r>
         </is>
       </c>
-      <c r="I116" s="34" t="inlineStr">
+      <c r="I117" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26414,10 +26531,10 @@
           </r>
         </is>
       </c>
-      <c r="J116" s="35" t="n">
+      <c r="J117" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="K116" s="34" t="inlineStr">
+      <c r="K117" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26429,15 +26546,15 @@
           </r>
         </is>
       </c>
-      <c r="L116" s="36" t="n">
+      <c r="L117" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M116" s="37" t="inlineStr">
+      <c r="M117" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N116" s="34" t="inlineStr">
+      <c r="N117" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26486,101 +26603,10 @@
           </r>
         </is>
       </c>
-      <c r="O116" s="38" t="inlineStr">
+      <c r="O117" s="38" t="inlineStr">
         <is>
           <t>open
 open</t>
-        </is>
-      </c>
-      <c r="P116" s="33" t="inlineStr"/>
-      <c r="Q116" s="33" t="inlineStr"/>
-      <c r="R116" s="39" t="inlineStr"/>
-      <c r="S116" s="39" t="inlineStr"/>
-    </row>
-    <row r="117" ht="114" customHeight="1">
-      <c r="A117" s="40" t="n"/>
-      <c r="B117" s="40" t="n"/>
-      <c r="C117" s="40" t="n"/>
-      <c r="D117" s="40" t="n"/>
-      <c r="E117" s="40" t="n"/>
-      <c r="F117" s="40" t="n"/>
-      <c r="G117" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H117" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Frame-drop accounting misses repeats: dropped frames are max(0, frame_id gap - 1), so a repeated or regressing frame_id counts as 0 (modeld.py:385); drops are forced to 0 for the first 10 runs and filtered with a 10 s time constant (386-389), so modeldLagging comes late</t>
-          </r>
-        </is>
-      </c>
-      <c r="I117" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
-          </r>
-        </is>
-      </c>
-      <c r="J117" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="K117" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
-          </r>
-        </is>
-      </c>
-      <c r="L117" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="M117" s="37" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N117" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-065 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
-          </r>
-        </is>
-      </c>
-      <c r="O117" s="38" t="inlineStr">
-        <is>
-          <t>open</t>
         </is>
       </c>
       <c r="P117" s="33" t="inlineStr"/>
@@ -26589,18 +26615,109 @@
       <c r="S117" s="39" t="inlineStr"/>
     </row>
     <row r="118" ht="114" customHeight="1">
-      <c r="A118" s="42" t="n"/>
-      <c r="B118" s="42" t="n"/>
-      <c r="C118" s="42" t="n"/>
-      <c r="D118" s="42" t="n"/>
-      <c r="E118" s="42" t="n"/>
-      <c r="F118" s="42" t="n"/>
-      <c r="G118" s="43" t="inlineStr">
+      <c r="A118" s="40" t="n"/>
+      <c r="B118" s="40" t="n"/>
+      <c r="C118" s="40" t="n"/>
+      <c r="D118" s="40" t="n"/>
+      <c r="E118" s="40" t="n"/>
+      <c r="F118" s="40" t="n"/>
+      <c r="G118" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H118" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Frame-drop accounting misses repeats: dropped frames are max(0, frame_id gap - 1), so a repeated or regressing frame_id counts as 0 (modeld.py:385); drops are forced to 0 for the first 10 runs and filtered with a 10 s time constant (386-389), so modeldLagging comes late</t>
+          </r>
+        </is>
+      </c>
+      <c r="I118" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J118" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K118" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
+          </r>
+        </is>
+      </c>
+      <c r="L118" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M118" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N118" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-065 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
+          </r>
+        </is>
+      </c>
+      <c r="O118" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P118" s="33" t="inlineStr"/>
+      <c r="Q118" s="33" t="inlineStr"/>
+      <c r="R118" s="39" t="inlineStr"/>
+      <c r="S118" s="39" t="inlineStr"/>
+    </row>
+    <row r="119" ht="114" customHeight="1">
+      <c r="A119" s="42" t="n"/>
+      <c r="B119" s="42" t="n"/>
+      <c r="C119" s="42" t="n"/>
+      <c r="D119" s="42" t="n"/>
+      <c r="E119" s="42" t="n"/>
+      <c r="F119" s="42" t="n"/>
+      <c r="G119" s="43" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H118" s="44" t="inlineStr">
+      <c r="H119" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26612,7 +26729,7 @@
           </r>
         </is>
       </c>
-      <c r="I118" s="44" t="inlineStr">
+      <c r="I119" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26624,241 +26741,8 @@
           </r>
         </is>
       </c>
-      <c r="J118" s="45" t="n">
+      <c r="J119" s="45" t="n">
         <v>5</v>
-      </c>
-      <c r="K118" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
-          </r>
-        </is>
-      </c>
-      <c r="L118" s="54" t="n">
-        <v>10</v>
-      </c>
-      <c r="M118" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N118" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-065 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
-          </r>
-        </is>
-      </c>
-      <c r="O118" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P118" s="43" t="inlineStr"/>
-      <c r="Q118" s="43" t="inlineStr"/>
-      <c r="R118" s="48" t="inlineStr"/>
-      <c r="S118" s="48" t="inlineStr"/>
-    </row>
-    <row r="119" ht="181.5" customHeight="1">
-      <c r="A119" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-090
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driving model process (modeld)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B119" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-090
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Publish model outputs (desired curvature, leads) for every road frame, computed from the current frame and calibration, and mark output that is not fit for use as invalid</t>
-          </r>
-        </is>
-      </c>
-      <c r="C119" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Loss of lateral control while engaged; the take-over alert follows within about 0.5 s</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>controlsd ends lateral control 0.5 s after the last modelV2 (TSR-602); selfdrived commIssue / processNotRunning soft disable; manager does not restart modeld</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>No modelV2</t>
-          </r>
-        </is>
-      </c>
-      <c r="D119" s="50" t="inlineStr">
-        <is>
-          <t>HZ-004</t>
-        </is>
-      </c>
-      <c r="E119" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F119" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-073 · crash
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>modeld stops while engaged</t>
-          </r>
-        </is>
-      </c>
-      <c r="G119" s="43" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H119" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Unhandled exception in the small-model path: a run exception re-raises (modeld.py:412-413); a short frame buffer or a missing output head raises (modeld.py:194; parse_model_outputs.py:24-28)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I119" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
-          </r>
-        </is>
-      </c>
-      <c r="J119" s="45" t="n">
-        <v>4</v>
       </c>
       <c r="K119" s="44" t="inlineStr">
         <is>
@@ -26900,39 +26784,11 @@
             </rPr>
             <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-066 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Unit tests for modeld output handling (parse, finiteness, frame-drop accounting) and include modeld in model_replay in LionDriver CI (with SWF-ACT-060)</t>
-          </r>
         </is>
       </c>
       <c r="O119" s="53" t="inlineStr">
         <is>
-          <t>open
-open</t>
+          <t>open</t>
         </is>
       </c>
       <c r="P119" s="43" t="inlineStr"/>
@@ -26940,7 +26796,7 @@
       <c r="R119" s="48" t="inlineStr"/>
       <c r="S119" s="48" t="inlineStr"/>
     </row>
-    <row r="120" ht="114" customHeight="1">
+    <row r="120" ht="181.5" customHeight="1">
       <c r="A120" s="49" t="inlineStr">
         <is>
           <r>
@@ -27002,7 +26858,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Any lateral or longitudinal hazard within the panda envelope</t>
+            <t>Loss of lateral control while engaged; the take-over alert follows within about 0.5 s</t>
           </r>
           <r>
             <rPr>
@@ -27028,7 +26884,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Outputs of an unvalidated model reach the controllers</t>
+            <t>controlsd ends lateral control 0.5 s after the last modelV2 (TSR-602); selfdrived commIssue / processNotRunning soft disable; manager does not restart modeld</t>
           </r>
           <r>
             <rPr>
@@ -27054,13 +26910,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driving or DM model weights or warp other than the analysed ones</t>
+            <t>No modelV2</t>
           </r>
         </is>
       </c>
       <c r="D120" s="50" t="inlineStr">
         <is>
-          <t>HZ-003</t>
+          <t>HZ-004</t>
         </is>
       </c>
       <c r="E120" s="51" t="n">
@@ -27075,17 +26931,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-074 · wrong_mode
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>A model file other than the released one is loaded</t>
+            <t xml:space="preserve">SWF-073 · crash
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld stops while engaged</t>
           </r>
         </is>
       </c>
@@ -27102,7 +26958,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Models are loaded with pickle and no hash, version or signature check (helpers.py:15-20; modeld.py:158-159; dmonitoringmodeld.py:22-48; GAP-22, TSR-616); they are compiled at build time from git-LFS sources (modeld/SConscript:41-52)</t>
+            <t>Unhandled exception in the small-model path: a run exception re-raises (modeld.py:412-413); a short frame buffer or a missing output head raises (modeld.py:194; parse_model_outputs.py:24-28)</t>
           </r>
         </is>
       </c>
@@ -27114,21 +26970,12 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Build from pinned LFS objects; release procedure (WP-P-10) draft</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/modeld/SConscript</t>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
           </r>
         </is>
       </c>
       <c r="J120" s="45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K120" s="44" t="inlineStr">
         <is>
@@ -27138,7 +26985,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• No test targets this cause</t>
+            <t>• modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
           </r>
         </is>
       </c>
@@ -27170,11 +27017,39 @@
             </rPr>
             <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-066 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unit tests for modeld output handling (parse, finiteness, frame-drop accounting) and include modeld in model_replay in LionDriver CI (with SWF-ACT-060)</t>
+          </r>
         </is>
       </c>
       <c r="O120" s="53" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P120" s="43" t="inlineStr"/>
@@ -27182,7 +27057,7 @@
       <c r="R120" s="48" t="inlineStr"/>
       <c r="S120" s="48" t="inlineStr"/>
     </row>
-    <row r="121" ht="100.5" customHeight="1">
+    <row r="121" ht="114" customHeight="1">
       <c r="A121" s="49" t="inlineStr">
         <is>
           <r>
@@ -27192,16 +27067,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-SE-102
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Camera calibration (calibrationd)</t>
+            <t xml:space="preserve">SWF-SE-090
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driving model process (modeld)</t>
           </r>
         </is>
       </c>
@@ -27214,16 +27089,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-FN-101
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Report camera calibration as valid only when the learned extrinsics match the mount</t>
+            <t xml:space="preserve">SWF-FN-090
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Publish model outputs (desired curvature, leads) for every road frame, computed from the current frame and calibration, and mark output that is not fit for use as invalid</t>
           </r>
         </is>
       </c>
@@ -27244,7 +27119,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Lateral control steers toward the lane boundary</t>
+            <t>Any lateral or longitudinal hazard within the panda envelope</t>
           </r>
           <r>
             <rPr>
@@ -27270,7 +27145,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>modeld warps the frames with a wrong pose; desired curvature biased</t>
+            <t>Outputs of an unvalidated model reach the controllers</t>
           </r>
           <r>
             <rPr>
@@ -27296,7 +27171,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>rpyCalib off by less than the recalibration thresholds</t>
+            <t>Driving or DM model weights or warp other than the analysed ones</t>
           </r>
         </is>
       </c>
@@ -27317,17 +27192,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-075 · corrupted
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Camera calibration reported valid while the extrinsics do not match the mount</t>
+            <t xml:space="preserve">SWF-074 · wrong_mode
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A model file other than the released one is loaded</t>
           </r>
         </is>
       </c>
@@ -27344,7 +27219,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Calibration learns only above 15 mph with a yaw rate below 2 deg/s and recalibrates only beyond the spread thresholds (calibrationd.py:33-46, 138-167, 190-201), so a mount that moved by less than the thresholds stays calibrated</t>
+            <t>Models are loaded with pickle and no hash, version or signature check (helpers.py:15-20; modeld.py:158-159; dmonitoringmodeld.py:22-48; GAP-22, TSR-616); they are compiled at build time from git-LFS sources (modeld/SConscript:41-52)</t>
           </r>
         </is>
       </c>
@@ -27356,36 +27231,36 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+            <t>• Build from pinned LFS objects; release procedure (WP-P-10) draft</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/modeld/SConscript</t>
           </r>
         </is>
       </c>
       <c r="J121" s="45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K121" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_calibrationd.py (CI) checks status transitions on synthetic data; targeted at the thresholds, not proven</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/locationd/test/test_calibrationd.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L121" s="45" t="n">
-        <v>8</v>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L121" s="54" t="n">
+        <v>10</v>
       </c>
       <c r="M121" s="52" t="inlineStr">
         <is>
@@ -27401,16 +27276,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-067 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+            <t xml:space="preserve">SWF-ACT-065 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
           </r>
         </is>
       </c>
@@ -27424,7 +27299,7 @@
       <c r="R121" s="48" t="inlineStr"/>
       <c r="S121" s="48" t="inlineStr"/>
     </row>
-    <row r="122" ht="127.5" customHeight="1">
+    <row r="122" ht="100.5" customHeight="1">
       <c r="A122" s="49" t="inlineStr">
         <is>
           <r>
@@ -27434,16 +27309,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-SE-103
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Online vehicle parameters (paramsd, torqued, lagd)</t>
+            <t xml:space="preserve">SWF-SE-102
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera calibration (calibrationd)</t>
           </r>
         </is>
       </c>
@@ -27456,16 +27331,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-FN-102
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Provide vehicle parameters within plausible bounds and report them invalid otherwise</t>
+            <t xml:space="preserve">SWF-FN-101
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Report camera calibration as valid only when the learned extrinsics match the mount</t>
           </r>
         </is>
       </c>
@@ -27486,7 +27361,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Lateral control steers toward the lane boundary or overshoots</t>
+            <t>Lateral control steers toward the lane boundary</t>
           </r>
           <r>
             <rPr>
@@ -27512,7 +27387,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Lateral controller gain or feed-forward wrong; vehicleParameters valid false raises paramsdTemporaryError only while calibrated</t>
+            <t>modeld warps the frames with a wrong pose; desired curvature biased</t>
           </r>
           <r>
             <rPr>
@@ -27538,7 +27413,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>steerRatio, stiffness, roll, angle offset, torque factor or lateral delay outside a plausible range</t>
+            <t>rpyCalib off by less than the recalibration thresholds</t>
           </r>
         </is>
       </c>
@@ -27559,17 +27434,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-076 · value_high
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Learned vehicle parameters implausible while used by controlsd</t>
+            <t xml:space="preserve">SWF-075 · corrupted
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera calibration reported valid while the extrinsics do not match the mount</t>
           </r>
         </is>
       </c>
@@ -27586,7 +27461,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>paramsd publishes values that are not clipped to its own validity bounds (paramsd.py:155-182), and controlsd uses steerRatio and stiffness with only a 0.1 floor and no validity gate (controlsd.py:88-91; SWF-042.C3)</t>
+            <t>Calibration learns only above 15 mph with a yaw rate below 2 deg/s and recalibrates only beyond the spread thresholds (calibrationd.py:33-46, 138-167, 190-201), so a mount that moved by less than the thresholds stays calibrated</t>
           </r>
         </is>
       </c>
@@ -27610,10 +27485,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_paramsd.py (CI) checks the saved-parameter handling; not designed for out-of-bound use</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_calibrationd.py (CI) checks status transitions on synthetic data; targeted at the thresholds, not proven</t>
           </r>
           <r>
             <rPr>
@@ -27622,12 +27497,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/locationd/test/test_paramsd.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L122" s="54" t="n">
-        <v>9</v>
+   openpilot/selfdrive/locationd/test/test_calibrationd.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L122" s="45" t="n">
+        <v>8</v>
       </c>
       <c r="M122" s="52" t="inlineStr">
         <is>
@@ -27643,16 +27518,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-045 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement TSR-605 margins on the host: bound latAccelOffset and torque parameters in controlsd, apply the acceleration rate limit after pitch compensation and the CarController PID, gate pitch compensation on a valid calibrated pose, and keep host torque/accel limits below the panda limits</t>
+            <t xml:space="preserve">SWF-ACT-067 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
           </r>
         </is>
       </c>
@@ -27666,7 +27541,7 @@
       <c r="R122" s="48" t="inlineStr"/>
       <c r="S122" s="48" t="inlineStr"/>
     </row>
-    <row r="123" ht="114" customHeight="1">
+    <row r="123" ht="127.5" customHeight="1">
       <c r="A123" s="49" t="inlineStr">
         <is>
           <r>
@@ -27676,16 +27551,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-SE-101
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>locationd pose filter</t>
+            <t xml:space="preserve">SWF-SE-103
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Online vehicle parameters (paramsd, torqued, lagd)</t>
           </r>
         </is>
       </c>
@@ -27698,16 +27573,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-FN-100
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Provide a calibrated pose from valid IMU and camera odometry, and report invalid inputs within the reaction time</t>
+            <t xml:space="preserve">SWF-FN-102
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide vehicle parameters within plausible bounds and report them invalid otherwise</t>
           </r>
         </is>
       </c>
@@ -27728,7 +27603,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Contributes to HZ-003 (roll compensation) and to an undetected excessive actuation</t>
+            <t>Lateral control steers toward the lane boundary or overshoots</t>
           </r>
           <r>
             <rPr>
@@ -27754,7 +27629,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Roll compensation, the excessive-actuation monitor and torqued work on a wrong pose</t>
+            <t>Lateral controller gain or feed-forward wrong; vehicleParameters valid false raises paramsdTemporaryError only while calibrated</t>
           </r>
           <r>
             <rPr>
@@ -27780,7 +27655,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>deviceMotion from an IMU that stopped or is implausible</t>
+            <t>steerRatio, stiffness, roll, angle offset, torque factor or lateral delay outside a plausible range</t>
           </r>
         </is>
       </c>
@@ -27801,17 +27676,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-077 · late
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>IMU or pose fault reported to the supervision late</t>
+            <t xml:space="preserve">SWF-076 · value_high
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Learned vehicle parameters implausible while used by controlsd</t>
           </r>
         </is>
       </c>
@@ -27828,7 +27703,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>selfdrived ignores accelerometer and gyro in its alive/valid checks and raises sensorDataInvalid only after 10 s without data (selfdrived.py:103, 456-458); deviceMotion.sensorsOK is not consumed by selfdrived (only paramsd and torqued)</t>
+            <t>paramsd publishes values that are not clipped to its own validity bounds (paramsd.py:155-182), and controlsd uses steerRatio and stiffness with only a 0.1 floor and no validity gate (controlsd.py:88-91; SWF-042.C3)</t>
           </r>
         </is>
       </c>
@@ -27845,7 +27720,7 @@
         </is>
       </c>
       <c r="J123" s="45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K123" s="44" t="inlineStr">
         <is>
@@ -27855,7 +27730,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_locationd_scenarios.py (CI; downloads a route) covers sensor faults in locationd; not designed for the selfdrived reaction time</t>
+            <t>• test_paramsd.py (CI) checks the saved-parameter handling; not designed for out-of-bound use</t>
           </r>
           <r>
             <rPr>
@@ -27864,7 +27739,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/locationd/test/test_locationd_scenarios.py</t>
+   openpilot/selfdrive/locationd/test/test_paramsd.py</t>
           </r>
         </is>
       </c>
@@ -27885,16 +27760,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-067 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+            <t xml:space="preserve">SWF-ACT-045 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-605 margins on the host: bound latAccelOffset and torque parameters in controlsd, apply the acceleration rate limit after pitch compensation and the CarController PID, gate pitch compensation on a valid calibrated pose, and keep host torque/accel limits below the panda limits</t>
           </r>
         </is>
       </c>
@@ -27908,52 +27783,52 @@
       <c r="R123" s="48" t="inlineStr"/>
       <c r="S123" s="48" t="inlineStr"/>
     </row>
-    <row r="124" ht="100.5" customHeight="1">
-      <c r="A124" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-110
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Camera acquisition (camerad)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B124" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-110
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Deliver every road, wide and driver camera frame once, in order and synchronised, and make a stopped or failed camera visible</t>
-          </r>
-        </is>
-      </c>
-      <c r="C124" s="30" t="inlineStr">
+    <row r="124" ht="114" customHeight="1">
+      <c r="A124" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-101
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>locationd pose filter</t>
+          </r>
+        </is>
+      </c>
+      <c r="B124" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-100
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Provide a calibrated pose from valid IMU and camera odometry, and report invalid inputs within the reaction time</t>
+          </r>
+        </is>
+      </c>
+      <c r="C124" s="49" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27970,7 +27845,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Lateral control from degraded model output</t>
+            <t>Contributes to HZ-003 (roll compensation) and to an undetected excessive actuation</t>
           </r>
           <r>
             <rPr>
@@ -27996,7 +27871,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>modeld runs on fewer or skewed frames (SWF-072); selfdrived cameraMalfunction / cameraFrameRate only when the rate or liveness fails</t>
+            <t>Roll compensation, the excessive-actuation monitor and torqued work on a wrong pose</t>
           </r>
           <r>
             <rPr>
@@ -28022,59 +27897,59 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Gaps in the frame stream, or main and wide frames out of sync</t>
-          </r>
-        </is>
-      </c>
-      <c r="D124" s="31" t="inlineStr">
+            <t>deviceMotion from an IMU that stopped or is implausible</t>
+          </r>
+        </is>
+      </c>
+      <c r="D124" s="50" t="inlineStr">
         <is>
           <t>HZ-003</t>
         </is>
       </c>
-      <c r="E124" s="32" t="n">
+      <c r="E124" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="F124" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-078 · omission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Road camera frames stop, are dropped or lose sync without an error flag</t>
-          </r>
-        </is>
-      </c>
-      <c r="G124" s="33" t="inlineStr">
+      <c r="F124" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-077 · late
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>IMU or pose fault reported to the supervision late</t>
+          </r>
+        </is>
+      </c>
+      <c r="G124" s="43" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H124" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>camerad never marks a frame invalid (messages default to valid, cereal/messaging/messaging.h:47); frames that fail sync or arrive out of order are dropped silently (spectra.cc:1407-1481), and a sensor that fails bring-up or an I2C write is only disabled with a log (spectra.cc:320-351)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I124" s="34" t="inlineStr">
+      <c r="H124" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>selfdrived ignores accelerometer and gyro in its alive/valid checks and raises sensorDataInvalid only after 10 s without data (selfdrived.py:103, 456-458); deviceMotion.sensorsOK is not consumed by selfdrived (only paramsd and torqued)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I124" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28086,10 +27961,10 @@
           </r>
         </is>
       </c>
-      <c r="J124" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K124" s="34" t="inlineStr">
+      <c r="J124" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K124" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28097,60 +27972,211 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_camerad.py (frame skips, sync, stress) is a hardware test, not run in LionDriver CI</t>
-          </r>
-        </is>
-      </c>
-      <c r="L124" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="M124" s="37" t="inlineStr">
+            <t>• test_locationd_scenarios.py (CI; downloads a route) covers sensor faults in locationd; not designed for the selfdrived reaction time</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/locationd/test/test_locationd_scenarios.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L124" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="M124" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N124" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-068 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Camera stream supervision: never ignore a road stream for the reference device (refuse engagement if it is absent at start), mark frames invalid on sync failure, and raise an event when a sensor is disabled; run the camerad hardware tests per release</t>
-          </r>
-        </is>
-      </c>
-      <c r="O124" s="38" t="inlineStr">
+      <c r="N124" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-067 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+          </r>
+        </is>
+      </c>
+      <c r="O124" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P124" s="33" t="inlineStr"/>
-      <c r="Q124" s="33" t="inlineStr"/>
-      <c r="R124" s="39" t="inlineStr"/>
-      <c r="S124" s="39" t="inlineStr"/>
+      <c r="P124" s="43" t="inlineStr"/>
+      <c r="Q124" s="43" t="inlineStr"/>
+      <c r="R124" s="48" t="inlineStr"/>
+      <c r="S124" s="48" t="inlineStr"/>
     </row>
     <row r="125" ht="100.5" customHeight="1">
-      <c r="A125" s="40" t="n"/>
-      <c r="B125" s="40" t="n"/>
-      <c r="C125" s="40" t="n"/>
-      <c r="D125" s="40" t="n"/>
-      <c r="E125" s="40" t="n"/>
-      <c r="F125" s="40" t="n"/>
+      <c r="A125" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-110
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera acquisition (camerad)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B125" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-110
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Deliver every road, wide and driver camera frame once, in order and synchronised, and make a stopped or failed camera visible</t>
+          </r>
+        </is>
+      </c>
+      <c r="C125" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral control from degraded model output</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>modeld runs on fewer or skewed frames (SWF-072); selfdrived cameraMalfunction / cameraFrameRate only when the rate or liveness fails</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Gaps in the frame stream, or main and wide frames out of sync</t>
+          </r>
+        </is>
+      </c>
+      <c r="D125" s="31" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E125" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F125" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-078 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Road camera frames stop, are dropped or lose sync without an error flag</t>
+          </r>
+        </is>
+      </c>
       <c r="G125" s="33" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="H125" s="34" t="inlineStr">
@@ -28161,7 +28187,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>If the narrow or wide road stream is absent when selfdrived initialises, it is put on the ignore_alive and ignore_valid lists for the whole drive (selfdrived.py:539-545), so a camera that is not up at start is never supervised</t>
+            <t>camerad never marks a frame invalid (messages default to valid, cereal/messaging/messaging.h:47); frames that fail sync or arrive out of order are dropped silently (spectra.cc:1407-1481), and a sensor that fails bring-up or an I2C write is only disabled with a log (spectra.cc:320-351)</t>
           </r>
         </is>
       </c>
@@ -28178,7 +28204,7 @@
         </is>
       </c>
       <c r="J125" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K125" s="34" t="inlineStr">
         <is>
@@ -28188,7 +28214,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• No test targets this cause</t>
+            <t>• test_camerad.py (frame skips, sync, stress) is a hardware test, not run in LionDriver CI</t>
           </r>
         </is>
       </c>
@@ -28233,30 +28259,30 @@
       <c r="S125" s="39" t="inlineStr"/>
     </row>
     <row r="126" ht="100.5" customHeight="1">
-      <c r="A126" s="42" t="n"/>
-      <c r="B126" s="42" t="n"/>
-      <c r="C126" s="42" t="n"/>
-      <c r="D126" s="42" t="n"/>
-      <c r="E126" s="42" t="n"/>
-      <c r="F126" s="42" t="n"/>
-      <c r="G126" s="43" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="H126" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>First-frame sync across cameras gives up after 40 frames and runs unsynchronised with only a log (spectra.cc:1550-1576); modeld only logs a main/wide skew over 10 ms (modeld.py:352-354)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I126" s="44" t="inlineStr">
+      <c r="A126" s="40" t="n"/>
+      <c r="B126" s="40" t="n"/>
+      <c r="C126" s="40" t="n"/>
+      <c r="D126" s="40" t="n"/>
+      <c r="E126" s="40" t="n"/>
+      <c r="F126" s="40" t="n"/>
+      <c r="G126" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H126" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>If the narrow or wide road stream is absent when selfdrived initialises, it is put on the ignore_alive and ignore_valid lists for the whole drive (selfdrived.py:539-545), so a camera that is not up at start is never supervised</t>
+          </r>
+        </is>
+      </c>
+      <c r="I126" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28268,10 +28294,10 @@
           </r>
         </is>
       </c>
-      <c r="J126" s="45" t="n">
+      <c r="J126" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="K126" s="44" t="inlineStr">
+      <c r="K126" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28283,15 +28309,15 @@
           </r>
         </is>
       </c>
-      <c r="L126" s="54" t="n">
+      <c r="L126" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M126" s="52" t="inlineStr">
+      <c r="M126" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N126" s="44" t="inlineStr">
+      <c r="N126" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28313,168 +28339,26 @@
           </r>
         </is>
       </c>
-      <c r="O126" s="53" t="inlineStr">
+      <c r="O126" s="38" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P126" s="43" t="inlineStr"/>
-      <c r="Q126" s="43" t="inlineStr"/>
-      <c r="R126" s="48" t="inlineStr"/>
-      <c r="S126" s="48" t="inlineStr"/>
+      <c r="P126" s="33" t="inlineStr"/>
+      <c r="Q126" s="33" t="inlineStr"/>
+      <c r="R126" s="39" t="inlineStr"/>
+      <c r="S126" s="39" t="inlineStr"/>
     </row>
     <row r="127" ht="100.5" customHeight="1">
-      <c r="A127" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-120
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>IMU acquisition (sensord)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B127" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-120
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Deliver accelerometer and gyro samples with correct timestamps, and mark implausible data invalid</t>
-          </r>
-        </is>
-      </c>
-      <c r="C127" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-003 through a wrong pose (SWF-077)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>locationd rejects them only if they fail its norm and cross-checks</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Accelerometer or gyro values out of range or repeated with valid true</t>
-          </r>
-        </is>
-      </c>
-      <c r="D127" s="50" t="inlineStr">
-        <is>
-          <t>HZ-003</t>
-        </is>
-      </c>
-      <c r="E127" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F127" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-079 · value_frozen
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>IMU samples implausible or stuck while published as valid</t>
-          </r>
-        </is>
-      </c>
+      <c r="A127" s="42" t="n"/>
+      <c r="B127" s="42" t="n"/>
+      <c r="C127" s="42" t="n"/>
+      <c r="D127" s="42" t="n"/>
+      <c r="E127" s="42" t="n"/>
+      <c r="F127" s="42" t="n"/>
       <c r="G127" s="43" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="H127" s="44" t="inlineStr">
@@ -28485,7 +28369,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No range, stuck-value or plausibility check at the source: every sample after the 0.5 s warm-up is valid (sensord.py:68-70; i2c_sensor.py:58-63); init and read errors are logged and sensord keeps running without the sensor (sensord.py:73-76, 104-126); self-test only with LSM_SELF_TEST=1</t>
+            <t>First-frame sync across cameras gives up after 40 frames and runs unsynchronised with only a log (spectra.cc:1550-1576); modeld only logs a main/wide skew over 10 ms (modeld.py:352-354)</t>
           </r>
         </is>
       </c>
@@ -28502,7 +28386,7 @@
         </is>
       </c>
       <c r="J127" s="45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K127" s="44" t="inlineStr">
         <is>
@@ -28512,7 +28396,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_sensord.py is a hardware test, not run in LionDriver CI</t>
+            <t>• No test targets this cause</t>
           </r>
         </is>
       </c>
@@ -28533,16 +28417,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-067 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+            <t xml:space="preserve">SWF-ACT-068 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera stream supervision: never ignore a road stream for the reference device (refuse engagement if it is absent at start), mark frames invalid on sync failure, and raise an event when a sensor is disabled; run the camerad hardware tests per release</t>
           </r>
         </is>
       </c>
@@ -28556,8 +28440,241 @@
       <c r="R127" s="48" t="inlineStr"/>
       <c r="S127" s="48" t="inlineStr"/>
     </row>
-    <row r="128" ht="195" customHeight="1">
-      <c r="A128" s="30" t="inlineStr">
+    <row r="128" ht="100.5" customHeight="1">
+      <c r="A128" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-120
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>IMU acquisition (sensord)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B128" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-120
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Deliver accelerometer and gyro samples with correct timestamps, and mark implausible data invalid</t>
+          </r>
+        </is>
+      </c>
+      <c r="C128" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-003 through a wrong pose (SWF-077)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>locationd rejects them only if they fail its norm and cross-checks</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Accelerometer or gyro values out of range or repeated with valid true</t>
+          </r>
+        </is>
+      </c>
+      <c r="D128" s="50" t="inlineStr">
+        <is>
+          <t>HZ-003</t>
+        </is>
+      </c>
+      <c r="E128" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-079 · value_frozen
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>IMU samples implausible or stuck while published as valid</t>
+          </r>
+        </is>
+      </c>
+      <c r="G128" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H128" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No range, stuck-value or plausibility check at the source: every sample after the 0.5 s warm-up is valid (sensord.py:68-70; i2c_sensor.py:58-63); init and read errors are logged and sensord keeps running without the sensor (sensord.py:73-76, 104-126); self-test only with LSM_SELF_TEST=1</t>
+          </r>
+        </is>
+      </c>
+      <c r="I128" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J128" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K128" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_sensord.py is a hardware test, not run in LionDriver CI</t>
+          </r>
+        </is>
+      </c>
+      <c r="L128" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M128" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N128" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-067 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
+          </r>
+        </is>
+      </c>
+      <c r="O128" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P128" s="43" t="inlineStr"/>
+      <c r="Q128" s="43" t="inlineStr"/>
+      <c r="R128" s="48" t="inlineStr"/>
+      <c r="S128" s="48" t="inlineStr"/>
+    </row>
+    <row r="129" ht="195" customHeight="1">
+      <c r="A129" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28579,7 +28696,7 @@
           </r>
         </is>
       </c>
-      <c r="B128" s="30" t="inlineStr">
+      <c r="B129" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28601,7 +28718,7 @@
           </r>
         </is>
       </c>
-      <c r="C128" s="30" t="inlineStr">
+      <c r="C129" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28674,15 +28791,15 @@
           </r>
         </is>
       </c>
-      <c r="D128" s="31" t="inlineStr">
+      <c r="D129" s="31" t="inlineStr">
         <is>
           <t>HZ-003</t>
         </is>
       </c>
-      <c r="E128" s="32" t="n">
+      <c r="E129" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F128" s="30" t="inlineStr">
+      <c r="F129" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28705,12 +28822,12 @@
           </r>
         </is>
       </c>
-      <c r="G128" s="33" t="inlineStr">
+      <c r="G129" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H128" s="34" t="inlineStr">
+      <c r="H129" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28722,7 +28839,7 @@
           </r>
         </is>
       </c>
-      <c r="I128" s="34" t="inlineStr">
+      <c r="I129" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28734,10 +28851,10 @@
           </r>
         </is>
       </c>
-      <c r="J128" s="35" t="n">
+      <c r="J129" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="K128" s="34" t="inlineStr">
+      <c r="K129" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28749,15 +28866,15 @@
           </r>
         </is>
       </c>
-      <c r="L128" s="36" t="n">
+      <c r="L129" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M128" s="37" t="inlineStr">
+      <c r="M129" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N128" s="34" t="inlineStr">
+      <c r="N129" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28806,30 +28923,30 @@
           </r>
         </is>
       </c>
-      <c r="O128" s="38" t="inlineStr">
+      <c r="O129" s="38" t="inlineStr">
         <is>
           <t>open
 open</t>
         </is>
       </c>
-      <c r="P128" s="33" t="inlineStr"/>
-      <c r="Q128" s="33" t="inlineStr"/>
-      <c r="R128" s="39" t="inlineStr"/>
-      <c r="S128" s="39" t="inlineStr"/>
+      <c r="P129" s="33" t="inlineStr"/>
+      <c r="Q129" s="33" t="inlineStr"/>
+      <c r="R129" s="39" t="inlineStr"/>
+      <c r="S129" s="39" t="inlineStr"/>
     </row>
-    <row r="129" ht="195" customHeight="1">
-      <c r="A129" s="42" t="n"/>
-      <c r="B129" s="42" t="n"/>
-      <c r="C129" s="42" t="n"/>
-      <c r="D129" s="42" t="n"/>
-      <c r="E129" s="42" t="n"/>
-      <c r="F129" s="42" t="n"/>
-      <c r="G129" s="43" t="inlineStr">
+    <row r="130" ht="195" customHeight="1">
+      <c r="A130" s="42" t="n"/>
+      <c r="B130" s="42" t="n"/>
+      <c r="C130" s="42" t="n"/>
+      <c r="D130" s="42" t="n"/>
+      <c r="E130" s="42" t="n"/>
+      <c r="F130" s="42" t="n"/>
+      <c r="G130" s="43" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H129" s="44" t="inlineStr">
+      <c r="H130" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28841,7 +28958,7 @@
           </r>
         </is>
       </c>
-      <c r="I129" s="44" t="inlineStr">
+      <c r="I130" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28853,10 +28970,10 @@
           </r>
         </is>
       </c>
-      <c r="J129" s="45" t="n">
+      <c r="J130" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="K129" s="44" t="inlineStr">
+      <c r="K130" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28868,15 +28985,15 @@
           </r>
         </is>
       </c>
-      <c r="L129" s="54" t="n">
+      <c r="L130" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="M129" s="52" t="inlineStr">
+      <c r="M130" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N129" s="44" t="inlineStr">
+      <c r="N130" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28925,268 +29042,18 @@
           </r>
         </is>
       </c>
-      <c r="O129" s="53" t="inlineStr">
+      <c r="O130" s="53" t="inlineStr">
         <is>
           <t>open
 open</t>
         </is>
       </c>
-      <c r="P129" s="43" t="inlineStr"/>
-      <c r="Q129" s="43" t="inlineStr"/>
-      <c r="R129" s="48" t="inlineStr"/>
-      <c r="S129" s="48" t="inlineStr"/>
-    </row>
-    <row r="130" ht="141" customHeight="1">
-      <c r="A130" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-131
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SubMaster liveness and validity</t>
-          </r>
-        </is>
-      </c>
-      <c r="B130" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-130
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Report an input as alive and valid only while it is received at its rate and flagged valid</t>
-          </r>
-        </is>
-      </c>
-      <c r="C130" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-003 and HZ-007 (control on held inputs)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Consumers act on held values for 0.1 s (100 Hz) to 1 s (10 Hz pandaStates) before any reaction</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SubMaster.alive true for up to 10 periods after the last message; freq_ok true on a 10 s or 1 s average</t>
-          </r>
-        </is>
-      </c>
-      <c r="D130" s="50" t="inlineStr">
-        <is>
-          <t>HZ-003</t>
-        </is>
-      </c>
-      <c r="E130" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F130" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-081 · value_stale
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>An input is reported alive and valid while it is stale</t>
-          </r>
-        </is>
-      </c>
-      <c r="G130" s="43" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H130" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>By design alive means received within 10 nominal periods and freq_ok passes if the 10 s or the 1 s average is within 0.8..1.2 of the rate (__init__.py:138-178, 265-278); TSR-602 asks 2 periods. SIMULATION=1 relaxes both checks (__init__.py:213, 265-266)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I130" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
-          </r>
-        </is>
-      </c>
-      <c r="J130" s="45" t="n">
-        <v>7</v>
-      </c>
-      <c r="K130" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_pub_sub_master.py (CI) tests the alive and valid semantics; targeted at the mechanism, not at the bound</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/cereal/messaging/tests/test_pub_sub_master.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L130" s="45" t="n">
-        <v>8</v>
-      </c>
-      <c r="M130" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N130" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-040 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement TSR-602 in controlsd: check age and valid of selfdriveState, carState, modelV2, longitudinalPlan, vehicleParameters and deviceMotion before use (≤ 2 periods); set latActive/longActive false and raise an immediate-disable event when stale; derive carControl.valid from these checks and have card stop actuating on carControl.valid false; give cruiseMismatch a disable type</t>
-          </r>
-        </is>
-      </c>
-      <c r="O130" s="55" t="inlineStr">
-        <is>
-          <t>in progress</t>
-        </is>
-      </c>
-      <c r="P130" s="43" t="inlineStr">
-        <is>
-          <t>10/3/4</t>
-        </is>
-      </c>
-      <c r="Q130" s="46" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="P130" s="43" t="inlineStr"/>
+      <c r="Q130" s="43" t="inlineStr"/>
       <c r="R130" s="48" t="inlineStr"/>
       <c r="S130" s="48" t="inlineStr"/>
     </row>
-    <row r="131" ht="181.5" customHeight="1">
+    <row r="131" ht="141" customHeight="1">
       <c r="A131" s="49" t="inlineStr">
         <is>
           <r>
@@ -29196,16 +29063,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-SE-140
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Process manager (manager)</t>
+            <t xml:space="preserve">SWF-SE-131
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SubMaster liveness and validity</t>
           </r>
         </is>
       </c>
@@ -29218,16 +29085,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-FN-140
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Run every process the configuration needs and report any that is not running</t>
+            <t xml:space="preserve">SWF-FN-130
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Report an input as alive and valid only while it is received at its rate and flagged valid</t>
           </r>
         </is>
       </c>
@@ -29248,7 +29115,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Take-over alerts not presented while the item runs</t>
+            <t>Contributes to HZ-003 and HZ-007 (control on held inputs)</t>
           </r>
           <r>
             <rPr>
@@ -29266,15 +29133,15 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-013 (driver-monitoring alerts not presented when soundd or ui is not running; the forced stop does not depend on them)</t>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Consumers act on held values for 0.1 s (100 Hz) to 1 s (10 Hz pandaStates) before any reaction</t>
           </r>
           <r>
             <rPr>
@@ -29292,32 +29159,6 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>No processNotRunning event; a process that selfdrived does not subscribe to (soundd, ui) is then not supervised at all</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
             <t xml:space="preserve">Local  </t>
           </r>
           <r>
@@ -29326,14 +29167,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>A process blocked or never started has no process entry, so managerState shows shouldBeRunning false</t>
+            <t>SubMaster.alive true for up to 10 periods after the last message; freq_ok true on a 10 s or 1 s average</t>
           </r>
         </is>
       </c>
       <c r="D131" s="50" t="inlineStr">
         <is>
-          <t>HZ-012
-HZ-013</t>
+          <t>HZ-003</t>
         </is>
       </c>
       <c r="E131" s="51" t="n">
@@ -29348,17 +29188,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-082 · omission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>A process the drive needs is not running and is not reported</t>
+            <t xml:space="preserve">SWF-081 · value_stale
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>An input is reported alive and valid while it is stale</t>
           </r>
         </is>
       </c>
@@ -29375,7 +29215,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The BLOCK environment variable or a process that never starts leaves proc None, so shouldBeRunning is false and no event fires (manager.py:110-112; process.py:121-129)</t>
+            <t>By design alive means received within 10 nominal periods and freq_ok passes if the 10 s or the 1 s average is within 0.8..1.2 of the rate (__init__.py:138-178, 265-278); TSR-602 asks 2 periods. SIMULATION=1 relaxes both checks (__init__.py:213, 265-266)</t>
           </r>
         </is>
       </c>
@@ -29387,7 +29227,22 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• No launch path sets BLOCK; setting it needs a shell on the device</t>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J131" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K131" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_pub_sub_master.py (CI) tests the alive and valid semantics; targeted at the mechanism, not at the bound</t>
           </r>
           <r>
             <rPr>
@@ -29396,36 +29251,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/system/manager/manager.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="J131" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K131" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_manager.py (CI) checks blacklisted processes do not start; not designed for the missing report</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/system/manager/test/test_manager.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L131" s="54" t="n">
-        <v>9</v>
+   openpilot/cereal/messaging/tests/test_pub_sub_master.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L131" s="45" t="n">
+        <v>8</v>
       </c>
       <c r="M131" s="52" t="inlineStr">
         <is>
@@ -29441,30 +29272,38 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-070 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only. WP-A-03 DFI-25</t>
-          </r>
-        </is>
-      </c>
-      <c r="O131" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P131" s="43" t="inlineStr"/>
-      <c r="Q131" s="43" t="inlineStr"/>
+            <t xml:space="preserve">SWF-ACT-040 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-602 in controlsd: check age and valid of selfdriveState, carState, modelV2, longitudinalPlan, vehicleParameters and deviceMotion before use (≤ 2 periods); set latActive/longActive false and raise an immediate-disable event when stale; derive carControl.valid from these checks and have card stop actuating on carControl.valid false; give cruiseMismatch a disable type</t>
+          </r>
+        </is>
+      </c>
+      <c r="O131" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+      <c r="P131" s="43" t="inlineStr">
+        <is>
+          <t>10/3/4</t>
+        </is>
+      </c>
+      <c r="Q131" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="R131" s="48" t="inlineStr"/>
       <c r="S131" s="48" t="inlineStr"/>
     </row>
-    <row r="132" ht="114" customHeight="1">
+    <row r="132" ht="181.5" customHeight="1">
       <c r="A132" s="49" t="inlineStr">
         <is>
           <r>
@@ -29526,7 +29365,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Item unavailable after one crash, with an alert</t>
+            <t>Take-over alerts not presented while the item runs</t>
           </r>
           <r>
             <rPr>
@@ -29544,6 +29383,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-013 (driver-monitoring alerts not presented when soundd or ui is not running; the forced stop does not depend on them)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -29552,7 +29417,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>processNotRunning (SOFT_DISABLE, NO_ENTRY) for the rest of the drive</t>
+            <t>No processNotRunning event; a process that selfdrived does not subscribe to (soundd, ui) is then not supervised at all</t>
           </r>
           <r>
             <rPr>
@@ -29578,13 +29443,18 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No restart and no watchdog: start() returns while proc is set, so the process is restarted only after an offroad transition</t>
-          </r>
-        </is>
-      </c>
-      <c r="D132" s="50" t="inlineStr"/>
+            <t>A process blocked or never started has no process entry, so managerState shows shouldBeRunning false</t>
+          </r>
+        </is>
+      </c>
+      <c r="D132" s="50" t="inlineStr">
+        <is>
+          <t>HZ-012
+HZ-013</t>
+        </is>
+      </c>
       <c r="E132" s="51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F132" s="49" t="inlineStr">
         <is>
@@ -29595,17 +29465,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-083 · omission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>A crashed process stays down for the rest of the drive</t>
+            <t xml:space="preserve">SWF-082 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A process the drive needs is not running and is not reported</t>
           </r>
         </is>
       </c>
@@ -29622,7 +29492,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>By design manager has no restart policy or process watchdog (process.py:142-154, 223-238)</t>
+            <t>The BLOCK environment variable or a process that never starts leaves proc None, so shouldBeRunning is false and no event fires (manager.py:110-112; process.py:121-129)</t>
           </r>
         </is>
       </c>
@@ -29634,12 +29504,21 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+            <t>• No launch path sets BLOCK; setting it needs a shell on the device</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/manager.py</t>
           </r>
         </is>
       </c>
       <c r="J132" s="45" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K132" s="44" t="inlineStr">
         <is>
@@ -29649,7 +29528,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_manager.py (CI); test_clean_exit is skipped; nothing tests restart behaviour</t>
+            <t>• test_manager.py (CI) checks blacklisted processes do not start; not designed for the missing report</t>
           </r>
           <r>
             <rPr>
@@ -29702,7 +29581,7 @@
       <c r="R132" s="48" t="inlineStr"/>
       <c r="S132" s="48" t="inlineStr"/>
     </row>
-    <row r="133" ht="141" customHeight="1">
+    <row r="133" ht="114" customHeight="1">
       <c r="A133" s="49" t="inlineStr">
         <is>
           <r>
@@ -29712,16 +29591,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-SE-150
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Software update (updated)</t>
+            <t xml:space="preserve">SWF-SE-140
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Process manager (manager)</t>
           </r>
         </is>
       </c>
@@ -29734,16 +29613,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-FN-150
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Install only the released, assured software version, and never change running software while driving</t>
+            <t xml:space="preserve">SWF-FN-140
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Run every process the configuration needs and report any that is not running</t>
           </r>
         </is>
       </c>
@@ -29764,7 +29643,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Unassured host and panda software drives the car</t>
+            <t>Item unavailable after one crash, with an alert</t>
           </r>
           <r>
             <rPr>
@@ -29782,15 +29661,15 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-006 (deceleration checked by an unassured envelope)</t>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>processNotRunning (SOFT_DISABLE, NO_ENTRY) for the rest of the drive</t>
           </r>
           <r>
             <rPr>
@@ -29808,32 +29687,6 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>It is swapped in at the next boot; pandad flashes the panda build of that checkout</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
             <t xml:space="preserve">Local  </t>
           </r>
           <r>
@@ -29842,18 +29695,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The finalized overlay holds another commit of the tracked branch, or of another remote</t>
-          </r>
-        </is>
-      </c>
-      <c r="D133" s="50" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-006</t>
-        </is>
-      </c>
+            <t>No restart and no watchdog: start() returns while proc is set, so the process is restarted only after an offroad transition</t>
+          </r>
+        </is>
+      </c>
+      <c r="D133" s="50" t="inlineStr"/>
       <c r="E133" s="51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F133" s="49" t="inlineStr">
         <is>
@@ -29864,17 +29712,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-084 · wrong_mode
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>An update installs software other than the released, assured version</t>
+            <t xml:space="preserve">SWF-083 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A crashed process stays down for the rest of the drive</t>
           </r>
         </is>
       </c>
@@ -29891,7 +29739,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No signature or commit-pin check: updated fetches the UpdaterTargetBranch (or the current branch) from the install's origin and trusts the git transport (updated.py:237-248, 343-410); there is no automatic rollback (launch_chffrplus.sh:52-65)</t>
+            <t>By design manager has no restart policy or process watchdog (process.py:142-154, 223-238)</t>
           </r>
         </is>
       </c>
@@ -29908,7 +29756,7 @@
         </is>
       </c>
       <c r="J133" s="45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K133" s="44" t="inlineStr">
         <is>
@@ -29918,12 +29766,21 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• No updated tests exist</t>
+            <t>• test_manager.py (CI); test_clean_exit is skipped; nothing tests restart behaviour</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/test/test_manager.py</t>
           </r>
         </is>
       </c>
       <c r="L133" s="54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M133" s="52" t="inlineStr">
         <is>
@@ -29939,16 +29796,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-ACT-071 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Update integrity: pin the update to signed release tags of the LionDriver repository and verify the signature before finalizing; define rollback (with the PFMEA OTA steps)</t>
+            <t xml:space="preserve">SWF-ACT-070 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only. WP-A-03 DFI-25</t>
           </r>
         </is>
       </c>
@@ -29962,8 +29819,268 @@
       <c r="R133" s="48" t="inlineStr"/>
       <c r="S133" s="48" t="inlineStr"/>
     </row>
-    <row r="134" ht="222" customHeight="1">
-      <c r="A134" s="30" t="inlineStr">
+    <row r="134" ht="141" customHeight="1">
+      <c r="A134" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-150
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Software update (updated)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B134" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-150
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Install only the released, assured software version, and never change running software while driving</t>
+          </r>
+        </is>
+      </c>
+      <c r="C134" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unassured host and panda software drives the car</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006 (deceleration checked by an unassured envelope)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>It is swapped in at the next boot; pandad flashes the panda build of that checkout</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The finalized overlay holds another commit of the tracked branch, or of another remote</t>
+          </r>
+        </is>
+      </c>
+      <c r="D134" s="50" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E134" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F134" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-084 · wrong_mode
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>An update installs software other than the released, assured version</t>
+          </r>
+        </is>
+      </c>
+      <c r="G134" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H134" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No signature or commit-pin check: updated fetches the UpdaterTargetBranch (or the current branch) from the install's origin and trusts the git transport (updated.py:237-248, 343-410); there is no automatic rollback (launch_chffrplus.sh:52-65)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I134" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirements for the element; no field-exposure credit (RT-1 §2.2)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J134" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K134" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No updated tests exist</t>
+          </r>
+        </is>
+      </c>
+      <c r="L134" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M134" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N134" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-071 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Update integrity: pin the update to signed release tags of the LionDriver repository and verify the signature before finalizing; define rollback (with the PFMEA OTA steps)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O134" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P134" s="43" t="inlineStr"/>
+      <c r="Q134" s="43" t="inlineStr"/>
+      <c r="R134" s="48" t="inlineStr"/>
+      <c r="S134" s="48" t="inlineStr"/>
+    </row>
+    <row r="135" ht="222" customHeight="1">
+      <c r="A135" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29985,7 +30102,7 @@
           </r>
         </is>
       </c>
-      <c r="B134" s="30" t="inlineStr">
+      <c r="B135" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30007,7 +30124,7 @@
           </r>
         </is>
       </c>
-      <c r="C134" s="30" t="inlineStr">
+      <c r="C135" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30080,15 +30197,15 @@
           </r>
         </is>
       </c>
-      <c r="D134" s="31" t="inlineStr">
+      <c r="D135" s="31" t="inlineStr">
         <is>
           <t>HZ-013</t>
         </is>
       </c>
-      <c r="E134" s="32" t="n">
+      <c r="E135" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F134" s="30" t="inlineStr">
+      <c r="F135" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30111,12 +30228,12 @@
           </r>
         </is>
       </c>
-      <c r="G134" s="33" t="inlineStr">
+      <c r="G135" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H134" s="34" t="inlineStr">
+      <c r="H135" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30128,7 +30245,7 @@
           </r>
         </is>
       </c>
-      <c r="I134" s="34" t="inlineStr">
+      <c r="I135" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30149,10 +30266,10 @@
           </r>
         </is>
       </c>
-      <c r="J134" s="35" t="n">
+      <c r="J135" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="K134" s="34" t="inlineStr">
+      <c r="K135" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30164,15 +30281,15 @@
           </r>
         </is>
       </c>
-      <c r="L134" s="36" t="n">
+      <c r="L135" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M134" s="37" t="inlineStr">
+      <c r="M135" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N134" s="34" t="inlineStr">
+      <c r="N135" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30221,30 +30338,30 @@
           </r>
         </is>
       </c>
-      <c r="O134" s="38" t="inlineStr">
+      <c r="O135" s="38" t="inlineStr">
         <is>
           <t>open
 open</t>
         </is>
       </c>
-      <c r="P134" s="33" t="inlineStr"/>
-      <c r="Q134" s="33" t="inlineStr"/>
-      <c r="R134" s="39" t="inlineStr"/>
-      <c r="S134" s="39" t="inlineStr"/>
+      <c r="P135" s="33" t="inlineStr"/>
+      <c r="Q135" s="33" t="inlineStr"/>
+      <c r="R135" s="39" t="inlineStr"/>
+      <c r="S135" s="39" t="inlineStr"/>
     </row>
-    <row r="135" ht="114" customHeight="1">
-      <c r="A135" s="42" t="n"/>
-      <c r="B135" s="42" t="n"/>
-      <c r="C135" s="42" t="n"/>
-      <c r="D135" s="42" t="n"/>
-      <c r="E135" s="42" t="n"/>
-      <c r="F135" s="42" t="n"/>
-      <c r="G135" s="43" t="inlineStr">
+    <row r="136" ht="114" customHeight="1">
+      <c r="A136" s="42" t="n"/>
+      <c r="B136" s="42" t="n"/>
+      <c r="C136" s="42" t="n"/>
+      <c r="D136" s="42" t="n"/>
+      <c r="E136" s="42" t="n"/>
+      <c r="F136" s="42" t="n"/>
+      <c r="G136" s="43" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H135" s="44" t="inlineStr">
+      <c r="H136" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30256,7 +30373,7 @@
           </r>
         </is>
       </c>
-      <c r="I135" s="44" t="inlineStr">
+      <c r="I136" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30277,10 +30394,10 @@
           </r>
         </is>
       </c>
-      <c r="J135" s="45" t="n">
+      <c r="J136" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="K135" s="44" t="inlineStr">
+      <c r="K136" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30292,15 +30409,15 @@
           </r>
         </is>
       </c>
-      <c r="L135" s="54" t="n">
+      <c r="L136" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="M135" s="52" t="inlineStr">
+      <c r="M136" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N135" s="44" t="inlineStr">
+      <c r="N136" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30322,18 +30439,18 @@
           </r>
         </is>
       </c>
-      <c r="O135" s="53" t="inlineStr">
+      <c r="O136" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P135" s="43" t="inlineStr"/>
-      <c r="Q135" s="43" t="inlineStr"/>
-      <c r="R135" s="48" t="inlineStr"/>
-      <c r="S135" s="48" t="inlineStr"/>
+      <c r="P136" s="43" t="inlineStr"/>
+      <c r="Q136" s="43" t="inlineStr"/>
+      <c r="R136" s="48" t="inlineStr"/>
+      <c r="S136" s="48" t="inlineStr"/>
     </row>
-    <row r="136" ht="154.5" customHeight="1">
-      <c r="A136" s="30" t="inlineStr">
+    <row r="137" ht="154.5" customHeight="1">
+      <c r="A137" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30355,7 +30472,7 @@
           </r>
         </is>
       </c>
-      <c r="B136" s="30" t="inlineStr">
+      <c r="B137" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30377,7 +30494,7 @@
           </r>
         </is>
       </c>
-      <c r="C136" s="30" t="inlineStr">
+      <c r="C137" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30450,15 +30567,15 @@
           </r>
         </is>
       </c>
-      <c r="D136" s="31" t="inlineStr">
+      <c r="D137" s="31" t="inlineStr">
         <is>
           <t>HZ-013</t>
         </is>
       </c>
-      <c r="E136" s="32" t="n">
+      <c r="E137" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F136" s="30" t="inlineStr">
+      <c r="F137" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30481,12 +30598,12 @@
           </r>
         </is>
       </c>
-      <c r="G136" s="33" t="inlineStr">
+      <c r="G137" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H136" s="34" t="inlineStr">
+      <c r="H137" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30498,7 +30615,7 @@
           </r>
         </is>
       </c>
-      <c r="I136" s="34" t="inlineStr">
+      <c r="I137" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30510,10 +30627,10 @@
           </r>
         </is>
       </c>
-      <c r="J136" s="35" t="n">
+      <c r="J137" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="K136" s="34" t="inlineStr">
+      <c r="K137" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30534,15 +30651,15 @@
           </r>
         </is>
       </c>
-      <c r="L136" s="36" t="n">
+      <c r="L137" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="M136" s="37" t="inlineStr">
+      <c r="M137" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N136" s="34" t="inlineStr">
+      <c r="N137" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30564,29 +30681,29 @@
           </r>
         </is>
       </c>
-      <c r="O136" s="38" t="inlineStr">
+      <c r="O137" s="38" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P136" s="33" t="inlineStr"/>
-      <c r="Q136" s="33" t="inlineStr"/>
-      <c r="R136" s="39" t="inlineStr"/>
-      <c r="S136" s="39" t="inlineStr"/>
+      <c r="P137" s="33" t="inlineStr"/>
+      <c r="Q137" s="33" t="inlineStr"/>
+      <c r="R137" s="39" t="inlineStr"/>
+      <c r="S137" s="39" t="inlineStr"/>
     </row>
-    <row r="137" ht="262.5" customHeight="1">
-      <c r="A137" s="42" t="n"/>
-      <c r="B137" s="42" t="n"/>
-      <c r="C137" s="42" t="n"/>
-      <c r="D137" s="42" t="n"/>
-      <c r="E137" s="42" t="n"/>
-      <c r="F137" s="42" t="n"/>
-      <c r="G137" s="43" t="inlineStr">
+    <row r="138" ht="262.5" customHeight="1">
+      <c r="A138" s="42" t="n"/>
+      <c r="B138" s="42" t="n"/>
+      <c r="C138" s="42" t="n"/>
+      <c r="D138" s="42" t="n"/>
+      <c r="E138" s="42" t="n"/>
+      <c r="F138" s="42" t="n"/>
+      <c r="G138" s="43" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H137" s="44" t="inlineStr">
+      <c r="H138" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30598,7 +30715,7 @@
           </r>
         </is>
       </c>
-      <c r="I137" s="44" t="inlineStr">
+      <c r="I138" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30619,10 +30736,10 @@
           </r>
         </is>
       </c>
-      <c r="J137" s="45" t="n">
+      <c r="J138" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="K137" s="44" t="inlineStr">
+      <c r="K138" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30643,15 +30760,15 @@
           </r>
         </is>
       </c>
-      <c r="L137" s="45" t="n">
+      <c r="L138" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="M137" s="52" t="inlineStr">
+      <c r="M138" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N137" s="44" t="inlineStr">
+      <c r="N138" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30700,252 +30817,10 @@
           </r>
         </is>
       </c>
-      <c r="O137" s="53" t="inlineStr">
+      <c r="O138" s="53" t="inlineStr">
         <is>
           <t>open
 open</t>
-        </is>
-      </c>
-      <c r="P137" s="43" t="inlineStr"/>
-      <c r="Q137" s="43" t="inlineStr"/>
-      <c r="R137" s="48" t="inlineStr"/>
-      <c r="S137" s="48" t="inlineStr"/>
-    </row>
-    <row r="138" ht="208.5" customHeight="1">
-      <c r="A138" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-006
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Steering torque checks</t>
-          </r>
-        </is>
-      </c>
-      <c r="B138" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-014
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Back steering torque off toward zero while the driver overrides, and reject frames that increase torque opposing the driver beyond a driver allowance (TSR-304; not implemented on the LKA path)</t>
-          </r>
-        </is>
-      </c>
-      <c r="C138" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Item resists the driver's steering within the panda torque bound</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The only override check is the host's MAX_USER_TORQUE of 500 units (carcontroller.py:33, 83); with a host fault, or below 500 units by design (SWF-038), torque up to the 1500 limit keeps opposing the driver</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>STEERING_LKA (0x2E4) frames that oppose the driver pass: the Toyota LKA check is magnitude, rate and measured-torque error only (TorqueMotorLimited); STEER_TORQUE_DRIVER is decoded (toyota.h:221-223) but used only on the LTA path (toyota.h:421-424)</t>
-          </r>
-        </is>
-      </c>
-      <c r="D138" s="50" t="inlineStr">
-        <is>
-          <t>HZ-009</t>
-        </is>
-      </c>
-      <c r="E138" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F138" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-087 · omission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Envelope passes LKA torque that opposes the driver while the driver overrides the steering</t>
-          </r>
-        </is>
-      </c>
-      <c r="G138" s="43" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H138" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>By design the envelope has no driver-override check on the LKA path (GAP-02): TSR-304 (driver allowance, and back-off while the driver torque exceeds T_ovr; decided as DQ-053, 2026-10-14) is not implemented in toyota.h, in either build</t>
-          </r>
-        </is>
-      </c>
-      <c r="I138" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream design (a bounded torque the driver can overpower); requirement TSR-304 not implemented, so O 8 (RT-2 §2), as the other by-design gaps</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/modes/toyota.h</t>
-          </r>
-        </is>
-      </c>
-      <c r="J138" s="45" t="n">
-        <v>8</v>
-      </c>
-      <c r="K138" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_toyota.py tests the measured-torque limit (MotorTorqueSteeringSafetyTest, MAX_TORQUE_ERROR 350); no test of torque opposing the driver on the LKA path</t>
-          </r>
-        </is>
-      </c>
-      <c r="L138" s="54" t="n">
-        <v>10</v>
-      </c>
-      <c r="M138" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N138" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-ACT-074 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Envelope override check (TSR-304, DQ-053): in toyota.h reject 0x2E4 frames that increase torque opposing STEER_TORQUE_DRIVER beyond the driver allowance, and back off toward zero at no less than the down rate while the override lasts; report the state to the SoC (TSR-628). Add opendbc safety tests and mutation for both branches; host counterpart SWF-ACT-046</t>
-          </r>
-        </is>
-      </c>
-      <c r="O138" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
         </is>
       </c>
       <c r="P138" s="43" t="inlineStr"/>
@@ -30953,8 +30828,250 @@
       <c r="R138" s="48" t="inlineStr"/>
       <c r="S138" s="48" t="inlineStr"/>
     </row>
-    <row r="139" ht="249" customHeight="1">
-      <c r="A139" s="30" t="inlineStr">
+    <row r="139" ht="208.5" customHeight="1">
+      <c r="A139" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Steering torque checks</t>
+          </r>
+        </is>
+      </c>
+      <c r="B139" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-014
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Back steering torque off toward zero while the driver overrides, and reject frames that increase torque opposing the driver beyond a driver allowance (TSR-304; not implemented on the LKA path)</t>
+          </r>
+        </is>
+      </c>
+      <c r="C139" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item resists the driver's steering within the panda torque bound</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The only override check is the host's MAX_USER_TORQUE of 500 units (carcontroller.py:33, 83); with a host fault, or below 500 units by design (SWF-038), torque up to the 1500 limit keeps opposing the driver</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>STEERING_LKA (0x2E4) frames that oppose the driver pass: the Toyota LKA check is magnitude, rate and measured-torque error only (TorqueMotorLimited); STEER_TORQUE_DRIVER is decoded (toyota.h:221-223) but used only on the LTA path (toyota.h:421-424)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D139" s="50" t="inlineStr">
+        <is>
+          <t>HZ-009</t>
+        </is>
+      </c>
+      <c r="E139" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F139" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-087 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Envelope passes LKA torque that opposes the driver while the driver overrides the steering</t>
+          </r>
+        </is>
+      </c>
+      <c r="G139" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H139" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>By design the envelope has no driver-override check on the LKA path (GAP-02): TSR-304 (driver allowance, and back-off while the driver torque exceeds T_ovr; decided as DQ-053, 2026-10-14) is not implemented in toyota.h, in either build</t>
+          </r>
+        </is>
+      </c>
+      <c r="I139" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream design (a bounded torque the driver can overpower); requirement TSR-304 not implemented, so O 8 (RT-2 §2), as the other by-design gaps</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/modes/toyota.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J139" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K139" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_toyota.py tests the measured-torque limit (MotorTorqueSteeringSafetyTest, MAX_TORQUE_ERROR 350); no test of torque opposing the driver on the LKA path</t>
+          </r>
+        </is>
+      </c>
+      <c r="L139" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M139" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N139" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-ACT-074 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Envelope override check (TSR-304, DQ-053): in toyota.h reject 0x2E4 frames that increase torque opposing STEER_TORQUE_DRIVER beyond the driver allowance, and back off toward zero at no less than the down rate while the override lasts; report the state to the SoC (TSR-628). Add opendbc safety tests and mutation for both branches; host counterpart SWF-ACT-046</t>
+          </r>
+        </is>
+      </c>
+      <c r="O139" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P139" s="43" t="inlineStr"/>
+      <c r="Q139" s="43" t="inlineStr"/>
+      <c r="R139" s="48" t="inlineStr"/>
+      <c r="S139" s="48" t="inlineStr"/>
+    </row>
+    <row r="140" ht="249" customHeight="1">
+      <c r="A140" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30976,7 +31093,7 @@
           </r>
         </is>
       </c>
-      <c r="B139" s="30" t="inlineStr">
+      <c r="B140" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30998,7 +31115,7 @@
           </r>
         </is>
       </c>
-      <c r="C139" s="30" t="inlineStr">
+      <c r="C140" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31071,15 +31188,15 @@
           </r>
         </is>
       </c>
-      <c r="D139" s="31" t="inlineStr">
+      <c r="D140" s="31" t="inlineStr">
         <is>
           <t>HZ-004</t>
         </is>
       </c>
-      <c r="E139" s="32" t="n">
+      <c r="E140" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F139" s="30" t="inlineStr">
+      <c r="F140" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31102,12 +31219,12 @@
           </r>
         </is>
       </c>
-      <c r="G139" s="33" t="inlineStr">
+      <c r="G140" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H139" s="34" t="inlineStr">
+      <c r="H140" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31119,7 +31236,7 @@
           </r>
         </is>
       </c>
-      <c r="I139" s="34" t="inlineStr">
+      <c r="I140" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31140,10 +31257,10 @@
           </r>
         </is>
       </c>
-      <c r="J139" s="35" t="n">
+      <c r="J140" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="K139" s="34" t="inlineStr">
+      <c r="K140" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31164,15 +31281,15 @@
           </r>
         </is>
       </c>
-      <c r="L139" s="35" t="n">
+      <c r="L140" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="M139" s="37" t="inlineStr">
+      <c r="M140" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N139" s="34" t="inlineStr">
+      <c r="N140" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31221,40 +31338,40 @@
           </r>
         </is>
       </c>
-      <c r="O139" s="56" t="inlineStr">
+      <c r="O140" s="56" t="inlineStr">
         <is>
           <t>completed
 open</t>
         </is>
       </c>
-      <c r="P139" s="33" t="inlineStr">
+      <c r="P140" s="33" t="inlineStr">
         <is>
           <t>10/5/8
 10/5/4</t>
         </is>
       </c>
-      <c r="Q139" s="33" t="inlineStr">
+      <c r="Q140" s="33" t="inlineStr">
         <is>
           <t>H
 H</t>
         </is>
       </c>
-      <c r="R139" s="39" t="inlineStr"/>
-      <c r="S139" s="39" t="inlineStr"/>
+      <c r="R140" s="39" t="inlineStr"/>
+      <c r="S140" s="39" t="inlineStr"/>
     </row>
-    <row r="140" ht="249" customHeight="1">
-      <c r="A140" s="42" t="n"/>
-      <c r="B140" s="42" t="n"/>
-      <c r="C140" s="42" t="n"/>
-      <c r="D140" s="42" t="n"/>
-      <c r="E140" s="42" t="n"/>
-      <c r="F140" s="42" t="n"/>
-      <c r="G140" s="43" t="inlineStr">
+    <row r="141" ht="249" customHeight="1">
+      <c r="A141" s="42" t="n"/>
+      <c r="B141" s="42" t="n"/>
+      <c r="C141" s="42" t="n"/>
+      <c r="D141" s="42" t="n"/>
+      <c r="E141" s="42" t="n"/>
+      <c r="F141" s="42" t="n"/>
+      <c r="G141" s="43" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H140" s="44" t="inlineStr">
+      <c r="H141" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31266,7 +31383,7 @@
           </r>
         </is>
       </c>
-      <c r="I140" s="44" t="inlineStr">
+      <c r="I141" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31287,10 +31404,10 @@
           </r>
         </is>
       </c>
-      <c r="J140" s="45" t="n">
+      <c r="J141" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="K140" s="44" t="inlineStr">
+      <c r="K141" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31311,15 +31428,15 @@
           </r>
         </is>
       </c>
-      <c r="L140" s="45" t="n">
+      <c r="L141" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="M140" s="52" t="inlineStr">
+      <c r="M141" s="52" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N140" s="44" t="inlineStr">
+      <c r="N141" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31368,281 +31485,28 @@
           </r>
         </is>
       </c>
-      <c r="O140" s="47" t="inlineStr">
+      <c r="O141" s="47" t="inlineStr">
         <is>
           <t>completed
 open</t>
         </is>
       </c>
-      <c r="P140" s="43" t="inlineStr">
+      <c r="P141" s="43" t="inlineStr">
         <is>
           <t>10/5/8
 10/5/4</t>
         </is>
       </c>
-      <c r="Q140" s="43" t="inlineStr">
+      <c r="Q141" s="43" t="inlineStr">
         <is>
           <t>H
 H</t>
         </is>
       </c>
-      <c r="R140" s="48" t="inlineStr"/>
-      <c r="S140" s="48" t="inlineStr"/>
-    </row>
-    <row r="141" ht="208.5" customHeight="1">
-      <c r="A141" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-SE-005
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Controls-allowed logic</t>
-          </r>
-        </is>
-      </c>
-      <c r="B141" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-FN-004
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Allow controls on rising edge of PCM cruise; withdraw on cruise off, brake press, invalid or lagging safety messages</t>
-          </r>
-        </is>
-      </c>
-      <c r="C141" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Brief actuation without the driver's cruise engagement, from an implausible PCM state</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-006 (the grant covers longitudinal commands; braking without the driver's engagement for up to the 150 ms tolerance, HE-04.4)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The item holds authority while main is off until the 150 ms main-off tolerance revokes it</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>pcm_engage_pending stays set after toyota_cruise_main_check refuses a CRUISE_ACTIVE edge for MAIN_ON = 0, so a heartbeat-engaged flag within 1 s grants controls_allowed</t>
-          </r>
-        </is>
-      </c>
-      <c r="D141" s="50" t="inlineStr">
-        <is>
-          <t>HZ-010
-HZ-006</t>
-        </is>
-      </c>
-      <c r="E141" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F141" s="49" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SWF-089 · commission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Authority granted while PCM cruise main is off, through an engagement window left open by a refused cruise edge</t>
-          </r>
-        </is>
-      </c>
-      <c r="G141" s="43" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H141" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Defect in the reference-build engagement window (LS-06, TSR-301): the window was opened before the MAIN_ON = 0 refusal and not closed by it, against SWSR-405(c). Found by the state-machine charts (SM-F1, #158) after BL-005; fixed by opendbc#17 (032bbef, pcm_engage_cancel), in the pin since BL-006</t>
-          </r>
-        </is>
-      </c>
-      <c r="I141" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Requirement SWSR-405(c); reference-build code with MISRA C:2012 in CI in both variants</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/07-supporting/impact/change-2026-10-17-pin-98d3be1.md</t>
-          </r>
-        </is>
-      </c>
-      <c r="J141" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="K141" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_main_off_closes_engagement_window (test_toyota.py, both paths and a control case; removing either call fails it), run with 100 % line coverage and mutation in the reference variant in CI. Not on target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L141" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="M141" s="46" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N141" s="44" t="inlineStr"/>
-      <c r="O141" s="44" t="inlineStr"/>
-      <c r="P141" s="43" t="inlineStr"/>
-      <c r="Q141" s="43" t="inlineStr"/>
       <c r="R141" s="48" t="inlineStr"/>
       <c r="S141" s="48" t="inlineStr"/>
     </row>
-    <row r="142" ht="195" customHeight="1">
+    <row r="142" ht="208.5" customHeight="1">
       <c r="A142" s="49" t="inlineStr">
         <is>
           <r>
@@ -31652,16 +31516,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-SE-009
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay malfunction detection</t>
+            <t xml:space="preserve">SWF-SE-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Controls-allowed logic</t>
           </r>
         </is>
       </c>
@@ -31674,16 +31538,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-FN-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Detect a relay malfunction and block all item transmission</t>
+            <t xml:space="preserve">SWF-FN-004
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Allow controls on rising edge of PCM cruise; withdraw on cruise off, brake press, invalid or lagging safety messages</t>
           </r>
         </is>
       </c>
@@ -31704,7 +31568,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Item and stock camera commands combine on the bus until the malfunction is detected again</t>
+            <t>Brief actuation without the driver's cruise engagement, from an implausible PCM state</t>
           </r>
           <r>
             <rPr>
@@ -31730,7 +31594,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Contributes to HZ-006 (stock ACC and item 0x343 combine on the bus, as SWF-012)</t>
+            <t>Contributes to HZ-006 (the grant covers longitudinal commands; braking without the driver's engagement for up to the 150 ms tolerance, HE-04.4)</t>
           </r>
           <r>
             <rPr>
@@ -31756,7 +31620,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>A mode cycle (host request or heartbeat-loss recovery) followed by a quick re-engagement grants authority with the harness relay still faulty</t>
+            <t>The item holds authority while main is off until the 150 ms main-off tolerance revokes it</t>
           </r>
           <r>
             <rPr>
@@ -31782,13 +31646,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>set_safety_hooks clears relay_malfunction, and stock_ecu_check looks again only after the new mode has run for more than 1 s</t>
+            <t>pcm_engage_pending stays set after toyota_cruise_main_check refuses a CRUISE_ACTIVE edge for MAIN_ON = 0, so a heartbeat-engaged flag within 1 s grants controls_allowed</t>
           </r>
         </is>
       </c>
       <c r="D142" s="50" t="inlineStr">
         <is>
-          <t>HZ-002
+          <t>HZ-010
 HZ-006</t>
         </is>
       </c>
@@ -31804,17 +31668,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SWF-090 · omission
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay-malfunction reaction cleared by a safety-mode change before the malfunction is detected again</t>
+            <t xml:space="preserve">SWF-089 · commission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Authority granted while PCM cruise main is off, through an engagement window left open by a refused cruise edge</t>
           </r>
         </is>
       </c>
@@ -31831,7 +31695,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Defect at BL-005 (DFA DM-25): the relay-malfunction reaction lived in opendbc state that a mode change resets. Fixed in the reference build by panda#17 (0a7da85): the reference lock latches a relay malfunction for the ignition cycle and refuses TOYOTA until ignition off, in the pin since BL-006</t>
+            <t>Defect in the reference-build engagement window (LS-06, TSR-301): the window was opened before the MAIN_ON = 0 refusal and not closed by it, against SWSR-405(c). Found by the state-machine charts (SM-F1, #158) after BL-005; fixed by opendbc#17 (032bbef, pcm_engage_cancel), in the pin since BL-006</t>
           </r>
         </is>
       </c>
@@ -31843,7 +31707,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Reference lock (TSR-619 family) extended by DFA DM-25; MISRA C:2012 clean in both variants; firmware built with -Werror</t>
+            <t>• Requirement SWSR-405(c); reference-build code with MISRA C:2012 in CI in both variants</t>
           </r>
           <r>
             <rPr>
@@ -31852,7 +31716,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/07-supporting/impact/change-2026-10-17-relay-malfunction-latch.md</t>
+   assurance/07-supporting/impact/change-2026-10-17-pin-98d3be1.md</t>
           </r>
         </is>
       </c>
@@ -31867,7 +31731,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Host unit tests compiled against the real firmware headers, run by panda CI (reference_lock suite, 18 tests, 4 new; 3 fail without the gate). Not on target hardware</t>
+            <t>• test_main_off_closes_engagement_window (test_toyota.py, both paths and a control case; removing either call fails it), run with 100 % line coverage and mutation in the reference variant in CI. Not on target</t>
           </r>
           <r>
             <rPr>
@@ -31876,7 +31740,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   panda/tests/reference_lock/test_reference_lock.py</t>
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
           </r>
         </is>
       </c>
@@ -31895,33 +31759,283 @@
       <c r="R142" s="48" t="inlineStr"/>
       <c r="S142" s="48" t="inlineStr"/>
     </row>
+    <row r="143" ht="195" customHeight="1">
+      <c r="A143" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-SE-009
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Relay malfunction detection</t>
+          </r>
+        </is>
+      </c>
+      <c r="B143" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Detect a relay malfunction and block all item transmission</t>
+          </r>
+        </is>
+      </c>
+      <c r="C143" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item and stock camera commands combine on the bus until the malfunction is detected again</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006 (stock ACC and item 0x343 combine on the bus, as SWF-012)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A mode cycle (host request or heartbeat-loss recovery) followed by a quick re-engagement grants authority with the harness relay still faulty</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set_safety_hooks clears relay_malfunction, and stock_ecu_check looks again only after the new mode has run for more than 1 s</t>
+          </r>
+        </is>
+      </c>
+      <c r="D143" s="50" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E143" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F143" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SWF-090 · omission
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Relay-malfunction reaction cleared by a safety-mode change before the malfunction is detected again</t>
+          </r>
+        </is>
+      </c>
+      <c r="G143" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H143" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Defect at BL-005 (DFA DM-25): the relay-malfunction reaction lived in opendbc state that a mode change resets. Fixed in the reference build by panda#17 (0a7da85): the reference lock latches a relay malfunction for the ignition cycle and refuses TOYOTA until ignition off, in the pin since BL-006</t>
+          </r>
+        </is>
+      </c>
+      <c r="I143" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Reference lock (TSR-619 family) extended by DFA DM-25; MISRA C:2012 clean in both variants; firmware built with -Werror</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/07-supporting/impact/change-2026-10-17-relay-malfunction-latch.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J143" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Host unit tests compiled against the real firmware headers, run by panda CI (reference_lock suite, 18 tests, 4 new; 3 fail without the gate). Not on target hardware</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   panda/tests/reference_lock/test_reference_lock.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L143" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M143" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N143" s="44" t="inlineStr"/>
+      <c r="O143" s="44" t="inlineStr"/>
+      <c r="P143" s="43" t="inlineStr"/>
+      <c r="Q143" s="43" t="inlineStr"/>
+      <c r="R143" s="48" t="inlineStr"/>
+      <c r="S143" s="48" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S142"/>
-  <mergeCells count="232">
+  <autoFilter ref="A2:S143"/>
+  <mergeCells count="238">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="E92:E93"/>
-    <mergeCell ref="B124:B126"/>
     <mergeCell ref="E39:E40"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="A137:A138"/>
     <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C137:C138"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="F111:F113"/>
+    <mergeCell ref="E140:E141"/>
+    <mergeCell ref="D117:D119"/>
+    <mergeCell ref="F117:F119"/>
+    <mergeCell ref="F125:F127"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E137:E138"/>
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E124:E126"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C114:C115"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="C87:C89"/>
-    <mergeCell ref="A114:A115"/>
     <mergeCell ref="E74:E75"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="E3:E5"/>
@@ -31930,30 +32044,27 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="F72:F73"/>
-    <mergeCell ref="D134:D135"/>
-    <mergeCell ref="F134:F135"/>
     <mergeCell ref="A49:A51"/>
     <mergeCell ref="F103:F105"/>
     <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C116:C118"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="D66:D68"/>
     <mergeCell ref="A22:A23"/>
-    <mergeCell ref="F136:F137"/>
     <mergeCell ref="F87:F89"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="E41:E42"/>
-    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="E115:E116"/>
     <mergeCell ref="A35:A36"/>
-    <mergeCell ref="D114:D115"/>
     <mergeCell ref="C69:C70"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="F66:F68"/>
+    <mergeCell ref="E135:E136"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="D140:D141"/>
     <mergeCell ref="B49:B51"/>
     <mergeCell ref="B90:B91"/>
     <mergeCell ref="A45:A46"/>
@@ -31961,40 +32072,46 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A112:A114"/>
     <mergeCell ref="F49:F51"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E128:E129"/>
     <mergeCell ref="C100:C101"/>
-    <mergeCell ref="F116:F118"/>
     <mergeCell ref="F35:F36"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="A96:A98"/>
+    <mergeCell ref="C109:C110"/>
     <mergeCell ref="C96:C98"/>
     <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="C125:C127"/>
     <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="D135:D136"/>
+    <mergeCell ref="F135:F136"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="B76:B78"/>
+    <mergeCell ref="E112:E114"/>
+    <mergeCell ref="A129:A130"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="B125:B127"/>
     <mergeCell ref="E96:E98"/>
     <mergeCell ref="F100:F101"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="F109:F110"/>
+    <mergeCell ref="E117:E119"/>
     <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="C140:C141"/>
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="A115:A116"/>
     <mergeCell ref="I1:M1"/>
-    <mergeCell ref="B111:B113"/>
     <mergeCell ref="B92:B93"/>
-    <mergeCell ref="D111:D113"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A124:A126"/>
     <mergeCell ref="D30:D31"/>
     <mergeCell ref="D39:D40"/>
-    <mergeCell ref="C124:C126"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B32:B33"/>
@@ -32004,46 +32121,47 @@
     <mergeCell ref="C74:C75"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C117:C119"/>
+    <mergeCell ref="A107:A108"/>
     <mergeCell ref="B103:B105"/>
+    <mergeCell ref="D125:D127"/>
     <mergeCell ref="C58:C59"/>
     <mergeCell ref="D103:D105"/>
+    <mergeCell ref="C107:C108"/>
     <mergeCell ref="E58:E59"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="D90:D91"/>
     <mergeCell ref="E52:E53"/>
-    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="D112:D114"/>
+    <mergeCell ref="F137:F138"/>
+    <mergeCell ref="A125:A127"/>
     <mergeCell ref="B87:B89"/>
-    <mergeCell ref="D136:D137"/>
     <mergeCell ref="D87:D89"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="F74:F75"/>
     <mergeCell ref="F96:F98"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F139:F140"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="E69:E70"/>
     <mergeCell ref="E76:E78"/>
-    <mergeCell ref="E116:E118"/>
+    <mergeCell ref="F129:F130"/>
     <mergeCell ref="C66:C68"/>
     <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C115:C116"/>
     <mergeCell ref="E66:E68"/>
-    <mergeCell ref="A111:A113"/>
-    <mergeCell ref="C111:C113"/>
-    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="D115:D116"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="F140:F141"/>
     <mergeCell ref="F41:F42"/>
-    <mergeCell ref="E111:E113"/>
+    <mergeCell ref="D107:D108"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="F115:F116"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E114:E115"/>
-    <mergeCell ref="D124:D126"/>
-    <mergeCell ref="F124:F126"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="F43:F44"/>
@@ -32057,27 +32175,27 @@
     <mergeCell ref="E72:E73"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C39:C40"/>
-    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="C112:C114"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E139:E140"/>
     <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="E129:E130"/>
     <mergeCell ref="E87:E89"/>
     <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B135:B136"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="B72:B73"/>
-    <mergeCell ref="D128:D129"/>
     <mergeCell ref="B100:B101"/>
-    <mergeCell ref="F128:F129"/>
     <mergeCell ref="E43:E44"/>
+    <mergeCell ref="B109:B110"/>
     <mergeCell ref="B47:B48"/>
+    <mergeCell ref="D109:D110"/>
     <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B136:B137"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="A76:A78"/>
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="C76:C78"/>
+    <mergeCell ref="E107:E108"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C92:C93"/>
     <mergeCell ref="B54:B56"/>
@@ -32086,10 +32204,14 @@
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="D54:D56"/>
-    <mergeCell ref="F114:F115"/>
-    <mergeCell ref="A108:A109"/>
     <mergeCell ref="C90:C91"/>
     <mergeCell ref="E90:E91"/>
+    <mergeCell ref="A117:A119"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="F112:F114"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="D137:D138"/>
     <mergeCell ref="C52:C53"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="D49:D51"/>
@@ -32105,17 +32227,19 @@
     <mergeCell ref="E45:E46"/>
     <mergeCell ref="D96:D98"/>
     <mergeCell ref="A103:A105"/>
-    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="A109:A110"/>
     <mergeCell ref="C103:C105"/>
+    <mergeCell ref="B129:B130"/>
     <mergeCell ref="D58:D59"/>
+    <mergeCell ref="D129:D130"/>
     <mergeCell ref="F58:F59"/>
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="E100:E101"/>
-    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="E109:E110"/>
     <mergeCell ref="E47:E48"/>
-    <mergeCell ref="E136:E137"/>
     <mergeCell ref="E103:E105"/>
     <mergeCell ref="D60:D61"/>
+    <mergeCell ref="F107:F108"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="F60:F61"/>
     <mergeCell ref="D69:D70"/>
@@ -32125,14 +32249,13 @@
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F76:F78"/>
     <mergeCell ref="D100:D101"/>
-    <mergeCell ref="C108:C109"/>
     <mergeCell ref="D35:D36"/>
-    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="B115:B116"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138 R139 R140 R141 R142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94 R95 R96 R97 R98 R99 R100 R101 R102 R103 R104 R105 R106 R107 R108 R109 R110 R111 R112 R113 R114 R115 R116 R117 R118 R119 R120 R121 R122 R123 R124 R125 R126 R127 R128 R129 R130 R131 R132 R133 R134 R135 R136 R137 R138 R139 R140 R141 R142 R143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32140,7 +32263,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.4 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.5 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -32155,7 +32278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -34313,7 +34436,7 @@
       <c r="H55" s="61" t="inlineStr"/>
       <c r="I55" s="61" t="inlineStr"/>
     </row>
-    <row r="56" ht="33" customHeight="1">
+    <row r="56" ht="154.5" customHeight="1">
       <c r="A56" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-063</t>
@@ -34336,7 +34459,7 @@
       </c>
       <c r="E56" s="61" t="inlineStr">
         <is>
-          <t>decision pending</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F56" s="61" t="inlineStr">
@@ -34344,9 +34467,21 @@
           <t>SWF-067.C1</t>
         </is>
       </c>
-      <c r="G56" s="61" t="inlineStr"/>
-      <c r="H56" s="61" t="inlineStr"/>
-      <c r="I56" s="61" t="inlineStr"/>
+      <c r="G56" s="61" t="inlineStr">
+        <is>
+          <t>10/5/8</t>
+        </is>
+      </c>
+      <c r="H56" s="63" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I56" s="61" t="inlineStr">
+        <is>
+          <t>DQ-221 A implemented in #287 (69cddaa): assured_config.py (settings_in_scope), selfdrived.py (add_reference_entry_events, distance_button_pressed), events.py (settingNotAssured); tests in test_assured_config.py; change record assurance/07-supporting/impact/change-2026-10-19-reference-entry-checks.md. The tests ran locally only (the 22 of 24 that do not need the compiled Params library pass, per the #287 merge note); the CI unit_tests job has not run them (scons setup fails on the git-lfs 404). Completes when CI runs them; not verified in the vehicle (change record OI-5)</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="87" customHeight="1">
       <c r="A57" s="61" t="inlineStr">
@@ -34913,8 +35048,43 @@
       </c>
       <c r="I71" s="61" t="inlineStr"/>
     </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="61" t="inlineStr">
+        <is>
+          <t>SWF-ACT-079</t>
+        </is>
+      </c>
+      <c r="B72" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C72" s="61" t="inlineStr">
+        <is>
+          <t>Apply the lead's decision on setting changes while engaged (DQ-222): lock the following distance and Experimental Mode while engaged on the reference platform, disengage on a change, or keep today's entry-only check; with a test</t>
+        </is>
+      </c>
+      <c r="D72" s="61" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E72" s="61" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="F72" s="61" t="inlineStr">
+        <is>
+          <t>SWF-067.C2</t>
+        </is>
+      </c>
+      <c r="G72" s="61" t="inlineStr"/>
+      <c r="H72" s="61" t="inlineStr"/>
+      <c r="I72" s="61" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I71"/>
+  <autoFilter ref="A1:I72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.5 · draft</t>
+          <t>1.6 · draft</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>71 (65)</t>
+          <t>71 (64)</t>
         </is>
       </c>
     </row>
@@ -24571,7 +24571,7 @@
       <c r="R106" s="48" t="inlineStr"/>
       <c r="S106" s="48" t="inlineStr"/>
     </row>
-    <row r="107" ht="154.5" customHeight="1">
+    <row r="107" ht="141" customHeight="1">
       <c r="A107" s="30" t="inlineStr">
         <is>
           <r>
@@ -24766,10 +24766,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_assured_config.py: each setting refuses entry, entry only, other platforms unchanged, distance button ignored on the reference platform. Collected by the CI unit_tests job but not yet run there (the scons jobs fail in setup on the git-lfs 404); run locally for #287 only. D 8 once CI runs it, D 4 with mutation</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_assured_config.py: each setting refuses entry, entry only, other platforms unchanged, distance button ignored on the reference platform. Run by the CI unit_tests job since the LFS mirror returned (tests run 39296172878 at 6126485: 1578 passed, 0 failed); not proven by mutation, so D 8, D 4 with mutation</t>
           </r>
           <r>
             <rPr>
@@ -24782,8 +24782,8 @@
           </r>
         </is>
       </c>
-      <c r="L107" s="36" t="n">
-        <v>9</v>
+      <c r="L107" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="M107" s="37" t="inlineStr">
         <is>
@@ -24812,9 +24812,9 @@
           </r>
         </is>
       </c>
-      <c r="O107" s="57" t="inlineStr">
-        <is>
-          <t>in progress</t>
+      <c r="O107" s="56" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="P107" s="33" t="inlineStr">
@@ -32263,7 +32263,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.5 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.6 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -34436,7 +34436,7 @@
       <c r="H55" s="61" t="inlineStr"/>
       <c r="I55" s="61" t="inlineStr"/>
     </row>
-    <row r="56" ht="154.5" customHeight="1">
+    <row r="56" ht="141" customHeight="1">
       <c r="A56" s="61" t="inlineStr">
         <is>
           <t>SWF-ACT-063</t>
@@ -34457,9 +34457,9 @@
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E56" s="61" t="inlineStr">
-        <is>
-          <t>in progress</t>
+      <c r="E56" s="62" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F56" s="61" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="I56" s="61" t="inlineStr">
         <is>
-          <t>DQ-221 A implemented in #287 (69cddaa): assured_config.py (settings_in_scope), selfdrived.py (add_reference_entry_events, distance_button_pressed), events.py (settingNotAssured); tests in test_assured_config.py; change record assurance/07-supporting/impact/change-2026-10-19-reference-entry-checks.md. The tests ran locally only (the 22 of 24 that do not need the compiled Params library pass, per the #287 merge note); the CI unit_tests job has not run them (scons setup fails on the git-lfs 404). Completes when CI runs them; not verified in the vehicle (change record OI-5)</t>
+          <t>DQ-221 A implemented in #287 (69cddaa): assured_config.py (settings_in_scope), selfdrived.py (add_reference_entry_events, distance_button_pressed), events.py (settingNotAssured); tests in test_assured_config.py, collected by the CI unit_tests job and green there in tests run 39296172878 (6126485, 2026-10-19: 1578 passed, 0 failed); change record assurance/07-supporting/impact/change-2026-10-19-reference-entry-checks.md. Unit-tested, not proven by mutation and not verified in the vehicle (change record OI-5). Achieved: O5 D8 (rev 1.6)</t>
         </is>
       </c>
     </row>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -5742,7 +5742,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• pandad (reference build) configures a car safety mode only on a panda whose health packet carries HEALTH_FLAG_REFERENCE_BUILD; otherwise the panda stays in NOOUTPUT and selfdrived raises controlsMismatch and pandaNotReferenceBuild (panda_safety.cc:73-83, selfdrived.py:377-381; TSR-619, TSR-514). A build opted out on both sides (firmware and pandad) is not caught</t>
+            <t>• pandad (reference build) configures a car safety mode only on a panda whose health packet carries HEALTH_FLAG_REFERENCE_BUILD; otherwise the panda stays in NOOUTPUT and selfdrived raises controlsMismatch and pandaNotReferenceBuild (panda_safety.cc:73-83, selfdrived.py:380-384; TSR-619, TSR-514). A build opted out on both sides (firmware and pandad) is not caught</t>
           </r>
           <r>
             <rPr>
@@ -11795,7 +11795,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Test-only environment flags reach the vehicle: REPLAY sets the state to enabled when a panda reports controlsAllowed, bypassing ENABLE/NO_ENTRY (selfdrived.py:493-494); SIMULATION ignores cabinCameraState and managerState and makes every SubMaster alive/freq check pass once seen (selfdrived.py:88-89; cereal/messaging/__init__.py:211,265-266)</t>
+            <t>Test-only environment flags reach the vehicle: REPLAY sets the state to enabled when a panda reports controlsAllowed, bypassing ENABLE/NO_ENTRY (selfdrived.py:496-497); SIMULATION ignores cabinCameraState and managerState and makes every SubMaster alive/freq check pass once seen (selfdrived.py:88-89; cereal/messaging/__init__.py:211,265-266)</t>
           </r>
         </is>
       </c>
@@ -12037,7 +12037,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>carState is read from its own socket with a 20 ms timeout and the previous carState is reused when nothing arrives (selfdrived.py:85, 474-475); carState is not in the SubMaster, so it has no alive/freq check. A card stall freezes brakePressed, cruiseState and canValid, so no driver-action event is raised; the stall is only seen indirectly (selfdrivedLagging after about 0.2 s, carOutput commIssue after 0.1 s), both SOFT_DISABLE (3 s or longer, SWF-033.C2)</t>
+            <t>carState is read from its own socket with a 20 ms timeout and the previous carState is reused when nothing arrives (selfdrived.py:85, 477-478); carState is not in the SubMaster, so it has no alive/freq check. A card stall freezes brakePressed, cruiseState and canValid, so no driver-action event is raised; the stall is only seen indirectly (selfdrivedLagging after about 0.2 s, carOutput commIssue after 0.1 s), both SOFT_DISABLE (3 s or longer, SWF-033.C2)</t>
           </r>
         </is>
       </c>
@@ -12137,7 +12137,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Defect in the brake/gas rising-edge logic (selfdrived.py:255-258), in the canValid gate on car events (selfdrived.py:244-246), or in the USER_DISABLE priority of the state machine (state.py:31-33)</t>
+            <t>Defect in the brake/gas rising-edge logic (selfdrived.py:258-261), in the canValid gate on car events (selfdrived.py:247-249), or in the USER_DISABLE priority of the state machine (state.py:31-33)</t>
           </r>
         </is>
       </c>
@@ -12423,7 +12423,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Panda fault flags other than relayMalfunction get no reaction in selfdrived (pandaStates.faults: interruptRate*, heartbeatLoopWatchdog, registerDivergent, ...), and SPI error bursts are not supervised (IA host-supervision OI-2). At BL-004 heartbeatLost, safetyTxBlocked and txRateExceeded were not read either; since #51 they are (pandaTxRateExceeded, pandaHeartbeatLost, pandaTxBlocked, immediate disable; selfdrived.py:364-372, TSR-615). The EPS-fault flag is covered by the EPS status events from card</t>
+            <t>Panda fault flags other than relayMalfunction get no reaction in selfdrived (pandaStates.faults: interruptRate*, heartbeatLoopWatchdog, registerDivergent, ...), and SPI error bursts are not supervised (IA host-supervision OI-2). At BL-004 heartbeatLost, safetyTxBlocked and txRateExceeded were not read either; since #51 they are (pandaTxRateExceeded, pandaHeartbeatLost, pandaTxBlocked, immediate disable; selfdrived.py:367-375, TSR-615). The EPS-fault flag is covered by the EPS status events from card</t>
           </r>
         </is>
       </c>
@@ -12444,7 +12444,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:364-375</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:367-378</t>
           </r>
         </is>
       </c>
@@ -12532,7 +12532,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Defect in the BL-005 flag reactions: a wrong field, a missed panda index, or the safetyTxBlocked baseline not moved after a panda reset, so a flag the panda raises gives no disable (selfdrived.py:364-372, supervision.py TxBlockedMonitor)</t>
+            <t>Defect in the BL-005 flag reactions: a wrong field, a missed panda index, or the safetyTxBlocked baseline not moved after a panda reset, so a flag the panda raises gives no disable (selfdrived.py:367-375, supervision.py TxBlockedMonitor)</t>
           </r>
         </is>
       </c>
@@ -12649,7 +12649,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Diagnostics masked on the big-model path: commIssue is suppressed for every service while ChestnutLoading is set and for 5 s after, and posenet, locationd, paramsd and modeldLagging checks are skipped (selfdrived.py:386-390, 409, 463; GAP-17, TSR-603). Active only when the chestnut models are compiled and the accelerator or a USB-C cable is detected (modeld.py:232); nothing enforces its absence in the reference configuration</t>
+            <t>Diagnostics masked on the big-model path: commIssue is suppressed for every service while ChestnutLoading is set and for 5 s after, and posenet, locationd, paramsd and modeldLagging checks are skipped (selfdrived.py:389-393, 412, 466; GAP-17, TSR-603). Active only when the chestnut models are compiled and the accelerator or a USB-C cable is detected (modeld.py:232); nothing enforces its absence in the reference configuration</t>
           </r>
         </is>
       </c>
@@ -12918,7 +12918,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loss or staleness of an input to the control law is handled as SOFT_DISABLE (commIssue, commIssueAvgFreq, processNotRunning, modeldLagging, selfdrivedLagging; events.py:853-872, 886-896), i.e. 3 s of continued actuation (state.py:7, 38-41); sensorDataInvalid only after 10 s without IMU data (selfdrived.py:420-421). TSR-601 asks immediate disable; no event is justified against an FTTI (SFM-016, GAP-16)</t>
+            <t>Loss or staleness of an input to the control law is handled as SOFT_DISABLE (commIssue, commIssueAvgFreq, processNotRunning, modeldLagging, selfdrivedLagging; events.py:853-872, 886-896), i.e. 3 s of continued actuation (state.py:7, 38-41); sensorDataInvalid only after 10 s without IMU data (selfdrived.py:423-424). TSR-601 asks immediate disable; no event is justified against an FTTI (SFM-016, GAP-16)</t>
           </r>
         </is>
       </c>
@@ -13027,7 +13027,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Every timer counts loop iterations, not time: soft_disable_timer (state.py:20, 40), mismatch_counter, cruise_mismatch_counter and the sm.frame gates (selfdrived.py:340, 420, 427). The loop is paced by the carState receive (20 ms timeout) with monitor_time only (selfdrived.py:85, 607-609) and does blocking Params writes (selfdrived.py:222, 308, 470), so when it slows, every timeout stretches (3 s soft disable is 6 s at 50 Hz)</t>
+            <t>Every timer counts loop iterations, not time: soft_disable_timer (state.py:20, 40), mismatch_counter, cruise_mismatch_counter and the sm.frame gates (selfdrived.py:343, 423, 430). The loop is paced by the carState receive (20 ms timeout) with monitor_time only (selfdrived.py:85, 611-613) and does blocking Params writes (selfdrived.py:225, 311, 473), so when it slows, every timeout stretches (3 s soft disable is 6 s at 50 Hz)</t>
           </r>
         </is>
       </c>
@@ -13496,7 +13496,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Safety model, parameter and alternative-experience mismatch is ignored for the first 10 s after selfdrived starts (sm.frame*DT_CTRL &gt; 10, selfdrived.py:340), so an engagement in that window with a wrong mode or parameter that still grants controls is not refused</t>
+            <t>Safety model, parameter and alternative-experience mismatch is ignored for the first 10 s after selfdrived starts (sm.frame*DT_CTRL &gt; 10, selfdrived.py:343), so an engagement in that window with a wrong mode or parameter that still grants controls is not refused</t>
           </r>
           <r>
             <rPr>
@@ -13517,7 +13517,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Initialization takes up to 6 s (selfdrived.py:479-482); the wrong mode itself needs SWF-013 (reference lock not built at BL-004; default build at BL-005, so a wrong mode or parameter is refused by the panda and no grant follows)</t>
+            <t>• Initialization takes up to 6 s (selfdrived.py:482-485); the wrong mode itself needs SWF-013 (reference lock not built at BL-004; default build at BL-005, so a wrong mode or parameter is refused by the panda and no grant follows)</t>
           </r>
           <r>
             <rPr>
@@ -13526,7 +13526,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:339-341</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:342-344</t>
           </r>
         </is>
       </c>
@@ -14288,7 +14288,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Hang or starvation of the Python process (blocking Params writes in the 100 Hz loop, selfdrived.py:222, 308, 470; GIL contention with params_thread; CPU load); no process watchdog for selfdrived (process_config.py:97)</t>
+            <t>Hang or starvation of the Python process (blocking Params writes in the 100 Hz loop, selfdrived.py:225, 311, 473; GIL contention with params_thread; CPU load); no process watchdog for selfdrived (process_config.py:97)</t>
           </r>
           <r>
             <rPr>
@@ -14309,7 +14309,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Real-time priority CTRL_HIGH on core 4 (selfdrived.py:616); manager restarts a dead process but not a hung one (system/manager/process.py:223-238)</t>
+            <t>• Real-time priority CTRL_HIGH on core 4 (selfdrived.py:620); manager restarts a dead process but not a hung one (system/manager/process.py:223-238)</t>
           </r>
           <r>
             <rPr>
@@ -14318,7 +14318,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:615-618</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:619-622</t>
           </r>
         </is>
       </c>
@@ -14693,7 +14693,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The counter is reset whenever |aEgo - IMU acceleration| &gt;= 2 m/s² (device_motion_valid, helpers.py:45-46), which also holds in wheel slip or lock during a gross event (SFM-030.C2); no check until a calibrated pose exists (selfdrived.py:305); latched pose reused when deviceMotion stops (selfdrived.py:301-303)</t>
+            <t>The counter is reset whenever |aEgo - IMU acceleration| &gt;= 2 m/s² (device_motion_valid, helpers.py:45-46), which also holds in wheel slip or lock during a gross event (SFM-030.C2); no check until a calibrated pose exists (selfdrived.py:308); latched pose reused when deviceMotion stops (selfdrived.py:304-306)</t>
           </r>
         </is>
       </c>
@@ -15186,7 +15186,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>At BL-004 cruiseMismatch had no reaction or alert and was raised only after 6 s. Since #51 (BL-005) it is raised after 1 s (CRUISE_MISMATCH_TIME, selfdrived.py:461-465) with "Stock Cruise Still Engaged / Press Cancel or Brake" and a repeating prompt (TSR-308). Remaining cause: a defect in the new reaction, and the counter counts loop iterations, not time (SWF-033.C2). The cancel request itself is SWF-048</t>
+            <t>At BL-004 cruiseMismatch had no reaction or alert and was raised only after 6 s. Since #51 (BL-005) it is raised after 1 s (CRUISE_MISMATCH_TIME, selfdrived.py:464-468) with "Stock Cruise Still Engaged / Press Cancel or Brake" and a repeating prompt (TSR-308). Remaining cause: a defect in the new reaction, and the counter counts loop iterations, not time (SWF-033.C2). The cancel request itself is SWF-048</t>
           </r>
         </is>
       </c>
@@ -16807,7 +16807,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>selfdrived suppresses commIssue while the big model is loading or settling (selfdrived.py:388-390), so held modelV2 got no reaction for that window at BL-004. Since #51 the controlsd freshness gate stops lateral actuation on a modelV2 more than 0.5 s old whatever selfdrived suppresses; the alert is still masked (TSR-603)</t>
+            <t>selfdrived suppresses commIssue while the big model is loading or settling (selfdrived.py:391-393), so held modelV2 got no reaction for that window at BL-004. Since #51 the controlsd freshness gate stops lateral actuation on a modelV2 more than 0.5 s old whatever selfdrived suppresses; the alert is still masked (TSR-603)</t>
           </r>
         </is>
       </c>
@@ -18714,7 +18714,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>cancel = CS.cruiseState.enabled and not CC.enabled (controlsd.py:163), where CC.enabled is the unchecked selfdriveState (SWF-040.C1), and it is sent only inside the 33 Hz ACC_CONTROL frame (carcontroller.py:187, 253) while card is actuating. The selfdrived backstop does nothing: cruiseMismatch fires after 6 s (selfdrived.py:425-428) but has no alert or disable type (events.py:458-460, commented out)</t>
+            <t>cancel = CS.cruiseState.enabled and not CC.enabled (controlsd.py:163), where CC.enabled is the unchecked selfdriveState (SWF-040.C1), and it is sent only inside the 33 Hz ACC_CONTROL frame (carcontroller.py:187, 253) while card is actuating. The selfdrived backstop does nothing: cruiseMismatch fires after 6 s (selfdrived.py:428-431) but has no alert or disable type (events.py:458-460, commented out)</t>
           </r>
         </is>
       </c>
@@ -19004,7 +19004,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Operational rule only (WP-V-07 bans developer modes; INS-19 reference parameters); TSR-613 (path absent from reference builds) not met (GAP-20). Permanent "Lateral Maneuver Mode" banner when active (selfdrived.py:186-188)</t>
+            <t>• Operational rule only (WP-V-07 bans developer modes; INS-19 reference parameters); TSR-613 (path absent from reference builds) not met (GAP-20). Permanent "Lateral Maneuver Mode" banner when active (selfdrived.py:189-191)</t>
           </r>
           <r>
             <rPr>
@@ -19428,7 +19428,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>fcw event from modelV2.meta.hardBrakePredicted or longitudinalPlan.fcw with no alive, valid or age check of its own (selfdrived.py:472-477)</t>
+            <t>fcw event from modelV2.meta.hardBrakePredicted or longitudinalPlan.fcw with no alive, valid or age check of its own (selfdrived.py:475-480)</t>
           </r>
         </is>
       </c>
@@ -23966,7 +23966,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Plans from invalid or stale inputs: plannerd has no validity gate of its own and uses the leads whatever radarState.valid says (long_mpc.py:313-314); longitudinalPlan.valid = sm.all_checks() is published, but controlsd does not read it, so the reaction is selfdrived commIssue (soft disable, 3 s of continued control) (longitudinal_planner.py:156; selfdrived.py:427-433)</t>
+            <t>Plans from invalid or stale inputs: plannerd has no validity gate of its own and uses the leads whatever radarState.valid says (long_mpc.py:313-314); longitudinalPlan.valid = sm.all_checks() is published, but controlsd does not read it, so the reaction is selfdrived commIssue (soft disable, 3 s of continued control) (longitudinal_planner.py:156; selfdrived.py:430-436)</t>
           </r>
         </is>
       </c>
@@ -25776,7 +25776,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Radar faults reach the planner as data: plannerd uses the leads whatever radarState.valid says, and radarFault / radarTempUnavailable are SOFT_DISABLE (selfdrived.py:410-416; events.py:878-886), so a faulted lead is used for the 3 s soft disable</t>
+            <t>Radar faults reach the planner as data: plannerd uses the leads whatever radarState.valid says, and radarFault / radarTempUnavailable are SOFT_DISABLE (selfdrived.py:413-419; events.py:878-886), so a faulted lead is used for the 3 s soft disable</t>
           </r>
         </is>
       </c>
@@ -27945,7 +27945,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>selfdrived ignores accelerometer and gyro in its alive/valid checks and raises sensorDataInvalid only after 10 s without data (selfdrived.py:103, 456-458); deviceMotion.sensorsOK is not consumed by selfdrived (only paramsd and torqued)</t>
+            <t>selfdrived ignores accelerometer and gyro in its alive/valid checks and raises sensorDataInvalid only after 10 s without data (selfdrived.py:103, 459-461); deviceMotion.sensorsOK is not consumed by selfdrived (only paramsd and torqued)</t>
           </r>
         </is>
       </c>
@@ -28278,7 +28278,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>If the narrow or wide road stream is absent when selfdrived initialises, it is put on the ignore_alive and ignore_valid lists for the whole drive (selfdrived.py:539-545), so a camera that is not up at start is never supervised</t>
+            <t>If the narrow or wide road stream is absent when selfdrived initialises, it is put on the ignore_alive and ignore_valid lists for the whole drive (selfdrived.py:543-549), so a camera that is not up at start is never supervised</t>
           </r>
         </is>
       </c>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -252,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -393,9 +393,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -817,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.6 · draft</t>
+          <t>1.7 · draft</t>
         </is>
       </c>
     </row>
@@ -946,7 +943,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>71 (64)</t>
+          <t>71 (63)</t>
         </is>
       </c>
     </row>
@@ -24830,7 +24827,7 @@
       <c r="R107" s="39" t="inlineStr"/>
       <c r="S107" s="39" t="inlineStr"/>
     </row>
-    <row r="108" ht="87" customHeight="1">
+    <row r="108" ht="168" customHeight="1">
       <c r="A108" s="42" t="n"/>
       <c r="B108" s="42" t="n"/>
       <c r="C108" s="42" t="n"/>
@@ -24850,7 +24847,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>A setting changed in the settings menu while engaged (following distance, Experimental Mode) takes effect at once; the gate refuses only the next engagement (change record OI-3). What the item should do then is queued for the lead (DQ-403)</t>
+            <t>Defect in the hold of settings changed while engaged (DQ-403 A, #342): apply_settings applies the stored ExperimentalMode or following distance while the item is engaged on the reference platform (enabled or reference_platform read wrongly, or a path that writes experimental_mode or personality directly), so a menu change takes the engaged item outside the assured configuration</t>
           </r>
         </is>
       </c>
@@ -24862,7 +24859,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Defaults set to the assured values; the deviation is logged with a configuration hash</t>
+            <t>• Lead decision DQ-403 A implemented in #342 (18b15cd, merged 5d4ba6e, after BL-006); change record change-2026-10-20-settings-held-while-engaged; upstream review, ruff + ty. No SWSR yet (change record OI-3)</t>
           </r>
           <r>
             <rPr>
@@ -24871,22 +24868,22 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/assured_config.py</t>
+   assurance/07-supporting/impact/change-2026-10-20-settings-held-while-engaged.md</t>
           </r>
         </is>
       </c>
       <c r="J108" s="45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K108" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No check while engaged; test_assured_config.py checks that the gate is entry-only, which is this behaviour</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_assured_config.py TestSettingsHeldWhileEngaged (5 tests: held while engaged, applied after disengagement, next engagement refused, applied at once while disengaged, other platforms unchanged; 4 fail on the code before #342). Run by the CI unit_tests job (tests run 39348218534 at 18b15cd: 1583 passed, 0 failed); not proven by mutation, so D 8, D 4 with mutation</t>
           </r>
           <r>
             <rPr>
@@ -24899,8 +24896,8 @@
           </r>
         </is>
       </c>
-      <c r="L108" s="54" t="n">
-        <v>10</v>
+      <c r="L108" s="45" t="n">
+        <v>8</v>
       </c>
       <c r="M108" s="52" t="inlineStr">
         <is>
@@ -24929,13 +24926,21 @@
           </r>
         </is>
       </c>
-      <c r="O108" s="59" t="inlineStr">
-        <is>
-          <t>decision pending</t>
-        </is>
-      </c>
-      <c r="P108" s="43" t="inlineStr"/>
-      <c r="Q108" s="43" t="inlineStr"/>
+      <c r="O108" s="47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P108" s="43" t="inlineStr">
+        <is>
+          <t>10/5/8</t>
+        </is>
+      </c>
+      <c r="Q108" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R108" s="48" t="inlineStr"/>
       <c r="S108" s="48" t="inlineStr"/>
     </row>
@@ -32263,7 +32268,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.6 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.7 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -32293,122 +32298,122 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="60" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="60" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="60" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="60" t="inlineStr">
+      <c r="F1" s="59" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="60" t="inlineStr">
+      <c r="G1" s="59" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="60" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="60" t="inlineStr">
+      <c r="I1" s="59" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>Run the opendbc safety suite and the mutation tests as a blocking gate in LionDriver CI for every change and submodule bump</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="62" t="inlineStr">
+      <c r="E2" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F2" s="61" t="inlineStr"/>
-      <c r="G2" s="61" t="inlineStr">
+      <c r="F2" s="60" t="inlineStr"/>
+      <c r="G2" s="60" t="inlineStr">
         <is>
           <t>10/5/3</t>
         </is>
       </c>
-      <c r="H2" s="63" t="inlineStr">
+      <c r="H2" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I2" s="61" t="inlineStr">
+      <c r="I2" s="60" t="inlineStr">
         <is>
           <t>.github/workflows/safety.yaml (CR-CI-05, merged from liondriver-dev): safety tests with 100% line coverage, MISRA and mutation jobs on push and pull request. Branch protection making them blocking is not verified here</t>
         </is>
       </c>
     </row>
     <row r="3" ht="141" customHeight="1">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>Requirements-based tests for the panda safety model, traced to the draft TSRs and SWSRs (assurance WP-S-02, WP-W-02); the requirements exist as drafts, the tests do not</t>
         </is>
       </c>
-      <c r="D3" s="61" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="61" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="61" t="inlineStr">
+      <c r="F3" s="60" t="inlineStr">
         <is>
           <t>SWF-001.C2
 SWF-002.C1
@@ -32422,426 +32427,426 @@
 SWF-017.C1</t>
         </is>
       </c>
-      <c r="G3" s="61" t="inlineStr">
+      <c r="G3" s="60" t="inlineStr">
         <is>
           <t>10/3/3</t>
         </is>
       </c>
-      <c r="H3" s="64" t="inlineStr">
+      <c r="H3" s="63" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I3" s="61" t="inlineStr"/>
+      <c r="I3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="46.5" customHeight="1">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from vehicle measurements (FSC FOI-001, DFA DM-10) and set panda limits from them, independently of the SoC limits</t>
         </is>
       </c>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="61" t="inlineStr">
+      <c r="F4" s="60" t="inlineStr">
         <is>
           <t>SWF-001.C1
 SWF-003.C1
 SWF-003.C3</t>
         </is>
       </c>
-      <c r="G4" s="61" t="inlineStr"/>
-      <c r="H4" s="61" t="inlineStr"/>
-      <c r="I4" s="61" t="inlineStr"/>
+      <c r="G4" s="60" t="inlineStr"/>
+      <c r="H4" s="60" t="inlineStr"/>
+      <c r="I4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="100.5" customHeight="1">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-004</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>Implement the panda configuration lock (LD-DES-001 DR-01..DR-07, DR-05 for ELM327)</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="61" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F5" s="61" t="inlineStr">
+      <c r="F5" s="60" t="inlineStr">
         <is>
           <t>SWF-013.C1</t>
         </is>
       </c>
-      <c r="G5" s="61" t="inlineStr"/>
-      <c r="H5" s="61" t="inlineStr"/>
-      <c r="I5" s="61" t="inlineStr">
+      <c r="G5" s="60" t="inlineStr"/>
+      <c r="H5" s="60" t="inlineStr"/>
+      <c r="I5" s="60" t="inlineStr">
         <is>
           <t>Implemented for the reference build in panda#4 (9f60e17); D-12 decided. The reference build is the default since #36/#41 (SWF-ACT-009 completed). DR-05 (ELM327 refused after the car mode until ignition off) in panda#16 (a55bdfc). Open: the remaining LD-DES-001 requirements (firmware authenticity), HIL test test_11_reference_lock not run (D-04)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46.5" customHeight="1">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-005</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>Add an acceleration-rate (jerk) check to the panda longitudinal checks, or justify the absence with characterized powertrain rate limits (OI-002)</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>SWF-004.C1</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr"/>
-      <c r="H6" s="61" t="inlineStr"/>
-      <c r="I6" s="61" t="inlineStr"/>
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="46.5" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-006</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Verify on the vehicle that the PCM cancels cruise on brake (FSC FOI-006) so PCM_CRUISE can be credited as the diverse brake path; add a safety test for brake-without-cruise-cancel</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="61" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>SWF-005.C1</t>
         </is>
       </c>
-      <c r="G7" s="61" t="inlineStr"/>
-      <c r="H7" s="61" t="inlineStr"/>
-      <c r="I7" s="61" t="inlineStr"/>
+      <c r="G7" s="60" t="inlineStr"/>
+      <c r="H7" s="60" t="inlineStr"/>
+      <c r="I7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="114" customHeight="1">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-007</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Derive RX-lag and heartbeat timeouts from the FTTI and check them at 8 Hz or faster while controls are allowed (LD-DES-001 DR-20)</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="61" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>SWF-006.C1
 SWF-014.C1
 SWF-014.C2</t>
         </is>
       </c>
-      <c r="G8" s="61" t="inlineStr"/>
-      <c r="H8" s="61" t="inlineStr"/>
-      <c r="I8" s="61" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr">
         <is>
           <t>RX lag: 5 periods at 100 Hz (opendbc#1, panda#3). Heartbeat loss: 0.3 s at 100 Hz (panda#7, BL-003). BL-005: actuation frames supervised for arrival, 50 ms STEERING_LKA and 100 ms ACC_CONTROL (TSR-408, opendbc#11, reference build by default), which bounds a control-loop stall behind a live heartbeat (SWF-014.C2 AP L). Engaged mismatch still about 3 s at 1 Hz; FTTI derivation and confirmation of the timeouts on reference logs open</t>
         </is>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-008</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Add a unit or static check that every host TX path calls can_send with skip_tx_hook=false</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="61" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>SWF-016.C1</t>
         </is>
       </c>
-      <c r="G9" s="61" t="inlineStr"/>
-      <c r="H9" s="61" t="inlineStr"/>
-      <c r="I9" s="61" t="inlineStr"/>
+      <c r="G9" s="60" t="inlineStr"/>
+      <c r="H9" s="60" t="inlineStr"/>
+      <c r="I9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="127.5" customHeight="1">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-009</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Make LIONDRIVER_REFERENCE=1 (with RELEASE=1) the only firmware build used for the reference configuration: set it in openpilot's panda build and the release procedure, and have the host check it (e.g. a version or health flag) before engaging</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="62" t="inlineStr">
+      <c r="E10" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F10" s="61" t="inlineStr">
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>SWF-001.C3
 SWF-008.C1
 SWF-013.C2</t>
         </is>
       </c>
-      <c r="G10" s="61" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H10" s="64" t="inlineStr">
+      <c r="H10" s="63" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" s="61" t="inlineStr">
+      <c r="I10" s="60" t="inlineStr">
         <is>
           <t>SConstruct builds the panda firmware and pandad with LIONDRIVER_REFERENCE=1 by default (#36, #41); pandad sets a car mode only on a panda reporting HEALTH_FLAG_REFERENCE_BUILD (TSR-619, panda#12); release_variant.sh selects the reference variant and the CI job panda_reference_release_build checks every firmware compile for -DLIONDRIVER_REFERENCE (#80, green at 20569e9). The signed release image and its install check stay with PFMEA (PFM-001) and SWF-ACT-028</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-010</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Restrict ELM327 TX to the UDS services fingerprinting and radar disable need, and refuse it above standstill (WP-W-04 OI-6)</t>
         </is>
       </c>
-      <c r="D11" s="61" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="61" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F11" s="61" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>SWF-015.C1</t>
         </is>
       </c>
-      <c r="G11" s="61" t="inlineStr"/>
-      <c r="H11" s="61" t="inlineStr"/>
-      <c r="I11" s="61" t="inlineStr">
+      <c r="G11" s="60" t="inlineStr"/>
+      <c r="H11" s="60" t="inlineStr"/>
+      <c r="I11" s="60" t="inlineStr">
         <is>
           <t>Reference build: ELM327 refused after the car mode until ignition off (panda#16, DR-05, host-tested). Open: frame-content restriction and a motion condition before the car mode</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46.5" customHeight="1">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-011</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Confirm the LSI range from the STM32H725 datasheet and run the watchdog HIL test (test_10_hw_watchdog) on the bench, including a long soak for spurious resets (D-04)</t>
         </is>
       </c>
-      <c r="D12" s="61" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E12" s="61" t="inlineStr">
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="61" t="inlineStr">
+      <c r="F12" s="60" t="inlineStr">
         <is>
           <t>SWF-018.C1
 SWF-019.C1</t>
         </is>
       </c>
-      <c r="G12" s="61" t="inlineStr"/>
-      <c r="H12" s="61" t="inlineStr"/>
-      <c r="I12" s="61" t="inlineStr"/>
+      <c r="G12" s="60" t="inlineStr"/>
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="73.5" customHeight="1">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-020</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Bind the heartbeat to the command path. Send engaged=1 only while selfdriveState is enabled and the forwarding thread has sent a sendcan batch less than 0.1 s ago, or add a sequence or age field the panda checks (TSR-409, TSR-602). Coordinate with SWF-ACT-007 (panda engaged-mismatch at 0.3 s)</t>
         </is>
       </c>
-      <c r="D13" s="61" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E13" s="61" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="61" t="inlineStr">
+      <c r="F13" s="60" t="inlineStr">
         <is>
           <t>SWF-020.C1</t>
         </is>
       </c>
-      <c r="G13" s="61" t="inlineStr"/>
-      <c r="H13" s="61" t="inlineStr"/>
-      <c r="I13" s="61" t="inlineStr"/>
+      <c r="G13" s="60" t="inlineStr"/>
+      <c r="H13" s="60" t="inlineStr"/>
+      <c r="I13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="87" customHeight="1">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-021</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C14" s="61" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Make link failure bounded and visible. Send the heartbeat independently of the health read. Give control transfers a finite timeout and bound the fail-recovery loop. Clear connected and exit on a persistent failure. Do not reset or DFU-recover the internal panda from pandad.py while onroad unless needed. In selfdrived (EL-04), raise the controlsAllowed-mismatch alert within 0.1-0.2 s instead of 200 frames</t>
         </is>
       </c>
-      <c r="D14" s="61" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E14" s="61" t="inlineStr">
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F14" s="61" t="inlineStr">
+      <c r="F14" s="60" t="inlineStr">
         <is>
           <t>SWF-021.C1
 SWF-021.C2
@@ -32849,313 +32854,313 @@
 SWF-027.C2</t>
         </is>
       </c>
-      <c r="G14" s="61" t="inlineStr"/>
-      <c r="H14" s="61" t="inlineStr"/>
-      <c r="I14" s="61" t="inlineStr">
+      <c r="G14" s="60" t="inlineStr"/>
+      <c r="H14" s="60" t="inlineStr"/>
+      <c r="I14" s="60" t="inlineStr">
         <is>
           <t>selfdrived part done in part: controlsMismatch within 2 samples and 0.5 s (#51, TSR-621), pandaHeartbeatLost on the panda flag (TSR-615). The pandad parts (heartbeat independent of the health read, finite control-transfer timeout) are open</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-022</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C15" s="61" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Host allow-list for the reference configuration (TOYOTA, param 73, alternative experience 0) before 0xdc/0xdf. Read back the mode, param and alternative experience from health, and set safety_configured_ only on a match. Retry or refuse ControlsReady on a mismatch</t>
         </is>
       </c>
-      <c r="D15" s="61" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E15" s="61" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F15" s="61" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr">
         <is>
           <t>SWF-022.C1
 SWF-022.C2</t>
         </is>
       </c>
-      <c r="G15" s="61" t="inlineStr"/>
-      <c r="H15" s="61" t="inlineStr"/>
-      <c r="I15" s="61" t="inlineStr">
+      <c r="G15" s="60" t="inlineStr"/>
+      <c r="H15" s="60" t="inlineStr"/>
+      <c r="I15" s="60" t="inlineStr">
         <is>
           <t>Not started on the host. BL-005: the panda reference lock refuses any mode but TOYOTA/73 in the default build, which removes the unsafe direction of SWF-022.C1; the host allow-list and readback remain for diagnosability</t>
         </is>
       </c>
     </row>
     <row r="16" ht="73.5" customHeight="1">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-023</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C16" s="61" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>Derive the sendcan maximum age from the FTTI and the control period (e.g. 0.1 s). Compare it in one clock domain (stamp with CLOCK_BOOTTIME, or compare with CLOCK_MONOTONIC). After a stall, keep only the newest frame per address instead of replaying the backlog. Decide whether events with valid=false are forwarded</t>
         </is>
       </c>
-      <c r="D16" s="61" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E16" s="61" t="inlineStr">
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="61" t="inlineStr">
+      <c r="F16" s="60" t="inlineStr">
         <is>
           <t>SWF-023.C1
 SWF-024.C1</t>
         </is>
       </c>
-      <c r="G16" s="61" t="inlineStr"/>
-      <c r="H16" s="61" t="inlineStr"/>
-      <c r="I16" s="61" t="inlineStr"/>
+      <c r="G16" s="60" t="inlineStr"/>
+      <c r="H16" s="60" t="inlineStr"/>
+      <c r="I16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="73.5" customHeight="1">
-      <c r="A17" s="61" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-024</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>Add host unit tests for the pandad logic, run in CI (unit_tests via test_native.py): the sendcan age gate including the clock domain, the heartbeat engaged derivation, the fault-bit mapping, and the safety setter sequence and readback, using a fake Panda. Show they fail on mutated gates so D can be rated as proven</t>
         </is>
       </c>
-      <c r="D17" s="61" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E17" s="61" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F17" s="61" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr">
         <is>
           <t>SWF-023.C1
 SWF-024.C1
 SWF-025.C1</t>
         </is>
       </c>
-      <c r="G17" s="61" t="inlineStr"/>
-      <c r="H17" s="61" t="inlineStr"/>
-      <c r="I17" s="61" t="inlineStr"/>
+      <c r="G17" s="60" t="inlineStr"/>
+      <c r="H17" s="60" t="inlineStr"/>
+      <c r="I17" s="60" t="inlineStr"/>
     </row>
     <row r="18" ht="87" customHeight="1">
-      <c r="A18" s="61" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-025</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C18" s="61" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>Fix the faults mapping. Size the list from the mapped bits only, log unknown bits, and add the panda bit 27 (interruptRateSoundDma) to cereal FaultType (log.capnp, pandad.cc:257-268)</t>
         </is>
       </c>
-      <c r="D18" s="61" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E18" s="62" t="inlineStr">
+      <c r="E18" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F18" s="61" t="inlineStr">
+      <c r="F18" s="60" t="inlineStr">
         <is>
           <t>SWF-025.C1</t>
         </is>
       </c>
-      <c r="G18" s="61" t="inlineStr">
+      <c r="G18" s="60" t="inlineStr">
         <is>
           <t>8/5/4</t>
         </is>
       </c>
-      <c r="H18" s="65" t="inlineStr">
+      <c r="H18" s="64" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I18" s="61" t="inlineStr">
+      <c r="I18" s="60" t="inlineStr">
         <is>
           <t>Merged in jherrodthomas/LionDriver#48 (3534bc2): fill_panda_faults, interruptRateSoundDma @27, tests/test_pandad_faults run by test_native.py in CI unit_tests; fails with the old sizing. Impact record assurance/07-supporting/impact/change-2026-10-13-pandad-fault-mapping.md. SWF-025.C1 re-rated O 8-&gt;5, D 10-&gt;4 (AP H-&gt;M)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-026</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="61" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>Report frames that pandad drops (age gate, failed bulk write) in pandaStates or a pandad event, and have selfdrived disable with an alert while engaged (closes System FMEA SFM-005.C2 and SFM-011.C2 on the host side)</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E19" s="61" t="inlineStr">
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="61" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>SWF-024.C1
 SWF-024.C2</t>
         </is>
       </c>
-      <c r="G19" s="61" t="inlineStr"/>
-      <c r="H19" s="61" t="inlineStr"/>
-      <c r="I19" s="61" t="inlineStr"/>
+      <c r="G19" s="60" t="inlineStr"/>
+      <c r="H19" s="60" t="inlineStr"/>
+      <c r="I19" s="60" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-027</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C20" s="61" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>Replace the XOR checksums on the SPI link with a CRC (host spi.cc and panda firmware), or justify XOR with a residual-error analysis that uses the measured SPI error rate (spi_error_count) and the Toyota message checksum as a diverse check</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="D20" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="E20" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F20" s="61" t="inlineStr">
+      <c r="F20" s="60" t="inlineStr">
         <is>
           <t>SWF-026.C1</t>
         </is>
       </c>
-      <c r="G20" s="61" t="inlineStr"/>
-      <c r="H20" s="61" t="inlineStr"/>
-      <c r="I20" s="61" t="inlineStr"/>
+      <c r="G20" s="60" t="inlineStr"/>
+      <c r="H20" s="60" t="inlineStr"/>
+      <c r="I20" s="60" t="inlineStr"/>
     </row>
     <row r="21" ht="87" customHeight="1">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-028</t>
         </is>
       </c>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C21" s="61" t="inlineStr">
+      <c r="C21" s="60" t="inlineStr">
         <is>
           <t>Build and flash only the LIONDRIVER_REFERENCE firmware for the reference configuration, and have pandad check a reference-build flag or version before setting a car mode (with SWF-ACT-009). Compile out BOARDD_SKIP_FW_CHECK, STARTED, FAKESEND, SPI_ERR_PROB and BOARDD_LOOPBACK in release builds</t>
         </is>
       </c>
-      <c r="D21" s="61" t="inlineStr">
+      <c r="D21" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E21" s="61" t="inlineStr">
+      <c r="E21" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr">
+      <c r="F21" s="60" t="inlineStr">
         <is>
           <t>SWF-022.C1
 SWF-028.C1
 SWF-028.C2</t>
         </is>
       </c>
-      <c r="G21" s="61" t="inlineStr"/>
-      <c r="H21" s="61" t="inlineStr"/>
-      <c r="I21" s="61" t="inlineStr">
+      <c r="G21" s="60" t="inlineStr"/>
+      <c r="H21" s="60" t="inlineStr"/>
+      <c r="I21" s="60" t="inlineStr">
         <is>
           <t>Reference firmware built by default and the reference-build flag checked before a car mode (#36, #41, TSR-619). Open: check that the panda runs the assured release image (version or signature of the released build, not any reference build), a host test of the check, and compiling out the test hooks</t>
         </is>
       </c>
     </row>
     <row r="22" ht="114" customHeight="1">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-029</t>
         </is>
       </c>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C22" s="61" t="inlineStr">
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>Run the pandad hardware tests (test_pandad.py, test_pandad_spi.py, test_pandad_loopback.py) on a comma 3X before release. While engaged on a bench, inject: stopping selfdrived, controlsd and card; killing or hanging pandad; SPI errors; and a panda reset. Measure the time to no output and to the SoC alert (FSR-007 verification, D-04)</t>
         </is>
       </c>
-      <c r="D22" s="61" t="inlineStr">
+      <c r="D22" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E22" s="61" t="inlineStr">
+      <c r="E22" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F22" s="61" t="inlineStr">
+      <c r="F22" s="60" t="inlineStr">
         <is>
           <t>SWF-020.C1
 SWF-021.C1
@@ -33167,37 +33172,37 @@
 SWF-029.C2</t>
         </is>
       </c>
-      <c r="G22" s="61" t="inlineStr"/>
-      <c r="H22" s="61" t="inlineStr"/>
-      <c r="I22" s="61" t="inlineStr"/>
+      <c r="G22" s="60" t="inlineStr"/>
+      <c r="H22" s="60" t="inlineStr"/>
+      <c r="I22" s="60" t="inlineStr"/>
     </row>
     <row r="23" ht="87" customHeight="1">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-030</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C23" s="61" t="inlineStr">
+      <c r="C23" s="60" t="inlineStr">
         <is>
           <t>Requirements-based tests for selfdrived traced to FSR-030/033/034/036 and TSR-601/606/617/621: state machine, data_sample/update_events with synthetic carState, pandaStates and SubMaster faults (brake, cancel, stale or missing services, panda mismatch), helpers.py and alert priority; prove them with a mutation run on state.py, selfdrived.py and helpers.py</t>
         </is>
       </c>
-      <c r="D23" s="61" t="inlineStr">
+      <c r="D23" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E23" s="61" t="inlineStr">
+      <c r="E23" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F23" s="61" t="inlineStr">
+      <c r="F23" s="60" t="inlineStr">
         <is>
           <t>SWF-030.C1
 SWF-031.C2
@@ -33205,116 +33210,116 @@
 SWF-034.C1</t>
         </is>
       </c>
-      <c r="G23" s="61" t="inlineStr">
+      <c r="G23" s="60" t="inlineStr">
         <is>
           <t>10/5/4</t>
         </is>
       </c>
-      <c r="H23" s="63" t="inlineStr">
+      <c r="H23" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I23" s="61" t="inlineStr"/>
+      <c r="I23" s="60" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="61" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-031</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C24" s="61" t="inlineStr">
+      <c r="C24" s="60" t="inlineStr">
         <is>
           <t>Reference-configuration guard: refuse engagement (permanent NO_ENTRY) when REPLAY, SIMULATION or TESTING_CLOSET is set or the big-model (chestnut) path is active, and exclude that path from reference builds (TSR-603, TSR-613)</t>
         </is>
       </c>
-      <c r="D24" s="61" t="inlineStr">
+      <c r="D24" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E24" s="61" t="inlineStr">
+      <c r="E24" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F24" s="61" t="inlineStr">
+      <c r="F24" s="60" t="inlineStr">
         <is>
           <t>SWF-030.C2
 SWF-032.C2</t>
         </is>
       </c>
-      <c r="G24" s="61" t="inlineStr"/>
-      <c r="H24" s="61" t="inlineStr"/>
-      <c r="I24" s="61" t="inlineStr"/>
+      <c r="G24" s="60" t="inlineStr"/>
+      <c r="H24" s="60" t="inlineStr"/>
+      <c r="I24" s="60" t="inlineStr"/>
     </row>
     <row r="25" ht="46.5" customHeight="1">
-      <c r="A25" s="61" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-032</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C25" s="61" t="inlineStr">
+      <c r="C25" s="60" t="inlineStr">
         <is>
           <t>Supervise carState freshness in selfdrived (age of the last message, at most 2 periods) and raise an immediate disable when it is stale, instead of reusing the previous carState</t>
         </is>
       </c>
-      <c r="D25" s="61" t="inlineStr">
+      <c r="D25" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E25" s="61" t="inlineStr">
+      <c r="E25" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F25" s="61" t="inlineStr">
+      <c r="F25" s="60" t="inlineStr">
         <is>
           <t>SWF-031.C1</t>
         </is>
       </c>
-      <c r="G25" s="61" t="inlineStr"/>
-      <c r="H25" s="61" t="inlineStr"/>
-      <c r="I25" s="61" t="inlineStr"/>
+      <c r="G25" s="60" t="inlineStr"/>
+      <c r="H25" s="60" t="inlineStr"/>
+      <c r="I25" s="60" t="inlineStr"/>
     </row>
     <row r="26" ht="87" customHeight="1">
-      <c r="A26" s="61" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-033</t>
         </is>
       </c>
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C26" s="61" t="inlineStr">
+      <c r="C26" s="60" t="inlineStr">
         <is>
           <t>Panda status supervision per TSR-615, TSR-621 and TSR-626a: controlsMismatch within 2 samples and 0.5 s (time-based); safety model/parameter mismatch as NO_ENTRY from start instead of a 10 s grace; pandaStates older than 0.2 s treated as mismatch; immediate disable on heartbeatLost, rising safetyTxBlocked, txRateExceeded and any panda fault flag</t>
         </is>
       </c>
-      <c r="D26" s="61" t="inlineStr">
+      <c r="D26" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E26" s="61" t="inlineStr">
+      <c r="E26" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F26" s="61" t="inlineStr">
+      <c r="F26" s="60" t="inlineStr">
         <is>
           <t>SWF-032.C1
 SWF-034.C1
@@ -33322,258 +33327,258 @@
 SWF-034.C3</t>
         </is>
       </c>
-      <c r="G26" s="61" t="inlineStr"/>
-      <c r="H26" s="61" t="inlineStr"/>
-      <c r="I26" s="61" t="inlineStr">
+      <c r="G26" s="60" t="inlineStr"/>
+      <c r="H26" s="60" t="inlineStr"/>
+      <c r="I26" s="60" t="inlineStr">
         <is>
           <t>controlsMismatch within 2 consecutive samples and 0.5 s done (selfdrived/supervision.py, unit tests; impact record change-2026-10-13-host-supervision.md). Open: safety-model mismatch as NO_ENTRY from start, pandaStates age</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46.5" customHeight="1">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-034</t>
         </is>
       </c>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C27" s="61" t="inlineStr">
+      <c r="C27" s="60" t="inlineStr">
         <is>
           <t>Give cruiseMismatch a warning and an ACC cancel retry within 1 s (TSR-308, GAP-19)</t>
         </is>
       </c>
-      <c r="D27" s="61" t="inlineStr">
+      <c r="D27" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E27" s="62" t="inlineStr">
+      <c r="E27" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F27" s="61" t="inlineStr">
+      <c r="F27" s="60" t="inlineStr">
         <is>
           <t>SWF-039.C1</t>
         </is>
       </c>
-      <c r="G27" s="61" t="inlineStr"/>
-      <c r="H27" s="61" t="inlineStr"/>
-      <c r="I27" s="61" t="inlineStr">
+      <c r="G27" s="60" t="inlineStr"/>
+      <c r="H27" s="60" t="inlineStr"/>
+      <c r="I27" s="60" t="inlineStr">
         <is>
           <t>cruiseMismatch after 1 s with a repeating prompt; controlsd keeps requesting the cancel (change-2026-10-13-host-supervision.md). Vehicle check under SWF-ACT-049</t>
         </is>
       </c>
     </row>
     <row r="28" ht="73.5" customHeight="1">
-      <c r="A28" s="61" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-035</t>
         </is>
       </c>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C28" s="61" t="inlineStr">
+      <c r="C28" s="60" t="inlineStr">
         <is>
           <t>Classify reactions per TSR-601 (immediate disable for loss or staleness of a control-law input) and justify each remaining SOFT_DISABLE against the FTTI (SFM-016, GAP-16); make soft-disable and mismatch timers time-based (monotonic clock); move blocking Params writes out of the 100 Hz loop</t>
         </is>
       </c>
-      <c r="D28" s="61" t="inlineStr">
+      <c r="D28" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E28" s="61" t="inlineStr">
+      <c r="E28" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F28" s="61" t="inlineStr">
+      <c r="F28" s="60" t="inlineStr">
         <is>
           <t>SWF-033.C1
 SWF-033.C2</t>
         </is>
       </c>
-      <c r="G28" s="61" t="inlineStr"/>
-      <c r="H28" s="61" t="inlineStr"/>
-      <c r="I28" s="61" t="inlineStr"/>
+      <c r="G28" s="60" t="inlineStr"/>
+      <c r="H28" s="60" t="inlineStr"/>
+      <c r="I28" s="60" t="inlineStr"/>
     </row>
     <row r="29" ht="87" customHeight="1">
-      <c r="A29" s="61" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-036</t>
         </is>
       </c>
-      <c r="B29" s="61" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C29" s="61" t="inlineStr">
+      <c r="C29" s="60" t="inlineStr">
         <is>
           <t>Rank soft and immediate disable takeover alerts above every WARNING and PERMANENT alert except FCW, keep the takeover sound when an AEB alert is shown, name the fault class in the text (canError, TSR-606), and add a test of the ordering. Rank the driver-monitoring level 2 and 3 alerts so that speedTooHigh or a later-starting HIGH alert cannot mask them (WP-A-03 DFI-25, SWF-035)</t>
         </is>
       </c>
-      <c r="D29" s="61" t="inlineStr">
+      <c r="D29" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E29" s="61" t="inlineStr">
+      <c r="E29" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F29" s="61" t="inlineStr">
+      <c r="F29" s="60" t="inlineStr">
         <is>
           <t>SWF-035.C1</t>
         </is>
       </c>
-      <c r="G29" s="61" t="inlineStr"/>
-      <c r="H29" s="61" t="inlineStr"/>
-      <c r="I29" s="61" t="inlineStr"/>
+      <c r="G29" s="60" t="inlineStr"/>
+      <c r="H29" s="60" t="inlineStr"/>
+      <c r="I29" s="60" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="61" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-037</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C30" s="61" t="inlineStr">
+      <c r="C30" s="60" t="inlineStr">
         <is>
           <t>selfdrived liveness: ui and soundd raise the critical takeover alert within 0.5 s of missing selfdriveState while engaged (EL-05 change, TSR-622); add a process watchdog for selfdrived; remove selfdrived from the fuzz NOT_TESTED list</t>
         </is>
       </c>
-      <c r="D30" s="61" t="inlineStr">
+      <c r="D30" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E30" s="61" t="inlineStr">
+      <c r="E30" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F30" s="61" t="inlineStr">
+      <c r="F30" s="60" t="inlineStr">
         <is>
           <t>SWF-036.C1
 SWF-036.C2</t>
         </is>
       </c>
-      <c r="G30" s="61" t="inlineStr"/>
-      <c r="H30" s="61" t="inlineStr"/>
-      <c r="I30" s="61" t="inlineStr"/>
+      <c r="G30" s="60" t="inlineStr"/>
+      <c r="H30" s="60" t="inlineStr"/>
+      <c r="I30" s="60" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="61" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-038</t>
         </is>
       </c>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C31" s="61" t="inlineStr">
+      <c r="C31" s="60" t="inlineStr">
         <is>
           <t>Revisit TSR-617: set excessive-actuation thresholds from the vehicle envelope and fork drive logs, bound the device_motion_valid reset, check longitudinal response during override, and add unit tests for helpers.py</t>
         </is>
       </c>
-      <c r="D31" s="61" t="inlineStr">
+      <c r="D31" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E31" s="61" t="inlineStr">
+      <c r="E31" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F31" s="61" t="inlineStr">
+      <c r="F31" s="60" t="inlineStr">
         <is>
           <t>SWF-037.C1
 SWF-037.C2</t>
         </is>
       </c>
-      <c r="G31" s="61" t="inlineStr"/>
-      <c r="H31" s="61" t="inlineStr"/>
-      <c r="I31" s="61" t="inlineStr"/>
+      <c r="G31" s="60" t="inlineStr"/>
+      <c r="H31" s="60" t="inlineStr"/>
+      <c r="I31" s="60" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="61" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-039</t>
         </is>
       </c>
-      <c r="B32" s="61" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C32" s="61" t="inlineStr">
+      <c r="C32" s="60" t="inlineStr">
         <is>
           <t>Resolve FSR-033 against the implementation: either revise FSR-033 to the actual yield strategy (integrator freeze, panda bound, override force verified by the FSR-031 vehicle test) or ramp the torque request down while steeringPressed</t>
         </is>
       </c>
-      <c r="D32" s="61" t="inlineStr">
+      <c r="D32" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E32" s="61" t="inlineStr">
+      <c r="E32" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F32" s="61" t="inlineStr">
+      <c r="F32" s="60" t="inlineStr">
         <is>
           <t>SWF-038.C1</t>
         </is>
       </c>
-      <c r="G32" s="61" t="inlineStr"/>
-      <c r="H32" s="61" t="inlineStr"/>
-      <c r="I32" s="61" t="inlineStr"/>
+      <c r="G32" s="60" t="inlineStr"/>
+      <c r="H32" s="60" t="inlineStr"/>
+      <c r="I32" s="60" t="inlineStr"/>
     </row>
     <row r="33" ht="100.5" customHeight="1">
-      <c r="A33" s="61" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-040</t>
         </is>
       </c>
-      <c r="B33" s="61" t="inlineStr">
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C33" s="61" t="inlineStr">
+      <c r="C33" s="60" t="inlineStr">
         <is>
           <t>Implement TSR-602 in controlsd: check age and valid of selfdriveState, carState, modelV2, longitudinalPlan, vehicleParameters and deviceMotion before use (≤ 2 periods); set latActive/longActive false and raise an immediate-disable event when stale; derive carControl.valid from these checks and have card stop actuating on carControl.valid false; give cruiseMismatch a disable type</t>
         </is>
       </c>
-      <c r="D33" s="61" t="inlineStr">
+      <c r="D33" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E33" s="61" t="inlineStr">
+      <c r="E33" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F33" s="61" t="inlineStr">
+      <c r="F33" s="60" t="inlineStr">
         <is>
           <t>SWF-040.C1
 SWF-042.C3
@@ -33584,170 +33589,170 @@
 SWF-081.C1</t>
         </is>
       </c>
-      <c r="G33" s="61" t="inlineStr">
+      <c r="G33" s="60" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H33" s="64" t="inlineStr">
+      <c r="H33" s="63" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I33" s="61" t="inlineStr">
+      <c r="I33" s="60" t="inlineStr">
         <is>
           <t>latActive/longActive gated on selfdriveState, carState, modelV2, longitudinalPlan (controls/lib/input_freshness.py, unit tests); threshold 10 periods, not 2; vehicleParameters and deviceMotion not yet included; reaction via commIssue (change-2026-10-13-host-supervision.md, OI-1)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="61" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-041</t>
         </is>
       </c>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C34" s="61" t="inlineStr">
+      <c r="C34" s="60" t="inlineStr">
         <is>
           <t>Implement TSR-604: treat any non-finite input or actuator value as a fault (immediate disable with alert), reset desired_curvature and both controllers' state, and guard lateralDelay before the int() conversion</t>
         </is>
       </c>
-      <c r="D34" s="61" t="inlineStr">
+      <c r="D34" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E34" s="61" t="inlineStr">
+      <c r="E34" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F34" s="61" t="inlineStr">
+      <c r="F34" s="60" t="inlineStr">
         <is>
           <t>SWF-045.C1
 SWF-045.C2
 SWF-047.C1</t>
         </is>
       </c>
-      <c r="G34" s="61" t="inlineStr">
+      <c r="G34" s="60" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H34" s="64" t="inlineStr">
+      <c r="H34" s="63" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I34" s="61" t="inlineStr">
+      <c r="I34" s="60" t="inlineStr">
         <is>
           <t>Non-finite desired curvature, roll, aTarget and lateralDelay no longer reach the controllers (one step skipped, desired_curvature reset); no fault event or alert yet (change-2026-10-13-host-supervision.md)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="46.5" customHeight="1">
-      <c r="A35" s="61" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-042</t>
         </is>
       </c>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B35" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C35" s="61" t="inlineStr">
+      <c r="C35" s="60" t="inlineStr">
         <is>
           <t>Reset the LatControlTorque PID (and LatControlPID) in reset(), or record why upstream carries the integrator over engagements; check against current upstream openpilot</t>
         </is>
       </c>
-      <c r="D35" s="61" t="inlineStr">
+      <c r="D35" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E35" s="61" t="inlineStr">
+      <c r="E35" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F35" s="61" t="inlineStr">
+      <c r="F35" s="60" t="inlineStr">
         <is>
           <t>SWF-042.C1</t>
         </is>
       </c>
-      <c r="G35" s="61" t="inlineStr"/>
-      <c r="H35" s="61" t="inlineStr"/>
-      <c r="I35" s="61" t="inlineStr"/>
+      <c r="G35" s="60" t="inlineStr"/>
+      <c r="H35" s="60" t="inlineStr"/>
+      <c r="I35" s="60" t="inlineStr"/>
     </row>
     <row r="36" ht="87" customHeight="1">
-      <c r="A36" s="61" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-043</t>
         </is>
       </c>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C36" s="61" t="inlineStr">
+      <c r="C36" s="60" t="inlineStr">
         <is>
           <t>Requirements-based unit tests for controlsd and the Toyota CarController (latActive/longActive gating table per FSR-006, zero torque and request bit off when not active, controller reset across disengagement, cancel on every disengagement path, active-torque frames accepted by the panda model at the limits), run in LionDriver CI and proven by mutation</t>
         </is>
       </c>
-      <c r="D36" s="61" t="inlineStr">
+      <c r="D36" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E36" s="61" t="inlineStr">
+      <c r="E36" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F36" s="61" t="inlineStr">
+      <c r="F36" s="60" t="inlineStr">
         <is>
           <t>SWF-041.C1
 SWF-042.C1
 SWF-047.C3</t>
         </is>
       </c>
-      <c r="G36" s="61" t="inlineStr"/>
-      <c r="H36" s="61" t="inlineStr"/>
-      <c r="I36" s="61" t="inlineStr"/>
+      <c r="G36" s="60" t="inlineStr"/>
+      <c r="H36" s="60" t="inlineStr"/>
+      <c r="I36" s="60" t="inlineStr"/>
     </row>
     <row r="37" ht="127.5" customHeight="1">
-      <c r="A37" s="61" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-044</t>
         </is>
       </c>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B37" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C37" s="61" t="inlineStr">
+      <c r="C37" s="60" t="inlineStr">
         <is>
           <t>Add NaN/inf and stale-input injection for controlsd and card (enable them in test_fuzzy.py with the Corolla fingerprint, or a dedicated test), and run the opendbc car tests (test_models, test_car_interfaces, test_lateral_limits) for Toyota in LionDriver CI</t>
         </is>
       </c>
-      <c r="D37" s="61" t="inlineStr">
+      <c r="D37" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E37" s="61" t="inlineStr">
+      <c r="E37" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F37" s="61" t="inlineStr">
+      <c r="F37" s="60" t="inlineStr">
         <is>
           <t>SWF-045.C1
 SWF-045.C2
@@ -33760,37 +33765,37 @@
 SWF-060.C1</t>
         </is>
       </c>
-      <c r="G37" s="61" t="inlineStr"/>
-      <c r="H37" s="61" t="inlineStr"/>
-      <c r="I37" s="61" t="inlineStr"/>
+      <c r="G37" s="60" t="inlineStr"/>
+      <c r="H37" s="60" t="inlineStr"/>
+      <c r="I37" s="60" t="inlineStr"/>
     </row>
     <row r="38" ht="73.5" customHeight="1">
-      <c r="A38" s="61" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-045</t>
         </is>
       </c>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C38" s="61" t="inlineStr">
+      <c r="C38" s="60" t="inlineStr">
         <is>
           <t>Implement TSR-605 margins on the host: bound latAccelOffset and torque parameters in controlsd, apply the acceleration rate limit after pitch compensation and the CarController PID, gate pitch compensation on a valid calibrated pose, and keep host torque/accel limits below the panda limits</t>
         </is>
       </c>
-      <c r="D38" s="61" t="inlineStr">
+      <c r="D38" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E38" s="61" t="inlineStr">
+      <c r="E38" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F38" s="61" t="inlineStr">
+      <c r="F38" s="60" t="inlineStr">
         <is>
           <t>SWF-042.C2
 SWF-042.C3
@@ -33799,409 +33804,409 @@
 SWF-076.C1</t>
         </is>
       </c>
-      <c r="G38" s="61" t="inlineStr"/>
-      <c r="H38" s="61" t="inlineStr"/>
-      <c r="I38" s="61" t="inlineStr"/>
+      <c r="G38" s="60" t="inlineStr"/>
+      <c r="H38" s="60" t="inlineStr"/>
+      <c r="I38" s="60" t="inlineStr"/>
     </row>
     <row r="39" ht="46.5" customHeight="1">
-      <c r="A39" s="61" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-046</t>
         </is>
       </c>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="B39" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C39" s="61" t="inlineStr">
+      <c r="C39" s="60" t="inlineStr">
         <is>
           <t>SoC counterpart of TSR-304 (STPA OI-2, FSR-033) - ramp commanded torque toward zero while steeringPressed, or leave latActive during a lateral override, with the override threshold taken from WP-C-08</t>
         </is>
       </c>
-      <c r="D39" s="61" t="inlineStr">
+      <c r="D39" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E39" s="61" t="inlineStr">
+      <c r="E39" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F39" s="61" t="inlineStr">
+      <c r="F39" s="60" t="inlineStr">
         <is>
           <t>SWF-044.C1</t>
         </is>
       </c>
-      <c r="G39" s="61" t="inlineStr"/>
-      <c r="H39" s="61" t="inlineStr"/>
-      <c r="I39" s="61" t="inlineStr"/>
+      <c r="G39" s="60" t="inlineStr"/>
+      <c r="H39" s="60" t="inlineStr"/>
+      <c r="I39" s="60" t="inlineStr"/>
     </row>
     <row r="40" ht="33" customHeight="1">
-      <c r="A40" s="61" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-047</t>
         </is>
       </c>
-      <c r="B40" s="61" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C40" s="61" t="inlineStr">
+      <c r="C40" s="60" t="inlineStr">
         <is>
           <t>Implement TSR-613: remove the lateralManeuverPlan subscription and the maneuver/joystick processes from the reference build</t>
         </is>
       </c>
-      <c r="D40" s="61" t="inlineStr">
+      <c r="D40" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E40" s="61" t="inlineStr">
+      <c r="E40" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F40" s="61" t="inlineStr">
+      <c r="F40" s="60" t="inlineStr">
         <is>
           <t>SWF-040.C1
 SWF-049.C1</t>
         </is>
       </c>
-      <c r="G40" s="61" t="inlineStr"/>
-      <c r="H40" s="61" t="inlineStr"/>
-      <c r="I40" s="61" t="inlineStr"/>
+      <c r="G40" s="60" t="inlineStr"/>
+      <c r="H40" s="60" t="inlineStr"/>
+      <c r="I40" s="60" t="inlineStr"/>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="61" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-048</t>
         </is>
       </c>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C41" s="61" t="inlineStr">
+      <c r="C41" s="60" t="inlineStr">
         <is>
           <t>Bench or HIL fault injection (WP-V-05) - stop or stall selfdrived, modeld, plannerd and controlsd while engaged and measure time to zero torque/acceleration and to the alert; run test_onroad timing tests on a comma 3X for each release</t>
         </is>
       </c>
-      <c r="D41" s="61" t="inlineStr">
+      <c r="D41" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E41" s="61" t="inlineStr">
+      <c r="E41" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F41" s="61" t="inlineStr">
+      <c r="F41" s="60" t="inlineStr">
         <is>
           <t>SWF-043.C1
 SWF-047.C2
 SWF-068.C2</t>
         </is>
       </c>
-      <c r="G41" s="61" t="inlineStr"/>
-      <c r="H41" s="61" t="inlineStr"/>
-      <c r="I41" s="61" t="inlineStr"/>
+      <c r="G41" s="60" t="inlineStr"/>
+      <c r="H41" s="60" t="inlineStr"/>
+      <c r="I41" s="60" t="inlineStr"/>
     </row>
     <row r="42" ht="33" customHeight="1">
-      <c r="A42" s="61" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-049</t>
         </is>
       </c>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C42" s="61" t="inlineStr">
+      <c r="C42" s="60" t="inlineStr">
         <is>
           <t>Vehicle test of PCM cancel and cluster state on each host disengagement path (fault disable, cancel button, brake, selfdrived loss)</t>
         </is>
       </c>
-      <c r="D42" s="61" t="inlineStr">
+      <c r="D42" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E42" s="61" t="inlineStr">
+      <c r="E42" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F42" s="61" t="inlineStr">
+      <c r="F42" s="60" t="inlineStr">
         <is>
           <t>SWF-039.C1
 SWF-048.C1</t>
         </is>
       </c>
-      <c r="G42" s="61" t="inlineStr"/>
-      <c r="H42" s="61" t="inlineStr"/>
-      <c r="I42" s="61" t="inlineStr"/>
+      <c r="G42" s="60" t="inlineStr"/>
+      <c r="H42" s="60" t="inlineStr"/>
+      <c r="I42" s="60" t="inlineStr"/>
     </row>
     <row r="43" ht="33" customHeight="1">
-      <c r="A43" s="61" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-050</t>
         </is>
       </c>
-      <c r="B43" s="61" t="inlineStr">
+      <c r="B43" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C43" s="61" t="inlineStr">
+      <c r="C43" s="60" t="inlineStr">
         <is>
           <t>Implement TSR-624: announce deceleration that traffic does not require at least 1 s before its onset, and ramp it within a_min and j_down</t>
         </is>
       </c>
-      <c r="D43" s="61" t="inlineStr">
+      <c r="D43" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E43" s="61" t="inlineStr">
+      <c r="E43" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F43" s="61" t="inlineStr">
+      <c r="F43" s="60" t="inlineStr">
         <is>
           <t>SWF-050.C1
 SWF-066.C1</t>
         </is>
       </c>
-      <c r="G43" s="61" t="inlineStr"/>
-      <c r="H43" s="61" t="inlineStr"/>
-      <c r="I43" s="61" t="inlineStr"/>
+      <c r="G43" s="60" t="inlineStr"/>
+      <c r="H43" s="60" t="inlineStr"/>
+      <c r="I43" s="60" t="inlineStr"/>
     </row>
     <row r="44" ht="33" customHeight="1">
-      <c r="A44" s="61" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-051</t>
         </is>
       </c>
-      <c r="B44" s="61" t="inlineStr">
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C44" s="61" t="inlineStr">
+      <c r="C44" s="60" t="inlineStr">
         <is>
           <t>Implement TSR-625: gate FCW on fresh and valid modelV2 and longitudinalPlan, with a unit test for a stale and an invalid input</t>
         </is>
       </c>
-      <c r="D44" s="61" t="inlineStr">
+      <c r="D44" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E44" s="61" t="inlineStr">
+      <c r="E44" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F44" s="61" t="inlineStr">
+      <c r="F44" s="60" t="inlineStr">
         <is>
           <t>SWF-051.C1</t>
         </is>
       </c>
-      <c r="G44" s="61" t="inlineStr"/>
-      <c r="H44" s="61" t="inlineStr"/>
-      <c r="I44" s="61" t="inlineStr"/>
+      <c r="G44" s="60" t="inlineStr"/>
+      <c r="H44" s="60" t="inlineStr"/>
+      <c r="I44" s="60" t="inlineStr"/>
     </row>
     <row r="45" ht="33" customHeight="1">
-      <c r="A45" s="61" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-052</t>
         </is>
       </c>
-      <c r="B45" s="61" t="inlineStr">
+      <c r="B45" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C45" s="61" t="inlineStr">
+      <c r="C45" s="60" t="inlineStr">
         <is>
           <t>Send the inactive acceleration from the Toyota CarController whenever CC.longActive is false, with a unit test</t>
         </is>
       </c>
-      <c r="D45" s="61" t="inlineStr">
+      <c r="D45" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E45" s="61" t="inlineStr">
+      <c r="E45" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F45" s="61" t="inlineStr">
+      <c r="F45" s="60" t="inlineStr">
         <is>
           <t>SWF-052.C1</t>
         </is>
       </c>
-      <c r="G45" s="61" t="inlineStr"/>
-      <c r="H45" s="61" t="inlineStr"/>
-      <c r="I45" s="61" t="inlineStr"/>
+      <c r="G45" s="60" t="inlineStr"/>
+      <c r="H45" s="60" t="inlineStr"/>
+      <c r="I45" s="60" t="inlineStr"/>
     </row>
     <row r="46" ht="46.5" customHeight="1">
-      <c r="A46" s="61" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-053</t>
         </is>
       </c>
-      <c r="B46" s="61" t="inlineStr">
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C46" s="61" t="inlineStr">
+      <c r="C46" s="60" t="inlineStr">
         <is>
           <t>Vehicle test of the PCM response when the inactive value replaces an active deceleration (TSR-208, AOU-05R); if the PCM steps, specify an item-side ramp after revocation (FSR-04.03)</t>
         </is>
       </c>
-      <c r="D46" s="61" t="inlineStr">
+      <c r="D46" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E46" s="61" t="inlineStr">
+      <c r="E46" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F46" s="61" t="inlineStr">
+      <c r="F46" s="60" t="inlineStr">
         <is>
           <t>SWF-053.C1</t>
         </is>
       </c>
-      <c r="G46" s="61" t="inlineStr"/>
-      <c r="H46" s="61" t="inlineStr"/>
-      <c r="I46" s="61" t="inlineStr"/>
+      <c r="G46" s="60" t="inlineStr"/>
+      <c r="H46" s="60" t="inlineStr"/>
+      <c r="I46" s="60" t="inlineStr"/>
     </row>
     <row r="47" ht="87" customHeight="1">
-      <c r="A47" s="61" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-055</t>
         </is>
       </c>
-      <c r="B47" s="61" t="inlineStr">
+      <c r="B47" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C47" s="61" t="inlineStr">
+      <c r="C47" s="60" t="inlineStr">
         <is>
           <t>Make the host supervision tests run in CI: test_supervision.py and test_input_freshness.py define plain classes, which tools/test_runner.py (unittest loader) collects as 0 tests. Derive them from unittest.TestCase (or the repo's test base class), check that the unit_tests job reports them, and prove them by a mutation of supervision.py and input_freshness.py so D can drop below 8</t>
         </is>
       </c>
-      <c r="D47" s="61" t="inlineStr">
+      <c r="D47" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E47" s="61" t="inlineStr">
+      <c r="E47" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F47" s="61" t="inlineStr">
+      <c r="F47" s="60" t="inlineStr">
         <is>
           <t>SWF-034.C1</t>
         </is>
       </c>
-      <c r="G47" s="61" t="inlineStr"/>
-      <c r="H47" s="61" t="inlineStr"/>
-      <c r="I47" s="61" t="inlineStr">
+      <c r="G47" s="60" t="inlineStr"/>
+      <c r="H47" s="60" t="inlineStr"/>
+      <c r="I47" s="60" t="inlineStr">
         <is>
           <t>Run in CI: #179 (487d4ef, 2026-10-17) derives both from unittest.TestCase; the unit_tests job of tests run 38991473673 reports 1555 passed (1535 before: 19 newly collected and 1 new EPS test). Mutation proof not done, so D stays 8</t>
         </is>
       </c>
     </row>
     <row r="48" ht="73.5" customHeight="1">
-      <c r="A48" s="61" t="inlineStr">
+      <c r="A48" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-054</t>
         </is>
       </c>
-      <c r="B48" s="61" t="inlineStr">
+      <c r="B48" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C48" s="61" t="inlineStr">
+      <c r="C48" s="60" t="inlineStr">
         <is>
           <t>Pin an opendbc commit that contains jherrodthomas/opendbc#15 (ATC-20, SWSR-518 amended per DQ-079; ATC-26, SWSR-311 amended per DQ-080), with its impact records moved to Integrated, and re-rate SWF-054 and SWF-055 at the new baseline. The fork merged it as 9859cb0 (master 515b9a2 also carries opendbc#16); the LionDriver pin is still 9a13f60</t>
         </is>
       </c>
-      <c r="D48" s="61" t="inlineStr">
+      <c r="D48" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E48" s="62" t="inlineStr">
+      <c r="E48" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F48" s="61" t="inlineStr">
+      <c r="F48" s="60" t="inlineStr">
         <is>
           <t>SWF-054.C1
 SWF-055.C1</t>
         </is>
       </c>
-      <c r="G48" s="61" t="inlineStr">
+      <c r="G48" s="60" t="inlineStr">
         <is>
           <t>10/3/4</t>
         </is>
       </c>
-      <c r="H48" s="64" t="inlineStr">
+      <c r="H48" s="63" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I48" s="61" t="inlineStr">
+      <c r="I48" s="60" t="inlineStr">
         <is>
           <t>Pinned at 515b9a2 (change-2026-10-16-pin-515b9a2), now 62b89a3 in BL-006; impact records change-2026-10-13-tx-rate-reengagement and change-2026-10-14-mode-set-regrant Integrated 2026-10-16; SWF-054.C1 and SWF-055.C1 re-rated at BL-006 (rev 1.4)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="87" customHeight="1">
-      <c r="A49" s="61" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-056</t>
         </is>
       </c>
-      <c r="B49" s="61" t="inlineStr">
+      <c r="B49" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C49" s="61" t="inlineStr">
+      <c r="C49" s="60" t="inlineStr">
         <is>
           <t>carState input supervision for the reference car: fixed RX timeouts from the DBC rates instead of the learned 1 Hz default, reject frames shorter than the DBC length for every signal carState uses, and a plausibility cross-check for the messages without checksum or counter (BRAKE_MODULE against PCM_CRUISE, WHEEL_SPEEDS against the IMU); with unit tests in LionDriver CI</t>
         </is>
       </c>
-      <c r="D49" s="61" t="inlineStr">
+      <c r="D49" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E49" s="61" t="inlineStr">
+      <c r="E49" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F49" s="61" t="inlineStr">
+      <c r="F49" s="60" t="inlineStr">
         <is>
           <t>SWF-056.C1
 SWF-056.C2
@@ -34209,73 +34214,73 @@
 SWF-057.C2</t>
         </is>
       </c>
-      <c r="G49" s="61" t="inlineStr"/>
-      <c r="H49" s="61" t="inlineStr"/>
-      <c r="I49" s="61" t="inlineStr"/>
+      <c r="G49" s="60" t="inlineStr"/>
+      <c r="H49" s="60" t="inlineStr"/>
+      <c r="I49" s="60" t="inlineStr"/>
     </row>
     <row r="50" ht="73.5" customHeight="1">
-      <c r="A50" s="61" t="inlineStr">
+      <c r="A50" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-057</t>
         </is>
       </c>
-      <c r="B50" s="61" t="inlineStr">
+      <c r="B50" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C50" s="61" t="inlineStr">
+      <c r="C50" s="60" t="inlineStr">
         <is>
           <t>Pin the reference identification: accept only an exact FW match to TOYOTA_COROLLA_TSS2 with the expected CarParams for the assured configuration (report a fuzzy match through assured_config), ignore FINGERPRINT in release builds, and re-query FW after a VIN-cache hit when an ECU version changed</t>
         </is>
       </c>
-      <c r="D50" s="61" t="inlineStr">
+      <c r="D50" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E50" s="61" t="inlineStr">
+      <c r="E50" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F50" s="61" t="inlineStr">
+      <c r="F50" s="60" t="inlineStr">
         <is>
           <t>SWF-058.C1
 SWF-058.C2</t>
         </is>
       </c>
-      <c r="G50" s="61" t="inlineStr"/>
-      <c r="H50" s="61" t="inlineStr"/>
-      <c r="I50" s="61" t="inlineStr"/>
+      <c r="G50" s="60" t="inlineStr"/>
+      <c r="H50" s="60" t="inlineStr"/>
+      <c r="I50" s="60" t="inlineStr"/>
     </row>
     <row r="51" ht="87" customHeight="1">
-      <c r="A51" s="61" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-058</t>
         </is>
       </c>
-      <c r="B51" s="61" t="inlineStr">
+      <c r="B51" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C51" s="61" t="inlineStr">
+      <c r="C51" s="60" t="inlineStr">
         <is>
           <t>Driver monitoring robustness: time-based policy timers (monotonic clock), a finiteness and length check of driverStateV2 (non-finite or empty treated as uncertain, not attentive), a length check on brakeDisengageProbs, and unit tests for each in CI (NaN pose, 16 Hz model, empty arrays); a DM frequency check tight enough to catch a slowed model (WP-A-03 DFI-32)</t>
         </is>
       </c>
-      <c r="D51" s="61" t="inlineStr">
+      <c r="D51" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E51" s="61" t="inlineStr">
+      <c r="E51" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F51" s="61" t="inlineStr">
+      <c r="F51" s="60" t="inlineStr">
         <is>
           <t>SWF-061.C1
 SWF-061.C2
@@ -34285,109 +34290,109 @@
 SWF-064.C1</t>
         </is>
       </c>
-      <c r="G51" s="61" t="inlineStr"/>
-      <c r="H51" s="61" t="inlineStr"/>
-      <c r="I51" s="61" t="inlineStr"/>
+      <c r="G51" s="60" t="inlineStr"/>
+      <c r="H51" s="60" t="inlineStr"/>
+      <c r="I51" s="60" t="inlineStr"/>
     </row>
     <row r="52" ht="73.5" customHeight="1">
-      <c r="A52" s="61" t="inlineStr">
+      <c r="A52" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-059</t>
         </is>
       </c>
-      <c r="B52" s="61" t="inlineStr">
+      <c r="B52" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C52" s="61" t="inlineStr">
+      <c r="C52" s="60" t="inlineStr">
         <is>
           <t>Implement the SG-010 safe state decided in DQ-365 (A, which absorbed DQ-220; TSR-633): after the forced deceleration keep the vehicle stopped and held and lock out re-engagement and resumption until the driver responds; add a terminal-alert test that checks standstill, hold and lockout</t>
         </is>
       </c>
-      <c r="D52" s="61" t="inlineStr">
+      <c r="D52" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E52" s="61" t="inlineStr">
+      <c r="E52" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F52" s="61" t="inlineStr">
+      <c r="F52" s="60" t="inlineStr">
         <is>
           <t>SWF-062.C1
 SWF-086.C2</t>
         </is>
       </c>
-      <c r="G52" s="61" t="inlineStr"/>
-      <c r="H52" s="61" t="inlineStr"/>
-      <c r="I52" s="61" t="inlineStr"/>
+      <c r="G52" s="60" t="inlineStr"/>
+      <c r="H52" s="60" t="inlineStr"/>
+      <c r="I52" s="60" t="inlineStr"/>
     </row>
     <row r="53" ht="46.5" customHeight="1">
-      <c r="A53" s="61" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-060</t>
         </is>
       </c>
-      <c r="B53" s="61" t="inlineStr">
+      <c r="B53" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C53" s="61" t="inlineStr">
+      <c r="C53" s="60" t="inlineStr">
         <is>
           <t>Run model_replay for dmonitoringmodeld and modeld in LionDriver CI, and add a non-finite / stale output injection test for dmonitoringd and modeld consumers</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D53" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="E53" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F53" s="61" t="inlineStr">
+      <c r="F53" s="60" t="inlineStr">
         <is>
           <t>SWF-063.C1
 SWF-072.C1</t>
         </is>
       </c>
-      <c r="G53" s="61" t="inlineStr"/>
-      <c r="H53" s="61" t="inlineStr"/>
-      <c r="I53" s="61" t="inlineStr"/>
+      <c r="G53" s="60" t="inlineStr"/>
+      <c r="H53" s="60" t="inlineStr"/>
+      <c r="I53" s="60" t="inlineStr"/>
     </row>
     <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="61" t="inlineStr">
+      <c r="A54" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-061</t>
         </is>
       </c>
-      <c r="B54" s="61" t="inlineStr">
+      <c r="B54" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C54" s="61" t="inlineStr">
+      <c r="C54" s="60" t="inlineStr">
         <is>
           <t>Longitudinal input validity: plannerd treats an invalid radarState as no lead plus a fault, and controlsd sets longActive false (with an event) when longitudinalPlan.valid is false; keep the coast limit when orientationNED is missing</t>
         </is>
       </c>
-      <c r="D54" s="61" t="inlineStr">
+      <c r="D54" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E54" s="61" t="inlineStr">
+      <c r="E54" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F54" s="61" t="inlineStr">
+      <c r="F54" s="60" t="inlineStr">
         <is>
           <t>SWF-065.C1
 SWF-065.C2
@@ -34395,121 +34400,121 @@
 SWF-070.C2</t>
         </is>
       </c>
-      <c r="G54" s="61" t="inlineStr"/>
-      <c r="H54" s="61" t="inlineStr"/>
-      <c r="I54" s="61" t="inlineStr"/>
+      <c r="G54" s="60" t="inlineStr"/>
+      <c r="H54" s="60" t="inlineStr"/>
+      <c r="I54" s="60" t="inlineStr"/>
     </row>
     <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="61" t="inlineStr">
+      <c r="A55" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-062</t>
         </is>
       </c>
-      <c r="B55" s="61" t="inlineStr">
+      <c r="B55" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C55" s="61" t="inlineStr">
+      <c r="C55" s="60" t="inlineStr">
         <is>
           <t>plannerd robustness: on an MPC failure keep the last valid solution for a bounded time and raise an event if it persists; rate-limit the final aTarget (TSR-624); handle an unknown personality as relaxed; add MPC-failure injection and plannerd fuzzing in CI</t>
         </is>
       </c>
-      <c r="D55" s="61" t="inlineStr">
+      <c r="D55" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E55" s="61" t="inlineStr">
+      <c r="E55" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F55" s="61" t="inlineStr">
+      <c r="F55" s="60" t="inlineStr">
         <is>
           <t>SWF-065.C2
 SWF-066.C1
 SWF-068.C1</t>
         </is>
       </c>
-      <c r="G55" s="61" t="inlineStr"/>
-      <c r="H55" s="61" t="inlineStr"/>
-      <c r="I55" s="61" t="inlineStr"/>
+      <c r="G55" s="60" t="inlineStr"/>
+      <c r="H55" s="60" t="inlineStr"/>
+      <c r="I55" s="60" t="inlineStr"/>
     </row>
     <row r="56" ht="141" customHeight="1">
-      <c r="A56" s="61" t="inlineStr">
+      <c r="A56" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-063</t>
         </is>
       </c>
-      <c r="B56" s="61" t="inlineStr">
+      <c r="B56" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C56" s="61" t="inlineStr">
+      <c r="C56" s="60" t="inlineStr">
         <is>
           <t>Apply the lead's decision on engagement outside the assured configuration (DQ-221): refuse engagement or keep logging, with a test</t>
         </is>
       </c>
-      <c r="D56" s="61" t="inlineStr">
+      <c r="D56" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E56" s="62" t="inlineStr">
+      <c r="E56" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F56" s="61" t="inlineStr">
+      <c r="F56" s="60" t="inlineStr">
         <is>
           <t>SWF-067.C1</t>
         </is>
       </c>
-      <c r="G56" s="61" t="inlineStr">
+      <c r="G56" s="60" t="inlineStr">
         <is>
           <t>10/5/8</t>
         </is>
       </c>
-      <c r="H56" s="63" t="inlineStr">
+      <c r="H56" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I56" s="61" t="inlineStr">
+      <c r="I56" s="60" t="inlineStr">
         <is>
           <t>DQ-221 A implemented in #287 (69cddaa): assured_config.py (settings_in_scope), selfdrived.py (add_reference_entry_events, distance_button_pressed), events.py (settingNotAssured); tests in test_assured_config.py, collected by the CI unit_tests job and green there in tests run 39296172878 (6126485, 2026-10-19: 1578 passed, 0 failed); change record assurance/07-supporting/impact/change-2026-10-19-reference-entry-checks.md. Unit-tested, not proven by mutation and not verified in the vehicle (change record OI-5). Achieved: O5 D8 (rev 1.6)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="87" customHeight="1">
-      <c r="A57" s="61" t="inlineStr">
+      <c r="A57" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-064</t>
         </is>
       </c>
-      <c r="B57" s="61" t="inlineStr">
+      <c r="B57" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C57" s="61" t="inlineStr">
+      <c r="C57" s="60" t="inlineStr">
         <is>
           <t>radard and FCW review against SG-005/SG-006 with the SOTIF analysis: catch the Kalman dt assertion (reset the filter), allow FCW from a confirmed radar-only lead, and decide the radar-only stationary target treatment (FI-2026-001 CA-002); tests for each</t>
         </is>
       </c>
-      <c r="D57" s="61" t="inlineStr">
+      <c r="D57" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E57" s="61" t="inlineStr">
+      <c r="E57" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F57" s="61" t="inlineStr">
+      <c r="F57" s="60" t="inlineStr">
         <is>
           <t>SWF-069.C1
 SWF-070.C1
@@ -34519,37 +34524,37 @@
 SWF-071.C2</t>
         </is>
       </c>
-      <c r="G57" s="61" t="inlineStr"/>
-      <c r="H57" s="61" t="inlineStr"/>
-      <c r="I57" s="61" t="inlineStr"/>
+      <c r="G57" s="60" t="inlineStr"/>
+      <c r="H57" s="60" t="inlineStr"/>
+      <c r="I57" s="60" t="inlineStr"/>
     </row>
     <row r="58" ht="73.5" customHeight="1">
-      <c r="A58" s="61" t="inlineStr">
+      <c r="A58" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-065</t>
         </is>
       </c>
-      <c r="B58" s="61" t="inlineStr">
+      <c r="B58" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C58" s="61" t="inlineStr">
+      <c r="C58" s="60" t="inlineStr">
         <is>
           <t>modeld output validity: check finiteness of every output used downstream (small model too, TSR-616), set modelV2.valid false on a non-finite output, a repeated or regressing frame_id, or an invalid calibration status; verify the model file hash at load (GAP-22). WP-A-03 DFI-30</t>
         </is>
       </c>
-      <c r="D58" s="61" t="inlineStr">
+      <c r="D58" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E58" s="61" t="inlineStr">
+      <c r="E58" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F58" s="61" t="inlineStr">
+      <c r="F58" s="60" t="inlineStr">
         <is>
           <t>SWF-072.C1
 SWF-072.C2
@@ -34558,530 +34563,542 @@
 SWF-074.C1</t>
         </is>
       </c>
-      <c r="G58" s="61" t="inlineStr"/>
-      <c r="H58" s="61" t="inlineStr"/>
-      <c r="I58" s="61" t="inlineStr"/>
+      <c r="G58" s="60" t="inlineStr"/>
+      <c r="H58" s="60" t="inlineStr"/>
+      <c r="I58" s="60" t="inlineStr"/>
     </row>
     <row r="59" ht="46.5" customHeight="1">
-      <c r="A59" s="61" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-066</t>
         </is>
       </c>
-      <c r="B59" s="61" t="inlineStr">
+      <c r="B59" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C59" s="61" t="inlineStr">
+      <c r="C59" s="60" t="inlineStr">
         <is>
           <t>Unit tests for modeld output handling (parse, finiteness, frame-drop accounting) and include modeld in model_replay in LionDriver CI (with SWF-ACT-060)</t>
         </is>
       </c>
-      <c r="D59" s="61" t="inlineStr">
+      <c r="D59" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E59" s="61" t="inlineStr">
+      <c r="E59" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F59" s="61" t="inlineStr">
+      <c r="F59" s="60" t="inlineStr">
         <is>
           <t>SWF-073.C1</t>
         </is>
       </c>
-      <c r="G59" s="61" t="inlineStr"/>
-      <c r="H59" s="61" t="inlineStr"/>
-      <c r="I59" s="61" t="inlineStr"/>
+      <c r="G59" s="60" t="inlineStr"/>
+      <c r="H59" s="60" t="inlineStr"/>
+      <c r="I59" s="60" t="inlineStr"/>
     </row>
     <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="61" t="inlineStr">
+      <c r="A60" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-067</t>
         </is>
       </c>
-      <c r="B60" s="61" t="inlineStr">
+      <c r="B60" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C60" s="61" t="inlineStr">
+      <c r="C60" s="60" t="inlineStr">
         <is>
           <t>Sensor and pose supervision: make selfdrived react to deviceMotion.sensorsOK and to IMU data older than a few periods (not 10 s); add range and stuck-value checks in sensord; review the calibration recalibration thresholds against the lateral error budget</t>
         </is>
       </c>
-      <c r="D60" s="61" t="inlineStr">
+      <c r="D60" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E60" s="61" t="inlineStr">
+      <c r="E60" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F60" s="61" t="inlineStr">
+      <c r="F60" s="60" t="inlineStr">
         <is>
           <t>SWF-075.C1
 SWF-077.C1
 SWF-079.C1</t>
         </is>
       </c>
-      <c r="G60" s="61" t="inlineStr"/>
-      <c r="H60" s="61" t="inlineStr"/>
-      <c r="I60" s="61" t="inlineStr"/>
+      <c r="G60" s="60" t="inlineStr"/>
+      <c r="H60" s="60" t="inlineStr"/>
+      <c r="I60" s="60" t="inlineStr"/>
     </row>
     <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="61" t="inlineStr">
+      <c r="A61" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-068</t>
         </is>
       </c>
-      <c r="B61" s="61" t="inlineStr">
+      <c r="B61" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C61" s="61" t="inlineStr">
+      <c r="C61" s="60" t="inlineStr">
         <is>
           <t>Camera stream supervision: never ignore a road stream for the reference device (refuse engagement if it is absent at start), mark frames invalid on sync failure, and raise an event when a sensor is disabled; run the camerad hardware tests per release</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D61" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="E61" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F61" s="60" t="inlineStr">
         <is>
           <t>SWF-078.C1
 SWF-078.C2
 SWF-078.C3</t>
         </is>
       </c>
-      <c r="G61" s="61" t="inlineStr"/>
-      <c r="H61" s="61" t="inlineStr"/>
-      <c r="I61" s="61" t="inlineStr"/>
+      <c r="G61" s="60" t="inlineStr"/>
+      <c r="H61" s="60" t="inlineStr"/>
+      <c r="I61" s="60" t="inlineStr"/>
     </row>
     <row r="62" ht="46.5" customHeight="1">
-      <c r="A62" s="61" t="inlineStr">
+      <c r="A62" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-069</t>
         </is>
       </c>
-      <c r="B62" s="61" t="inlineStr">
+      <c r="B62" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C62" s="61" t="inlineStr">
+      <c r="C62" s="60" t="inlineStr">
         <is>
           <t>Run the msgq tests in LionDriver CI and assess whether a payload checksum or a lost-message counter is needed for the safety-relevant services (selfdriveState, carControl, sendcan, pandaStates)</t>
         </is>
       </c>
-      <c r="D62" s="61" t="inlineStr">
+      <c r="D62" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="E62" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F62" s="61" t="inlineStr">
+      <c r="F62" s="60" t="inlineStr">
         <is>
           <t>SWF-080.C1
 SWF-080.C2</t>
         </is>
       </c>
-      <c r="G62" s="61" t="inlineStr"/>
-      <c r="H62" s="61" t="inlineStr"/>
-      <c r="I62" s="61" t="inlineStr"/>
+      <c r="G62" s="60" t="inlineStr"/>
+      <c r="H62" s="60" t="inlineStr"/>
+      <c r="I62" s="60" t="inlineStr"/>
     </row>
     <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="61" t="inlineStr">
+      <c r="A63" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-070</t>
         </is>
       </c>
-      <c r="B63" s="61" t="inlineStr">
+      <c r="B63" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C63" s="61" t="inlineStr">
+      <c r="C63" s="60" t="inlineStr">
         <is>
           <t>Manager supervision: report every process the configuration needs (including blocked or never started ones) in managerState, ignore BLOCK in release builds, and decide whether a crashed safety process may be restarted offroad only. WP-A-03 DFI-25</t>
         </is>
       </c>
-      <c r="D63" s="61" t="inlineStr">
+      <c r="D63" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E63" s="61" t="inlineStr">
+      <c r="E63" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F63" s="61" t="inlineStr">
+      <c r="F63" s="60" t="inlineStr">
         <is>
           <t>SWF-082.C1
 SWF-083.C1</t>
         </is>
       </c>
-      <c r="G63" s="61" t="inlineStr"/>
-      <c r="H63" s="61" t="inlineStr"/>
-      <c r="I63" s="61" t="inlineStr"/>
+      <c r="G63" s="60" t="inlineStr"/>
+      <c r="H63" s="60" t="inlineStr"/>
+      <c r="I63" s="60" t="inlineStr"/>
     </row>
     <row r="64" ht="46.5" customHeight="1">
-      <c r="A64" s="61" t="inlineStr">
+      <c r="A64" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-071</t>
         </is>
       </c>
-      <c r="B64" s="61" t="inlineStr">
+      <c r="B64" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C64" s="61" t="inlineStr">
+      <c r="C64" s="60" t="inlineStr">
         <is>
           <t>Update integrity: pin the update to signed release tags of the LionDriver repository and verify the signature before finalizing; define rollback (with the PFMEA OTA steps)</t>
         </is>
       </c>
-      <c r="D64" s="61" t="inlineStr">
+      <c r="D64" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E64" s="61" t="inlineStr">
+      <c r="E64" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F64" s="61" t="inlineStr">
+      <c r="F64" s="60" t="inlineStr">
         <is>
           <t>SWF-084.C1</t>
         </is>
       </c>
-      <c r="G64" s="61" t="inlineStr"/>
-      <c r="H64" s="61" t="inlineStr"/>
-      <c r="I64" s="61" t="inlineStr"/>
+      <c r="G64" s="60" t="inlineStr"/>
+      <c r="H64" s="60" t="inlineStr"/>
+      <c r="I64" s="60" t="inlineStr"/>
     </row>
     <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="61" t="inlineStr">
+      <c r="A65" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-072</t>
         </is>
       </c>
-      <c r="B65" s="61" t="inlineStr">
+      <c r="B65" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C65" s="61" t="inlineStr">
+      <c r="C65" s="60" t="inlineStr">
         <is>
           <t>Demo-mode interlock (TSR-610): selfdrived refuses engagement while IsDriverViewEnabled is set and raises a fault if it is set while engaged; the UI clears the parameter on the onroad transition; dmonitoringd ignores demo mode while started. Add a test with the item started</t>
         </is>
       </c>
-      <c r="D65" s="61" t="inlineStr">
+      <c r="D65" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E65" s="61" t="inlineStr">
+      <c r="E65" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F65" s="61" t="inlineStr">
+      <c r="F65" s="60" t="inlineStr">
         <is>
           <t>SWF-085.C1
 SWF-085.C2</t>
         </is>
       </c>
-      <c r="G65" s="61" t="inlineStr"/>
-      <c r="H65" s="61" t="inlineStr"/>
-      <c r="I65" s="61" t="inlineStr"/>
+      <c r="G65" s="60" t="inlineStr"/>
+      <c r="H65" s="60" t="inlineStr"/>
+      <c r="I65" s="60" t="inlineStr"/>
     </row>
     <row r="66" ht="87" customHeight="1">
-      <c r="A66" s="61" t="inlineStr">
+      <c r="A66" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-073</t>
         </is>
       </c>
-      <c r="B66" s="61" t="inlineStr">
+      <c r="B66" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C66" s="61" t="inlineStr">
+      <c r="C66" s="60" t="inlineStr">
         <is>
           <t>End-to-end test of the terminal reaction: drive policy, controlsd and plannerd from a recorded or synthetic unresponsive-driver input and check that forceDecel is set 5 s after the terminal alert and the vehicle reaches standstill within the time set for TSR-633; add a freshness check on driverMonitoringState in controlsd, and do not route the terminal reaction through plannerd alone (WP-A-03 DFI-33)</t>
         </is>
       </c>
-      <c r="D66" s="61" t="inlineStr">
+      <c r="D66" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E66" s="61" t="inlineStr">
+      <c r="E66" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F66" s="61" t="inlineStr">
+      <c r="F66" s="60" t="inlineStr">
         <is>
           <t>SWF-086.C1
 SWF-086.C2</t>
         </is>
       </c>
-      <c r="G66" s="61" t="inlineStr"/>
-      <c r="H66" s="61" t="inlineStr"/>
-      <c r="I66" s="61" t="inlineStr"/>
+      <c r="G66" s="60" t="inlineStr"/>
+      <c r="H66" s="60" t="inlineStr"/>
+      <c r="I66" s="60" t="inlineStr"/>
     </row>
     <row r="67" ht="73.5" customHeight="1">
-      <c r="A67" s="61" t="inlineStr">
+      <c r="A67" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-075</t>
         </is>
       </c>
-      <c r="B67" s="61" t="inlineStr">
+      <c r="B67" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C67" s="61" t="inlineStr">
+      <c r="C67" s="60" t="inlineStr">
         <is>
           <t>msgq protection for the control and supervision topics (WP-A-03 DFI-29): sequence or E2E protection so a skipped or altered message is detected, a subscriber-count guard so a 16th reader cannot evict the others, and host supervision of control credited only where it is independent of msgq</t>
         </is>
       </c>
-      <c r="D67" s="61" t="inlineStr">
+      <c r="D67" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E67" s="61" t="inlineStr">
+      <c r="E67" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F67" s="61" t="inlineStr">
+      <c r="F67" s="60" t="inlineStr">
         <is>
           <t>SWF-080.C1
 SWF-080.C2</t>
         </is>
       </c>
-      <c r="G67" s="61" t="inlineStr"/>
-      <c r="H67" s="61" t="inlineStr"/>
-      <c r="I67" s="61" t="inlineStr"/>
+      <c r="G67" s="60" t="inlineStr"/>
+      <c r="H67" s="60" t="inlineStr"/>
+      <c r="I67" s="60" t="inlineStr"/>
     </row>
     <row r="68" ht="46.5" customHeight="1">
-      <c r="A68" s="61" t="inlineStr">
+      <c r="A68" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-076</t>
         </is>
       </c>
-      <c r="B68" s="61" t="inlineStr">
+      <c r="B68" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C68" s="61" t="inlineStr">
+      <c r="C68" s="60" t="inlineStr">
         <is>
           <t>One publisher per control topic, enforced at subscribe time (WP-A-03 DFI-31): the comma four cabin-camera dialog must not publish selfdriveState, and the dialog is closed before the item goes onroad</t>
         </is>
       </c>
-      <c r="D68" s="61" t="inlineStr">
+      <c r="D68" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E68" s="61" t="inlineStr">
+      <c r="E68" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F68" s="61" t="inlineStr">
+      <c r="F68" s="60" t="inlineStr">
         <is>
           <t>SWF-085.C1</t>
         </is>
       </c>
-      <c r="G68" s="61" t="inlineStr"/>
-      <c r="H68" s="61" t="inlineStr"/>
-      <c r="I68" s="61" t="inlineStr"/>
+      <c r="G68" s="60" t="inlineStr"/>
+      <c r="H68" s="60" t="inlineStr"/>
+      <c r="I68" s="60" t="inlineStr"/>
     </row>
     <row r="69" ht="87" customHeight="1">
-      <c r="A69" s="61" t="inlineStr">
+      <c r="A69" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-074</t>
         </is>
       </c>
-      <c r="B69" s="61" t="inlineStr">
+      <c r="B69" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C69" s="61" t="inlineStr">
+      <c r="C69" s="60" t="inlineStr">
         <is>
           <t>Envelope override check (TSR-304, DQ-053): in toyota.h reject 0x2E4 frames that increase torque opposing STEER_TORQUE_DRIVER beyond the driver allowance, and back off toward zero at no less than the down rate while the override lasts; report the state to the SoC (TSR-628). Add opendbc safety tests and mutation for both branches; host counterpart SWF-ACT-046</t>
         </is>
       </c>
-      <c r="D69" s="61" t="inlineStr">
+      <c r="D69" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E69" s="61" t="inlineStr">
+      <c r="E69" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F69" s="61" t="inlineStr">
+      <c r="F69" s="60" t="inlineStr">
         <is>
           <t>SWF-087.C1</t>
         </is>
       </c>
-      <c r="G69" s="61" t="inlineStr"/>
-      <c r="H69" s="61" t="inlineStr"/>
-      <c r="I69" s="61" t="inlineStr"/>
+      <c r="G69" s="60" t="inlineStr"/>
+      <c r="H69" s="60" t="inlineStr"/>
+      <c r="I69" s="60" t="inlineStr"/>
     </row>
     <row r="70" ht="114" customHeight="1">
-      <c r="A70" s="61" t="inlineStr">
+      <c r="A70" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-077</t>
         </is>
       </c>
-      <c r="B70" s="61" t="inlineStr">
+      <c r="B70" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C70" s="61" t="inlineStr">
+      <c r="C70" s="60" t="inlineStr">
         <is>
           <t>Escalate the EPS-fault warning per TSR-607 (DQ-342 A, DQ-366 A): allow steerTempUnavailableSilent only for the first 1.5 s of the fault (steer_fault_frames, STEER_FAULT_SILENT_FRAMES), then the take-over request; give at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering; unit tests</t>
         </is>
       </c>
-      <c r="D70" s="61" t="inlineStr">
+      <c r="D70" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E70" s="62" t="inlineStr">
+      <c r="E70" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F70" s="61" t="inlineStr">
+      <c r="F70" s="60" t="inlineStr">
         <is>
           <t>SWF-088.C1
 SWF-088.C2</t>
         </is>
       </c>
-      <c r="G70" s="61" t="inlineStr">
+      <c r="G70" s="60" t="inlineStr">
         <is>
           <t>10/5/8</t>
         </is>
       </c>
-      <c r="H70" s="63" t="inlineStr">
+      <c r="H70" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I70" s="61" t="inlineStr">
+      <c r="I70" s="60" t="inlineStr">
         <is>
           <t>#174 (7158a9a) and #179 (487d4ef): openpilot/selfdrive/car/car_events.py:17, 169-187; openpilot/selfdrive/car/tests/test_steer_fault_warning.py (7 tests, unittest, collected by the unit_tests job); impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Implemented and unit-tested after BL-005, not verified on the vehicle and not proven by mutation. Achieved at BL-006: O5 D8 (rev 1.4)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="73.5" customHeight="1">
-      <c r="A71" s="61" t="inlineStr">
+      <c r="A71" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-078</t>
         </is>
       </c>
-      <c r="B71" s="61" t="inlineStr">
+      <c r="B71" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C71" s="61" t="inlineStr">
+      <c r="C71" s="60" t="inlineStr">
         <is>
           <t>Prove the EPS-fault warning tests: mutate the escalation in car_events.py (the STEER_FAULT_SILENT_FRAMES comparisons, the silent_steer_warning latch and the steering-held branch) and show test_steer_fault_warning.py fails on each mutant, in CI, so D can drop to 4 (System FMEA SFM-ACT-023 points to the same run)</t>
         </is>
       </c>
-      <c r="D71" s="61" t="inlineStr">
+      <c r="D71" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E71" s="61" t="inlineStr">
+      <c r="E71" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F71" s="61" t="inlineStr">
+      <c r="F71" s="60" t="inlineStr">
         <is>
           <t>SWF-088.C1
 SWF-088.C2</t>
         </is>
       </c>
-      <c r="G71" s="61" t="inlineStr">
+      <c r="G71" s="60" t="inlineStr">
         <is>
           <t>10/5/4</t>
         </is>
       </c>
-      <c r="H71" s="63" t="inlineStr">
+      <c r="H71" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I71" s="61" t="inlineStr"/>
+      <c r="I71" s="60" t="inlineStr"/>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="61" t="inlineStr">
+    <row r="72" ht="127.5" customHeight="1">
+      <c r="A72" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-079</t>
         </is>
       </c>
-      <c r="B72" s="61" t="inlineStr">
+      <c r="B72" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C72" s="61" t="inlineStr">
+      <c r="C72" s="60" t="inlineStr">
         <is>
           <t>Apply the lead's decision on setting changes while engaged (DQ-403): hold a menu change of an assured setting until the next engagement, disengage with a warning, or keep today's entry-only check; with a test</t>
         </is>
       </c>
-      <c r="D72" s="61" t="inlineStr">
+      <c r="D72" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
       <c r="E72" s="61" t="inlineStr">
         <is>
-          <t>decision pending</t>
-        </is>
-      </c>
-      <c r="F72" s="61" t="inlineStr">
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F72" s="60" t="inlineStr">
         <is>
           <t>SWF-067.C2</t>
         </is>
       </c>
-      <c r="G72" s="61" t="inlineStr"/>
-      <c r="H72" s="61" t="inlineStr"/>
-      <c r="I72" s="61" t="inlineStr"/>
+      <c r="G72" s="60" t="inlineStr">
+        <is>
+          <t>10/5/8</t>
+        </is>
+      </c>
+      <c r="H72" s="62" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I72" s="60" t="inlineStr">
+        <is>
+          <t>DQ-403 A implemented in #342 (18b15cd, merged 5d4ba6e): selfdrived.py apply_settings and the stored settings; 5 tests in test_assured_config.py TestSettingsHeldWhileEngaged, green in the CI unit_tests job (tests run 39348218534: 1583 passed, 0 failed); change record assurance/07-supporting/impact/change-2026-10-20-settings-held-while-engaged.md. Unit-tested, not proven by mutation and not verified in the vehicle (change record OI-4). Achieved: O5 D8 (rev 1.7)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I72"/>
@@ -35106,181 +35123,181 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="60" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="60" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="60" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>Panda safety model (opendbc safety + panda firmware integration)</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr"/>
-      <c r="E2" s="61" t="inlineStr"/>
+      <c r="D2" s="60" t="inlineStr"/>
+      <c r="E2" s="60" t="inlineStr"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    RX validation and RX timing checks</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D3" s="61" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="61" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-005: Validate safety-relevant RX messages (checksum, counter, quality flag, timing)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    TX whitelist and dispatch</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-001: Transmit only whitelisted messages, each passed through the mode-specific check</t>
         </is>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Forwarding hook</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="61" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-007: Block stock-camera messages the item replaces; forward all others, including stock pre-collision messages</t>
         </is>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-005</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Controls-allowed logic</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-004: Allow controls on rising edge of PCM cruise; withdraw on cruise off, brake press, invalid or lagging safety messages</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-006</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Steering torque checks</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-002: Block steering requests outside torque magnitude, rate and measured-torque-error limits, and any torque while controls are not allowed
 SWF-FN-014: Back steering torque off toward zero while the driver overrides, and reject frames that increase torque opposing the driver beyond a driver allowance (TSR-304; not implemented on the LKA path)</t>
@@ -35288,443 +35305,443 @@
       </c>
     </row>
     <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-007</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Longitudinal checks</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-003: Block acceleration outside the range, and any non-inactive acceleration while controls are not allowed or the accelerator is pressed</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-008</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Toyota safety mode</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-006: Decode Toyota vehicle state: EPS torque, cruise state, brake, accelerator, wheel speeds</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-009</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Relay malfunction detection</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-008: Detect a relay malfunction and block all item transmission</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-010</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Safety mode registry and initialization</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D11" s="61" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E11" s="61" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-009: Install only the safety model and parameter intended for the vehicle</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-011</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda main loop: safety mode and heartbeat</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D12" s="61" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E12" s="61" t="inlineStr">
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-010: Withdraw controls when the host heartbeat is lost or reports not engaged</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-012</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda host command handler</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D13" s="61" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E13" s="61" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-011: Accept host configuration commands only when they cannot widen what is transmitted</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-013</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda CAN send path</t>
         </is>
       </c>
-      <c r="C14" s="61" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D14" s="61" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E14" s="61" t="inlineStr">
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-012: Route every host transmission through the safety check</t>
         </is>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-014</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Panda hardware watchdog and 100 Hz safety task</t>
         </is>
       </c>
-      <c r="C15" s="61" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D15" s="61" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-001</t>
         </is>
       </c>
-      <c r="E15" s="61" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-013: Reset the MCU, which releases the relay, within 0.1 s when the safety task or main loop stops; never reset while both run normally</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>pandad (panda daemon and SoC-panda link)</t>
         </is>
       </c>
-      <c r="C16" s="61" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D16" s="61" t="inlineStr"/>
-      <c r="E16" s="61" t="inlineStr"/>
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="46.5" customHeight="1">
-      <c r="A17" s="61" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-021</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Main loop and heartbeat</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D17" s="61" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E17" s="61" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-020: Send the heartbeat at 10 Hz. It reports engaged only while the SoC is engaged and actively commanding, so that the panda can withdraw authority when the host stops (supports FSR-005 and FSR-007, which are allocated to EL-07)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="33" customHeight="1">
-      <c r="A18" s="61" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-022</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Safety mode setter</t>
         </is>
       </c>
-      <c r="C18" s="61" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D18" s="61" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E18" s="61" t="inlineStr">
+      <c r="E18" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-021: Put the panda in the safety model, parameter and alternative experience for the identified vehicle, only when onroad, and in NO_OUTPUT when offroad, with ignition off or on exit</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-023</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    sendcan forwarding thread</t>
         </is>
       </c>
-      <c r="C19" s="61" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E19" s="61" t="inlineStr">
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-022: Forward each sendcan batch to the panda once, in order, only while it is fresh, and make any failure to forward visible to the SoC</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-024</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    CAN RX and panda state publishing</t>
         </is>
       </c>
-      <c r="C20" s="61" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="D20" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="E20" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-023: Publish received CAN and the panda state (mode, parameter, controlsAllowed, RX-check validity, faults) correctly and on time, so the SoC can detect a mismatch or fault and disable</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33" customHeight="1">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-025</t>
         </is>
       </c>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    SPI transport</t>
         </is>
       </c>
-      <c r="C21" s="61" t="inlineStr">
+      <c r="C21" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D21" s="61" t="inlineStr">
+      <c r="D21" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E21" s="61" t="inlineStr">
+      <c r="E21" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-024: Transfer commands and data between SoC and panda without undetected corruption. Detect link failure in bounded time and report it</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33" customHeight="1">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-026</t>
         </is>
       </c>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Launcher and firmware check</t>
         </is>
       </c>
-      <c r="C22" s="61" t="inlineStr">
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D22" s="61" t="inlineStr">
+      <c r="D22" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-020</t>
         </is>
       </c>
-      <c r="E22" s="61" t="inlineStr">
+      <c r="E22" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-025: Run pandad only against the intended panda firmware. Recover a panda in DFU or bootstub without disturbing an active drive</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>selfdrived (engagement supervision)</t>
         </is>
       </c>
-      <c r="C23" s="61" t="inlineStr">
+      <c r="C23" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D23" s="61" t="inlineStr"/>
-      <c r="E23" s="61" t="inlineStr"/>
+      <c r="D23" s="60" t="inlineStr"/>
+      <c r="E23" s="60" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="61" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-031</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Engagement state machine</t>
         </is>
       </c>
-      <c r="C24" s="61" t="inlineStr">
+      <c r="C24" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D24" s="61" t="inlineStr">
+      <c r="D24" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E24" s="61" t="inlineStr">
+      <c r="E24" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-030: Engage only on an ENABLE event with no NO_ENTRY event active
 SWF-FN-031: Go to disabled in the same cycle on USER_DISABLE or IMMEDIATE_DISABLE, and within SOFT_DISABLE_TIME on a persisting SOFT_DISABLE
@@ -35733,27 +35750,27 @@
       </c>
     </row>
     <row r="25" ht="73.5" customHeight="1">
-      <c r="A25" s="61" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-032</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Input sampling and event generation</t>
         </is>
       </c>
-      <c r="C25" s="61" t="inlineStr">
+      <c r="C25" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D25" s="61" t="inlineStr">
+      <c r="D25" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E25" s="61" t="inlineStr">
+      <c r="E25" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-032: Raise fault and driver-action events from carState, pandaStates and process/message supervision, including controlsMismatch when the panda safety model, parameter or controls-allowed disagrees
 SWF-FN-038: Detect PCM cruise active while not engaged and warn the driver
@@ -35762,154 +35779,154 @@
       </c>
     </row>
     <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="61" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-033</t>
         </is>
       </c>
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Event catalogue and reaction mapping</t>
         </is>
       </c>
-      <c r="C26" s="61" t="inlineStr">
+      <c r="C26" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D26" s="61" t="inlineStr">
+      <c r="D26" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E26" s="61" t="inlineStr">
+      <c r="E26" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-033: Give each event the reaction type (no entry, soft or immediate disable, user disable) and alert its fault requires</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-034</t>
         </is>
       </c>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Alert manager</t>
         </is>
       </c>
-      <c r="C27" s="61" t="inlineStr">
+      <c r="C27" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D27" s="61" t="inlineStr">
+      <c r="D27" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E27" s="61" t="inlineStr">
+      <c r="E27" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-034: Present the most urgent alert; every takeover request visual and audible</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="61" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-035</t>
         </is>
       </c>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Excessive actuation check</t>
         </is>
       </c>
-      <c r="C28" s="61" t="inlineStr">
+      <c r="C28" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D28" s="61" t="inlineStr">
+      <c r="D28" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E28" s="61" t="inlineStr">
+      <c r="E28" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-035: Detect excessive longitudinal or lateral vehicle response while engaged and soft-disable</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33" customHeight="1">
-      <c r="A29" s="61" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-036</t>
         </is>
       </c>
-      <c r="B29" s="61" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    selfdriveState publication and main loop</t>
         </is>
       </c>
-      <c r="C29" s="61" t="inlineStr">
+      <c r="C29" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D29" s="61" t="inlineStr">
+      <c r="D29" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-030</t>
         </is>
       </c>
-      <c r="E29" s="61" t="inlineStr">
+      <c r="E29" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-036: Publish selfdriveState (enabled, active, alert) every 10 ms cycle, consistent with the state machine</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="61" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>Control (controlsd, lateral/longitudinal controllers, Toyota CarController hand-off)</t>
         </is>
       </c>
-      <c r="C30" s="61" t="inlineStr">
+      <c r="C30" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D30" s="61" t="inlineStr"/>
-      <c r="E30" s="61" t="inlineStr"/>
+      <c r="D30" s="60" t="inlineStr"/>
+      <c r="E30" s="60" t="inlineStr"/>
     </row>
     <row r="31" ht="127.5" customHeight="1">
-      <c r="A31" s="61" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-041</t>
         </is>
       </c>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    controlsd main loop, input handling and actuator gating</t>
         </is>
       </c>
-      <c r="C31" s="61" t="inlineStr">
+      <c r="C31" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D31" s="61" t="inlineStr">
+      <c r="D31" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E31" s="61" t="inlineStr">
+      <c r="E31" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-040: Request lateral control only while selfdriveState is active, no EPS fault is reported and the car is above the minimum steer speed; request longitudinal control only while enabled and not overridden
 SWF-FN-041: Compute actuation only from fresh, valid and finite inputs (selfdriveState, modelV2, longitudinalPlan, vehicleParameters, lateralTorqueParameters, deviceMotion), and stop actuating otherwise
@@ -35919,108 +35936,108 @@
       </c>
     </row>
     <row r="32" ht="33" customHeight="1">
-      <c r="A32" s="61" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-042</t>
         </is>
       </c>
-      <c r="B32" s="61" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Lateral torque controller</t>
         </is>
       </c>
-      <c r="C32" s="61" t="inlineStr">
+      <c r="C32" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D32" s="61" t="inlineStr">
+      <c r="D32" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E32" s="61" t="inlineStr">
+      <c r="E32" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-042: Generate a steering torque request that tracks the limited desired curvature within the envelope and yields while the driver steers</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1">
-      <c r="A33" s="61" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-043</t>
         </is>
       </c>
-      <c r="B33" s="61" t="inlineStr">
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Longitudinal controller</t>
         </is>
       </c>
-      <c r="C33" s="61" t="inlineStr">
+      <c r="C33" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D33" s="61" t="inlineStr">
+      <c r="D33" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E33" s="61" t="inlineStr">
+      <c r="E33" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-044: Generate an acceleration request within the range and rate envelope from the longitudinal plan</t>
         </is>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="61" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-044</t>
         </is>
       </c>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Curvature limiter</t>
         </is>
       </c>
-      <c r="C34" s="61" t="inlineStr">
+      <c r="C34" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D34" s="61" t="inlineStr">
+      <c r="D34" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E34" s="61" t="inlineStr">
+      <c r="E34" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-043: Limit desired curvature to the lateral acceleration, lateral jerk and curvature bounds</t>
         </is>
       </c>
     </row>
     <row r="35" ht="46.5" customHeight="1">
-      <c r="A35" s="61" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-045</t>
         </is>
       </c>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B35" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Toyota CarController</t>
         </is>
       </c>
-      <c r="C35" s="61" t="inlineStr">
+      <c r="C35" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D35" s="61" t="inlineStr">
+      <c r="D35" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E35" s="61" t="inlineStr">
+      <c r="E35" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-045: Apply torque magnitude, rate and measured-torque limits; send zero torque with the request bit cleared when lateral control is not active; send the ACC command within the acceleration range
 SWF-FN-050: Send the inactive acceleration in ACC_CONTROL whenever longitudinal control is not active</t>
@@ -36028,154 +36045,154 @@
       </c>
     </row>
     <row r="36" ht="33" customHeight="1">
-      <c r="A36" s="61" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-046</t>
         </is>
       </c>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    card actuation hand-off</t>
         </is>
       </c>
-      <c r="C36" s="61" t="inlineStr">
+      <c r="C36" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D36" s="61" t="inlineStr">
+      <c r="D36" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-040</t>
         </is>
       </c>
-      <c r="E36" s="61" t="inlineStr">
+      <c r="E36" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-047: Deliver every 10 ms control step to the vehicle, and stop sending item frames when carControl is no longer received</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="61" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-050</t>
         </is>
       </c>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B37" s="60" t="inlineStr">
         <is>
           <t>Car interface (card and the opendbc Toyota port, CAN parse and pack)</t>
         </is>
       </c>
-      <c r="C37" s="61" t="inlineStr">
+      <c r="C37" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D37" s="61" t="inlineStr"/>
-      <c r="E37" s="61" t="inlineStr"/>
+      <c r="D37" s="60" t="inlineStr"/>
+      <c r="E37" s="60" t="inlineStr"/>
     </row>
     <row r="38" ht="46.5" customHeight="1">
-      <c r="A38" s="61" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-051</t>
         </is>
       </c>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    CAN parser and Toyota carState</t>
         </is>
       </c>
-      <c r="C38" s="61" t="inlineStr">
+      <c r="C38" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D38" s="61" t="inlineStr">
+      <c r="D38" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-050</t>
         </is>
       </c>
-      <c r="E38" s="61" t="inlineStr">
+      <c r="E38" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-051: Provide brakePressed, gasPressed, steeringTorque/steeringPressed, cruise state, vEgo and EPS fault from current vehicle CAN, and report invalid or missing data as canValid false within the RX budget</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33" customHeight="1">
-      <c r="A39" s="61" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-052</t>
         </is>
       </c>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="B39" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Fingerprinting and CarParams</t>
         </is>
       </c>
-      <c r="C39" s="61" t="inlineStr">
+      <c r="C39" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D39" s="61" t="inlineStr">
+      <c r="D39" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-050</t>
         </is>
       </c>
-      <c r="E39" s="61" t="inlineStr">
+      <c r="E39" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-052: Identify the reference vehicle and produce its CarParams (TOYOTA_COROLLA_TSS2, safety parameter 73, openpilot longitudinal)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33" customHeight="1">
-      <c r="A40" s="61" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-053</t>
         </is>
       </c>
-      <c r="B40" s="61" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    CAN packer and Toyota message construction</t>
         </is>
       </c>
-      <c r="C40" s="61" t="inlineStr">
+      <c r="C40" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D40" s="61" t="inlineStr">
+      <c r="D40" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-050</t>
         </is>
       </c>
-      <c r="E40" s="61" t="inlineStr">
+      <c r="E40" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-053: Pack actuation and HUD frames with the commanded values, the correct scaling, counter and checksum</t>
         </is>
       </c>
     </row>
     <row r="41" ht="73.5" customHeight="1">
-      <c r="A41" s="61" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-054</t>
         </is>
       </c>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    card main loop and stock AEB interlock</t>
         </is>
       </c>
-      <c r="C41" s="61" t="inlineStr">
+      <c r="C41" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D41" s="61" t="inlineStr">
+      <c r="D41" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-050</t>
         </is>
       </c>
-      <c r="E41" s="61" t="inlineStr">
+      <c r="E41" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-054: Run the car interface every CAN cycle, publish carState, and actuate only the latest carControl
 SWF-FN-055: Raise the EPS-fault warning while engaged (TSR-607); the take-over request, with the lighter prompt only for the first 1.5 s after an override or at standstill, and at least the lighter prompt when the fault lasts over 1.5 s while the driver keeps steering</t>
@@ -36183,503 +36200,503 @@
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="61" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-060</t>
         </is>
       </c>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
         </is>
       </c>
-      <c r="C42" s="61" t="inlineStr">
+      <c r="C42" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D42" s="61" t="inlineStr"/>
-      <c r="E42" s="61" t="inlineStr"/>
+      <c r="D42" s="60" t="inlineStr"/>
+      <c r="E42" s="60" t="inlineStr"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="61" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-061</t>
         </is>
       </c>
-      <c r="B43" s="61" t="inlineStr">
+      <c r="B43" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Driver-monitoring model process</t>
         </is>
       </c>
-      <c r="C43" s="61" t="inlineStr">
+      <c r="C43" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D43" s="61" t="inlineStr">
+      <c r="D43" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-060</t>
         </is>
       </c>
-      <c r="E43" s="61" t="inlineStr">
+      <c r="E43" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-060: Estimate face, eye and attention state of the driver for every cabin camera frame</t>
         </is>
       </c>
     </row>
     <row r="44" ht="33" customHeight="1">
-      <c r="A44" s="61" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-062</t>
         </is>
       </c>
-      <c r="B44" s="61" t="inlineStr">
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Monitoring policy and dmonitoringd</t>
         </is>
       </c>
-      <c r="C44" s="61" t="inlineStr">
+      <c r="C44" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D44" s="61" t="inlineStr">
+      <c r="D44" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-060</t>
         </is>
       </c>
-      <c r="E44" s="61" t="inlineStr">
+      <c r="E44" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-061: Escalate an inattentive or unresponsive driver within the policy times (vision 5/8/13 s, wheel-touch 5/15/25 s) and request the terminal reaction</t>
         </is>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="61" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-070</t>
         </is>
       </c>
-      <c r="B45" s="61" t="inlineStr">
+      <c r="B45" s="60" t="inlineStr">
         <is>
           <t>Longitudinal planning (plannerd)</t>
         </is>
       </c>
-      <c r="C45" s="61" t="inlineStr">
+      <c r="C45" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D45" s="61" t="inlineStr"/>
-      <c r="E45" s="61" t="inlineStr"/>
+      <c r="D45" s="60" t="inlineStr"/>
+      <c r="E45" s="60" t="inlineStr"/>
     </row>
     <row r="46" ht="33" customHeight="1">
-      <c r="A46" s="61" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-071</t>
         </is>
       </c>
-      <c r="B46" s="61" t="inlineStr">
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Longitudinal planner and MPC</t>
         </is>
       </c>
-      <c r="C46" s="61" t="inlineStr">
+      <c r="C46" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D46" s="61" t="inlineStr">
+      <c r="D46" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-070</t>
         </is>
       </c>
-      <c r="E46" s="61" t="inlineStr">
+      <c r="E46" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-070: Plan an acceleration within the envelope that keeps the following distance to a lead and stops for a stopped lead</t>
         </is>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="61" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-072</t>
         </is>
       </c>
-      <c r="B47" s="61" t="inlineStr">
+      <c r="B47" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Forward collision warning decision</t>
         </is>
       </c>
-      <c r="C47" s="61" t="inlineStr">
+      <c r="C47" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D47" s="61" t="inlineStr">
+      <c r="D47" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-070</t>
         </is>
       </c>
-      <c r="E47" s="61" t="inlineStr">
+      <c r="E47" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-071: Raise a forward collision warning when a collision with the lead is predicted</t>
         </is>
       </c>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="61" t="inlineStr">
+      <c r="A48" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-080</t>
         </is>
       </c>
-      <c r="B48" s="61" t="inlineStr">
+      <c r="B48" s="60" t="inlineStr">
         <is>
           <t>Lead estimation (radard and the Toyota radar interface)</t>
         </is>
       </c>
-      <c r="C48" s="61" t="inlineStr">
+      <c r="C48" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D48" s="61" t="inlineStr"/>
-      <c r="E48" s="61" t="inlineStr"/>
+      <c r="D48" s="60" t="inlineStr"/>
+      <c r="E48" s="60" t="inlineStr"/>
     </row>
     <row r="49" ht="33" customHeight="1">
-      <c r="A49" s="61" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-081</t>
         </is>
       </c>
-      <c r="B49" s="61" t="inlineStr">
+      <c r="B49" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Lead selection and radar/vision fusion</t>
         </is>
       </c>
-      <c r="C49" s="61" t="inlineStr">
+      <c r="C49" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D49" s="61" t="inlineStr">
+      <c r="D49" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-080</t>
         </is>
       </c>
-      <c r="E49" s="61" t="inlineStr">
+      <c r="E49" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-080: Provide the lead state (distance, relative speed and acceleration) from radar tracks matched to model leads, and flag radar faults</t>
         </is>
       </c>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="61" t="inlineStr">
+      <c r="A50" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-090</t>
         </is>
       </c>
-      <c r="B50" s="61" t="inlineStr">
+      <c r="B50" s="60" t="inlineStr">
         <is>
           <t>Driving model process (modeld)</t>
         </is>
       </c>
-      <c r="C50" s="61" t="inlineStr">
+      <c r="C50" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D50" s="61" t="inlineStr"/>
-      <c r="E50" s="61" t="inlineStr"/>
+      <c r="D50" s="60" t="inlineStr"/>
+      <c r="E50" s="60" t="inlineStr"/>
     </row>
     <row r="51" ht="33" customHeight="1">
-      <c r="A51" s="61" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-091</t>
         </is>
       </c>
-      <c r="B51" s="61" t="inlineStr">
+      <c r="B51" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Model execution, output parsing and validity</t>
         </is>
       </c>
-      <c r="C51" s="61" t="inlineStr">
+      <c r="C51" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D51" s="61" t="inlineStr">
+      <c r="D51" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-090</t>
         </is>
       </c>
-      <c r="E51" s="61" t="inlineStr">
+      <c r="E51" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-090: Publish model outputs (desired curvature, leads) for every road frame, computed from the current frame and calibration, and mark output that is not fit for use as invalid</t>
         </is>
       </c>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="61" t="inlineStr">
+      <c r="A52" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-100</t>
         </is>
       </c>
-      <c r="B52" s="61" t="inlineStr">
+      <c r="B52" s="60" t="inlineStr">
         <is>
           <t>Localization and calibration (locationd, calibrationd, paramsd, torqued, lagd)</t>
         </is>
       </c>
-      <c r="C52" s="61" t="inlineStr">
+      <c r="C52" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D52" s="61" t="inlineStr"/>
-      <c r="E52" s="61" t="inlineStr"/>
+      <c r="D52" s="60" t="inlineStr"/>
+      <c r="E52" s="60" t="inlineStr"/>
     </row>
     <row r="53" ht="33" customHeight="1">
-      <c r="A53" s="61" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-101</t>
         </is>
       </c>
-      <c r="B53" s="61" t="inlineStr">
+      <c r="B53" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    locationd pose filter</t>
         </is>
       </c>
-      <c r="C53" s="61" t="inlineStr">
+      <c r="C53" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D53" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-100</t>
         </is>
       </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="E53" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-100: Provide a calibrated pose from valid IMU and camera odometry, and report invalid inputs within the reaction time</t>
         </is>
       </c>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="61" t="inlineStr">
+      <c r="A54" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-102</t>
         </is>
       </c>
-      <c r="B54" s="61" t="inlineStr">
+      <c r="B54" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Camera calibration (calibrationd)</t>
         </is>
       </c>
-      <c r="C54" s="61" t="inlineStr">
+      <c r="C54" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D54" s="61" t="inlineStr">
+      <c r="D54" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-100</t>
         </is>
       </c>
-      <c r="E54" s="61" t="inlineStr">
+      <c r="E54" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-101: Report camera calibration as valid only when the learned extrinsics match the mount</t>
         </is>
       </c>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="61" t="inlineStr">
+      <c r="A55" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-103</t>
         </is>
       </c>
-      <c r="B55" s="61" t="inlineStr">
+      <c r="B55" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Online vehicle parameters (paramsd, torqued, lagd)</t>
         </is>
       </c>
-      <c r="C55" s="61" t="inlineStr">
+      <c r="C55" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D55" s="61" t="inlineStr">
+      <c r="D55" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-100</t>
         </is>
       </c>
-      <c r="E55" s="61" t="inlineStr">
+      <c r="E55" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-102: Provide vehicle parameters within plausible bounds and report them invalid otherwise</t>
         </is>
       </c>
     </row>
     <row r="56" ht="33" customHeight="1">
-      <c r="A56" s="61" t="inlineStr">
+      <c r="A56" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-110</t>
         </is>
       </c>
-      <c r="B56" s="61" t="inlineStr">
+      <c r="B56" s="60" t="inlineStr">
         <is>
           <t>Camera acquisition (camerad)</t>
         </is>
       </c>
-      <c r="C56" s="61" t="inlineStr">
+      <c r="C56" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D56" s="61" t="inlineStr"/>
-      <c r="E56" s="61" t="inlineStr">
+      <c r="D56" s="60" t="inlineStr"/>
+      <c r="E56" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-110: Deliver every road, wide and driver camera frame once, in order and synchronised, and make a stopped or failed camera visible</t>
         </is>
       </c>
     </row>
     <row r="57" ht="33" customHeight="1">
-      <c r="A57" s="61" t="inlineStr">
+      <c r="A57" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-120</t>
         </is>
       </c>
-      <c r="B57" s="61" t="inlineStr">
+      <c r="B57" s="60" t="inlineStr">
         <is>
           <t>IMU acquisition (sensord)</t>
         </is>
       </c>
-      <c r="C57" s="61" t="inlineStr">
+      <c r="C57" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D57" s="61" t="inlineStr"/>
-      <c r="E57" s="61" t="inlineStr">
+      <c r="D57" s="60" t="inlineStr"/>
+      <c r="E57" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-120: Deliver accelerometer and gyro samples with correct timestamps, and mark implausible data invalid</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="61" t="inlineStr">
+      <c r="A58" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-130</t>
         </is>
       </c>
-      <c r="B58" s="61" t="inlineStr">
+      <c r="B58" s="60" t="inlineStr">
         <is>
           <t>Messaging (cereal and msgq)</t>
         </is>
       </c>
-      <c r="C58" s="61" t="inlineStr">
+      <c r="C58" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D58" s="61" t="inlineStr"/>
-      <c r="E58" s="61" t="inlineStr"/>
+      <c r="D58" s="60" t="inlineStr"/>
+      <c r="E58" s="60" t="inlineStr"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="61" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-131</t>
         </is>
       </c>
-      <c r="B59" s="61" t="inlineStr">
+      <c r="B59" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    SubMaster liveness and validity</t>
         </is>
       </c>
-      <c r="C59" s="61" t="inlineStr">
+      <c r="C59" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D59" s="61" t="inlineStr">
+      <c r="D59" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-130</t>
         </is>
       </c>
-      <c r="E59" s="61" t="inlineStr">
+      <c r="E59" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-130: Report an input as alive and valid only while it is received at its rate and flagged valid</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="61" t="inlineStr">
+      <c r="A60" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-132</t>
         </is>
       </c>
-      <c r="B60" s="61" t="inlineStr">
+      <c r="B60" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    msgq ring buffer</t>
         </is>
       </c>
-      <c r="C60" s="61" t="inlineStr">
+      <c r="C60" s="60" t="inlineStr">
         <is>
           <t>sw_unit</t>
         </is>
       </c>
-      <c r="D60" s="61" t="inlineStr">
+      <c r="D60" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-130</t>
         </is>
       </c>
-      <c r="E60" s="61" t="inlineStr">
+      <c r="E60" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-131: Deliver every published message intact to each subscriber, or make the loss visible</t>
         </is>
       </c>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="61" t="inlineStr">
+      <c r="A61" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-140</t>
         </is>
       </c>
-      <c r="B61" s="61" t="inlineStr">
+      <c r="B61" s="60" t="inlineStr">
         <is>
           <t>Process manager (manager)</t>
         </is>
       </c>
-      <c r="C61" s="61" t="inlineStr">
+      <c r="C61" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr"/>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="D61" s="60" t="inlineStr"/>
+      <c r="E61" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-140: Run every process the configuration needs and report any that is not running</t>
         </is>
       </c>
     </row>
     <row r="62" ht="33" customHeight="1">
-      <c r="A62" s="61" t="inlineStr">
+      <c r="A62" s="60" t="inlineStr">
         <is>
           <t>SWF-SE-150</t>
         </is>
       </c>
-      <c r="B62" s="61" t="inlineStr">
+      <c r="B62" s="60" t="inlineStr">
         <is>
           <t>Software update (updated)</t>
         </is>
       </c>
-      <c r="C62" s="61" t="inlineStr">
+      <c r="C62" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D62" s="61" t="inlineStr"/>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="D62" s="60" t="inlineStr"/>
+      <c r="E62" s="60" t="inlineStr">
         <is>
           <t>SWF-FN-150: Install only the released, assured software version, and never change running software while driving</t>
         </is>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -22635,7 +22635,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Timers count frames, not time: one awareness step of DT_DMON = 0.05 s per driverStateV2 message (policy.py:224, 233; dmonitoringd.py:21-23). A model running at 16 Hz still passes the frequency check and stretches the 13 s terminal to about 16 s</t>
+            <t>Timers count frames, not time: one awareness step of DT_DMON = 0.05 s per driverStateV2 message (policy.py:228, 237; dmonitoringd.py:21-23). A model running at 16 Hz still passes the frequency check and stretches the 13 s terminal to about 16 s</t>
           </r>
         </is>
       </c>
@@ -22735,7 +22735,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Defect in the awareness arithmetic, thresholds or recovery factor (1 - T1/T3, 1 - T2/T3, recovery 1.25-5; policy.py:31-52, 222-233, 383-401)</t>
+            <t>Defect in the awareness arithmetic, thresholds or recovery factor (1 - T1/T3, 1 - T2/T3, recovery 1.25-5; policy.py:31-52, 226-237, 398-418)</t>
           </r>
         </is>
       </c>
@@ -22844,7 +22844,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Exemptions reset or hold awareness: below 2.8 m/s awareness is held at the pre-alert level, and under the wheel-touch policy any steering or gas input resets it (policy.py:29, 361, 374, 485). A light accelerator touch satisfies the wheel-touch policy</t>
+            <t>Exemptions reset or hold awareness: below 2.8 m/s awareness is held at the pre-alert level, and under the wheel-touch policy any steering or gas input resets it (policy.py:29, 376, 389, 502). A light accelerator touch satisfies the wheel-touch policy</t>
           </r>
         </is>
       </c>
@@ -23346,7 +23346,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No finiteness or validity check: driverStateV2 is always published valid (dmonitoringmodeld.py:99) and neither process checks for NaN. By code reading a NaN pose with a finite std compares false against the pose thresholds, so the driver counts as attentive (policy.py:254-272); a NaN face probability counts as no face (the conservative direction). Not tested</t>
+            <t>No finiteness or validity check: driverStateV2 is always published valid (dmonitoringmodeld.py:99) and neither process checks for NaN. By code reading a NaN pose with a finite std compares false against the pose thresholds, so the driver counts as attentive (policy.py:258-276); a NaN face probability counts as no face (the conservative direction). Not tested</t>
           </r>
         </is>
       </c>
@@ -23465,7 +23465,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Empty face arrays make _update_states return early, so face_detected and the last pose stay as they were while the event logic runs (policy.py:290-292)</t>
+            <t>Empty face arrays make _update_states return early, so face_detected and the last pose stay as they were while the event logic runs (policy.py:294-296)</t>
           </r>
         </is>
       </c>
@@ -23694,7 +23694,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Unhandled exception: brakeDisengageProbs[0] is read without a length check (policy.py:486); model and warp loading have no error handling (dmonitoringmodeld.py:22-48); no try/except in either loop</t>
+            <t>Unhandled exception: brakeDisengageProbs[0] is read without a length check (policy.py:503); model and warp loading have no error handling (dmonitoringmodeld.py:22-48); no try/except in either loop</t>
           </r>
         </is>
       </c>
@@ -30172,7 +30172,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Alerts still escalate on the camera input, with strict pose thresholds and no wheel-touch reset; but the wheel-side lock is off while engaged (policy.py:287), so the monitored seat can switch, and the policy ignores the real speed, gear and engagement</t>
+            <t>Alerts still escalate on the camera input, with strict pose thresholds and no wheel-touch reset; but the wheel-side lock is off while engaged (policy.py:291), so the monitored seat can switch, and the policy ignores the real speed, gear and engagement</t>
           </r>
           <r>
             <rPr>
@@ -30198,7 +30198,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>run_step uses a synthetic vehicle state (speed 30 m/s, enabled, no driver input, brake-disengage probability 1.0, zero calibration) instead of carState, selfdriveState and extrinsicsCalibration, and skips the input validity gate except for driverStateV2 (dmonitoringd.py:26-29; policy.py:470-479)</t>
+            <t>run_step uses a synthetic vehicle state (speed 30 m/s, enabled, no driver input, brake-disengage probability 1.0, zero calibration) instead of carState, selfdriveState and extrinsicsCalibration, and skips the input validity gate except for driverStateV2 (dmonitoringd.py:26-29; policy.py:487-496)</t>
           </r>
         </is>
       </c>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.7 · draft</t>
+          <t>1.8 · draft</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• TX arrival supervision in the 100 Hz safety task, started at the grant (safety.h tx_arrival_checks, toyota.h:599-606); timeouts from TSR-408, not yet confirmed on reference drive logs (IA tx-arrival OI-1). The engaged-mismatch path (about 3 s) is unchanged</t>
+            <t>• TX arrival supervision in the 100 Hz safety task, started at the grant (safety.h tx_arrival_checks, toyota.h:599-606); timeouts from TSR-408, not yet confirmed on reference drive logs (IA tx-arrival OI-1). The engaged-mismatch path (about 3 s at BL-006) revokes 0.3 s after the first not-engaged heartbeat since panda f4803c5, reference build, after BL-006 (TSR-307(a))</t>
           </r>
           <r>
             <rPr>
@@ -15300,7 +15300,7 @@
       <c r="R63" s="48" t="inlineStr"/>
       <c r="S63" s="48" t="inlineStr"/>
     </row>
-    <row r="64" ht="262.5" customHeight="1">
+    <row r="64" ht="289.5" customHeight="1">
       <c r="A64" s="49" t="inlineStr">
         <is>
           <r>
@@ -15414,7 +15414,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Steering and acceleration continue with no supervision of model, localizer or comm faults; pandad drops heartbeat engaged after 0.1 s (pandad.cc:424) but the panda withdraws only after the engaged-mismatch count, about 3 s (panda main.c:226-232, SWF-014.C2)</t>
+            <t>Steering and acceleration continue with no supervision of model, localizer or comm faults; pandad drops heartbeat engaged after 0.1 s (pandad.cc:424) but the panda withdraws only after the engaged-mismatch count, about 3 s (panda main.c:226-232, SWF-014.C2); 0.3 s since panda f4803c5, reference build, after BL-006 (TSR-307(a))</t>
           </r>
           <r>
             <rPr>
@@ -18636,7 +18636,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>PCM cruise stays engaged; the panda keeps controls allowed until the heartbeat-mismatch revoke (about 3 s)</t>
+            <t>PCM cruise stays engaged; the panda keeps controls allowed until the heartbeat-mismatch revoke (about 3 s at BL-006; since panda f4803c5, reference build, after BL-006, 0.3 s after the first not-engaged heartbeat, with the panda siren 0.5 s after it while cruise stays on, TSR-307(a), TSR-516(c))</t>
           </r>
           <r>
             <rPr>
@@ -32268,7 +32268,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.7 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.8 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -19069,7 +19069,7 @@
       <c r="R80" s="48" t="inlineStr"/>
       <c r="S80" s="48" t="inlineStr"/>
     </row>
-    <row r="81" ht="154.5" customHeight="1">
+    <row r="81" ht="168" customHeight="1">
       <c r="A81" s="49" t="inlineStr">
         <is>
           <r>
@@ -19231,7 +19231,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No lead time between the announcement and the onset of a fault soft-disable deceleration. Only the driver-monitoring no-response deceleration is preceded by escalating alerts (driverUnresponsive1..3); TSR-624 is recorded as partial</t>
+            <t>No lead time between the announcement and the onset of a fault soft-disable deceleration, which TSR-624 allows since DQ-407 A (the slow-down is at most -1.2 m/s² over the 3 s soft disable and its alert sounds from the first frame). Only the driver-monitoring no-response deceleration is preceded by escalating alerts (driverUnresponsive1..3); TSR-624 is recorded as partial</t>
           </r>
         </is>
       </c>
@@ -19254,6 +19254,32 @@
             <t xml:space="preserve">
    openpilot/selfdrive/monitoring/policy.py</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• The fault soft-disable alert sounds from the first frame of its deceleration, which is bounded by A_CRUISE_MIN (-1.2 m/s²) for SOFT_DISABLE_TIME (3 s); TSR-624 accepts this order (DQ-407 A)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/state.py</t>
+          </r>
         </is>
       </c>
       <c r="J81" s="45" t="n">
@@ -19297,7 +19323,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Implement TSR-624: announce deceleration that traffic does not require at least 1 s before its onset, and ramp it within a_min and j_down</t>
+            <t>Implement TSR-624: announce the driver-monitoring no-response deceleration at least 1 s before its onset (a fault soft-disable deceleration may start with its alert, DQ-407 A), and ramp both within a_min and j_down</t>
           </r>
         </is>
       </c>
@@ -24298,7 +24324,7 @@
       <c r="R105" s="48" t="inlineStr"/>
       <c r="S105" s="48" t="inlineStr"/>
     </row>
-    <row r="106" ht="168" customHeight="1">
+    <row r="106" ht="181.5" customHeight="1">
       <c r="A106" s="49" t="inlineStr">
         <is>
           <r>
@@ -24526,7 +24552,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Implement TSR-624: announce deceleration that traffic does not require at least 1 s before its onset, and ramp it within a_min and j_down</t>
+            <t>Implement TSR-624: announce the driver-monitoring no-response deceleration at least 1 s before its onset (a fault soft-disable deceleration may start with its alert, DQ-407 A), and ramp both within a_min and j_down</t>
           </r>
           <r>
             <rPr>
@@ -33952,7 +33978,7 @@
       <c r="H42" s="60" t="inlineStr"/>
       <c r="I42" s="60" t="inlineStr"/>
     </row>
-    <row r="43" ht="33" customHeight="1">
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-050</t>
@@ -33965,7 +33991,7 @@
       </c>
       <c r="C43" s="60" t="inlineStr">
         <is>
-          <t>Implement TSR-624: announce deceleration that traffic does not require at least 1 s before its onset, and ramp it within a_min and j_down</t>
+          <t>Implement TSR-624: announce the driver-monitoring no-response deceleration at least 1 s before its onset (a fault soft-disable deceleration may start with its alert, DQ-407 A), and ramp both within a_min and j_down</t>
         </is>
       </c>
       <c r="D43" s="60" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -1401,7 +1401,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Limits copied from upstream vehicle tuning; no independent envelope (FSC FOI-001, DFA DFI-14)</t>
+            <t>• Limits copied from upstream vehicle tuning; no independent envelope (FSC FOI-001, DFA DFI-08)</t>
           </r>
           <r>
             <rPr>
@@ -2509,7 +2509,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Panda limit taken from the platform minimum, not a vehicle envelope (assurance GAP-04, TSR-202 without rationale, WP-A-03 DFI-14 / DM-10)</t>
+            <t>• Panda limit taken from the platform minimum, not a vehicle envelope (assurance GAP-04, TSR-202 without rationale, WP-A-03 DFI-08 / DM-10)</t>
           </r>
           <r>
             <rPr>
@@ -6426,7 +6426,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>ELM327 TX hook allows any ISO 15765 diagnostic frame with no service, ignition or motion condition. BL-005, reference build (default): once TOYOTA has been accepted with the ignition on, ELM327 is refused until the ignition goes off (panda#16, LD-DES-001 DR-05, DFA DFI-08). Before the car mode in each ignition cycle (fingerprinting, radar disable), or for a whole drive in which the car mode is never set, the content is still unrestricted</t>
+            <t>ELM327 TX hook allows any ISO 15765 diagnostic frame with no service, ignition or motion condition. BL-005, reference build (default): once TOYOTA has been accepted with the ignition on, ELM327 is refused until the ignition goes off (panda#16, LD-DES-001 DR-05, DFA DFI-13c). Before the car mode in each ignition cycle (fingerprinting, radar disable), or for a whole drive in which the car mode is never set, the content is still unrestricted</t>
           </r>
         </is>
       </c>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.9 · draft</t>
+          <t>1.10 · draft</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17">
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -943,7 +943,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>73 (63)</t>
+          <t>73 (62)</t>
         </is>
       </c>
     </row>
@@ -17980,7 +17980,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• process_replay covers card on the Corolla segment; not designed for implausible pitch or step requests. opendbc test_carcontroller.py (6 cases, BL-007) targets the final rate limit and the stock-AEB cap, not the pitch input, and is not run by LionDriver CI (D 9 rule)</t>
+            <t>• process_replay covers card on the Corolla segment; not designed for implausible pitch or step requests. opendbc test_carcontroller.py (6 cases, BL-007, run by the tests.yaml unit_tests job) targets the final rate limit and the stock-AEB cap, not the pitch input</t>
           </r>
           <r>
             <rPr>
@@ -19160,6 +19160,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (PC-1, PC-2), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_reference_build.py (debug processes not registered, debug params do not change the control processes, the reference release ships no debug process, the default build is the reference build), run by the CI unit_tests job; not proven by mutation (D 8)</t>
           </r>
           <r>
@@ -19174,11 +19200,11 @@
         </is>
       </c>
       <c r="L81" s="45" t="n">
-        <v>8</v>
-      </c>
-      <c r="M81" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
+        <v>4</v>
+      </c>
+      <c r="M81" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="N81" s="44" t="inlineStr">
@@ -19213,7 +19239,7 @@
       <c r="R81" s="48" t="inlineStr"/>
       <c r="S81" s="48" t="inlineStr"/>
     </row>
-    <row r="82" ht="208.5" customHeight="1">
+    <row r="82" ht="222" customHeight="1">
       <c r="A82" s="49" t="inlineStr">
         <is>
           <r>
@@ -19437,6 +19463,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (AN-1, AN-2), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_monitoring.py (the countdown runs 5 s to 0 and the stop starts at least 1 s after the announcement) and test_minimum_risk.py (alert texts and sounds, the new event wired), run by the CI unit_tests job; not proven by mutation (D 8, RT-2)</t>
           </r>
           <r>
@@ -19451,7 +19503,7 @@
         </is>
       </c>
       <c r="L82" s="45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M82" s="52" t="inlineStr">
         <is>
@@ -22850,6 +22902,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (PO-1, PO-2, PO-3), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_monitoring.py TestFirstAlertTime (5 tests: skipped frames, uncertain pose, face lost past orange) and test_somehow_indecisive_model (vision timers 5 / 8 / 13 s), run by the CI unit_tests job; 6 fail without the change; not proven by mutation (D 8, RT-2)</t>
           </r>
           <r>
@@ -22864,7 +22942,7 @@
         </is>
       </c>
       <c r="L97" s="35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M97" s="37" t="inlineStr">
         <is>
@@ -23121,7 +23199,7 @@
       <c r="R99" s="39" t="inlineStr"/>
       <c r="S99" s="39" t="inlineStr"/>
     </row>
-    <row r="100" ht="141" customHeight="1">
+    <row r="100" ht="208.5" customHeight="1">
       <c r="A100" s="42" t="n"/>
       <c r="B100" s="42" t="n"/>
       <c r="C100" s="42" t="n"/>
@@ -23177,6 +23255,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (WT-1), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_monitoring.py, 6 distance tests (constant speeds 0-120 km/h, ±1.5 m/s² ramps, interaction reset, vision recovery, disengaged, low speed), run by the CI unit_tests job; 5 fail on the previous logic; not proven by mutation; vehicle validation open (WP-V-02 §4.4)</t>
           </r>
           <r>
@@ -23191,7 +23295,7 @@
         </is>
       </c>
       <c r="L100" s="45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M100" s="52" t="inlineStr">
         <is>
@@ -23230,7 +23334,7 @@
       <c r="R100" s="48" t="inlineStr"/>
       <c r="S100" s="48" t="inlineStr"/>
     </row>
-    <row r="101" ht="249" customHeight="1">
+    <row r="101" ht="262.5" customHeight="1">
       <c r="A101" s="49" t="inlineStr">
         <is>
           <r>
@@ -23422,6 +23526,32 @@
       </c>
       <c r="K101" s="44" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Mutation in CI covers part of this cause (MR-1..MR-3: the latch class; the controlsd forceDecel hold, the alert re-raise and the lockout timing are not mutated), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -24865,7 +24995,7 @@
       <c r="R108" s="48" t="inlineStr"/>
       <c r="S108" s="48" t="inlineStr"/>
     </row>
-    <row r="109" ht="141" customHeight="1">
+    <row r="109" ht="235.5" customHeight="1">
       <c r="A109" s="30" t="inlineStr">
         <is>
           <r>
@@ -25057,6 +25187,32 @@
       </c>
       <c r="K109" s="34" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Mutation in CI covers part of this cause (AC-1: assured_config.evaluate; add_reference_entry_events, reference_platform and the distance button are not mutated), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -25124,7 +25280,7 @@
       <c r="R109" s="39" t="inlineStr"/>
       <c r="S109" s="39" t="inlineStr"/>
     </row>
-    <row r="110" ht="168" customHeight="1">
+    <row r="110" ht="249" customHeight="1">
       <c r="A110" s="42" t="n"/>
       <c r="B110" s="42" t="n"/>
       <c r="C110" s="42" t="n"/>
@@ -25180,6 +25336,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (AC-2), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_assured_config.py TestSettingsHeldWhileEngaged (5 tests: held while engaged, applied after disengagement, next engagement refused, applied at once while disengaged, other platforms unchanged; 4 fail on the code before #342). Run by the CI unit_tests job (tests run 39348218534 at 18b15cd: 1583 passed, 0 failed); not proven by mutation, so D 8, D 4 with mutation</t>
           </r>
           <r>
@@ -25194,7 +25376,7 @@
         </is>
       </c>
       <c r="L110" s="45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M110" s="52" t="inlineStr">
         <is>
@@ -31570,6 +31752,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (CE-1, CE-2), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_steer_fault_warning.py (7 unittest tests, collected by the unit_tests job); targeted at the escalation, not proven by mutation (D 8 at best, RT-2), not on the vehicle</t>
           </r>
           <r>
@@ -31584,7 +31792,7 @@
         </is>
       </c>
       <c r="L142" s="35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M142" s="37" t="inlineStr">
         <is>
@@ -31643,7 +31851,7 @@
       <c r="O142" s="56" t="inlineStr">
         <is>
           <t>completed
-open</t>
+completed</t>
         </is>
       </c>
       <c r="P142" s="33" t="inlineStr">
@@ -31717,6 +31925,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (CE-3), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_steer_fault_warning.py (the steering-held case), collected by the unit_tests job; not proven by mutation, not on the vehicle</t>
           </r>
           <r>
@@ -31731,7 +31965,7 @@
         </is>
       </c>
       <c r="L143" s="45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M143" s="52" t="inlineStr">
         <is>
@@ -31790,7 +32024,7 @@
       <c r="O143" s="47" t="inlineStr">
         <is>
           <t>completed
-open</t>
+completed</t>
         </is>
       </c>
       <c r="P143" s="43" t="inlineStr">
@@ -32314,7 +32548,7 @@
       <c r="R145" s="48" t="inlineStr"/>
       <c r="S145" s="48" t="inlineStr"/>
     </row>
-    <row r="146" ht="168" customHeight="1">
+    <row r="146" ht="262.5" customHeight="1">
       <c r="A146" s="30" t="inlineStr">
         <is>
           <r>
@@ -32539,6 +32773,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (DT-1..DT-5), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_vehicle_dtc.py (each active bit alone, unsupported bit ignored, exempt code, silent, 0x7F 0x19 0x11, malformed, availability 0x30, no address, raised error, retry count), run by the CI unit_tests job with mocked UDS responses; not proven by mutation (D 8). Whether the reference car's EPS and ABS/VSC answer 0x19 is open (VS-SQ-20, change record OI-1)</t>
           </r>
           <r>
@@ -32553,7 +32813,7 @@
         </is>
       </c>
       <c r="L146" s="35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M146" s="37" t="inlineStr">
         <is>
@@ -32582,9 +32842,9 @@
           </r>
         </is>
       </c>
-      <c r="O146" s="38" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O146" s="57" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P146" s="33" t="inlineStr">
@@ -32600,7 +32860,7 @@
       <c r="R146" s="39" t="inlineStr"/>
       <c r="S146" s="39" t="inlineStr"/>
     </row>
-    <row r="147" ht="127.5" customHeight="1">
+    <row r="147" ht="195" customHeight="1">
       <c r="A147" s="42" t="n"/>
       <c r="B147" s="42" t="n"/>
       <c r="C147" s="42" t="n"/>
@@ -32656,6 +32916,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Mutation in CI covers part of this cause (DT-6, DT-7: dtc_entry_events; the start-up read of the record in selfdrived is not mutated), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_vehicle_dtc_entry.py (each outcome raises its no-entry event on the reference platform; other platforms unchanged), run by the CI unit_tests job; not proven by mutation (D 8)</t>
           </r>
           <r>
@@ -32699,9 +32985,9 @@
           </r>
         </is>
       </c>
-      <c r="O147" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O147" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P147" s="43" t="inlineStr">
@@ -33104,7 +33390,7 @@
       <c r="R149" s="48" t="inlineStr"/>
       <c r="S149" s="48" t="inlineStr"/>
     </row>
-    <row r="150" ht="114" customHeight="1">
+    <row r="150" ht="168" customHeight="1">
       <c r="A150" s="30" t="inlineStr">
         <is>
           <r>
@@ -33302,6 +33588,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Mutation in CI covers part of this cause (AE-1, AE-2: stock_aeb_stand_down; its call in controlsd is not covered by a test), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_stock_aeb.py (cap from the first frame, braking kept), run by the CI unit_tests job since the LFS mirror returned; not proven by mutation (D 8)</t>
           </r>
           <r>
@@ -33345,9 +33657,9 @@
           </r>
         </is>
       </c>
-      <c r="O150" s="38" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O150" s="57" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P150" s="33" t="inlineStr">
@@ -33363,7 +33675,7 @@
       <c r="R150" s="39" t="inlineStr"/>
       <c r="S150" s="39" t="inlineStr"/>
     </row>
-    <row r="151" ht="114" customHeight="1">
+    <row r="151" ht="127.5" customHeight="1">
       <c r="A151" s="42" t="n"/>
       <c r="B151" s="42" t="n"/>
       <c r="C151" s="42" t="n"/>
@@ -33416,10 +33728,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• opendbc test_carcontroller.py (6 cases; 3 fail on the previous code), not run by LionDriver CI (D 9 rule)</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• opendbc test_carcontroller.py (6 cases; 3 fail on the previous code), run by the LionDriver tests.yaml unit_tests job (step "Run opendbc Toyota car tests"); targeted, not proven by mutation (D 8). Corrected from D 9 after BL-007: rev 1.9 said it was not run</t>
           </r>
           <r>
             <rPr>
@@ -33432,8 +33744,8 @@
           </r>
         </is>
       </c>
-      <c r="L151" s="54" t="n">
-        <v>9</v>
+      <c r="L151" s="45" t="n">
+        <v>8</v>
       </c>
       <c r="M151" s="52" t="inlineStr">
         <is>
@@ -33462,9 +33774,9 @@
           </r>
         </is>
       </c>
-      <c r="O151" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O151" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P151" s="43" t="inlineStr">
@@ -33749,7 +34061,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.9 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.10 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -35363,7 +35675,7 @@
       <c r="H40" s="60" t="inlineStr"/>
       <c r="I40" s="60" t="inlineStr">
         <is>
-          <t>Processes done: DQ-131 A (be0b4ff, BL-007) leaves joystick, maneuversd and lateral_maneuversd out of the reference build (process_config.py REFERENCE_EXCLUDED_PROCS; test_reference_build.py in CI); SWF-049.C1 O7 D10 -&gt; O3 D8. Open: the lateralManeuverPlan subscription and path in controlsd</t>
+          <t>Processes done: DQ-131 A (be0b4ff, BL-007) leaves joystick, maneuversd and lateral_maneuversd out of the reference build (process_config.py REFERENCE_EXCLUDED_PROCS; test_reference_build.py in CI); SWF-049.C1 O7 D10 -&gt; O3 D8, then D 4 (AP L) once mutation-proven (PC-1, PC-2). Open: the lateralManeuverPlan subscription and path in controlsd</t>
         </is>
       </c>
     </row>
@@ -36510,7 +36822,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="73.5" customHeight="1">
+    <row r="71" ht="100.5" customHeight="1">
       <c r="A71" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-078</t>
@@ -36531,9 +36843,9 @@
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E71" s="60" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E71" s="61" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F71" s="60" t="inlineStr">
@@ -36552,7 +36864,11 @@
           <t>H</t>
         </is>
       </c>
-      <c r="I71" s="60" t="inlineStr"/>
+      <c r="I71" s="60" t="inlineStr">
+        <is>
+          <t>tools/ci/host_mutation.py with tools/ci/host_mutants.toml (CE-1..CE-3), run by the tests.yaml unit_tests job after the unit tests: test_steer_fault_warning.py fails on each mutant of the STEER_FAULT_SILENT_FRAMES comparisons, the silent_steer_warning latch and the steering-held branch. Achieved after BL-007: SWF-088.C1, .C2 O5 D4 (rev 1.10). Not verified on the vehicle</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="127.5" customHeight="1">
       <c r="A72" s="60" t="inlineStr">
@@ -36624,7 +36940,7 @@
       </c>
       <c r="E73" s="60" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F73" s="60" t="inlineStr">
@@ -36643,7 +36959,11 @@
           <t>H</t>
         </is>
       </c>
-      <c r="I73" s="60" t="inlineStr"/>
+      <c r="I73" s="60" t="inlineStr">
+        <is>
+          <t>Mutation done (DT-1..DT-7, host_mutation.py in CI): SWF-091.C1 D 4; C2 in part. Open: the vehicle check VS-SQ-20 and the mutation of the start-up record read in selfdrived</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="60" customHeight="1">
       <c r="A74" s="60" t="inlineStr">
@@ -36668,7 +36988,7 @@
       </c>
       <c r="E74" s="60" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F74" s="60" t="inlineStr">
@@ -36687,7 +37007,11 @@
           <t>H</t>
         </is>
       </c>
-      <c r="I74" s="60" t="inlineStr"/>
+      <c r="I74" s="60" t="inlineStr">
+        <is>
+          <t>Host part done: stock_aeb_stand_down mutated in CI (AE-1, AE-2); the opendbc Toyota car tests already run in the unit_tests job. Open: a test of the controlsd call, mutation of the opendbc cap, the AOU-04R vehicle test</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I74"/>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.10 · draft</t>
+          <t>1.11 · draft</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -11184,7 +11184,7 @@
       <c r="R42" s="39" t="inlineStr"/>
       <c r="S42" s="39" t="inlineStr"/>
     </row>
-    <row r="43" ht="114" customHeight="1">
+    <row r="43" ht="262.5" customHeight="1">
       <c r="A43" s="42" t="n"/>
       <c r="B43" s="42" t="n"/>
       <c r="C43" s="42" t="n"/>
@@ -11204,12 +11204,38 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Test hooks are read from the environment in the production binary. BOARDD_SKIP_FW_CHECK skips the firmware check (pandad.cc:52), STARTED spoofs ignition so the car mode is kept with ignition off (pandad.cc:223-225), FAKESEND drops TX, and SPI_ERR_PROB corrupts transfers (spi.cc:280)</t>
+            <t>Test hooks are read from the environment in the production binary: BOARDD_SKIP_FW_CHECK skips the firmware check (pandad.cc:52), STARTED spoofs ignition so the car mode is kept with ignition off (pandad.cc:223-225), FAKESEND drops TX, and SPI_ERR_PROB corrupts transfers (spi.cc:280). Since DQ-425 A (after BL-007) manager removes them on the device in the reference build, so the remaining cause is a defect in that guard, a new hook not in its list, or pandad started outside manager</t>
           </r>
         </is>
       </c>
       <c r="I43" s="44" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Reference build on the device (DQ-425 A, after BL-007): manager removes the test-only switches from its environment before it starts any process and logs the ones it removed (system/manager/reference_env.py); every process it starts inherits that environment. A process started by hand from a shell bypasses it (cybersecurity, CSG-03)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/reference_env.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -11237,19 +11263,28 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L43" s="54" t="n">
-        <v>10</v>
-      </c>
-      <c r="M43" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_reference_env.py (6 tests: each switch removed, PC and non-reference builds unchanged, removed before BLOCK is read and before any process starts, each switch still read somewhere) in the CI unit_tests job, proven by mutants RE-1..RE-4 (tools/ci/host_mutation.py); D 4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/test/test_reference_env.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L43" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="N43" s="44" t="inlineStr">
@@ -11881,7 +11916,7 @@
       <c r="R46" s="39" t="inlineStr"/>
       <c r="S46" s="39" t="inlineStr"/>
     </row>
-    <row r="47" ht="114" customHeight="1">
+    <row r="47" ht="235.5" customHeight="1">
       <c r="A47" s="42" t="n"/>
       <c r="B47" s="42" t="n"/>
       <c r="C47" s="42" t="n"/>
@@ -11901,12 +11936,38 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Test-only environment flags reach the vehicle: REPLAY sets the state to enabled when a panda reports controlsAllowed, bypassing ENABLE/NO_ENTRY (selfdrived.py:496-497); SIMULATION ignores cabinCameraState and managerState and makes every SubMaster alive/freq check pass once seen (selfdrived.py:88-89; cereal/messaging/__init__.py:211,265-266)</t>
+            <t>Test-only environment flags reach the vehicle: REPLAY sets the state to enabled when a panda reports controlsAllowed, bypassing ENABLE/NO_ENTRY (selfdrived.py:496-497); SIMULATION ignores cabinCameraState and managerState and makes every SubMaster alive/freq check pass once seen (selfdrived.py:88-89; cereal/messaging/__init__.py:211,265-266). Since DQ-425 A (after BL-007) manager removes REPLAY, SIMULATION and TESTING_CLOSET on the device in the reference build; the remaining cause is a defect in that guard or selfdrived started outside manager</t>
           </r>
         </is>
       </c>
       <c r="I47" s="44" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Reference build on the device (DQ-425 A, after BL-007): manager removes the test-only switches from its environment before it starts any process and logs the ones it removed (system/manager/reference_env.py); every process it starts inherits that environment. A process started by hand from a shell bypasses it (cybersecurity, CSG-03)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/reference_env.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -11934,19 +11995,28 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L47" s="54" t="n">
-        <v>10</v>
-      </c>
-      <c r="M47" s="52" t="inlineStr">
-        <is>
-          <t>H</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_reference_env.py (6 tests: each switch removed, PC and non-reference builds unchanged, removed before BLOCK is read and before any process starts, each switch still read somewhere) in the CI unit_tests job, proven by mutants RE-1..RE-4 (tools/ci/host_mutation.py); D 4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/system/manager/test/test_reference_env.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L47" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M47" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="N47" s="44" t="inlineStr">
@@ -11971,9 +12041,9 @@
           </r>
         </is>
       </c>
-      <c r="O47" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O47" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P47" s="43" t="inlineStr"/>
@@ -12825,9 +12895,9 @@
           </r>
         </is>
       </c>
-      <c r="O52" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O52" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P52" s="43" t="inlineStr"/>
@@ -22056,9 +22126,9 @@
           </r>
         </is>
       </c>
-      <c r="O93" s="38" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O93" s="57" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P93" s="33" t="inlineStr"/>
@@ -22066,7 +22136,7 @@
       <c r="R93" s="39" t="inlineStr"/>
       <c r="S93" s="39" t="inlineStr"/>
     </row>
-    <row r="94" ht="114" customHeight="1">
+    <row r="94" ht="127.5" customHeight="1">
       <c r="A94" s="42" t="n"/>
       <c r="B94" s="42" t="n"/>
       <c r="C94" s="42" t="n"/>
@@ -22098,7 +22168,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• No launch path sets FINGERPRINT; the cache is upstream behaviour</t>
+            <t>• No launch path sets FINGERPRINT; the cache is upstream behaviour. Since DQ-425 A (after BL-007) manager removes FINGERPRINT on the device in the reference build (test_reference_env.py, mutants RE-1..RE-4); the VIN-cache reuse is unchanged, so O and D are kept</t>
           </r>
           <r>
             <rPr>
@@ -22156,9 +22226,9 @@
           </r>
         </is>
       </c>
-      <c r="O94" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O94" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P94" s="43" t="inlineStr"/>
@@ -29988,7 +30058,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• No launch path sets BLOCK; setting it needs a shell on the device</t>
+            <t>• No launch path sets BLOCK; setting it needs a shell on the device. Since DQ-425 A (after BL-007) manager removes BLOCK on the device in the reference build before reading it (test_reference_env.py); a process that never starts for another reason is still not reported, so O and D are kept</t>
           </r>
           <r>
             <rPr>
@@ -30055,9 +30125,9 @@
           </r>
         </is>
       </c>
-      <c r="O134" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O134" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P134" s="43" t="inlineStr"/>
@@ -30293,9 +30363,9 @@
           </r>
         </is>
       </c>
-      <c r="O135" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O135" s="55" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P135" s="43" t="inlineStr"/>
@@ -34061,7 +34131,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.10 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.11 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -34889,7 +34959,7 @@
       <c r="H20" s="60" t="inlineStr"/>
       <c r="I20" s="60" t="inlineStr"/>
     </row>
-    <row r="21" ht="87" customHeight="1">
+    <row r="21" ht="154.5" customHeight="1">
       <c r="A21" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-028</t>
@@ -34926,7 +34996,7 @@
       <c r="H21" s="60" t="inlineStr"/>
       <c r="I21" s="60" t="inlineStr">
         <is>
-          <t>Reference firmware built by default and the reference-build flag checked before a car mode (#36, #41, TSR-619). Open: check that the panda runs the assured release image (version or signature of the released build, not any reference build), a host test of the check, and compiling out the test hooks</t>
+          <t>Reference firmware built by default and the reference-build flag checked before a car mode (#36, #41, TSR-619). Open: check that the panda runs the assured release image (version or signature of the released build, not any reference build), a host test of the check, and compiling out the test hooks After BL-007 (DQ-425 A): instead of compiling them out, manager removes BOARDD_SKIP_FW_CHECK, STARTED, FAKESEND, SPI_ERR_PROB and BOARDD_LOOPBACK on the device in the reference build (reference_env.py, mutation-proven test in CI); SWF-028.C2 AP H -&gt; L. The release-image check stays open.</t>
         </is>
       </c>
     </row>
@@ -35041,7 +35111,7 @@
       </c>
       <c r="E24" s="60" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F24" s="60" t="inlineStr">
@@ -35052,7 +35122,11 @@
       </c>
       <c r="G24" s="60" t="inlineStr"/>
       <c r="H24" s="60" t="inlineStr"/>
-      <c r="I24" s="60" t="inlineStr"/>
+      <c r="I24" s="60" t="inlineStr">
+        <is>
+          <t>After BL-007 (DQ-425 A): REPLAY, SIMULATION and TESTING_CLOSET removed by manager on the device in the reference build (reference_env.py, mutation-proven test in CI); SWF-030.C2 AP H -&gt; L. Open: the big-model (chestnut) path</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="46.5" customHeight="1">
       <c r="A25" s="60" t="inlineStr">
@@ -36045,7 +36119,7 @@
       </c>
       <c r="E50" s="60" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F50" s="60" t="inlineStr">
@@ -36056,7 +36130,11 @@
       </c>
       <c r="G50" s="60" t="inlineStr"/>
       <c r="H50" s="60" t="inlineStr"/>
-      <c r="I50" s="60" t="inlineStr"/>
+      <c r="I50" s="60" t="inlineStr">
+        <is>
+          <t>After BL-007 (DQ-425 A): FINGERPRINT removed by manager on the device in the reference build. Open: exact FW match, CarParams check, re-query after a VIN-cache hit</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="100.5" customHeight="1">
       <c r="A51" s="60" t="inlineStr">
@@ -36548,7 +36626,7 @@
       </c>
       <c r="E63" s="60" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F63" s="60" t="inlineStr">
@@ -36559,7 +36637,11 @@
       </c>
       <c r="G63" s="60" t="inlineStr"/>
       <c r="H63" s="60" t="inlineStr"/>
-      <c r="I63" s="60" t="inlineStr"/>
+      <c r="I63" s="60" t="inlineStr">
+        <is>
+          <t>After BL-007 (DQ-425 A): BLOCK removed by manager on the device in the reference build before it is read. Open: report every needed process in managerState, restart policy</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="46.5" customHeight="1">
       <c r="A64" s="60" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.11 · draft</t>
+          <t>1.12 · draft</t>
         </is>
       </c>
     </row>
@@ -23404,7 +23404,7 @@
       <c r="R100" s="48" t="inlineStr"/>
       <c r="S100" s="48" t="inlineStr"/>
     </row>
-    <row r="101" ht="262.5" customHeight="1">
+    <row r="101" ht="303" customHeight="1">
       <c r="A101" s="49" t="inlineStr">
         <is>
           <r>
@@ -23602,7 +23602,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Mutation in CI covers part of this cause (MR-1..MR-3: the latch class; the controlsd forceDecel hold, the alert re-raise and the lockout timing are not mutated), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (MR-1..MR-7: the latch class, the controlsd forceDecel hold and its hand-off to the car, the alert re-raise in selfdrived and the lockout timing), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8 (rev 1.12)</t>
           </r>
           <r>
             <rPr>
@@ -23642,7 +23642,7 @@
         </is>
       </c>
       <c r="L101" s="45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M101" s="52" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
       <c r="R108" s="48" t="inlineStr"/>
       <c r="S108" s="48" t="inlineStr"/>
     </row>
-    <row r="109" ht="235.5" customHeight="1">
+    <row r="109" ht="276" customHeight="1">
       <c r="A109" s="30" t="inlineStr">
         <is>
           <r>
@@ -25263,7 +25263,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Mutation in CI covers part of this cause (AC-1: assured_config.evaluate; add_reference_entry_events, reference_platform and the distance button are not mutated), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (AC-1, AC-3..AC-6: assured_config.evaluate, the reference_platform flag set at start, add_reference_entry_events and the distance button), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8 (rev 1.12)</t>
           </r>
           <r>
             <rPr>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="L109" s="35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M109" s="37" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
       <c r="R146" s="39" t="inlineStr"/>
       <c r="S146" s="39" t="inlineStr"/>
     </row>
-    <row r="147" ht="195" customHeight="1">
+    <row r="147" ht="235.5" customHeight="1">
       <c r="A147" s="42" t="n"/>
       <c r="B147" s="42" t="n"/>
       <c r="C147" s="42" t="n"/>
@@ -32986,7 +32986,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Mutation in CI covers part of this cause (DT-6, DT-7: dtc_entry_events; the start-up read of the record in selfdrived is not mutated), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (DT-6..DT-11: dtc_entry_events, the start-up read of the record in selfdrived, a missing record, the REPLAY and simulator exemption), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8 (rev 1.12)</t>
           </r>
           <r>
             <rPr>
@@ -33026,7 +33026,7 @@
         </is>
       </c>
       <c r="L147" s="45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M147" s="52" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
       <c r="R149" s="48" t="inlineStr"/>
       <c r="S149" s="48" t="inlineStr"/>
     </row>
-    <row r="150" ht="168" customHeight="1">
+    <row r="150" ht="249" customHeight="1">
       <c r="A150" s="30" t="inlineStr">
         <is>
           <r>
@@ -33658,7 +33658,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Mutation in CI covers part of this cause (AE-1, AE-2: stock_aeb_stand_down; its call in controlsd is not covered by a test), tools/ci/host_mutation.py; D stays 8 until the rest is proven</t>
+            <t>• Proven by mutation in CI (after BL-007): the tests fail on each hand-written mutant of this cause (AE-1..AE-3: stock_aeb_stand_down and its call in controlsd, test_controlsd_call_sites.py), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 8 (rev 1.12). A mutant that caps the target but passes the uncapped PID limits on is equivalent on the reference tuning (ki 0) and is not counted</t>
           </r>
           <r>
             <rPr>
@@ -33698,7 +33698,7 @@
         </is>
       </c>
       <c r="L150" s="35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M150" s="37" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.11 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.12 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -36181,7 +36181,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="114" customHeight="1">
+    <row r="52" ht="141" customHeight="1">
       <c r="A52" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-059</t>
@@ -36217,7 +36217,7 @@
       <c r="H52" s="60" t="inlineStr"/>
       <c r="I52" s="60" t="inlineStr">
         <is>
-          <t>#372 (dacd8f7, BL-007): selfdrive/selfdrived/minimum_risk.py, selfdriveState.minimumRiskManeuver, controlsd keeps forceDecel; test_minimum_risk.py, test_monitoring.py (lockout from the takeover) and a stay-stopped longitudinal maneuver in CI. Open outside this action: the PCM standstill hold over time (AOU-16 vehicle test) and the stop deceleration (SWF-086.C2). Not verified on the vehicle, not proven by mutation. Achieved at BL-007: SWF-062.C1 O5 D8</t>
+          <t>#372 (dacd8f7, BL-007): selfdrive/selfdrived/minimum_risk.py, selfdriveState.minimumRiskManeuver, controlsd keeps forceDecel; test_minimum_risk.py, test_monitoring.py (lockout from the takeover) and a stay-stopped longitudinal maneuver in CI. Open outside this action: the PCM standstill hold over time (AOU-16 vehicle test) and the stop deceleration (SWF-086.C2). Not verified on the vehicle. Achieved at BL-007: SWF-062.C1 O5 D8; after BL-007 proven by mutation (MR-1..MR-7, test_controlsd_call_sites.py for the controlsd hold), D 4 (rev 1.12)</t>
         </is>
       </c>
     </row>
@@ -36332,7 +36332,7 @@
       <c r="H55" s="60" t="inlineStr"/>
       <c r="I55" s="60" t="inlineStr"/>
     </row>
-    <row r="56" ht="141" customHeight="1">
+    <row r="56" ht="168" customHeight="1">
       <c r="A56" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-063</t>
@@ -36375,7 +36375,7 @@
       </c>
       <c r="I56" s="60" t="inlineStr">
         <is>
-          <t>DQ-221 A implemented in #287 (69cddaa): assured_config.py (settings_in_scope), selfdrived.py (add_reference_entry_events, distance_button_pressed), events.py (settingNotAssured); tests in test_assured_config.py, collected by the CI unit_tests job and green there in tests run 39296172878 (6126485, 2026-10-19: 1578 passed, 0 failed); change record assurance/07-supporting/impact/change-2026-10-19-reference-entry-checks.md. Unit-tested, not proven by mutation and not verified in the vehicle (change record OI-5). Achieved: O5 D8 (rev 1.6)</t>
+          <t>DQ-221 A implemented in #287 (69cddaa): assured_config.py (settings_in_scope), selfdrived.py (add_reference_entry_events, distance_button_pressed), events.py (settingNotAssured); tests in test_assured_config.py, collected by the CI unit_tests job and green there in tests run 39296172878 (6126485, 2026-10-19: 1578 passed, 0 failed); change record assurance/07-supporting/impact/change-2026-10-19-reference-entry-checks.md. Unit-tested, not proven by mutation and not verified in the vehicle (change record OI-5). Achieved: O5 D8 (rev 1.6); after BL-007 proven by mutation (AC-1, AC-3..AC-6, test_selfdrived_start.py for the reference_platform flag), D 4 (rev 1.12)</t>
         </is>
       </c>
     </row>
@@ -37043,11 +37043,11 @@
       </c>
       <c r="I73" s="60" t="inlineStr">
         <is>
-          <t>Mutation done (DT-1..DT-7, host_mutation.py in CI): SWF-091.C1 D 4; C2 in part. Open: the vehicle check VS-SQ-20 and the mutation of the start-up record read in selfdrived</t>
+          <t>Mutation done (DT-1..DT-11, host_mutation.py in CI): SWF-091.C1 D 4 (rev 1.10); SWF-091.C2 D 4 (rev 1.12), with test_selfdrived_start.py running the real SelfdriveD constructor (the start-up read, a missing record, the REPLAY and simulator exemption). Open: the vehicle check VS-SQ-20</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
+    <row r="74" ht="87" customHeight="1">
       <c r="A74" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-081</t>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="I74" s="60" t="inlineStr">
         <is>
-          <t>Host part done: stock_aeb_stand_down mutated in CI (AE-1, AE-2); the opendbc Toyota car tests already run in the unit_tests job. Open: a test of the controlsd call, mutation of the opendbc cap, the AOU-04R vehicle test</t>
+          <t>Host part done: stock_aeb_stand_down and its call in controlsd mutated in CI (AE-1..AE-3; test_controlsd_call_sites.py runs the real Controls.state_control), so SWF-093.C1 D 4 (rev 1.12); the opendbc Toyota car tests already run in the unit_tests job. Open: mutation of the opendbc cap (SWF-093.C2), the AOU-04R vehicle test</t>
         </is>
       </c>
     </row>

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.12 · draft</t>
+          <t>1.13 · draft</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>73 (62)</t>
+          <t>73 (61)</t>
         </is>
       </c>
     </row>
@@ -16233,7 +16233,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>LatControlTorque does not reset its PID integrator when lateral control ends: controlsd calls LaC.reset() when not latActive (controlsd.py:112-113), but LatControlTorque has no reset() override and the base class clears only sat_time (latcontrol.py:19-20); the inactive branch skips pid.update (latcontrol_torque.py:114-116). The integrator from the last engagement (bounded by the lat-accel limits, pid.py:48-55) is added on the next engagement</t>
+            <t>Defect in the integrator reset (after BL-007, change-2026-10-29-lateral-integrator-reset): LatControlTorque.reset or LatControlPID.reset does not clear the PID, or controlsd does not call LaC.reset() when lateral control ends, so the integrator from the last engagement (bounded by the lat-accel limits, pid.py:48-55) is added on the next one. Up to rev 1.12 the reset was missing in both controllers (O 7, D 10)</t>
           </r>
         </is>
       </c>
@@ -16245,7 +16245,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream review and lint; LatControlCurvature does reset its PID (latcontrol_curvature.py:28-31), so the omission may be an oversight or deliberate upstream; no requirement states either</t>
+            <t>• LionDriver change: both controllers reset their PID in reset(), as LatControlCurvature does (latcontrol_torque.py, latcontrol_pid.py); targeted unit tests; reviewed in the PR, not independently; no requirement yet (SWF-ACT-043); O 5</t>
           </r>
           <r>
             <rPr>
@@ -16254,27 +16254,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/controls/lib/latcontrol_curvature.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-lateral-integrator-reset.md</t>
           </r>
         </is>
       </c>
       <c r="J67" s="35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K67" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_latcontrol.py covers saturation only; test_latcontrol_torque_buffer.py covers the request buffer only; nothing checks controller state across disengagement</t>
-          </r>
-        </is>
-      </c>
-      <c r="L67" s="36" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Proven by mutation in CI: test_latcontrol.py (TestLatControlReset, the reference Corolla TSS2 torque controller, PID and curvature) and test_controlsd_call_sites.py (TestLateralResetCallSite, the real Controls.state_control) fail on each hand-written mutant of this cause (LR-1..LR-3: either reset, and the controlsd call), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 10 (rev 1.13)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_latcontrol.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L67" s="35" t="n">
+        <v>4</v>
       </c>
       <c r="M67" s="37" t="inlineStr">
         <is>
@@ -16330,14 +16339,22 @@
           </r>
         </is>
       </c>
-      <c r="O67" s="38" t="inlineStr">
-        <is>
-          <t>open
+      <c r="O67" s="56" t="inlineStr">
+        <is>
+          <t>completed
 open</t>
         </is>
       </c>
-      <c r="P67" s="33" t="inlineStr"/>
-      <c r="Q67" s="33" t="inlineStr"/>
+      <c r="P67" s="33" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="Q67" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R67" s="39" t="inlineStr"/>
       <c r="S67" s="39" t="inlineStr"/>
     </row>
@@ -34131,7 +34148,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.12 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.13 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -35524,7 +35541,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="46.5" customHeight="1">
+    <row r="35" ht="114" customHeight="1">
       <c r="A35" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-042</t>
@@ -35545,9 +35562,9 @@
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E35" s="61" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F35" s="60" t="inlineStr">
@@ -35555,9 +35572,21 @@
           <t>SWF-042.C1</t>
         </is>
       </c>
-      <c r="G35" s="60" t="inlineStr"/>
-      <c r="H35" s="60" t="inlineStr"/>
-      <c r="I35" s="60" t="inlineStr"/>
+      <c r="G35" s="60" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="H35" s="62" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I35" s="60" t="inlineStr">
+        <is>
+          <t>Both controllers reset their PID in reset() (DQ-426 A, decider Claude; change-2026-10-29-lateral-integrator-reset). Upstream master e376168 (2026-10-27) still has no reset in either; it gives no reason, so LionDriver diverges, as LatControlCurvature already does. Tested on the reference controller and through controlsd, proven by mutants LR-1..LR-3 in CI (rev 1.13). The requirement and the full gating table stay with SWF-ACT-043</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="87" customHeight="1">
       <c r="A36" s="60" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.13 · draft</t>
+          <t>1.14 · draft</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>73 (61)</t>
+          <t>73 (60)</t>
         </is>
       </c>
     </row>
@@ -30812,7 +30812,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The cabin camera dialog sets IsDriverViewEnabled and clears it only when the dialog closes (ui/onroad/cabin_camera_dialog.py:18-22; ui/mici/onroad/cabin_camera_dialog.py:44, 52). The dialog opens only offroad, but stays open across the onroad transition: the comma four UI pops it 2.5 s after going onroad (mici/layouts/main.py:112-124, not while onboarding), the comma 3X UI on its interactive timeout or a touch (cabin_camera_dialog.py:16). dmonitoringd re-reads the parameter every 40 frames, 2 s (dmonitoringd.py:36-38). While open, the comma four dialog also publishes its own selfdriveState with only alertSound set (mici cabin_camera_dialog.py:48, 102-116), a second publisher beside selfdrived</t>
+            <t>The driver-camera view left open across the onroad transition (cabin camera dialog, ui/onroad/cabin_camera_dialog.py:18-22; ui/mici/onroad/cabin_camera_dialog.py:44, 52; the comma four UI closes it 2.5 s after going onroad, the comma 3X UI on its timeout or a touch). Since rev 1.14 (after BL-007, DQ-427, change-2026-10-29-driver-view-interlock) dmonitoringd uses demo mode only while card is not running, so the remaining cause is a defect in that check (demo_active or its call in the loop) or in the selfdrived interlock of SWF-085.C2. The comma four dialog also publishes its own selfdriveState (second publisher, SWF-ACT-076). Up to rev 1.13: demo mode applied whenever the parameter was set (O 5, D 10)</t>
           </r>
         </is>
       </c>
@@ -30824,7 +30824,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• The dialog buttons are disabled onroad (layouts/settings/device.py:61; mici device_layout.py:185); the comma four UI closes dialogs after going onroad. Upstream code, reviewed upstream; ruff and ty in LionDriver CI; no LionDriver software requirement implemented (TSR-610 not met)</t>
+            <t>• LionDriver change with a requirement (TSR-610, SWSR-610): demo mode only while card is not running (dmonitoringd.demo_active); upstream UI disables the dialog buttons onroad; reviewed in the PR, not independently; O 5</t>
           </r>
           <r>
             <rPr>
@@ -30833,7 +30833,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/ui/mici/layouts/main.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-driver-view-interlock.md</t>
           </r>
         </is>
       </c>
@@ -30845,15 +30845,24 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test covers demo mode with the item started; test_widget_leaks only constructs the dialogs</t>
-          </r>
-        </is>
-      </c>
-      <c r="L137" s="36" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Proven by mutation in CI: test_driver_view.py runs the real dmonitoringd loop offroad and started, and fails on each hand-written mutant of this cause (DV-5, DV-6, and DV-1, DV-3, DV-4 for the selfdrived side), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 10 (rev 1.14)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_driver_view.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L137" s="35" t="n">
+        <v>4</v>
       </c>
       <c r="M137" s="37" t="inlineStr">
         <is>
@@ -30909,18 +30918,26 @@
           </r>
         </is>
       </c>
-      <c r="O137" s="38" t="inlineStr">
-        <is>
-          <t>open
+      <c r="O137" s="56" t="inlineStr">
+        <is>
+          <t>completed
 open</t>
         </is>
       </c>
-      <c r="P137" s="33" t="inlineStr"/>
-      <c r="Q137" s="33" t="inlineStr"/>
+      <c r="P137" s="33" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="Q137" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R137" s="39" t="inlineStr"/>
       <c r="S137" s="39" t="inlineStr"/>
     </row>
-    <row r="138" ht="114" customHeight="1">
+    <row r="138" ht="141" customHeight="1">
       <c r="A138" s="42" t="n"/>
       <c r="B138" s="42" t="n"/>
       <c r="C138" s="42" t="n"/>
@@ -30940,7 +30957,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No engagement interlock: nothing in selfdrived or controlsd reads IsDriverViewEnabled, so a parameter left set (written by tooling, or a UI crash before hide_event; it is cleared only at manager start, params_keys.h:61) keeps demo mode for the drive (GAP-20, TSR-610 not met)</t>
+            <t>Defect in the selfdrived interlock (rev 1.14, DQ-427): IsDriverViewEnabled left set (written by tooling, or a UI crash before hide_event; cleared only at manager start, params_keys.h:61) not read at start or by the parameter thread, or driverViewActive not raised, or without its NO_ENTRY and SOFT_DISABLE. Up to rev 1.13 there was no interlock at all (GAP-20; O 8, D 10)</t>
           </r>
         </is>
       </c>
@@ -30952,7 +30969,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream design with no interlock; requirement TSR-610 not implemented, so O 8 (RT-2 §2), as the other by-design gaps</t>
+            <t>• LionDriver change with a requirement (TSR-610, SWSR-610): selfdrived raises driverViewActive while the parameter is set; reviewed in the PR, not independently; O 5</t>
           </r>
           <r>
             <rPr>
@@ -30961,27 +30978,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/monitoring/dmonitoringd.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-driver-view-interlock.md</t>
           </r>
         </is>
       </c>
       <c r="J138" s="45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K138" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test; fault-injection scenario VS-FI-23 (params tampering) is specified in WP-V-05 but not run</t>
-          </r>
-        </is>
-      </c>
-      <c r="L138" s="54" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Proven by mutation in CI: test_driver_view.py (real SelfdriveD constructor, update_events and parameter thread) fails on each hand-written mutant of this cause (DV-1..DV-4), tools/ci/host_mutation.py; so D 4 (RT-2), from D 10 (rev 1.14). Fault-injection scenario VS-FI-23 (params tampering) is still not run</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_driver_view.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L138" s="45" t="n">
+        <v>4</v>
       </c>
       <c r="M138" s="52" t="inlineStr">
         <is>
@@ -31010,13 +31036,21 @@
           </r>
         </is>
       </c>
-      <c r="O138" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P138" s="43" t="inlineStr"/>
-      <c r="Q138" s="43" t="inlineStr"/>
+      <c r="O138" s="47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P138" s="43" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="Q138" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R138" s="48" t="inlineStr"/>
       <c r="S138" s="48" t="inlineStr"/>
     </row>
@@ -34148,7 +34182,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.13 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.14 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -36707,7 +36741,7 @@
       <c r="H64" s="60" t="inlineStr"/>
       <c r="I64" s="60" t="inlineStr"/>
     </row>
-    <row r="65" ht="60" customHeight="1">
+    <row r="65" ht="168" customHeight="1">
       <c r="A65" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-072</t>
@@ -36728,9 +36762,9 @@
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E65" s="60" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E65" s="61" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F65" s="60" t="inlineStr">
@@ -36739,9 +36773,21 @@
 SWF-085.C2</t>
         </is>
       </c>
-      <c r="G65" s="60" t="inlineStr"/>
-      <c r="H65" s="60" t="inlineStr"/>
-      <c r="I65" s="60" t="inlineStr"/>
+      <c r="G65" s="60" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="H65" s="62" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I65" s="60" t="inlineStr">
+        <is>
+          <t>Done with a different third part (DQ-427 A, decider Claude; change-2026-10-29-driver-view-interlock): selfdrived raises driverViewActive (NO_ENTRY, SOFT_DISABLE) while IsDriverViewEnabled is set, and dmonitoringd uses demo mode only while card is not running. The UI does not clear the parameter on the onroad transition: with both checks the parameter has no effect on monitoring while started and blocks engagement, so the driver closes the view. Tested with the item started (test_driver_view.py, real dmonitoringd loop and SelfdriveD), mutants DV-1..DV-6 (rev 1.14). The second selfdriveState publisher stays with SWF-ACT-076</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="87" customHeight="1">
       <c r="A66" s="60" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.14 · draft</t>
+          <t>1.15 · draft</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>73 (60)</t>
+          <t>73 (59)</t>
         </is>
       </c>
     </row>
@@ -19629,7 +19629,7 @@
       <c r="R82" s="48" t="inlineStr"/>
       <c r="S82" s="48" t="inlineStr"/>
     </row>
-    <row r="83" ht="114" customHeight="1">
+    <row r="83" ht="168" customHeight="1">
       <c r="A83" s="49" t="inlineStr">
         <is>
           <r>
@@ -19791,7 +19791,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The FCW condition reads the last received modelV2 and longitudinalPlan; a held or invalid message keeps raising FCW in the same cycle in which commIssue is raised (TSR-625 freshness gate not implemented)</t>
+            <t>Defect in the FCW freshness gate (after BL-007, TSR-625, change-2026-10-29-fcw-input-freshness): modelV2 or longitudinalPlan not checked for validity or for an age within 2 nominal periods (supervision.fcw_inputs_fresh), or selfdrived raising FCW without the gate, so a held or invalid message keeps raising FCW. Up to rev 1.14 there was no gate (O 7, D 10)</t>
           </r>
         </is>
       </c>
@@ -19803,7 +19803,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream design, reviewed; no derived freshness requirement for FCW inputs at BL-004</t>
+            <t>• LionDriver change with a requirement (TSR-625, SWSR-625): FCW only while both inputs are valid and received within 2 periods (10 selfdrived frames); reviewed in the PR, not independently; O 5</t>
           </r>
           <r>
             <rPr>
@@ -19812,27 +19812,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-fcw-input-freshness.md</t>
           </r>
         </is>
       </c>
       <c r="J83" s="45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K83" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L83" s="54" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Proven by mutation in CI: test_fcw_freshness.py (the gate, and the real SelfdriveD.update_events with a hard-brake prediction) fails on each hand-written mutant of this cause (FC-1..FC-5: validity, the 2-period bound, never received, the planner input, the call in selfdrived), tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 10 (rev 1.15)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_fcw_freshness.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L83" s="45" t="n">
+        <v>4</v>
       </c>
       <c r="M83" s="52" t="inlineStr">
         <is>
@@ -19861,13 +19870,21 @@
           </r>
         </is>
       </c>
-      <c r="O83" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P83" s="43" t="inlineStr"/>
-      <c r="Q83" s="43" t="inlineStr"/>
+      <c r="O83" s="47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P83" s="43" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="Q83" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R83" s="48" t="inlineStr"/>
       <c r="S83" s="48" t="inlineStr"/>
     </row>
@@ -34182,7 +34199,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.14 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.15 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -35929,7 +35946,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="33" customHeight="1">
+    <row r="44" ht="100.5" customHeight="1">
       <c r="A44" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-051</t>
@@ -35950,9 +35967,9 @@
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E44" s="60" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E44" s="61" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F44" s="60" t="inlineStr">
@@ -35960,9 +35977,21 @@
           <t>SWF-051.C1</t>
         </is>
       </c>
-      <c r="G44" s="60" t="inlineStr"/>
-      <c r="H44" s="60" t="inlineStr"/>
-      <c r="I44" s="60" t="inlineStr"/>
+      <c r="G44" s="60" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="H44" s="62" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I44" s="60" t="inlineStr">
+        <is>
+          <t>selfdrived raises FCW only while modelV2 and longitudinalPlan are valid and received within 2 nominal periods (supervision.fcw_inputs_fresh, change-2026-10-29-fcw-input-freshness); test_fcw_freshness.py covers a stale and an invalid input of each, through the real SelfdriveD; mutants FC-1..FC-5 (rev 1.15). The FCW trigger-source log and the false-FCW rate target of SWSR-625 stay open (WP-V-02)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="33" customHeight="1">
       <c r="A45" s="60" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/sw-fmea-review.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.15 · draft</t>
+          <t>1.16 · draft</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>73 (59)</t>
+          <t>73 (58)</t>
         </is>
       </c>
     </row>
@@ -19888,7 +19888,7 @@
       <c r="R83" s="48" t="inlineStr"/>
       <c r="S83" s="48" t="inlineStr"/>
     </row>
-    <row r="84" ht="100.5" customHeight="1">
+    <row r="84" ht="141" customHeight="1">
       <c r="A84" s="49" t="inlineStr">
         <is>
           <r>
@@ -20050,7 +20050,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The Toyota CarController takes pcm_accel_cmd from actuators.accel with no longActive gate (carcontroller.py:197-250); the inactive value relies on LongControl returning 0 in its off state (longcontrol.py:65-67), so a defect or stale carControl upstream passes through</t>
+            <t>Defect in the inactive-value gate of the Toyota CarController (after BL-007, opendbc f23b4fa, change-2026-10-29-toyota-inactive-accel): while CC.longActive is false ACCEL_CMD is not INACTIVE_ACCEL, so a defect or a stale carControl upstream passes a braking request through. Up to rev 1.15 pcm_accel_cmd came from actuators.accel with no longActive gate and relied on LongControl returning 0 in its off state (O 6, D 9)</t>
           </r>
         </is>
       </c>
@@ -20062,7 +20062,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream review, ruff and ty in CI; no requirement for the inactive value on the host</t>
+            <t>• LionDriver change to the opendbc Toyota port (opendbc#22): INACTIVE_ACCEL whenever CC.longActive is false, on 0x343 and 0x183; targeted tests; reviewed in the PR, not independently; no host requirement for the inactive value (TSR-203 is the envelope's); O 5</t>
           </r>
           <r>
             <rPr>
@@ -20071,22 +20071,22 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   opendbc_repo/opendbc/car/toyota/carcontroller.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-toyota-inactive-accel.md</t>
           </r>
         </is>
       </c>
       <c r="J84" s="45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K84" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• process_replay covers card on the Corolla segment; not designed for a non-zero request while not engaged</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Proven by mutation in CI: opendbc test_carcontroller.py (the inactive value for -3.5, -0.5 and +1.5 m/s² requests, the decoded ACC_CONTROL frame, the rate-limited return) fails on mutant IA-1, tools/ci/host_mutation.py in the tests.yaml unit_tests job; so D 4 (RT-2), from D 9 (rev 1.16)</t>
           </r>
           <r>
             <rPr>
@@ -20095,12 +20095,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/test/process_replay/test_processes.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L84" s="54" t="n">
-        <v>9</v>
+   opendbc_repo/opendbc/car/toyota/tests/test_carcontroller.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L84" s="45" t="n">
+        <v>4</v>
       </c>
       <c r="M84" s="52" t="inlineStr">
         <is>
@@ -20129,13 +20129,21 @@
           </r>
         </is>
       </c>
-      <c r="O84" s="53" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P84" s="43" t="inlineStr"/>
-      <c r="Q84" s="43" t="inlineStr"/>
+      <c r="O84" s="47" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P84" s="43" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="Q84" s="52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R84" s="48" t="inlineStr"/>
       <c r="S84" s="48" t="inlineStr"/>
     </row>
@@ -33813,7 +33821,7 @@
       <c r="R150" s="39" t="inlineStr"/>
       <c r="S150" s="39" t="inlineStr"/>
     </row>
-    <row r="151" ht="127.5" customHeight="1">
+    <row r="151" ht="154.5" customHeight="1">
       <c r="A151" s="42" t="n"/>
       <c r="B151" s="42" t="n"/>
       <c r="C151" s="42" t="n"/>
@@ -33869,7 +33877,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• opendbc test_carcontroller.py (6 cases; 3 fail on the previous code), run by the LionDriver tests.yaml unit_tests job (step "Run opendbc Toyota car tests"); targeted, not proven by mutation (D 8). Corrected from D 9 after BL-007: rev 1.9 said it was not run</t>
+            <t>• Proven by mutation in CI (rev 1.16): opendbc test_carcontroller.py, run by the LionDriver tests.yaml unit_tests job, fails on each hand-written mutant of the cap (AE-5: cap not applied during the event, AE-6: cap above 0), tools/ci/host_mutation.py; so D 4 (RT-2), from D 8. D 9 -&gt; 8 after BL-007 (rev 1.10: the tests are run by CI)</t>
           </r>
           <r>
             <rPr>
@@ -33883,7 +33891,7 @@
         </is>
       </c>
       <c r="L151" s="45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M151" s="52" t="inlineStr">
         <is>
@@ -34199,7 +34207,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.15 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSW FMEA — safety-relevant software elements · rev 1.16 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -35993,7 +36001,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="33" customHeight="1">
+    <row r="45" ht="73.5" customHeight="1">
       <c r="A45" s="60" t="inlineStr">
         <is>
           <t>SWF-ACT-052</t>
@@ -36014,9 +36022,9 @@
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E45" s="60" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E45" s="61" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F45" s="60" t="inlineStr">
@@ -36024,9 +36032,21 @@
           <t>SWF-052.C1</t>
         </is>
       </c>
-      <c r="G45" s="60" t="inlineStr"/>
-      <c r="H45" s="60" t="inlineStr"/>
-      <c r="I45" s="60" t="inlineStr"/>
+      <c r="G45" s="60" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="H45" s="62" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I45" s="60" t="inlineStr">
+        <is>
+          <t>opendbc#22 (merge f23b4fa, pinned in LionDriver): the Toyota CarController sends INACTIVE_ACCEL whenever CC.longActive is false; three new test_carcontroller.py cases, mutant IA-1 killed (rev 1.16). The PCM response to the inactive value stays with SWF-ACT-053 (AOU-05R)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="46.5" customHeight="1">
       <c r="A46" s="60" t="inlineStr">
@@ -37195,7 +37215,7 @@
       </c>
       <c r="I74" s="60" t="inlineStr">
         <is>
-          <t>Host part done: stock_aeb_stand_down and its call in controlsd mutated in CI (AE-1..AE-3; test_controlsd_call_sites.py runs the real Controls.state_control), so SWF-093.C1 D 4 (rev 1.12); the opendbc Toyota car tests already run in the unit_tests job. Open: mutation of the opendbc cap (SWF-093.C2), the AOU-04R vehicle test</t>
+          <t>Mutation done: stock_aeb_stand_down and its call in controlsd (AE-1..AE-3; test_controlsd_call_sites.py runs the real Controls.state_control), so SWF-093.C1 D 4 (rev 1.12); the opendbc cap (AE-5, AE-6, test_carcontroller.py in the unit_tests job), so SWF-093.C2 D 4 (rev 1.16). Open: the AOU-04R vehicle test</t>
         </is>
       </c>
     </row>
